--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G4">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G17">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G24">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G29">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G37">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G48">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G50">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G63">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G108">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G113">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Aljustrelense</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Aljustrelense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G128">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vitória Setúbal</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vitória Setúbal</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G133">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G139">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G142">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G169">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G180">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G185">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G186">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G188">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G195">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G219">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G220">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G225">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G229">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G239">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G240">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G246">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G278">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G287">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G288">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G289">

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G82">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G112">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vitória Setúbal</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vitória Setúbal</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="G133">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G142">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G154">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G156">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G169">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G195">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G206">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G219">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G220">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G244">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="G246">

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU315"/>
+  <dimension ref="A1:AU319"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-09-13 04:30:00</t>
+          <t>2026-09-13 02:00:00</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4">
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-13 05:15:00</t>
+          <t>2026-09-13 04:30:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-13 05:30:00</t>
+          <t>2026-09-13 05:15:00</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8">
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-13 06:00:00</t>
+          <t>2026-09-13 05:30:00</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G10">
@@ -2060,22 +2060,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G11">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G12">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-13 06:30:00</t>
+          <t>2026-09-13 06:00:00</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G14">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G15">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G17">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-13 07:00:00</t>
+          <t>2026-09-13 06:30:00</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G33">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G40">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-13 07:15:00</t>
+          <t>2026-09-13 07:00:00</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-13 07:30:00</t>
+          <t>2026-09-13 07:15:00</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bình Phước</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-13 08:00:00</t>
+          <t>2026-09-13 07:30:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Bình Phước</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,22 +8743,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,22 +9232,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G58">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-13 08:30:00</t>
+          <t>2026-09-13 08:00:00</t>
         </is>
       </c>
     </row>
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G63">
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,22 +11188,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="G70">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G71">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-09-13 09:00:00</t>
+          <t>2026-09-13 08:30:00</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G76">
@@ -12818,22 +12818,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12981,22 +12981,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G82">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G83">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-09-13 09:15:00</t>
+          <t>2026-09-13 09:00:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G85">
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-09-13 09:30:00</t>
+          <t>2026-09-13 09:15:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,22 +14774,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G91">
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-09-13 09:45:00</t>
+          <t>2026-09-13 09:30:00</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G93">
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-09-13 10:00:00</t>
+          <t>2026-09-13 09:45:00</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G98">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G114">
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-13 10:30:00</t>
+          <t>2026-09-13 10:00:00</t>
         </is>
       </c>
     </row>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G116">
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-09-13 10:45:00</t>
+          <t>2026-09-13 10:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-09-13 11:00:00</t>
+          <t>2026-09-13 10:45:00</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G123">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aljustrelense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Aljustrelense</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G129">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vitória Setúbal</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Vitória Setúbal</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G139">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,22 +23576,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,22 +23902,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,22 +24065,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,22 +24228,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G158">
@@ -26179,12 +26179,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G159">
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-09-13 11:15:00</t>
+          <t>2026-09-13 11:00:00</t>
         </is>
       </c>
     </row>
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O160">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P160">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26428,10 +26428,10 @@
         <v>0</v>
       </c>
       <c r="AA160">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB160">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC160">
         <v>0</v>
@@ -26505,12 +26505,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-09-13 11:30:00</t>
+          <t>2026-09-13 11:15:00</t>
         </is>
       </c>
     </row>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G163">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G164">
@@ -27162,22 +27162,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G165">
@@ -27320,27 +27320,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G166">
@@ -27471,7 +27471,7 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>2026-09-13 11:45:00</t>
+          <t>2026-09-13 11:30:00</t>
         </is>
       </c>
     </row>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G168">
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G170">
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G172">
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G173">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:00</t>
+          <t>2026-09-13 11:45:00</t>
         </is>
       </c>
     </row>
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G176">
@@ -29118,22 +29118,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,22 +29770,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,7 +29933,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G184">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,22 +31074,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,22 +31237,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,22 +31400,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G191">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G195">
@@ -32210,27 +32210,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G196">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>2026-09-13 12:15:00</t>
+          <t>2026-09-13 12:00:00</t>
         </is>
       </c>
     </row>
@@ -32373,27 +32373,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G197">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>2026-09-13 12:15:00</t>
+          <t>2026-09-13 12:00:00</t>
         </is>
       </c>
     </row>
@@ -32536,12 +32536,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G198">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-09-13 12:30:00</t>
+          <t>2026-09-13 12:00:00</t>
         </is>
       </c>
     </row>
@@ -32699,27 +32699,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G199">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-09-13 12:30:00</t>
+          <t>2026-09-13 12:00:00</t>
         </is>
       </c>
     </row>
@@ -32862,12 +32862,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-09-13 12:30:00</t>
+          <t>2026-09-13 12:15:00</t>
         </is>
       </c>
     </row>
@@ -33025,27 +33025,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G201">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-09-13 12:30:00</t>
+          <t>2026-09-13 12:15:00</t>
         </is>
       </c>
     </row>
@@ -33193,22 +33193,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G208">
@@ -34329,27 +34329,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G209">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>2026-09-13 12:45:00</t>
+          <t>2026-09-13 12:30:00</t>
         </is>
       </c>
     </row>
@@ -34492,27 +34492,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G210">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>2026-09-13 13:00:00</t>
+          <t>2026-09-13 12:30:00</t>
         </is>
       </c>
     </row>
@@ -34655,27 +34655,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G211">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>2026-09-13 13:00:00</t>
+          <t>2026-09-13 12:30:00</t>
         </is>
       </c>
     </row>
@@ -34818,12 +34818,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G212">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>2026-09-13 13:00:00</t>
+          <t>2026-09-13 12:30:00</t>
         </is>
       </c>
     </row>
@@ -34981,27 +34981,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G213">
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-09-13 13:00:00</t>
+          <t>2026-09-13 12:45:00</t>
         </is>
       </c>
     </row>
@@ -35149,22 +35149,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,22 +35312,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G227">
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G228">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-09-13 13:15:00</t>
+          <t>2026-09-13 13:00:00</t>
         </is>
       </c>
     </row>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G229">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-09-13 13:15:00</t>
+          <t>2026-09-13 13:00:00</t>
         </is>
       </c>
     </row>
@@ -37752,27 +37752,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G230">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-09-13 13:15:00</t>
+          <t>2026-09-13 13:00:00</t>
         </is>
       </c>
     </row>
@@ -37915,27 +37915,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G231">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-09-13 13:15:00</t>
+          <t>2026-09-13 13:00:00</t>
         </is>
       </c>
     </row>
@@ -38078,12 +38078,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G232">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>2026-09-13 13:20:00</t>
+          <t>2026-09-13 13:15:00</t>
         </is>
       </c>
     </row>
@@ -38241,27 +38241,27 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G233">
@@ -38284,7 +38284,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N233">
@@ -38392,7 +38392,7 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>2026-09-13 13:30:00</t>
+          <t>2026-09-13 13:15:00</t>
         </is>
       </c>
     </row>
@@ -38404,27 +38404,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G234">
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>2026-09-13 13:30:00</t>
+          <t>2026-09-13 13:15:00</t>
         </is>
       </c>
     </row>
@@ -38567,27 +38567,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G235">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>2026-09-13 13:30:00</t>
+          <t>2026-09-13 13:15:00</t>
         </is>
       </c>
     </row>
@@ -38730,12 +38730,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G236">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-09-13 13:30:00</t>
+          <t>2026-09-13 13:20:00</t>
         </is>
       </c>
     </row>
@@ -38898,22 +38898,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G237">
@@ -38936,7 +38936,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N237">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G238">
@@ -39219,12 +39219,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="G239">
@@ -39370,7 +39370,7 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>2026-09-13 14:00:00</t>
+          <t>2026-09-13 13:30:00</t>
         </is>
       </c>
     </row>
@@ -39382,12 +39382,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G240">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>2026-09-13 14:00:00</t>
+          <t>2026-09-13 13:30:00</t>
         </is>
       </c>
     </row>
@@ -39545,12 +39545,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G241">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-09-13 14:00:00</t>
+          <t>2026-09-13 13:30:00</t>
         </is>
       </c>
     </row>
@@ -39708,12 +39708,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G242">
@@ -39859,7 +39859,7 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>2026-09-13 14:00:00</t>
+          <t>2026-09-13 13:30:00</t>
         </is>
       </c>
     </row>
@@ -39876,22 +39876,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G243">
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,22 +40528,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G251">
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G252">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G253">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G255">
@@ -41990,27 +41990,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G256">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>2026-09-13 14:15:00</t>
+          <t>2026-09-13 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42153,12 +42153,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G257">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-09-13 14:15:00</t>
+          <t>2026-09-13 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G258">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-09-13 14:15:00</t>
+          <t>2026-09-13 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42479,12 +42479,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="G259">
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-09-13 14:30:00</t>
+          <t>2026-09-13 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42642,12 +42642,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G260">
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-09-13 14:30:00</t>
+          <t>2026-09-13 14:15:00</t>
         </is>
       </c>
     </row>
@@ -42805,12 +42805,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G261">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-09-13 14:30:00</t>
+          <t>2026-09-13 14:15:00</t>
         </is>
       </c>
     </row>
@@ -42968,12 +42968,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G262">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-09-13 14:30:00</t>
+          <t>2026-09-13 14:15:00</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,22 +43299,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G265">
@@ -43620,27 +43620,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:00</t>
+          <t>2026-09-13 14:30:00</t>
         </is>
       </c>
     </row>
@@ -43783,12 +43783,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:00</t>
+          <t>2026-09-13 14:30:00</t>
         </is>
       </c>
     </row>
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:00</t>
+          <t>2026-09-13 14:30:00</t>
         </is>
       </c>
     </row>
@@ -44109,27 +44109,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:00</t>
+          <t>2026-09-13 14:30:00</t>
         </is>
       </c>
     </row>
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G272">
@@ -44766,22 +44766,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O275">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="P275">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45173,10 +45173,10 @@
         <v>0</v>
       </c>
       <c r="AA275">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB275">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AC275">
         <v>0</v>
@@ -45250,12 +45250,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G276">
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-09-13 15:15:00</t>
+          <t>2026-09-13 15:00:00</t>
         </is>
       </c>
     </row>
@@ -45413,27 +45413,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G277">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>2026-09-13 15:30:00</t>
+          <t>2026-09-13 15:00:00</t>
         </is>
       </c>
     </row>
@@ -45576,27 +45576,27 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G278">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-09-13 15:30:00</t>
+          <t>2026-09-13 15:00:00</t>
         </is>
       </c>
     </row>
@@ -45739,27 +45739,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45825,10 +45825,10 @@
         <v>0</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AC279">
         <v>0</v>
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>2026-09-13 15:30:00</t>
+          <t>2026-09-13 15:00:00</t>
         </is>
       </c>
     </row>
@@ -45902,12 +45902,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G280">
@@ -46053,7 +46053,7 @@
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>2026-09-13 15:30:00</t>
+          <t>2026-09-13 15:15:00</t>
         </is>
       </c>
     </row>
@@ -46065,27 +46065,27 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G281">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-09-13 15:45:00</t>
+          <t>2026-09-13 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46228,27 +46228,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O282">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P282">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46314,10 +46314,10 @@
         <v>0</v>
       </c>
       <c r="AA282">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB282">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC282">
         <v>0</v>
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-13 15:45:00</t>
+          <t>2026-09-13 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46391,12 +46391,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O283">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P283">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46477,10 +46477,10 @@
         <v>0</v>
       </c>
       <c r="AA283">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB283">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC283">
         <v>0</v>
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-09-13 16:00:00</t>
+          <t>2026-09-13 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46554,27 +46554,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G284">
@@ -46705,7 +46705,7 @@
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>2026-09-13 16:00:00</t>
+          <t>2026-09-13 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46717,27 +46717,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-09-13 16:00:00</t>
+          <t>2026-09-13 15:45:00</t>
         </is>
       </c>
     </row>
@@ -46880,12 +46880,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -46966,10 +46966,10 @@
         <v>0</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC286">
         <v>0</v>
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-09-13 16:00:00</t>
+          <t>2026-09-13 15:45:00</t>
         </is>
       </c>
     </row>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O287">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P287">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47129,10 +47129,10 @@
         <v>0</v>
       </c>
       <c r="AA287">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB287">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC287">
         <v>0</v>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G288">
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G289">
@@ -47537,7 +47537,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G290">
@@ -47700,7 +47700,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G291">
@@ -47863,22 +47863,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O292">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P292">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -47944,10 +47944,10 @@
         <v>0</v>
       </c>
       <c r="AA292">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB292">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC292">
         <v>0</v>
@@ -48026,22 +48026,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G293">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G294">
@@ -48352,22 +48352,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G295">
@@ -48515,22 +48515,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48596,10 +48596,10 @@
         <v>0</v>
       </c>
       <c r="AA296">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB296">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC296">
         <v>0</v>
@@ -48673,12 +48673,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G297">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-09-13 16:30:00</t>
+          <t>2026-09-13 16:00:00</t>
         </is>
       </c>
     </row>
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-09-13 16:30:00</t>
+          <t>2026-09-13 16:00:00</t>
         </is>
       </c>
     </row>
@@ -48999,27 +48999,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G299">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-09-13 17:00:00</t>
+          <t>2026-09-13 16:00:00</t>
         </is>
       </c>
     </row>
@@ -49162,12 +49162,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O300">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P300">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49248,10 +49248,10 @@
         <v>0</v>
       </c>
       <c r="AA300">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB300">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC300">
         <v>0</v>
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-09-13 17:30:00</t>
+          <t>2026-09-13 16:00:00</t>
         </is>
       </c>
     </row>
@@ -49325,27 +49325,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G301">
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-09-13 17:30:00</t>
+          <t>2026-09-13 16:30:00</t>
         </is>
       </c>
     </row>
@@ -49488,27 +49488,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G302">
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-09-13 18:00:00</t>
+          <t>2026-09-13 16:30:00</t>
         </is>
       </c>
     </row>
@@ -49651,12 +49651,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G303">
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-09-13 18:00:00</t>
+          <t>2026-09-13 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49814,12 +49814,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O304">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P304">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49900,10 +49900,10 @@
         <v>0</v>
       </c>
       <c r="AA304">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB304">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC304">
         <v>0</v>
@@ -49965,7 +49965,7 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>2026-09-13 18:15:00</t>
+          <t>2026-09-13 17:30:00</t>
         </is>
       </c>
     </row>
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G305">
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-09-13 18:30:00</t>
+          <t>2026-09-13 17:30:00</t>
         </is>
       </c>
     </row>
@@ -50140,7 +50140,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G306">
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-09-13 18:30:00</t>
+          <t>2026-09-13 18:00:00</t>
         </is>
       </c>
     </row>
@@ -50303,12 +50303,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G307">
@@ -50454,7 +50454,7 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>2026-09-13 18:30:00</t>
+          <t>2026-09-13 18:00:00</t>
         </is>
       </c>
     </row>
@@ -50466,12 +50466,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G308">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>2026-09-13 18:30:00</t>
+          <t>2026-09-13 18:15:00</t>
         </is>
       </c>
     </row>
@@ -50634,7 +50634,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G309">
@@ -50792,12 +50792,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G310">
@@ -50943,7 +50943,7 @@
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>2026-09-13 19:00:00</t>
+          <t>2026-09-13 18:30:00</t>
         </is>
       </c>
     </row>
@@ -50955,7 +50955,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G311">
@@ -51106,7 +51106,7 @@
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>2026-09-13 19:30:00</t>
+          <t>2026-09-13 18:30:00</t>
         </is>
       </c>
     </row>
@@ -51118,12 +51118,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G312">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>2026-09-13 20:00:00</t>
+          <t>2026-09-13 18:30:00</t>
         </is>
       </c>
     </row>
@@ -51281,12 +51281,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G313">
@@ -51432,7 +51432,7 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>2026-09-13 20:00:00</t>
+          <t>2026-09-13 18:30:00</t>
         </is>
       </c>
     </row>
@@ -51444,12 +51444,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G314">
@@ -51595,7 +51595,7 @@
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>2026-09-13 20:30:00</t>
+          <t>2026-09-13 19:00:00</t>
         </is>
       </c>
     </row>
@@ -51607,156 +51607,808 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="G315">
+        <v>0</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+      <c r="I315">
+        <v>0</v>
+      </c>
+      <c r="J315">
+        <v>0</v>
+      </c>
+      <c r="K315">
+        <v>0</v>
+      </c>
+      <c r="L315">
+        <v>0</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N315">
+        <v>0</v>
+      </c>
+      <c r="O315">
+        <v>0</v>
+      </c>
+      <c r="P315">
+        <v>0</v>
+      </c>
+      <c r="Q315">
+        <v>0</v>
+      </c>
+      <c r="R315">
+        <v>0</v>
+      </c>
+      <c r="S315">
+        <v>0</v>
+      </c>
+      <c r="T315">
+        <v>0</v>
+      </c>
+      <c r="U315">
+        <v>0</v>
+      </c>
+      <c r="V315">
+        <v>0</v>
+      </c>
+      <c r="W315">
+        <v>0</v>
+      </c>
+      <c r="X315">
+        <v>0</v>
+      </c>
+      <c r="Y315">
+        <v>0</v>
+      </c>
+      <c r="Z315">
+        <v>0</v>
+      </c>
+      <c r="AA315">
+        <v>0</v>
+      </c>
+      <c r="AB315">
+        <v>0</v>
+      </c>
+      <c r="AC315">
+        <v>0</v>
+      </c>
+      <c r="AD315">
+        <v>0</v>
+      </c>
+      <c r="AE315">
+        <v>0</v>
+      </c>
+      <c r="AF315">
+        <v>0</v>
+      </c>
+      <c r="AG315">
+        <v>0</v>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ315">
+        <v>0</v>
+      </c>
+      <c r="AK315">
+        <v>0</v>
+      </c>
+      <c r="AL315">
+        <v>0</v>
+      </c>
+      <c r="AM315">
+        <v>-1</v>
+      </c>
+      <c r="AN315">
+        <v>-1</v>
+      </c>
+      <c r="AO315">
+        <v>-1</v>
+      </c>
+      <c r="AP315">
+        <v>-1</v>
+      </c>
+      <c r="AQ315">
+        <v>0</v>
+      </c>
+      <c r="AR315">
+        <v>0</v>
+      </c>
+      <c r="AS315">
+        <v>0</v>
+      </c>
+      <c r="AT315">
+        <v>0</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>2026-09-13 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G316">
+        <v>0</v>
+      </c>
+      <c r="H316">
+        <v>0</v>
+      </c>
+      <c r="I316">
+        <v>0</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>0</v>
+      </c>
+      <c r="L316">
+        <v>0</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N316">
+        <v>0</v>
+      </c>
+      <c r="O316">
+        <v>0</v>
+      </c>
+      <c r="P316">
+        <v>0</v>
+      </c>
+      <c r="Q316">
+        <v>0</v>
+      </c>
+      <c r="R316">
+        <v>0</v>
+      </c>
+      <c r="S316">
+        <v>0</v>
+      </c>
+      <c r="T316">
+        <v>0</v>
+      </c>
+      <c r="U316">
+        <v>0</v>
+      </c>
+      <c r="V316">
+        <v>0</v>
+      </c>
+      <c r="W316">
+        <v>0</v>
+      </c>
+      <c r="X316">
+        <v>0</v>
+      </c>
+      <c r="Y316">
+        <v>0</v>
+      </c>
+      <c r="Z316">
+        <v>0</v>
+      </c>
+      <c r="AA316">
+        <v>0</v>
+      </c>
+      <c r="AB316">
+        <v>0</v>
+      </c>
+      <c r="AC316">
+        <v>0</v>
+      </c>
+      <c r="AD316">
+        <v>0</v>
+      </c>
+      <c r="AE316">
+        <v>0</v>
+      </c>
+      <c r="AF316">
+        <v>0</v>
+      </c>
+      <c r="AG316">
+        <v>0</v>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ316">
+        <v>0</v>
+      </c>
+      <c r="AK316">
+        <v>0</v>
+      </c>
+      <c r="AL316">
+        <v>0</v>
+      </c>
+      <c r="AM316">
+        <v>-1</v>
+      </c>
+      <c r="AN316">
+        <v>-1</v>
+      </c>
+      <c r="AO316">
+        <v>-1</v>
+      </c>
+      <c r="AP316">
+        <v>-1</v>
+      </c>
+      <c r="AQ316">
+        <v>0</v>
+      </c>
+      <c r="AR316">
+        <v>0</v>
+      </c>
+      <c r="AS316">
+        <v>0</v>
+      </c>
+      <c r="AT316">
+        <v>0</v>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>2026-09-13 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G317">
+        <v>0</v>
+      </c>
+      <c r="H317">
+        <v>0</v>
+      </c>
+      <c r="I317">
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <v>0</v>
+      </c>
+      <c r="K317">
+        <v>0</v>
+      </c>
+      <c r="L317">
+        <v>0</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N317">
+        <v>0</v>
+      </c>
+      <c r="O317">
+        <v>0</v>
+      </c>
+      <c r="P317">
+        <v>0</v>
+      </c>
+      <c r="Q317">
+        <v>0</v>
+      </c>
+      <c r="R317">
+        <v>0</v>
+      </c>
+      <c r="S317">
+        <v>0</v>
+      </c>
+      <c r="T317">
+        <v>0</v>
+      </c>
+      <c r="U317">
+        <v>0</v>
+      </c>
+      <c r="V317">
+        <v>0</v>
+      </c>
+      <c r="W317">
+        <v>0</v>
+      </c>
+      <c r="X317">
+        <v>0</v>
+      </c>
+      <c r="Y317">
+        <v>0</v>
+      </c>
+      <c r="Z317">
+        <v>0</v>
+      </c>
+      <c r="AA317">
+        <v>0</v>
+      </c>
+      <c r="AB317">
+        <v>0</v>
+      </c>
+      <c r="AC317">
+        <v>0</v>
+      </c>
+      <c r="AD317">
+        <v>0</v>
+      </c>
+      <c r="AE317">
+        <v>0</v>
+      </c>
+      <c r="AF317">
+        <v>0</v>
+      </c>
+      <c r="AG317">
+        <v>0</v>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ317">
+        <v>0</v>
+      </c>
+      <c r="AK317">
+        <v>0</v>
+      </c>
+      <c r="AL317">
+        <v>0</v>
+      </c>
+      <c r="AM317">
+        <v>-1</v>
+      </c>
+      <c r="AN317">
+        <v>-1</v>
+      </c>
+      <c r="AO317">
+        <v>-1</v>
+      </c>
+      <c r="AP317">
+        <v>-1</v>
+      </c>
+      <c r="AQ317">
+        <v>0</v>
+      </c>
+      <c r="AR317">
+        <v>0</v>
+      </c>
+      <c r="AS317">
+        <v>0</v>
+      </c>
+      <c r="AT317">
+        <v>0</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>2026-09-13 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="G318">
+        <v>0</v>
+      </c>
+      <c r="H318">
+        <v>0</v>
+      </c>
+      <c r="I318">
+        <v>0</v>
+      </c>
+      <c r="J318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>0</v>
+      </c>
+      <c r="L318">
+        <v>0</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N318">
+        <v>0</v>
+      </c>
+      <c r="O318">
+        <v>0</v>
+      </c>
+      <c r="P318">
+        <v>0</v>
+      </c>
+      <c r="Q318">
+        <v>0</v>
+      </c>
+      <c r="R318">
+        <v>0</v>
+      </c>
+      <c r="S318">
+        <v>0</v>
+      </c>
+      <c r="T318">
+        <v>0</v>
+      </c>
+      <c r="U318">
+        <v>0</v>
+      </c>
+      <c r="V318">
+        <v>0</v>
+      </c>
+      <c r="W318">
+        <v>0</v>
+      </c>
+      <c r="X318">
+        <v>0</v>
+      </c>
+      <c r="Y318">
+        <v>0</v>
+      </c>
+      <c r="Z318">
+        <v>0</v>
+      </c>
+      <c r="AA318">
+        <v>0</v>
+      </c>
+      <c r="AB318">
+        <v>0</v>
+      </c>
+      <c r="AC318">
+        <v>0</v>
+      </c>
+      <c r="AD318">
+        <v>0</v>
+      </c>
+      <c r="AE318">
+        <v>0</v>
+      </c>
+      <c r="AF318">
+        <v>0</v>
+      </c>
+      <c r="AG318">
+        <v>0</v>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ318">
+        <v>0</v>
+      </c>
+      <c r="AK318">
+        <v>0</v>
+      </c>
+      <c r="AL318">
+        <v>0</v>
+      </c>
+      <c r="AM318">
+        <v>-1</v>
+      </c>
+      <c r="AN318">
+        <v>-1</v>
+      </c>
+      <c r="AO318">
+        <v>-1</v>
+      </c>
+      <c r="AP318">
+        <v>-1</v>
+      </c>
+      <c r="AQ318">
+        <v>0</v>
+      </c>
+      <c r="AR318">
+        <v>0</v>
+      </c>
+      <c r="AS318">
+        <v>0</v>
+      </c>
+      <c r="AT318">
+        <v>0</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>2026-09-13 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
+      <c r="C319" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
+      <c r="D319" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
+      <c r="E319" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
+      <c r="F319" t="inlineStr">
         <is>
           <t>Philadelphia Union</t>
         </is>
       </c>
-      <c r="G315">
-        <v>0</v>
-      </c>
-      <c r="H315">
-        <v>0</v>
-      </c>
-      <c r="I315">
-        <v>0</v>
-      </c>
-      <c r="J315">
-        <v>0</v>
-      </c>
-      <c r="K315">
-        <v>0</v>
-      </c>
-      <c r="L315">
-        <v>0</v>
-      </c>
-      <c r="M315" t="inlineStr">
+      <c r="G319">
+        <v>0</v>
+      </c>
+      <c r="H319">
+        <v>0</v>
+      </c>
+      <c r="I319">
+        <v>0</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319">
+        <v>0</v>
+      </c>
+      <c r="L319">
+        <v>0</v>
+      </c>
+      <c r="M319" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N315">
-        <v>0</v>
-      </c>
-      <c r="O315">
-        <v>0</v>
-      </c>
-      <c r="P315">
-        <v>0</v>
-      </c>
-      <c r="Q315">
-        <v>0</v>
-      </c>
-      <c r="R315">
-        <v>0</v>
-      </c>
-      <c r="S315">
-        <v>0</v>
-      </c>
-      <c r="T315">
-        <v>0</v>
-      </c>
-      <c r="U315">
-        <v>0</v>
-      </c>
-      <c r="V315">
-        <v>0</v>
-      </c>
-      <c r="W315">
-        <v>0</v>
-      </c>
-      <c r="X315">
-        <v>0</v>
-      </c>
-      <c r="Y315">
-        <v>0</v>
-      </c>
-      <c r="Z315">
-        <v>0</v>
-      </c>
-      <c r="AA315">
-        <v>0</v>
-      </c>
-      <c r="AB315">
-        <v>0</v>
-      </c>
-      <c r="AC315">
-        <v>0</v>
-      </c>
-      <c r="AD315">
-        <v>0</v>
-      </c>
-      <c r="AE315">
-        <v>0</v>
-      </c>
-      <c r="AF315">
-        <v>0</v>
-      </c>
-      <c r="AG315">
-        <v>0</v>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ315">
-        <v>0</v>
-      </c>
-      <c r="AK315">
-        <v>0</v>
-      </c>
-      <c r="AL315">
-        <v>0</v>
-      </c>
-      <c r="AM315">
-        <v>-1</v>
-      </c>
-      <c r="AN315">
-        <v>-1</v>
-      </c>
-      <c r="AO315">
-        <v>-1</v>
-      </c>
-      <c r="AP315">
-        <v>-1</v>
-      </c>
-      <c r="AQ315">
-        <v>0</v>
-      </c>
-      <c r="AR315">
-        <v>0</v>
-      </c>
-      <c r="AS315">
-        <v>0</v>
-      </c>
-      <c r="AT315">
-        <v>0</v>
-      </c>
-      <c r="AU315" t="inlineStr">
+      <c r="N319">
+        <v>0</v>
+      </c>
+      <c r="O319">
+        <v>0</v>
+      </c>
+      <c r="P319">
+        <v>0</v>
+      </c>
+      <c r="Q319">
+        <v>0</v>
+      </c>
+      <c r="R319">
+        <v>0</v>
+      </c>
+      <c r="S319">
+        <v>0</v>
+      </c>
+      <c r="T319">
+        <v>0</v>
+      </c>
+      <c r="U319">
+        <v>0</v>
+      </c>
+      <c r="V319">
+        <v>0</v>
+      </c>
+      <c r="W319">
+        <v>0</v>
+      </c>
+      <c r="X319">
+        <v>0</v>
+      </c>
+      <c r="Y319">
+        <v>0</v>
+      </c>
+      <c r="Z319">
+        <v>0</v>
+      </c>
+      <c r="AA319">
+        <v>0</v>
+      </c>
+      <c r="AB319">
+        <v>0</v>
+      </c>
+      <c r="AC319">
+        <v>0</v>
+      </c>
+      <c r="AD319">
+        <v>0</v>
+      </c>
+      <c r="AE319">
+        <v>0</v>
+      </c>
+      <c r="AF319">
+        <v>0</v>
+      </c>
+      <c r="AG319">
+        <v>0</v>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ319">
+        <v>0</v>
+      </c>
+      <c r="AK319">
+        <v>0</v>
+      </c>
+      <c r="AL319">
+        <v>0</v>
+      </c>
+      <c r="AM319">
+        <v>-1</v>
+      </c>
+      <c r="AN319">
+        <v>-1</v>
+      </c>
+      <c r="AO319">
+        <v>-1</v>
+      </c>
+      <c r="AP319">
+        <v>-1</v>
+      </c>
+      <c r="AQ319">
+        <v>0</v>
+      </c>
+      <c r="AR319">
+        <v>0</v>
+      </c>
+      <c r="AS319">
+        <v>0</v>
+      </c>
+      <c r="AT319">
+        <v>0</v>
+      </c>
+      <c r="AU319" t="inlineStr">
         <is>
           <t>2026-09-13 22:00:00</t>
         </is>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU319"/>
+  <dimension ref="A1:AU320"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G9">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G229">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G231">
@@ -38078,12 +38078,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G232">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>2026-09-13 13:15:00</t>
+          <t>2026-09-13 13:00:00</t>
         </is>
       </c>
     </row>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,22 +38409,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G235">
@@ -38730,27 +38730,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G236">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-09-13 13:20:00</t>
+          <t>2026-09-13 13:15:00</t>
         </is>
       </c>
     </row>
@@ -38893,27 +38893,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G237">
@@ -38936,7 +38936,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N237">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-09-13 13:30:00</t>
+          <t>2026-09-13 13:20:00</t>
         </is>
       </c>
     </row>
@@ -39061,22 +39061,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G238">
@@ -39099,7 +39099,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N238">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G242">
@@ -39871,12 +39871,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G243">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>2026-09-13 14:00:00</t>
+          <t>2026-09-13 13:30:00</t>
         </is>
       </c>
     </row>
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,22 +40528,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,22 +40691,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G248">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G249">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="G251">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G252">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G253">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G256">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G259">
@@ -42642,27 +42642,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="G260">
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-09-13 14:15:00</t>
+          <t>2026-09-13 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42810,22 +42810,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G262">
@@ -43131,12 +43131,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G263">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>2026-09-13 14:30:00</t>
+          <t>2026-09-13 14:15:00</t>
         </is>
       </c>
     </row>
@@ -43299,22 +43299,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,22 +43462,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G265">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G266">
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G267">
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G268">
@@ -44114,7 +44114,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G269">
@@ -44272,27 +44272,27 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G270">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:00</t>
+          <t>2026-09-13 14:30:00</t>
         </is>
       </c>
     </row>
@@ -44440,22 +44440,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G271">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G272">
@@ -44766,22 +44766,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,7 +44929,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,22 +45092,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G275">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G276">
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G278">
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O279">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="P279">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45825,10 +45825,10 @@
         <v>0</v>
       </c>
       <c r="AA279">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB279">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AC279">
         <v>0</v>
@@ -45902,12 +45902,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -45988,10 +45988,10 @@
         <v>0</v>
       </c>
       <c r="AA280">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB280">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AC280">
         <v>0</v>
@@ -46053,7 +46053,7 @@
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>2026-09-13 15:15:00</t>
+          <t>2026-09-13 15:00:00</t>
         </is>
       </c>
     </row>
@@ -46065,27 +46065,27 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G281">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-09-13 15:30:00</t>
+          <t>2026-09-13 15:15:00</t>
         </is>
       </c>
     </row>
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G282">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G283">
@@ -46559,22 +46559,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G284">
@@ -46717,12 +46717,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-09-13 15:45:00</t>
+          <t>2026-09-13 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O286">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P286">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -46966,10 +46966,10 @@
         <v>0</v>
       </c>
       <c r="AA286">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB286">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC286">
         <v>0</v>
@@ -47043,27 +47043,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.87</v>
+        <v>5.75</v>
       </c>
       <c r="O287">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="P287">
-        <v>4.53</v>
+        <v>2.1</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47129,10 +47129,10 @@
         <v>0</v>
       </c>
       <c r="AA287">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB287">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC287">
         <v>0</v>
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-09-13 16:00:00</t>
+          <t>2026-09-13 15:45:00</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G289">
@@ -47537,22 +47537,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G290">
@@ -47700,22 +47700,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G293">
@@ -48189,22 +48189,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G294">
@@ -48352,22 +48352,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G295">
@@ -48515,22 +48515,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O296">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P296">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48596,10 +48596,10 @@
         <v>0</v>
       </c>
       <c r="AA296">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB296">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC296">
         <v>0</v>
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O297">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P297">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -48759,10 +48759,10 @@
         <v>0</v>
       </c>
       <c r="AA297">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB297">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC297">
         <v>0</v>
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G298">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G299">
@@ -49167,22 +49167,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G300">
@@ -49325,27 +49325,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G301">
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-09-13 16:30:00</t>
+          <t>2026-09-13 16:00:00</t>
         </is>
       </c>
     </row>
@@ -49493,7 +49493,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G302">
@@ -49651,27 +49651,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G303">
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-09-13 17:00:00</t>
+          <t>2026-09-13 16:30:00</t>
         </is>
       </c>
     </row>
@@ -49814,12 +49814,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O304">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P304">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49900,10 +49900,10 @@
         <v>0</v>
       </c>
       <c r="AA304">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB304">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC304">
         <v>0</v>
@@ -49965,7 +49965,7 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>2026-09-13 17:30:00</t>
+          <t>2026-09-13 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49982,7 +49982,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50063,10 +50063,10 @@
         <v>0</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC305">
         <v>0</v>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G306">
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-09-13 18:00:00</t>
+          <t>2026-09-13 17:30:00</t>
         </is>
       </c>
     </row>
@@ -50308,7 +50308,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G307">
@@ -50466,12 +50466,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G308">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>2026-09-13 18:15:00</t>
+          <t>2026-09-13 18:00:00</t>
         </is>
       </c>
     </row>
@@ -50629,12 +50629,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G309">
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-09-13 18:30:00</t>
+          <t>2026-09-13 18:15:00</t>
         </is>
       </c>
     </row>
@@ -50797,7 +50797,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G310">
@@ -50960,7 +50960,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G311">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G312">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G313">
@@ -51444,12 +51444,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G314">
@@ -51595,7 +51595,7 @@
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>2026-09-13 19:00:00</t>
+          <t>2026-09-13 18:30:00</t>
         </is>
       </c>
     </row>
@@ -51607,12 +51607,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G315">
@@ -51758,7 +51758,7 @@
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>2026-09-13 19:30:00</t>
+          <t>2026-09-13 19:00:00</t>
         </is>
       </c>
     </row>
@@ -51770,12 +51770,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G316">
@@ -51921,7 +51921,7 @@
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>2026-09-13 20:00:00</t>
+          <t>2026-09-13 19:30:00</t>
         </is>
       </c>
     </row>
@@ -51938,7 +51938,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G317">
@@ -52096,12 +52096,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G318">
@@ -52247,7 +52247,7 @@
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>2026-09-13 20:30:00</t>
+          <t>2026-09-13 20:00:00</t>
         </is>
       </c>
     </row>
@@ -52259,156 +52259,319 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="G319">
+        <v>0</v>
+      </c>
+      <c r="H319">
+        <v>0</v>
+      </c>
+      <c r="I319">
+        <v>0</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319">
+        <v>0</v>
+      </c>
+      <c r="L319">
+        <v>0</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N319">
+        <v>0</v>
+      </c>
+      <c r="O319">
+        <v>0</v>
+      </c>
+      <c r="P319">
+        <v>0</v>
+      </c>
+      <c r="Q319">
+        <v>0</v>
+      </c>
+      <c r="R319">
+        <v>0</v>
+      </c>
+      <c r="S319">
+        <v>0</v>
+      </c>
+      <c r="T319">
+        <v>0</v>
+      </c>
+      <c r="U319">
+        <v>0</v>
+      </c>
+      <c r="V319">
+        <v>0</v>
+      </c>
+      <c r="W319">
+        <v>0</v>
+      </c>
+      <c r="X319">
+        <v>0</v>
+      </c>
+      <c r="Y319">
+        <v>0</v>
+      </c>
+      <c r="Z319">
+        <v>0</v>
+      </c>
+      <c r="AA319">
+        <v>0</v>
+      </c>
+      <c r="AB319">
+        <v>0</v>
+      </c>
+      <c r="AC319">
+        <v>0</v>
+      </c>
+      <c r="AD319">
+        <v>0</v>
+      </c>
+      <c r="AE319">
+        <v>0</v>
+      </c>
+      <c r="AF319">
+        <v>0</v>
+      </c>
+      <c r="AG319">
+        <v>0</v>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ319">
+        <v>0</v>
+      </c>
+      <c r="AK319">
+        <v>0</v>
+      </c>
+      <c r="AL319">
+        <v>0</v>
+      </c>
+      <c r="AM319">
+        <v>-1</v>
+      </c>
+      <c r="AN319">
+        <v>-1</v>
+      </c>
+      <c r="AO319">
+        <v>-1</v>
+      </c>
+      <c r="AP319">
+        <v>-1</v>
+      </c>
+      <c r="AQ319">
+        <v>0</v>
+      </c>
+      <c r="AR319">
+        <v>0</v>
+      </c>
+      <c r="AS319">
+        <v>0</v>
+      </c>
+      <c r="AT319">
+        <v>0</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>2026-09-13 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
+      <c r="C320" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
+      <c r="D320" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr">
+      <c r="E320" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
+      <c r="F320" t="inlineStr">
         <is>
           <t>Philadelphia Union</t>
         </is>
       </c>
-      <c r="G319">
-        <v>0</v>
-      </c>
-      <c r="H319">
-        <v>0</v>
-      </c>
-      <c r="I319">
-        <v>0</v>
-      </c>
-      <c r="J319">
-        <v>0</v>
-      </c>
-      <c r="K319">
-        <v>0</v>
-      </c>
-      <c r="L319">
-        <v>0</v>
-      </c>
-      <c r="M319" t="inlineStr">
+      <c r="G320">
+        <v>0</v>
+      </c>
+      <c r="H320">
+        <v>0</v>
+      </c>
+      <c r="I320">
+        <v>0</v>
+      </c>
+      <c r="J320">
+        <v>0</v>
+      </c>
+      <c r="K320">
+        <v>0</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
+      </c>
+      <c r="M320" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N319">
-        <v>0</v>
-      </c>
-      <c r="O319">
-        <v>0</v>
-      </c>
-      <c r="P319">
-        <v>0</v>
-      </c>
-      <c r="Q319">
-        <v>0</v>
-      </c>
-      <c r="R319">
-        <v>0</v>
-      </c>
-      <c r="S319">
-        <v>0</v>
-      </c>
-      <c r="T319">
-        <v>0</v>
-      </c>
-      <c r="U319">
-        <v>0</v>
-      </c>
-      <c r="V319">
-        <v>0</v>
-      </c>
-      <c r="W319">
-        <v>0</v>
-      </c>
-      <c r="X319">
-        <v>0</v>
-      </c>
-      <c r="Y319">
-        <v>0</v>
-      </c>
-      <c r="Z319">
-        <v>0</v>
-      </c>
-      <c r="AA319">
-        <v>0</v>
-      </c>
-      <c r="AB319">
-        <v>0</v>
-      </c>
-      <c r="AC319">
-        <v>0</v>
-      </c>
-      <c r="AD319">
-        <v>0</v>
-      </c>
-      <c r="AE319">
-        <v>0</v>
-      </c>
-      <c r="AF319">
-        <v>0</v>
-      </c>
-      <c r="AG319">
-        <v>0</v>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI319" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ319">
-        <v>0</v>
-      </c>
-      <c r="AK319">
-        <v>0</v>
-      </c>
-      <c r="AL319">
-        <v>0</v>
-      </c>
-      <c r="AM319">
-        <v>-1</v>
-      </c>
-      <c r="AN319">
-        <v>-1</v>
-      </c>
-      <c r="AO319">
-        <v>-1</v>
-      </c>
-      <c r="AP319">
-        <v>-1</v>
-      </c>
-      <c r="AQ319">
-        <v>0</v>
-      </c>
-      <c r="AR319">
-        <v>0</v>
-      </c>
-      <c r="AS319">
-        <v>0</v>
-      </c>
-      <c r="AT319">
-        <v>0</v>
-      </c>
-      <c r="AU319" t="inlineStr">
+      <c r="N320">
+        <v>0</v>
+      </c>
+      <c r="O320">
+        <v>0</v>
+      </c>
+      <c r="P320">
+        <v>0</v>
+      </c>
+      <c r="Q320">
+        <v>0</v>
+      </c>
+      <c r="R320">
+        <v>0</v>
+      </c>
+      <c r="S320">
+        <v>0</v>
+      </c>
+      <c r="T320">
+        <v>0</v>
+      </c>
+      <c r="U320">
+        <v>0</v>
+      </c>
+      <c r="V320">
+        <v>0</v>
+      </c>
+      <c r="W320">
+        <v>0</v>
+      </c>
+      <c r="X320">
+        <v>0</v>
+      </c>
+      <c r="Y320">
+        <v>0</v>
+      </c>
+      <c r="Z320">
+        <v>0</v>
+      </c>
+      <c r="AA320">
+        <v>0</v>
+      </c>
+      <c r="AB320">
+        <v>0</v>
+      </c>
+      <c r="AC320">
+        <v>0</v>
+      </c>
+      <c r="AD320">
+        <v>0</v>
+      </c>
+      <c r="AE320">
+        <v>0</v>
+      </c>
+      <c r="AF320">
+        <v>0</v>
+      </c>
+      <c r="AG320">
+        <v>0</v>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ320">
+        <v>0</v>
+      </c>
+      <c r="AK320">
+        <v>0</v>
+      </c>
+      <c r="AL320">
+        <v>0</v>
+      </c>
+      <c r="AM320">
+        <v>-1</v>
+      </c>
+      <c r="AN320">
+        <v>-1</v>
+      </c>
+      <c r="AO320">
+        <v>-1</v>
+      </c>
+      <c r="AP320">
+        <v>-1</v>
+      </c>
+      <c r="AQ320">
+        <v>0</v>
+      </c>
+      <c r="AR320">
+        <v>0</v>
+      </c>
+      <c r="AS320">
+        <v>0</v>
+      </c>
+      <c r="AT320">
+        <v>0</v>
+      </c>
+      <c r="AU320" t="inlineStr">
         <is>
           <t>2026-09-13 22:00:00</t>
         </is>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G136">
@@ -22486,55 +22486,55 @@
         <v>0</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,22 +22924,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,22 +23739,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,22 +23902,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,22 +24065,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G147">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,22 +24554,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G158">
@@ -26184,7 +26184,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G159">
@@ -26342,27 +26342,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G160">
@@ -26493,7 +26493,7 @@
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>2026-09-13 11:15:00</t>
+          <t>2026-09-13 11:00:00</t>
         </is>
       </c>
     </row>
@@ -26505,12 +26505,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O161">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P161">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB161">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-09-13 11:15:00</t>
+          <t>2026-09-13 11:00:00</t>
         </is>
       </c>
     </row>
@@ -26668,12 +26668,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G162">
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>2026-09-13 11:30:00</t>
+          <t>2026-09-13 11:15:00</t>
         </is>
       </c>
     </row>
@@ -26831,12 +26831,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26917,10 +26917,10 @@
         <v>0</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC163">
         <v>0</v>
@@ -26982,7 +26982,7 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>2026-09-13 11:30:00</t>
+          <t>2026-09-13 11:15:00</t>
         </is>
       </c>
     </row>
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G164">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G165">
@@ -27325,22 +27325,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G166">
@@ -27483,12 +27483,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G167">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-09-13 11:45:00</t>
+          <t>2026-09-13 11:30:00</t>
         </is>
       </c>
     </row>
@@ -27646,27 +27646,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G168">
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-09-13 11:45:00</t>
+          <t>2026-09-13 11:30:00</t>
         </is>
       </c>
     </row>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G170">
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G172">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G173">
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G174">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:00</t>
+          <t>2026-09-13 11:45:00</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G175">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:00</t>
+          <t>2026-09-13 11:45:00</t>
         </is>
       </c>
     </row>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G176">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,22 +29281,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G178">
@@ -29332,55 +29332,55 @@
         <v>0</v>
       </c>
       <c r="Q178">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R178">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S178">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T178">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U178">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V178">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W178">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X178">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z178">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC178">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD178">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE178">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG178">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK178">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29444,22 +29444,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,22 +30096,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G184">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,22 +31726,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,22 +31889,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G197">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G199">
@@ -32862,27 +32862,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-09-13 12:15:00</t>
+          <t>2026-09-13 12:00:00</t>
         </is>
       </c>
     </row>
@@ -33025,27 +33025,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G201">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-09-13 12:15:00</t>
+          <t>2026-09-13 12:00:00</t>
         </is>
       </c>
     </row>
@@ -33188,27 +33188,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-09-13 12:30:00</t>
+          <t>2026-09-13 12:15:00</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G203">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-09-13 12:30:00</t>
+          <t>2026-09-13 12:15:00</t>
         </is>
       </c>
     </row>
@@ -33519,22 +33519,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,22 +34008,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="G209">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G212">
@@ -34981,27 +34981,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G213">
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-09-13 12:45:00</t>
+          <t>2026-09-13 12:30:00</t>
         </is>
       </c>
     </row>
@@ -35144,27 +35144,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-09-13 13:00:00</t>
+          <t>2026-09-13 12:30:00</t>
         </is>
       </c>
     </row>
@@ -35307,7 +35307,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G215">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-09-13 13:00:00</t>
+          <t>2026-09-13 12:45:00</t>
         </is>
       </c>
     </row>
@@ -35475,22 +35475,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G219">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G223">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G229">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G230">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G232">
@@ -38241,12 +38241,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G233">
@@ -38392,7 +38392,7 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>2026-09-13 13:15:00</t>
+          <t>2026-09-13 13:00:00</t>
         </is>
       </c>
     </row>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,22 +38572,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G236">
@@ -38893,27 +38893,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G237">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-09-13 13:20:00</t>
+          <t>2026-09-13 13:15:00</t>
         </is>
       </c>
     </row>
@@ -39056,27 +39056,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G238">
@@ -39099,7 +39099,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N238">
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-09-13 13:30:00</t>
+          <t>2026-09-13 13:20:00</t>
         </is>
       </c>
     </row>
@@ -39224,22 +39224,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G239">
@@ -39262,7 +39262,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G243">
@@ -40034,12 +40034,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G244">
@@ -40185,7 +40185,7 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>2026-09-13 14:00:00</t>
+          <t>2026-09-13 13:30:00</t>
         </is>
       </c>
     </row>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,22 +40691,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,22 +40854,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G249">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G250">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G251">
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="G252">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G253">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G254">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G257">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G260">
@@ -42805,27 +42805,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="G261">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-09-13 14:15:00</t>
+          <t>2026-09-13 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42973,22 +42973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G262">
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G263">
@@ -43294,12 +43294,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G264">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-09-13 14:30:00</t>
+          <t>2026-09-13 14:15:00</t>
         </is>
       </c>
     </row>
@@ -43462,22 +43462,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G265">
@@ -43625,22 +43625,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G266">
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G267">
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G268">
@@ -44114,7 +44114,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G269">
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G270">
@@ -44435,27 +44435,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G271">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:00</t>
+          <t>2026-09-13 14:30:00</t>
         </is>
       </c>
     </row>
@@ -44603,22 +44603,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G272">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,22 +45255,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G276">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G278">
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O280">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="P280">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -45988,10 +45988,10 @@
         <v>0</v>
       </c>
       <c r="AA280">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB280">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AC280">
         <v>0</v>
@@ -46065,12 +46065,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O281">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P281">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46151,10 +46151,10 @@
         <v>0</v>
       </c>
       <c r="AA281">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB281">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AC281">
         <v>0</v>
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-09-13 15:15:00</t>
+          <t>2026-09-13 15:00:00</t>
         </is>
       </c>
     </row>
@@ -46228,27 +46228,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-13 15:30:00</t>
+          <t>2026-09-13 15:15:00</t>
         </is>
       </c>
     </row>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G283">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,22 +46722,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G285">
@@ -46880,12 +46880,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-09-13 15:45:00</t>
+          <t>2026-09-13 15:30:00</t>
         </is>
       </c>
     </row>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O287">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P287">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47129,10 +47129,10 @@
         <v>0</v>
       </c>
       <c r="AA287">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB287">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC287">
         <v>0</v>
@@ -47206,27 +47206,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.87</v>
+        <v>5.75</v>
       </c>
       <c r="O288">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="P288">
-        <v>4.53</v>
+        <v>2.1</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB288">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-09-13 16:00:00</t>
+          <t>2026-09-13 15:45:00</t>
         </is>
       </c>
     </row>
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47455,10 +47455,10 @@
         <v>0</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC289">
         <v>0</v>
@@ -47537,7 +47537,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G290">
@@ -47700,22 +47700,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G291">

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18737,55 +18737,55 @@
         <v>0</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18900,55 +18900,55 @@
         <v>0</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G212">
@@ -37645,55 +37645,55 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T229">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U229">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V229">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W229">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X229">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z229">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA229">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB229">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK229">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38134,55 +38134,55 @@
         <v>0</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T232">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U232">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V232">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W232">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X232">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC232">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD232">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG232">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK232">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL232">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="G36">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,55 +10913,55 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13032,34 +13032,34 @@
         <v>5.38</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA78">
         <v>2.1</v>
@@ -13068,19 +13068,19 @@
         <v>1.72</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>0</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Vitória Setúbal</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vitória Setúbal</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G134">
@@ -22649,55 +22649,55 @@
         <v>0</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22812,55 +22812,55 @@
         <v>0</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G145">
@@ -24279,55 +24279,55 @@
         <v>0</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U147">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V147">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X147">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z147">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE147">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF147">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK147">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S148">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T148">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U148">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V148">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W148">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y148">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z148">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA148">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC148">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD148">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE148">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF148">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG148">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK148">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G150">
@@ -24768,55 +24768,55 @@
         <v>0</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z150">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF150">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG150">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK150">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V151">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W151">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X151">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y151">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z151">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD151">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF151">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG151">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25094,55 +25094,55 @@
         <v>0</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T152">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V152">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X152">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y152">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z152">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S160">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T160">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U160">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V160">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W160">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X160">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y160">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z160">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC160">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD160">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE160">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF160">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG160">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK160">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S162">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T162">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V162">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W162">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X162">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y162">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z162">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC162">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD162">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK162">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26887,34 +26887,34 @@
         <v>1.35</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA163">
         <v>1.5</v>
@@ -26923,19 +26923,19 @@
         <v>2.62</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V164">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X164">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y164">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z164">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK164">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S165">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T165">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U165">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V165">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W165">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X165">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z165">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA165">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD165">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE165">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK165">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X166">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T167">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U167">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V167">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W167">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X167">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y167">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z167">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD167">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE167">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG167">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK167">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S173">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T173">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U173">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V173">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W173">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X173">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y173">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z173">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC173">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD173">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE173">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF173">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG173">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK173">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T174">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U174">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V174">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W174">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X174">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE174">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF174">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG174">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AK174">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X177">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S184">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T184">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U184">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V184">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W184">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X184">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y184">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z184">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC184">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD184">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG184">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK184">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X188">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z188">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC188">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD188">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE188">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S189">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T189">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U189">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V189">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W189">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X189">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y189">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z189">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC189">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD189">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE189">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF189">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG189">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK189">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G194">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G201">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S202">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T202">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U202">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V202">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W202">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X202">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y202">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z202">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA202">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB202">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC202">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD202">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE202">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF202">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG202">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK202">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R203">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S203">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T203">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U203">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V203">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W203">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X203">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y203">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z203">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA203">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB203">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC203">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD203">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG203">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK203">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA205">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S208">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T208">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U208">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V208">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W208">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X208">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y208">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z208">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA208">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB208">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC208">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD208">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE208">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF208">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG208">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK208">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G212">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S217">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T217">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U217">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V217">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W217">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X217">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y217">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z217">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA217">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC217">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD217">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG217">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK217">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R222">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S222">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T222">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U222">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V222">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W222">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X222">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y222">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z222">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA222">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB222">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC222">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD222">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE222">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF222">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG222">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK222">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S227">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T227">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V227">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W227">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X227">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z227">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="AA227">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB227">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC227">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD227">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG227">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O231">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P231">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q232">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R232">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S232">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T232">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U232">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="V232">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W232">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X232">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y232">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z232">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA232">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB232">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC232">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD232">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE232">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF232">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG232">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK232">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S240">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T240">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U240">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V240">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X240">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y240">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z240">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC240">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD240">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE240">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF240">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG240">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK240">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39764,55 +39764,55 @@
         <v>0</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S242">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T242">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U242">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V242">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W242">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X242">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y242">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z242">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC242">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD242">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG242">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK242">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39918,64 +39918,64 @@
         </is>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O243">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P243">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q243">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R243">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S243">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T243">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U243">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V243">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W243">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X243">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y243">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z243">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA243">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB243">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC243">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD243">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE243">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF243">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG243">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK243">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40120,10 +40120,10 @@
         <v>0</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC244">
         <v>0</v>
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R245">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S245">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T245">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U245">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V245">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W245">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X245">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y245">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z245">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC245">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD245">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE245">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF245">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG245">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK245">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40407,64 +40407,64 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S246">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T246">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U246">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V246">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W246">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X246">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y246">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z246">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC246">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD246">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE246">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF246">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG246">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK246">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40579,55 +40579,55 @@
         <v>0</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S247">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T247">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U247">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V247">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W247">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X247">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z247">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC247">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD247">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG247">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK247">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41711,64 +41711,64 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q254">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R254">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S254">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T254">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U254">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V254">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W254">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X254">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y254">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z254">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA254">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB254">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC254">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD254">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE254">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF254">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG254">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK254">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,64 +41874,64 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -43187,55 +43187,55 @@
         <v>0</v>
       </c>
       <c r="Q263">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R263">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S263">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T263">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U263">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V263">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W263">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X263">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y263">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z263">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA263">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB263">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC263">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD263">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE263">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF263">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG263">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK263">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43380,10 +43380,10 @@
         <v>0</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC264">
         <v>0</v>
@@ -43504,64 +43504,64 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q265">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R265">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S265">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T265">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U265">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V265">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W265">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X265">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y265">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z265">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA265">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB265">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC265">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD265">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE265">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF265">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG265">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK265">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q269">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="R269">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T269">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V269">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W269">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X269">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y269">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z269">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE269">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF269">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG269">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK269">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y279">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z279">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46121,34 +46121,34 @@
         <v>11</v>
       </c>
       <c r="Q281">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R281">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S281">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T281">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="U281">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V281">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W281">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y281">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z281">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA281">
         <v>1.22</v>
@@ -46157,19 +46157,19 @@
         <v>4.2</v>
       </c>
       <c r="AC281">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD281">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE281">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF281">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG281">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK281">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46275,64 +46275,64 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL282">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U10">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
+        <v>1.04</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1.26</v>
+      </c>
+      <c r="Z10">
+        <v>3.2</v>
+      </c>
+      <c r="AA10">
+        <v>1.9</v>
+      </c>
+      <c r="AB10">
+        <v>1.8</v>
+      </c>
+      <c r="AC10">
+        <v>3.31</v>
+      </c>
+      <c r="AD10">
+        <v>1.26</v>
+      </c>
+      <c r="AE10">
         <v>1.06</v>
       </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>1.25</v>
-      </c>
-      <c r="Z10">
-        <v>3.28</v>
-      </c>
-      <c r="AA10">
-        <v>1.94</v>
-      </c>
-      <c r="AB10">
-        <v>1.85</v>
-      </c>
-      <c r="AC10">
-        <v>3.04</v>
-      </c>
-      <c r="AD10">
-        <v>1.33</v>
-      </c>
-      <c r="AE10">
-        <v>1.12</v>
-      </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>2.38</v>
+      </c>
+      <c r="R11">
         <v>2.2</v>
-      </c>
-      <c r="O11">
-        <v>3.4</v>
-      </c>
-      <c r="P11">
-        <v>2.85</v>
-      </c>
-      <c r="Q11">
-        <v>2.75</v>
-      </c>
-      <c r="R11">
-        <v>2.15</v>
       </c>
       <c r="S11">
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U11">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA11">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.31</v>
+        <v>3.04</v>
       </c>
       <c r="AD11">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G25">
@@ -4393,55 +4393,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="O62">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="P62">
+        <v>2.03</v>
+      </c>
+      <c r="Q62">
         <v>3.4</v>
       </c>
-      <c r="Q62">
-        <v>2.4</v>
-      </c>
       <c r="R62">
+        <v>2.3</v>
+      </c>
+      <c r="S62">
+        <v>1.26</v>
+      </c>
+      <c r="T62">
+        <v>3.6</v>
+      </c>
+      <c r="U62">
+        <v>2.31</v>
+      </c>
+      <c r="V62">
+        <v>1.57</v>
+      </c>
+      <c r="W62">
+        <v>1.12</v>
+      </c>
+      <c r="X62">
+        <v>1.02</v>
+      </c>
+      <c r="Y62">
+        <v>1.2</v>
+      </c>
+      <c r="Z62">
+        <v>4.5</v>
+      </c>
+      <c r="AA62">
+        <v>1.6</v>
+      </c>
+      <c r="AB62">
+        <v>2.18</v>
+      </c>
+      <c r="AC62">
         <v>2.5</v>
       </c>
-      <c r="S62">
+      <c r="AD62">
+        <v>1.5</v>
+      </c>
+      <c r="AE62">
+        <v>1.2</v>
+      </c>
+      <c r="AF62">
+        <v>1.53</v>
+      </c>
+      <c r="AG62">
+        <v>2.3</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.25</v>
       </c>
-      <c r="T62">
-        <v>3.5</v>
-      </c>
-      <c r="U62">
-        <v>2.2</v>
-      </c>
-      <c r="V62">
-        <v>1.62</v>
-      </c>
-      <c r="W62">
-        <v>1.13</v>
-      </c>
-      <c r="X62">
-        <v>1.03</v>
-      </c>
-      <c r="Y62">
-        <v>1.15</v>
-      </c>
-      <c r="Z62">
-        <v>5</v>
-      </c>
-      <c r="AA62">
-        <v>1.45</v>
-      </c>
-      <c r="AB62">
-        <v>2.55</v>
-      </c>
-      <c r="AC62">
-        <v>2.1</v>
-      </c>
-      <c r="AD62">
-        <v>1.57</v>
-      </c>
-      <c r="AE62">
-        <v>1.22</v>
-      </c>
-      <c r="AF62">
-        <v>1.44</v>
-      </c>
-      <c r="AG62">
-        <v>2.65</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.3</v>
-      </c>
       <c r="AK62">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="R63">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S63">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="U63">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="W63">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z63">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AA63">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.18</v>
+        <v>2.87</v>
       </c>
       <c r="AC63">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="AD63">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AE63">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF63">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG63">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,80 +10741,80 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q64">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="R64">
         <v>2.5</v>
       </c>
       <c r="S64">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="V64">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="W64">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA64">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB64">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="AC64">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AD64">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE64">
+        <v>1.22</v>
+      </c>
+      <c r="AF64">
+        <v>1.44</v>
+      </c>
+      <c r="AG64">
+        <v>2.65</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.3</v>
       </c>
-      <c r="AF64">
-        <v>1.4</v>
-      </c>
-      <c r="AG64">
-        <v>2.7</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.22</v>
-      </c>
       <c r="AK64">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,52 +12371,52 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q74">
-        <v>2.86</v>
+        <v>2.53</v>
       </c>
       <c r="R74">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S74">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T74">
         <v>2.56</v>
       </c>
       <c r="U74">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="V74">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W74">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z74">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="AA74">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AB74">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC74">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AD74">
         <v>1.19</v>
@@ -12425,10 +12425,10 @@
         <v>1.03</v>
       </c>
       <c r="AF74">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AG74">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK74">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,52 +12534,52 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.53</v>
+        <v>2.86</v>
       </c>
       <c r="R75">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S75">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T75">
         <v>2.56</v>
       </c>
       <c r="U75">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V75">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W75">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z75">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="AA75">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AB75">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC75">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AD75">
         <v>1.19</v>
@@ -12588,10 +12588,10 @@
         <v>1.03</v>
       </c>
       <c r="AF75">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AG75">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK75">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.81</v>
+        <v>1.66</v>
       </c>
       <c r="O82">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>1.79</v>
+        <v>4.33</v>
       </c>
       <c r="Q82">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="R82">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S82">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U82">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V82">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W82">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X82">
         <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z82">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA82">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC82">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD82">
+        <v>1.5</v>
+      </c>
+      <c r="AE82">
+        <v>1.2</v>
+      </c>
+      <c r="AF82">
         <v>1.57</v>
       </c>
-      <c r="AE82">
-        <v>1.22</v>
-      </c>
-      <c r="AF82">
-        <v>1.5</v>
-      </c>
       <c r="AG82">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.66</v>
+        <v>3.81</v>
       </c>
       <c r="O83">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P83">
-        <v>4.33</v>
+        <v>1.79</v>
       </c>
       <c r="Q83">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="R83">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S83">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="U83">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="V83">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W83">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X83">
         <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z83">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA83">
+        <v>1.48</v>
+      </c>
+      <c r="AB83">
+        <v>2.4</v>
+      </c>
+      <c r="AC83">
+        <v>2.23</v>
+      </c>
+      <c r="AD83">
         <v>1.57</v>
       </c>
-      <c r="AB83">
-        <v>2.25</v>
-      </c>
-      <c r="AC83">
-        <v>2.25</v>
-      </c>
-      <c r="AD83">
+      <c r="AE83">
+        <v>1.22</v>
+      </c>
+      <c r="AF83">
         <v>1.5</v>
       </c>
-      <c r="AE83">
-        <v>1.2</v>
-      </c>
-      <c r="AF83">
-        <v>1.57</v>
-      </c>
       <c r="AG83">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q104">
-        <v>3.75</v>
+        <v>2.14</v>
       </c>
       <c r="R104">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="S104">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T104">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="U104">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="V104">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="W104">
+        <v>1.09</v>
+      </c>
+      <c r="X104">
         <v>1.04</v>
       </c>
-      <c r="X104">
-        <v>1.02</v>
-      </c>
       <c r="Y104">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="Z104">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AA104">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AB104">
-        <v>1.68</v>
+        <v>2.23</v>
       </c>
       <c r="AC104">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="AD104">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AE104">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF104">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG104">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK104">
-        <v>1.3</v>
+        <v>2.07</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
         <v>3.75</v>
       </c>
-      <c r="P105">
-        <v>4.7</v>
-      </c>
-      <c r="Q105">
-        <v>2.14</v>
-      </c>
       <c r="R105">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="S105">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T105">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="U105">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="V105">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="W105">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X105">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z105">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AA105">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AB105">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="AC105">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
       <c r="AD105">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AE105">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF105">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG105">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>2.07</v>
+        <v>1.3</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,10 +17596,10 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -17608,10 +17608,10 @@
         <v>0</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W106">
         <v>0</v>
@@ -17620,31 +17620,31 @@
         <v>0</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G127">
@@ -22323,10 +22323,10 @@
         <v>0</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S135">
         <v>0</v>
@@ -22335,10 +22335,10 @@
         <v>0</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W135">
         <v>0</v>
@@ -22347,31 +22347,31 @@
         <v>0</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE135">
         <v>0</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22975,10 +22975,10 @@
         <v>0</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -22987,10 +22987,10 @@
         <v>0</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W139">
         <v>0</v>
@@ -22999,31 +22999,31 @@
         <v>0</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE139">
         <v>0</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,80 +24759,80 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q150">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="R150">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S150">
+        <v>1.4</v>
+      </c>
+      <c r="T150">
+        <v>2.62</v>
+      </c>
+      <c r="U150">
+        <v>2.91</v>
+      </c>
+      <c r="V150">
         <v>1.36</v>
       </c>
-      <c r="T150">
-        <v>2.79</v>
-      </c>
-      <c r="U150">
-        <v>2.63</v>
-      </c>
-      <c r="V150">
-        <v>1.4</v>
-      </c>
       <c r="W150">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X150">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y150">
         <v>1.3</v>
       </c>
       <c r="Z150">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA150">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB150">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC150">
         <v>3.5</v>
       </c>
       <c r="AD150">
+        <v>1.22</v>
+      </c>
+      <c r="AE150">
+        <v>1.04</v>
+      </c>
+      <c r="AF150">
+        <v>1.75</v>
+      </c>
+      <c r="AG150">
+        <v>2</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ150">
         <v>1.25</v>
       </c>
-      <c r="AE150">
-        <v>1.08</v>
-      </c>
-      <c r="AF150">
-        <v>1.8</v>
-      </c>
-      <c r="AG150">
-        <v>1.91</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ150">
-        <v>1.33</v>
-      </c>
       <c r="AK150">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O151">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P151">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q151">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="R151">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S151">
+        <v>1.36</v>
+      </c>
+      <c r="T151">
+        <v>2.79</v>
+      </c>
+      <c r="U151">
+        <v>2.63</v>
+      </c>
+      <c r="V151">
         <v>1.4</v>
       </c>
-      <c r="T151">
-        <v>2.62</v>
-      </c>
-      <c r="U151">
-        <v>2.91</v>
-      </c>
-      <c r="V151">
-        <v>1.36</v>
-      </c>
       <c r="W151">
+        <v>1.07</v>
+      </c>
+      <c r="X151">
         <v>1.06</v>
-      </c>
-      <c r="X151">
-        <v>1.03</v>
       </c>
       <c r="Y151">
         <v>1.3</v>
       </c>
       <c r="Z151">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA151">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB151">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC151">
         <v>3.5</v>
       </c>
       <c r="AD151">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE151">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF151">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG151">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK151">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -29658,10 +29658,10 @@
         <v>0</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -29670,10 +29670,10 @@
         <v>0</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W180">
         <v>0</v>
@@ -29682,31 +29682,31 @@
         <v>0</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O181">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S181">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T181">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U181">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V181">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W181">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X181">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z181">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA181">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB181">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC181">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD181">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG181">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK181">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U182">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V182">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W182">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X182">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y182">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z182">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB182">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG182">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK182">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S183">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T183">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U183">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V183">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W183">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X183">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z183">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA183">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB183">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC183">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD183">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE183">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF183">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG183">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK183">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G192">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G194">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T198">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V198">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X198">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z198">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE198">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG198">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S199">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T199">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U199">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V199">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="W199">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y199">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z199">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA199">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB199">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC199">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD199">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE199">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG199">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK199">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S200">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T200">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U200">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V200">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W200">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X200">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y200">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z200">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC200">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD200">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE200">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG200">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK200">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X201">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S207">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T207">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U207">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V207">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W207">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X207">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y207">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z207">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA207">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB207">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG207">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK207">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -35387,31 +35387,31 @@
         <v>0</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA215">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD215">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE215">
         <v>0</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK215">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35526,10 +35526,10 @@
         <v>0</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -35538,10 +35538,10 @@
         <v>0</v>
       </c>
       <c r="U216">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V216">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W216">
         <v>0</v>
@@ -35550,31 +35550,31 @@
         <v>0</v>
       </c>
       <c r="Y216">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z216">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA216">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC216">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD216">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE216">
         <v>0</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG216">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK216">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,80 +41874,80 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.17</v>
+        <v>2.51</v>
       </c>
       <c r="O255">
-        <v>7.25</v>
+        <v>3.13</v>
       </c>
       <c r="P255">
-        <v>16.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q255">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="R255">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="S255">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="T255">
-        <v>3.58</v>
+        <v>2.65</v>
       </c>
       <c r="U255">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="V255">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="W255">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X255">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y255">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="Z255">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="AA255">
+        <v>2.17</v>
+      </c>
+      <c r="AB255">
+        <v>1.55</v>
+      </c>
+      <c r="AC255">
+        <v>4.1</v>
+      </c>
+      <c r="AD255">
+        <v>1.2</v>
+      </c>
+      <c r="AE255">
+        <v>1.06</v>
+      </c>
+      <c r="AF255">
+        <v>1.91</v>
+      </c>
+      <c r="AG255">
+        <v>1.83</v>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ255">
+        <v>1.44</v>
+      </c>
+      <c r="AK255">
         <v>1.45</v>
-      </c>
-      <c r="AB255">
-        <v>2.6</v>
-      </c>
-      <c r="AC255">
-        <v>2.2</v>
-      </c>
-      <c r="AD255">
-        <v>1.61</v>
-      </c>
-      <c r="AE255">
-        <v>1.2</v>
-      </c>
-      <c r="AF255">
-        <v>2.3</v>
-      </c>
-      <c r="AG255">
-        <v>1.57</v>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ255">
-        <v>1.08</v>
-      </c>
-      <c r="AK255">
-        <v>5.05</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,80 +42037,80 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.51</v>
+        <v>1.17</v>
       </c>
       <c r="O256">
-        <v>3.13</v>
+        <v>7.25</v>
       </c>
       <c r="P256">
+        <v>16.5</v>
+      </c>
+      <c r="Q256">
+        <v>1.5</v>
+      </c>
+      <c r="R256">
+        <v>2.95</v>
+      </c>
+      <c r="S256">
+        <v>1.22</v>
+      </c>
+      <c r="T256">
+        <v>3.58</v>
+      </c>
+      <c r="U256">
+        <v>2.16</v>
+      </c>
+      <c r="V256">
+        <v>1.6</v>
+      </c>
+      <c r="W256">
+        <v>1.16</v>
+      </c>
+      <c r="X256">
+        <v>1.01</v>
+      </c>
+      <c r="Y256">
+        <v>1.11</v>
+      </c>
+      <c r="Z256">
+        <v>5</v>
+      </c>
+      <c r="AA256">
+        <v>1.45</v>
+      </c>
+      <c r="AB256">
         <v>2.6</v>
       </c>
-      <c r="Q256">
-        <v>3.25</v>
-      </c>
-      <c r="R256">
-        <v>2</v>
-      </c>
-      <c r="S256">
-        <v>1.49</v>
-      </c>
-      <c r="T256">
-        <v>2.65</v>
-      </c>
-      <c r="U256">
-        <v>3.3</v>
-      </c>
-      <c r="V256">
-        <v>1.28</v>
-      </c>
-      <c r="W256">
-        <v>1.03</v>
-      </c>
-      <c r="X256">
+      <c r="AC256">
+        <v>2.2</v>
+      </c>
+      <c r="AD256">
+        <v>1.61</v>
+      </c>
+      <c r="AE256">
+        <v>1.2</v>
+      </c>
+      <c r="AF256">
+        <v>2.3</v>
+      </c>
+      <c r="AG256">
+        <v>1.57</v>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ256">
         <v>1.08</v>
       </c>
-      <c r="Y256">
-        <v>1.4</v>
-      </c>
-      <c r="Z256">
-        <v>2.8</v>
-      </c>
-      <c r="AA256">
-        <v>2.17</v>
-      </c>
-      <c r="AB256">
-        <v>1.55</v>
-      </c>
-      <c r="AC256">
-        <v>4.1</v>
-      </c>
-      <c r="AD256">
-        <v>1.2</v>
-      </c>
-      <c r="AE256">
-        <v>1.06</v>
-      </c>
-      <c r="AF256">
-        <v>1.91</v>
-      </c>
-      <c r="AG256">
-        <v>1.83</v>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ256">
-        <v>1.44</v>
-      </c>
       <c r="AK256">
-        <v>1.45</v>
+        <v>5.05</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -43024,55 +43024,55 @@
         <v>0</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -47425,34 +47425,34 @@
         <v>4.53</v>
       </c>
       <c r="Q289">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R289">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S289">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T289">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U289">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V289">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W289">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X289">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z289">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA289">
         <v>2.05</v>
@@ -47461,19 +47461,19 @@
         <v>1.75</v>
       </c>
       <c r="AC289">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD289">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE289">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF289">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG289">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK289">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL289">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
         <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="AA4">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AB4">
+        <v>1.66</v>
+      </c>
+      <c r="AC4">
+        <v>3.91</v>
+      </c>
+      <c r="AD4">
+        <v>1.19</v>
+      </c>
+      <c r="AE4">
+        <v>1.06</v>
+      </c>
+      <c r="AF4">
         <v>1.83</v>
       </c>
-      <c r="AC4">
-        <v>3.14</v>
-      </c>
-      <c r="AD4">
-        <v>1.3</v>
-      </c>
-      <c r="AE4">
-        <v>1.07</v>
-      </c>
-      <c r="AF4">
-        <v>1.71</v>
-      </c>
       <c r="AG4">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AK4">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="Q5">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="R5">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
         <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U5">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>3.01</v>
+        <v>3.37</v>
       </c>
       <c r="AA5">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AB5">
+        <v>1.83</v>
+      </c>
+      <c r="AC5">
+        <v>3.14</v>
+      </c>
+      <c r="AD5">
+        <v>1.3</v>
+      </c>
+      <c r="AE5">
+        <v>1.07</v>
+      </c>
+      <c r="AF5">
+        <v>1.71</v>
+      </c>
+      <c r="AG5">
+        <v>1.97</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.66</v>
       </c>
-      <c r="AC5">
-        <v>3.91</v>
-      </c>
-      <c r="AD5">
-        <v>1.19</v>
-      </c>
-      <c r="AE5">
-        <v>1.06</v>
-      </c>
-      <c r="AF5">
-        <v>1.83</v>
-      </c>
-      <c r="AG5">
-        <v>1.86</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.44</v>
-      </c>
       <c r="AK5">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>2.38</v>
+      </c>
+      <c r="R10">
         <v>2.2</v>
-      </c>
-      <c r="O10">
-        <v>3.4</v>
-      </c>
-      <c r="P10">
-        <v>2.85</v>
-      </c>
-      <c r="Q10">
-        <v>2.75</v>
-      </c>
-      <c r="R10">
-        <v>2.15</v>
       </c>
       <c r="S10">
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U10">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA10">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB10">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
-        <v>3.31</v>
+        <v>3.04</v>
       </c>
       <c r="AD10">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U11">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
+        <v>1.04</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1.26</v>
+      </c>
+      <c r="Z11">
+        <v>3.2</v>
+      </c>
+      <c r="AA11">
+        <v>1.9</v>
+      </c>
+      <c r="AB11">
+        <v>1.8</v>
+      </c>
+      <c r="AC11">
+        <v>3.31</v>
+      </c>
+      <c r="AD11">
+        <v>1.26</v>
+      </c>
+      <c r="AE11">
         <v>1.06</v>
       </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
-        <v>1.25</v>
-      </c>
-      <c r="Z11">
-        <v>3.28</v>
-      </c>
-      <c r="AA11">
-        <v>1.94</v>
-      </c>
-      <c r="AB11">
-        <v>1.85</v>
-      </c>
-      <c r="AC11">
-        <v>3.04</v>
-      </c>
-      <c r="AD11">
-        <v>1.33</v>
-      </c>
-      <c r="AE11">
-        <v>1.12</v>
-      </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.66</v>
+        <v>3.81</v>
       </c>
       <c r="O82">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P82">
-        <v>4.33</v>
+        <v>1.79</v>
       </c>
       <c r="Q82">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="R82">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="V82">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W82">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X82">
         <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z82">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA82">
+        <v>1.48</v>
+      </c>
+      <c r="AB82">
+        <v>2.4</v>
+      </c>
+      <c r="AC82">
+        <v>2.23</v>
+      </c>
+      <c r="AD82">
         <v>1.57</v>
       </c>
-      <c r="AB82">
-        <v>2.25</v>
-      </c>
-      <c r="AC82">
-        <v>2.25</v>
-      </c>
-      <c r="AD82">
+      <c r="AE82">
+        <v>1.22</v>
+      </c>
+      <c r="AF82">
         <v>1.5</v>
       </c>
-      <c r="AE82">
-        <v>1.2</v>
-      </c>
-      <c r="AF82">
-        <v>1.57</v>
-      </c>
       <c r="AG82">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.81</v>
+        <v>1.66</v>
       </c>
       <c r="O83">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
-        <v>1.79</v>
+        <v>4.33</v>
       </c>
       <c r="Q83">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="R83">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U83">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V83">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W83">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X83">
         <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA83">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB83">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC83">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD83">
+        <v>1.5</v>
+      </c>
+      <c r="AE83">
+        <v>1.2</v>
+      </c>
+      <c r="AF83">
         <v>1.57</v>
       </c>
-      <c r="AE83">
-        <v>1.22</v>
-      </c>
-      <c r="AF83">
-        <v>1.5</v>
-      </c>
       <c r="AG83">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
         <v>3.75</v>
       </c>
-      <c r="P104">
-        <v>4.7</v>
-      </c>
-      <c r="Q104">
-        <v>2.14</v>
-      </c>
       <c r="R104">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="S104">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T104">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="U104">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="V104">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="W104">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z104">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AA104">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AB104">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="AC104">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
       <c r="AD104">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AE104">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF104">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK104">
-        <v>2.07</v>
+        <v>1.3</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q105">
-        <v>3.75</v>
+        <v>2.14</v>
       </c>
       <c r="R105">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="S105">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T105">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="U105">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="V105">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="W105">
+        <v>1.09</v>
+      </c>
+      <c r="X105">
         <v>1.04</v>
       </c>
-      <c r="X105">
-        <v>1.02</v>
-      </c>
       <c r="Y105">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="Z105">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AA105">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AB105">
-        <v>1.68</v>
+        <v>2.23</v>
       </c>
       <c r="AC105">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="AD105">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AE105">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF105">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG105">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK105">
-        <v>1.3</v>
+        <v>2.07</v>
       </c>
       <c r="AL105">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>2.95</v>
       </c>
       <c r="O8">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P8">
         <v>2.25</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="O9">
         <v>3.05</v>
@@ -1785,25 +1785,25 @@
         <v>2.35</v>
       </c>
       <c r="Q9">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1.02</v>
@@ -1812,7 +1812,7 @@
         <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA9">
         <v>2</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
         <v>1.4</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5534,22 +5534,22 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
         <v>0</v>
@@ -5558,31 +5558,31 @@
         <v>0</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -9446,16 +9446,16 @@
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R56">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
         <v>1.32</v>
       </c>
       <c r="T56">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U56">
         <v>2.75</v>
@@ -9464,34 +9464,34 @@
         <v>1.4</v>
       </c>
       <c r="W56">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
         <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z56">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA56">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB56">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AC56">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD56">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE56">
         <v>1.1</v>
       </c>
       <c r="AF56">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG56">
         <v>1.95</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK56">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9763,25 +9763,25 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="O58">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="P58">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="Q58">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R58">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S58">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T58">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U58">
         <v>2.75</v>
@@ -9790,37 +9790,37 @@
         <v>1.4</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z58">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA58">
-        <v>2.03</v>
+        <v>1.68</v>
       </c>
       <c r="AB58">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AC58">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AD58">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE58">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG58">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.23</v>
+        <v>1.78</v>
       </c>
       <c r="O78">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="Q78">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="U78">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="V78">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="Z78">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA78">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="AB78">
-        <v>2.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC78">
-        <v>1.86</v>
+        <v>3.05</v>
       </c>
       <c r="AD78">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="AE78">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF78">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG78">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>4.5</v>
+        <v>1.94</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,65 +13186,65 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.78</v>
+        <v>1.23</v>
       </c>
       <c r="O79">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="P79">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="Q79">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="S79">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T79">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="U79">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="V79">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="W79">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X79">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="Z79">
-        <v>3.8</v>
+        <v>6.25</v>
       </c>
       <c r="AA79">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="AB79">
+        <v>2.99</v>
+      </c>
+      <c r="AC79">
+        <v>1.86</v>
+      </c>
+      <c r="AD79">
+        <v>1.77</v>
+      </c>
+      <c r="AE79">
+        <v>1.33</v>
+      </c>
+      <c r="AF79">
+        <v>1.75</v>
+      </c>
+      <c r="AG79">
         <v>1.95</v>
       </c>
-      <c r="AC79">
-        <v>3.05</v>
-      </c>
-      <c r="AD79">
-        <v>1.32</v>
-      </c>
-      <c r="AE79">
-        <v>1.13</v>
-      </c>
-      <c r="AF79">
-        <v>1.7</v>
-      </c>
-      <c r="AG79">
-        <v>2.04</v>
-      </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK79">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O80">
         <v>3.2</v>
       </c>
       <c r="P80">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="Q80">
         <v>3</v>
       </c>
       <c r="R80">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S80">
+        <v>1.44</v>
+      </c>
+      <c r="T80">
+        <v>2.56</v>
+      </c>
+      <c r="U80">
+        <v>3.05</v>
+      </c>
+      <c r="V80">
         <v>1.36</v>
-      </c>
-      <c r="T80">
-        <v>2.88</v>
-      </c>
-      <c r="U80">
-        <v>3.1</v>
-      </c>
-      <c r="V80">
-        <v>1.31</v>
       </c>
       <c r="W80">
         <v>1.05</v>
       </c>
       <c r="X80">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z80">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AA80">
         <v>2.12</v>
       </c>
       <c r="AB80">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AC80">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AD80">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE80">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF80">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG80">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="O83">
         <v>3.55</v>
@@ -13871,31 +13871,31 @@
         <v>1.05</v>
       </c>
       <c r="Y83">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AA83">
         <v>1.79</v>
       </c>
       <c r="AB83">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC83">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD83">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE83">
         <v>1.13</v>
       </c>
       <c r="AF83">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG83">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -15637,58 +15637,58 @@
         <v>3.2</v>
       </c>
       <c r="P94">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Q94">
-        <v>3.9</v>
+        <v>4.46</v>
       </c>
       <c r="R94">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S94">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T94">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="U94">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="V94">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
         <v>1.05</v>
       </c>
       <c r="X94">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z94">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="AA94">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AB94">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC94">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="AD94">
         <v>1.22</v>
       </c>
       <c r="AE94">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF94">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG94">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15794,19 +15794,19 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O95">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P95">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q95">
         <v>2.82</v>
       </c>
       <c r="R95">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S95">
         <v>1.39</v>
@@ -15957,16 +15957,16 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="O96">
+        <v>3.2</v>
+      </c>
+      <c r="P96">
         <v>3.25</v>
       </c>
-      <c r="P96">
-        <v>3.55</v>
-      </c>
       <c r="Q96">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="R96">
         <v>2.02</v>
@@ -15978,10 +15978,10 @@
         <v>2.67</v>
       </c>
       <c r="U96">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="V96">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W96">
         <v>1.04</v>
@@ -15996,25 +15996,25 @@
         <v>3.2</v>
       </c>
       <c r="AA96">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB96">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC96">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD96">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE96">
         <v>1.06</v>
       </c>
       <c r="AF96">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG96">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -18239,16 +18239,16 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O110">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q110">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="R110">
         <v>1.91</v>
@@ -18260,7 +18260,7 @@
         <v>2.42</v>
       </c>
       <c r="U110">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V110">
         <v>1.29</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -18417,49 +18417,49 @@
         <v>1.89</v>
       </c>
       <c r="S111">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T111">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U111">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="V111">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W111">
         <v>1.01</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z111">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA111">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AB111">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC111">
-        <v>3.86</v>
+        <v>4.05</v>
       </c>
       <c r="AD111">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE111">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF111">
+        <v>1.86</v>
+      </c>
+      <c r="AG111">
         <v>1.81</v>
-      </c>
-      <c r="AG111">
-        <v>1.86</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18574,56 +18574,56 @@
         <v>0</v>
       </c>
       <c r="Q112">
-        <v>3.88</v>
+        <v>4.39</v>
       </c>
       <c r="R112">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S112">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T112">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="U112">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V112">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W112">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y112">
+        <v>1.27</v>
+      </c>
+      <c r="Z112">
+        <v>3.14</v>
+      </c>
+      <c r="AA112">
+        <v>1.96</v>
+      </c>
+      <c r="AB112">
+        <v>1.74</v>
+      </c>
+      <c r="AC112">
+        <v>3.34</v>
+      </c>
+      <c r="AD112">
         <v>1.24</v>
       </c>
-      <c r="Z112">
-        <v>3.34</v>
-      </c>
-      <c r="AA112">
+      <c r="AE112">
+        <v>1.04</v>
+      </c>
+      <c r="AF112">
+        <v>1.76</v>
+      </c>
+      <c r="AG112">
         <v>1.88</v>
       </c>
-      <c r="AB112">
-        <v>1.81</v>
-      </c>
-      <c r="AC112">
-        <v>3.14</v>
-      </c>
-      <c r="AD112">
-        <v>1.27</v>
-      </c>
-      <c r="AE112">
-        <v>1.06</v>
-      </c>
-      <c r="AF112">
-        <v>1.68</v>
-      </c>
-      <c r="AG112">
-        <v>2.02</v>
-      </c>
       <c r="AH112" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK112">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,34 +18728,34 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O113">
         <v>3.1</v>
       </c>
       <c r="P113">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q113">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R113">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S113">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T113">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="U113">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="V113">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W113">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X113">
         <v>1.04</v>
@@ -18767,7 +18767,7 @@
         <v>2.62</v>
       </c>
       <c r="AA113">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AB113">
         <v>1.57</v>
@@ -19220,7 +19220,7 @@
         <v>1.38</v>
       </c>
       <c r="O116">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P116">
         <v>7.3</v>
@@ -19229,22 +19229,22 @@
         <v>1.81</v>
       </c>
       <c r="R116">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="S116">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T116">
         <v>4.05</v>
       </c>
       <c r="U116">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="V116">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W116">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X116">
         <v>1.02</v>
@@ -19253,22 +19253,22 @@
         <v>1.12</v>
       </c>
       <c r="Z116">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA116">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB116">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AC116">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD116">
         <v>1.81</v>
       </c>
       <c r="AE116">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF116">
         <v>1.6</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK116">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O165">
         <v>3.2</v>
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30177,10 +30177,10 @@
         <v>0</v>
       </c>
       <c r="AA183">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB183">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC183">
         <v>0</v>
@@ -30953,34 +30953,34 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="O188">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="P188">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Q188">
-        <v>3.31</v>
+        <v>3.22</v>
       </c>
       <c r="R188">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="S188">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="T188">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="U188">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="V188">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W188">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X188">
         <v>1.05</v>
@@ -30989,19 +30989,19 @@
         <v>1.45</v>
       </c>
       <c r="Z188">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AA188">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AB188">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC188">
         <v>4.25</v>
       </c>
       <c r="AD188">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE188">
         <v>1.02</v>
@@ -31614,22 +31614,22 @@
         <v>0</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S192">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T192">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U192">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V192">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W192">
         <v>0</v>
@@ -31638,31 +31638,31 @@
         <v>0</v>
       </c>
       <c r="Y192">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z192">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC192">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD192">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE192">
         <v>0</v>
       </c>
       <c r="AF192">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG192">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK192">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32622,10 +32622,10 @@
         <v>0</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC198">
         <v>0</v>
@@ -32785,10 +32785,10 @@
         <v>0</v>
       </c>
       <c r="AA199">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB199">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC199">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36697,10 +36697,10 @@
         <v>0</v>
       </c>
       <c r="AA223">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB223">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC223">
         <v>0</v>
@@ -36860,10 +36860,10 @@
         <v>0</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC224">
         <v>0</v>
@@ -37645,22 +37645,22 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T229">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U229">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V229">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W229">
         <v>0</v>
@@ -37669,31 +37669,31 @@
         <v>0</v>
       </c>
       <c r="Y229">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z229">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA229">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB229">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE229">
         <v>0</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK229">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37808,22 +37808,22 @@
         <v>0</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R230">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S230">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T230">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U230">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V230">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W230">
         <v>0</v>
@@ -37832,31 +37832,31 @@
         <v>0</v>
       </c>
       <c r="Y230">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z230">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA230">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB230">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC230">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD230">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE230">
         <v>0</v>
       </c>
       <c r="AF230">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG230">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK230">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q235">
         <v>3.06</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39468,10 +39468,10 @@
         <v>0</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC240">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40609,10 +40609,10 @@
         <v>0</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC247">
         <v>0</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41750,10 +41750,10 @@
         <v>0</v>
       </c>
       <c r="AA254">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB254">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC254">
         <v>0</v>
@@ -42239,10 +42239,10 @@
         <v>0</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC257">
         <v>0</v>
@@ -43217,10 +43217,10 @@
         <v>0</v>
       </c>
       <c r="AA263">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB263">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC263">
         <v>0</v>
@@ -43380,10 +43380,10 @@
         <v>0</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC264">
         <v>0</v>
@@ -43543,10 +43543,10 @@
         <v>0</v>
       </c>
       <c r="AA265">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB265">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC265">
         <v>0</v>
@@ -46966,10 +46966,10 @@
         <v>0</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC286">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O53">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q53">
         <v>3.72</v>
@@ -8981,16 +8981,16 @@
         <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="AA53">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB53">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC53">
         <v>2.68</v>
@@ -8999,7 +8999,7 @@
         <v>1.37</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF53">
         <v>1.62</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G147">
@@ -24279,55 +24279,55 @@
         <v>0</v>
       </c>
       <c r="Q147">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="R147">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S147">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="T147">
-        <v>4.3</v>
+        <v>5.15</v>
       </c>
       <c r="U147">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="V147">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="W147">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="X147">
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z147">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA147">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB147">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AC147">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AD147">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AE147">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF147">
         <v>1.33</v>
       </c>
       <c r="AG147">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK147">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G148">
@@ -24442,25 +24442,25 @@
         <v>0</v>
       </c>
       <c r="Q148">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="R148">
-        <v>3.2</v>
+        <v>2.61</v>
       </c>
       <c r="S148">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="T148">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="U148">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="V148">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="W148">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="X148">
         <v>0</v>
@@ -24469,28 +24469,28 @@
         <v>1.03</v>
       </c>
       <c r="Z148">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AA148">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AB148">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="AC148">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AD148">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="AE148">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AF148">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AG148">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK148">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G149">
@@ -24605,55 +24605,55 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="R149">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S149">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="T149">
-        <v>5.15</v>
+        <v>4.3</v>
       </c>
       <c r="U149">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="V149">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="W149">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="X149">
         <v>1.01</v>
       </c>
       <c r="Y149">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z149">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA149">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB149">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AC149">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AD149">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AE149">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AF149">
         <v>1.33</v>
       </c>
       <c r="AG149">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK149">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G150">
@@ -24768,25 +24768,25 @@
         <v>0</v>
       </c>
       <c r="Q150">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="R150">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="S150">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="T150">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="U150">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="V150">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="W150">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="X150">
         <v>0</v>
@@ -24795,28 +24795,28 @@
         <v>1.03</v>
       </c>
       <c r="Z150">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AA150">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AB150">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="AC150">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AD150">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="AE150">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AF150">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AG150">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK150">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -42689,40 +42689,40 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="O260">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P260">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
       </c>
       <c r="R260">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S260">
         <v>1.49</v>
       </c>
       <c r="T260">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U260">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V260">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W260">
+        <v>1.07</v>
+      </c>
+      <c r="X260">
         <v>1.03</v>
       </c>
-      <c r="X260">
-        <v>1.08</v>
-      </c>
       <c r="Y260">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z260">
         <v>2.8</v>
@@ -42731,16 +42731,16 @@
         <v>2.17</v>
       </c>
       <c r="AB260">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC260">
         <v>4.1</v>
       </c>
       <c r="AD260">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE260">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF260">
         <v>1.91</v>
@@ -42762,7 +42762,7 @@
         <v>1.44</v>
       </c>
       <c r="AK260">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42855,61 +42855,61 @@
         <v>1.17</v>
       </c>
       <c r="O261">
-        <v>7.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P261">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Q261">
         <v>1.5</v>
       </c>
       <c r="R261">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="S261">
         <v>1.22</v>
       </c>
       <c r="T261">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U261">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V261">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W261">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X261">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y261">
         <v>1.11</v>
       </c>
       <c r="Z261">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA261">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB261">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="AC261">
         <v>2.2</v>
       </c>
       <c r="AD261">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE261">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF261">
         <v>2.3</v>
       </c>
       <c r="AG261">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>1.08</v>
       </c>
       <c r="AK261">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -45469,10 +45469,10 @@
         <v>0</v>
       </c>
       <c r="Q277">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="R277">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="S277">
         <v>1.36</v>
@@ -45481,13 +45481,13 @@
         <v>2.63</v>
       </c>
       <c r="U277">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V277">
         <v>1.33</v>
       </c>
       <c r="W277">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X277">
         <v>1.02</v>
@@ -45517,7 +45517,7 @@
         <v>1.84</v>
       </c>
       <c r="AG277">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK277">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O281">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P281">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q289">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R289">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S289">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T289">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U289">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V289">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W289">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X289">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y289">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z289">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC289">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD289">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE289">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF289">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG289">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK289">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P290">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X290">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q291">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R291">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S291">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T291">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U291">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V291">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W291">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X291">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y291">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z291">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA291">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB291">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC291">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AD291">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE291">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF291">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG291">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK291">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC299">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O300">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P300">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q300">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R300">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S300">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T300">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U300">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V300">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W300">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X300">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y300">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z300">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA300">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB300">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC300">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD300">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE300">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF300">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG300">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK300">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G321">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G322">

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -45475,10 +45475,10 @@
         <v>2.04</v>
       </c>
       <c r="S277">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T277">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U277">
         <v>3</v>
@@ -45496,16 +45496,16 @@
         <v>1.3</v>
       </c>
       <c r="Z277">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA277">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AB277">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC277">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AD277">
         <v>1.25</v>
@@ -45533,7 +45533,7 @@
         <v>1.24</v>
       </c>
       <c r="AK277">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="O289">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="P289">
-        <v>3.2</v>
+        <v>4.85</v>
       </c>
       <c r="Q289">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="R289">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="S289">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T289">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U289">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V289">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W289">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X289">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y289">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Z289">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA289">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AB289">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AC289">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AD289">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AE289">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF289">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AG289">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AK289">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,65 +47579,65 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.63</v>
+        <v>2.7</v>
       </c>
       <c r="O290">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="P290">
-        <v>4.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q290">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="R290">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="S290">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="T290">
+        <v>1.99</v>
+      </c>
+      <c r="U290">
+        <v>4.5</v>
+      </c>
+      <c r="V290">
+        <v>1.17</v>
+      </c>
+      <c r="W290">
+        <v>1.02</v>
+      </c>
+      <c r="X290">
+        <v>1.18</v>
+      </c>
+      <c r="Y290">
+        <v>1.72</v>
+      </c>
+      <c r="Z290">
+        <v>2</v>
+      </c>
+      <c r="AA290">
+        <v>3.2</v>
+      </c>
+      <c r="AB290">
+        <v>1.26</v>
+      </c>
+      <c r="AC290">
+        <v>7.5</v>
+      </c>
+      <c r="AD290">
+        <v>1.04</v>
+      </c>
+      <c r="AE290">
+        <v>1.02</v>
+      </c>
+      <c r="AF290">
         <v>2.4</v>
       </c>
-      <c r="U290">
-        <v>3.75</v>
-      </c>
-      <c r="V290">
-        <v>1.22</v>
-      </c>
-      <c r="W290">
-        <v>1.04</v>
-      </c>
-      <c r="X290">
-        <v>1.1</v>
-      </c>
-      <c r="Y290">
+      <c r="AG290">
         <v>1.5</v>
       </c>
-      <c r="Z290">
-        <v>2.45</v>
-      </c>
-      <c r="AA290">
-        <v>2.49</v>
-      </c>
-      <c r="AB290">
-        <v>1.44</v>
-      </c>
-      <c r="AC290">
-        <v>5.1</v>
-      </c>
-      <c r="AD290">
-        <v>1.14</v>
-      </c>
-      <c r="AE290">
-        <v>1.04</v>
-      </c>
-      <c r="AF290">
-        <v>2.18</v>
-      </c>
-      <c r="AG290">
-        <v>1.46</v>
-      </c>
       <c r="AH290" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AK290">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
+        <v>2.3</v>
+      </c>
+      <c r="O291">
+        <v>2.75</v>
+      </c>
+      <c r="P291">
+        <v>3.2</v>
+      </c>
+      <c r="Q291">
+        <v>2.9</v>
+      </c>
+      <c r="R291">
+        <v>1.85</v>
+      </c>
+      <c r="S291">
+        <v>1.57</v>
+      </c>
+      <c r="T291">
+        <v>2.3</v>
+      </c>
+      <c r="U291">
+        <v>4</v>
+      </c>
+      <c r="V291">
+        <v>1.2</v>
+      </c>
+      <c r="W291">
+        <v>1.03</v>
+      </c>
+      <c r="X291">
+        <v>1.08</v>
+      </c>
+      <c r="Y291">
+        <v>1.56</v>
+      </c>
+      <c r="Z291">
+        <v>2.25</v>
+      </c>
+      <c r="AA291">
         <v>2.7</v>
       </c>
-      <c r="O291">
-        <v>2.62</v>
-      </c>
-      <c r="P291">
-        <v>2.75</v>
-      </c>
-      <c r="Q291">
-        <v>3.5</v>
-      </c>
-      <c r="R291">
-        <v>1.75</v>
-      </c>
-      <c r="S291">
-        <v>1.73</v>
-      </c>
-      <c r="T291">
-        <v>1.99</v>
-      </c>
-      <c r="U291">
-        <v>4.5</v>
-      </c>
-      <c r="V291">
-        <v>1.17</v>
-      </c>
-      <c r="W291">
-        <v>1.02</v>
-      </c>
-      <c r="X291">
-        <v>1.18</v>
-      </c>
-      <c r="Y291">
-        <v>1.72</v>
-      </c>
-      <c r="Z291">
-        <v>2</v>
-      </c>
-      <c r="AA291">
-        <v>3.2</v>
-      </c>
       <c r="AB291">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC291">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AD291">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AE291">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF291">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG291">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AK291">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -49698,10 +49698,10 @@
         </is>
       </c>
       <c r="N303">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="O303">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="P303">
         <v>2.02</v>
@@ -51820,58 +51820,58 @@
         <v>1.61</v>
       </c>
       <c r="O316">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P316">
         <v>5.25</v>
       </c>
       <c r="Q316">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="R316">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S316">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="T316">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="U316">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V316">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W316">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X316">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y316">
         <v>1.4</v>
       </c>
       <c r="Z316">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AA316">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB316">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC316">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="AD316">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE316">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF316">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG316">
         <v>1.62</v>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK316">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -52469,13 +52469,13 @@
         </is>
       </c>
       <c r="N320">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O320">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P320">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q320">
         <v>0</v>
@@ -52508,10 +52508,10 @@
         <v>0</v>
       </c>
       <c r="AA320">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB320">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC320">
         <v>0</v>
@@ -52632,13 +52632,13 @@
         </is>
       </c>
       <c r="N321">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O321">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P321">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q321">
         <v>0</v>
@@ -52958,7 +52958,7 @@
         </is>
       </c>
       <c r="N323">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O323">
         <v>4.2</v>
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q324">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R324">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S324">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T324">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U324">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V324">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W324">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X324">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y324">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z324">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA324">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB324">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC324">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD324">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE324">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF324">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG324">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK324">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AL324">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
         <v>2.6</v>
@@ -810,34 +810,34 @@
         <v>3</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S3">
         <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
         <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA3">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AB3">
         <v>1.66</v>
@@ -849,13 +849,13 @@
         <v>1.24</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK3">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
         <v>2</v>
@@ -4076,7 +4076,7 @@
         <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="U23">
         <v>2.73</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O289">
+        <v>2.62</v>
+      </c>
+      <c r="P289">
         <v>2.75</v>
       </c>
-      <c r="P289">
+      <c r="Q289">
+        <v>3.5</v>
+      </c>
+      <c r="R289">
+        <v>1.75</v>
+      </c>
+      <c r="S289">
+        <v>1.73</v>
+      </c>
+      <c r="T289">
+        <v>1.99</v>
+      </c>
+      <c r="U289">
+        <v>4.5</v>
+      </c>
+      <c r="V289">
+        <v>1.17</v>
+      </c>
+      <c r="W289">
+        <v>1.02</v>
+      </c>
+      <c r="X289">
+        <v>1.18</v>
+      </c>
+      <c r="Y289">
+        <v>1.72</v>
+      </c>
+      <c r="Z289">
+        <v>2</v>
+      </c>
+      <c r="AA289">
         <v>3.2</v>
       </c>
-      <c r="Q289">
-        <v>2.9</v>
-      </c>
-      <c r="R289">
-        <v>1.85</v>
-      </c>
-      <c r="S289">
-        <v>1.57</v>
-      </c>
-      <c r="T289">
-        <v>2.3</v>
-      </c>
-      <c r="U289">
-        <v>4</v>
-      </c>
-      <c r="V289">
-        <v>1.2</v>
-      </c>
-      <c r="W289">
-        <v>1.03</v>
-      </c>
-      <c r="X289">
-        <v>1.08</v>
-      </c>
-      <c r="Y289">
-        <v>1.56</v>
-      </c>
-      <c r="Z289">
-        <v>2.25</v>
-      </c>
-      <c r="AA289">
-        <v>2.7</v>
-      </c>
       <c r="AB289">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AC289">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AD289">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AE289">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF289">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AG289">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AK289">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
+        <v>2.3</v>
+      </c>
+      <c r="O290">
+        <v>2.75</v>
+      </c>
+      <c r="P290">
+        <v>3.2</v>
+      </c>
+      <c r="Q290">
+        <v>2.9</v>
+      </c>
+      <c r="R290">
+        <v>1.85</v>
+      </c>
+      <c r="S290">
+        <v>1.57</v>
+      </c>
+      <c r="T290">
+        <v>2.3</v>
+      </c>
+      <c r="U290">
+        <v>4</v>
+      </c>
+      <c r="V290">
+        <v>1.2</v>
+      </c>
+      <c r="W290">
+        <v>1.03</v>
+      </c>
+      <c r="X290">
+        <v>1.08</v>
+      </c>
+      <c r="Y290">
+        <v>1.56</v>
+      </c>
+      <c r="Z290">
+        <v>2.25</v>
+      </c>
+      <c r="AA290">
         <v>2.7</v>
       </c>
-      <c r="O290">
-        <v>2.62</v>
-      </c>
-      <c r="P290">
-        <v>2.75</v>
-      </c>
-      <c r="Q290">
-        <v>3.5</v>
-      </c>
-      <c r="R290">
-        <v>1.75</v>
-      </c>
-      <c r="S290">
-        <v>1.73</v>
-      </c>
-      <c r="T290">
-        <v>1.99</v>
-      </c>
-      <c r="U290">
-        <v>4.5</v>
-      </c>
-      <c r="V290">
-        <v>1.17</v>
-      </c>
-      <c r="W290">
-        <v>1.02</v>
-      </c>
-      <c r="X290">
-        <v>1.18</v>
-      </c>
-      <c r="Y290">
-        <v>1.72</v>
-      </c>
-      <c r="Z290">
-        <v>2</v>
-      </c>
-      <c r="AA290">
-        <v>3.2</v>
-      </c>
       <c r="AB290">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC290">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AD290">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AE290">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF290">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG290">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AK290">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL290">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="O195">
-        <v>3.34</v>
+        <v>3.06</v>
       </c>
       <c r="P195">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P263">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43380,10 +43380,10 @@
         <v>0</v>
       </c>
       <c r="AA264">
+        <v>2</v>
+      </c>
+      <c r="AB264">
         <v>1.8</v>
-      </c>
-      <c r="AB264">
-        <v>2</v>
       </c>
       <c r="AC264">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
+        <v>2.3</v>
+      </c>
+      <c r="O289">
+        <v>2.75</v>
+      </c>
+      <c r="P289">
+        <v>3.2</v>
+      </c>
+      <c r="Q289">
+        <v>2.9</v>
+      </c>
+      <c r="R289">
+        <v>1.85</v>
+      </c>
+      <c r="S289">
+        <v>1.57</v>
+      </c>
+      <c r="T289">
+        <v>2.3</v>
+      </c>
+      <c r="U289">
+        <v>4</v>
+      </c>
+      <c r="V289">
+        <v>1.2</v>
+      </c>
+      <c r="W289">
+        <v>1.03</v>
+      </c>
+      <c r="X289">
+        <v>1.08</v>
+      </c>
+      <c r="Y289">
+        <v>1.56</v>
+      </c>
+      <c r="Z289">
+        <v>2.25</v>
+      </c>
+      <c r="AA289">
         <v>2.7</v>
       </c>
-      <c r="O289">
-        <v>2.62</v>
-      </c>
-      <c r="P289">
-        <v>2.75</v>
-      </c>
-      <c r="Q289">
-        <v>3.5</v>
-      </c>
-      <c r="R289">
-        <v>1.75</v>
-      </c>
-      <c r="S289">
-        <v>1.73</v>
-      </c>
-      <c r="T289">
-        <v>1.99</v>
-      </c>
-      <c r="U289">
-        <v>4.5</v>
-      </c>
-      <c r="V289">
-        <v>1.17</v>
-      </c>
-      <c r="W289">
-        <v>1.02</v>
-      </c>
-      <c r="X289">
-        <v>1.18</v>
-      </c>
-      <c r="Y289">
-        <v>1.72</v>
-      </c>
-      <c r="Z289">
-        <v>2</v>
-      </c>
-      <c r="AA289">
-        <v>3.2</v>
-      </c>
       <c r="AB289">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC289">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AD289">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AE289">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF289">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG289">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AK289">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="O290">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="P290">
-        <v>3.2</v>
+        <v>4.85</v>
       </c>
       <c r="Q290">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="R290">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="S290">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T290">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U290">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V290">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W290">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X290">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y290">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Z290">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA290">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AB290">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AC290">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AD290">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AE290">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF290">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AG290">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AK290">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,65 +47742,65 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.63</v>
+        <v>2.7</v>
       </c>
       <c r="O291">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="P291">
-        <v>4.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q291">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="R291">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="S291">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="T291">
+        <v>1.99</v>
+      </c>
+      <c r="U291">
+        <v>4.5</v>
+      </c>
+      <c r="V291">
+        <v>1.17</v>
+      </c>
+      <c r="W291">
+        <v>1.02</v>
+      </c>
+      <c r="X291">
+        <v>1.18</v>
+      </c>
+      <c r="Y291">
+        <v>1.72</v>
+      </c>
+      <c r="Z291">
+        <v>2</v>
+      </c>
+      <c r="AA291">
+        <v>3.2</v>
+      </c>
+      <c r="AB291">
+        <v>1.26</v>
+      </c>
+      <c r="AC291">
+        <v>7.5</v>
+      </c>
+      <c r="AD291">
+        <v>1.04</v>
+      </c>
+      <c r="AE291">
+        <v>1.02</v>
+      </c>
+      <c r="AF291">
         <v>2.4</v>
       </c>
-      <c r="U291">
-        <v>3.75</v>
-      </c>
-      <c r="V291">
-        <v>1.22</v>
-      </c>
-      <c r="W291">
-        <v>1.04</v>
-      </c>
-      <c r="X291">
-        <v>1.1</v>
-      </c>
-      <c r="Y291">
+      <c r="AG291">
         <v>1.5</v>
       </c>
-      <c r="Z291">
-        <v>2.45</v>
-      </c>
-      <c r="AA291">
-        <v>2.49</v>
-      </c>
-      <c r="AB291">
-        <v>1.44</v>
-      </c>
-      <c r="AC291">
-        <v>5.1</v>
-      </c>
-      <c r="AD291">
-        <v>1.14</v>
-      </c>
-      <c r="AE291">
-        <v>1.04</v>
-      </c>
-      <c r="AF291">
-        <v>2.18</v>
-      </c>
-      <c r="AG291">
-        <v>1.46</v>
-      </c>
       <c r="AH291" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AK291">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="O300">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P300">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="Q300">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R300">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S300">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="T300">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U300">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="V300">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W300">
+        <v>1.02</v>
+      </c>
+      <c r="X300">
+        <v>1.03</v>
+      </c>
+      <c r="Y300">
+        <v>1.4</v>
+      </c>
+      <c r="Z300">
+        <v>2.72</v>
+      </c>
+      <c r="AA300">
+        <v>2.21</v>
+      </c>
+      <c r="AB300">
+        <v>1.53</v>
+      </c>
+      <c r="AC300">
+        <v>4.2</v>
+      </c>
+      <c r="AD300">
+        <v>1.18</v>
+      </c>
+      <c r="AE300">
         <v>1.01</v>
       </c>
-      <c r="X300">
-        <v>1.07</v>
-      </c>
-      <c r="Y300">
-        <v>1.53</v>
-      </c>
-      <c r="Z300">
-        <v>2.52</v>
-      </c>
-      <c r="AA300">
-        <v>2.43</v>
-      </c>
-      <c r="AB300">
-        <v>1.48</v>
-      </c>
-      <c r="AC300">
-        <v>5.01</v>
-      </c>
-      <c r="AD300">
-        <v>1.12</v>
-      </c>
-      <c r="AE300">
-        <v>1.04</v>
-      </c>
       <c r="AF300">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG300">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK300">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="O301">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P301">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Q301">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R301">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S301">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="T301">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U301">
-        <v>3.08</v>
+        <v>3.48</v>
       </c>
       <c r="V301">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W301">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X301">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y301">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z301">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="AA301">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="AB301">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC301">
-        <v>4.2</v>
+        <v>5.01</v>
       </c>
       <c r="AD301">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE301">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF301">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG301">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK301">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -52508,10 +52508,10 @@
         <v>0</v>
       </c>
       <c r="AA320">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB320">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC320">
         <v>0</v>
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O324">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="P324">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q324">
         <v>1.62</v>
@@ -53136,19 +53136,19 @@
         <v>2.8</v>
       </c>
       <c r="S324">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T324">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U324">
         <v>2.11</v>
       </c>
       <c r="V324">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="W324">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X324">
         <v>1.01</v>
@@ -53166,7 +53166,7 @@
         <v>3</v>
       </c>
       <c r="AC324">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AD324">
         <v>1.7</v>
@@ -53178,7 +53178,7 @@
         <v>1.76</v>
       </c>
       <c r="AG324">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK324">
         <v>3.78</v>
@@ -54108,10 +54108,10 @@
         <v>2.37</v>
       </c>
       <c r="Q330">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="R330">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S330">
         <v>1.22</v>
@@ -54141,10 +54141,10 @@
         <v>1.44</v>
       </c>
       <c r="AB330">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AC330">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD330">
         <v>1.68</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -804,46 +804,46 @@
         <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q3">
         <v>3</v>
       </c>
       <c r="R3">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T3">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
         <v>3</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AA3">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AB3">
         <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="AD3">
         <v>1.24</v>
@@ -852,10 +852,10 @@
         <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AK3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
         <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
         <v>1.44</v>
@@ -985,40 +985,40 @@
         <v>3.08</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
         <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA4">
         <v>2.12</v>
       </c>
       <c r="AB4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>3.74</v>
+        <v>3.91</v>
       </c>
       <c r="AD4">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
         <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
         <v>3.1</v>
       </c>
       <c r="P5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q5">
-        <v>4.37</v>
+        <v>3.95</v>
       </c>
       <c r="R5">
         <v>2.15</v>
@@ -1142,16 +1142,16 @@
         <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="U5">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.06</v>
@@ -1160,13 +1160,13 @@
         <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="AA5">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB5">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AC5">
         <v>3.14</v>
@@ -1178,7 +1178,7 @@
         <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG5">
         <v>2</v>
@@ -1197,7 +1197,7 @@
         <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q23">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="R23">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="S23">
         <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="U23">
         <v>2.73</v>
@@ -4085,7 +4085,7 @@
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1</v>
@@ -4097,10 +4097,10 @@
         <v>3.24</v>
       </c>
       <c r="AA23">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB23">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC23">
         <v>3.24</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
+        <v>1.73</v>
+      </c>
+      <c r="AK23">
         <v>1.28</v>
-      </c>
-      <c r="AK23">
-        <v>1.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,61 +4221,61 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="P24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q24">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="V24">
         <v>1.55</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
         <v>4.6</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB24">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AC24">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AD24">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG24">
         <v>2.15</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4396,46 +4396,46 @@
         <v>2.1</v>
       </c>
       <c r="R25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
         <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U25">
-        <v>2.47</v>
+        <v>2.68</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="AA25">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC25">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
         <v>1.73</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
         <v>2.15</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O58">
         <v>3.75</v>
@@ -9778,16 +9778,16 @@
         <v>2.25</v>
       </c>
       <c r="S58">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T58">
         <v>3.12</v>
       </c>
       <c r="U58">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V58">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W58">
         <v>1.11</v>
@@ -9805,22 +9805,22 @@
         <v>1.62</v>
       </c>
       <c r="AB58">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC58">
         <v>2.5</v>
       </c>
       <c r="AD58">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE58">
         <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>2.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
         <v>1.09</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q61">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="R61">
         <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U61">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="V61">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB61">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="AC61">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AD61">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AE61">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF61">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG61">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK61">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="R62">
         <v>2.5</v>
       </c>
       <c r="S62">
+        <v>1.21</v>
+      </c>
+      <c r="T62">
+        <v>3.75</v>
+      </c>
+      <c r="U62">
+        <v>2.01</v>
+      </c>
+      <c r="V62">
+        <v>1.75</v>
+      </c>
+      <c r="W62">
+        <v>1.18</v>
+      </c>
+      <c r="X62">
+        <v>1.01</v>
+      </c>
+      <c r="Y62">
+        <v>1.08</v>
+      </c>
+      <c r="Z62">
+        <v>5.75</v>
+      </c>
+      <c r="AA62">
+        <v>1.4</v>
+      </c>
+      <c r="AB62">
+        <v>3.08</v>
+      </c>
+      <c r="AC62">
+        <v>1.95</v>
+      </c>
+      <c r="AD62">
+        <v>1.82</v>
+      </c>
+      <c r="AE62">
+        <v>1.25</v>
+      </c>
+      <c r="AF62">
+        <v>1.4</v>
+      </c>
+      <c r="AG62">
+        <v>2.7</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.2</v>
       </c>
-      <c r="T62">
-        <v>3.8</v>
-      </c>
-      <c r="U62">
-        <v>2.18</v>
-      </c>
-      <c r="V62">
-        <v>1.64</v>
-      </c>
-      <c r="W62">
-        <v>1.17</v>
-      </c>
-      <c r="X62">
-        <v>1.02</v>
-      </c>
-      <c r="Y62">
-        <v>1.15</v>
-      </c>
-      <c r="Z62">
-        <v>5</v>
-      </c>
-      <c r="AA62">
-        <v>1.47</v>
-      </c>
-      <c r="AB62">
-        <v>2.44</v>
-      </c>
-      <c r="AC62">
-        <v>2.21</v>
-      </c>
-      <c r="AD62">
-        <v>1.6</v>
-      </c>
-      <c r="AE62">
-        <v>1.27</v>
-      </c>
-      <c r="AF62">
-        <v>1.43</v>
-      </c>
-      <c r="AG62">
-        <v>2.63</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.29</v>
-      </c>
       <c r="AK62">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -12860,31 +12860,31 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="O77">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="P77">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q77">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R77">
         <v>2.9</v>
       </c>
       <c r="S77">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T77">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U77">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="V77">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="W77">
         <v>1.2</v>
@@ -12893,19 +12893,19 @@
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z77">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA77">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB77">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC77">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD77">
         <v>1.85</v>
@@ -12914,7 +12914,7 @@
         <v>1.36</v>
       </c>
       <c r="AF77">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG77">
         <v>1.95</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK77">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,31 +13023,31 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O78">
         <v>3.6</v>
       </c>
       <c r="P78">
-        <v>3.75</v>
+        <v>4.13</v>
       </c>
       <c r="Q78">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S78">
         <v>1.33</v>
       </c>
       <c r="T78">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U78">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="V78">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W78">
         <v>1.07</v>
@@ -13059,13 +13059,13 @@
         <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA78">
         <v>1.77</v>
       </c>
       <c r="AB78">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC78">
         <v>3.1</v>
@@ -13077,10 +13077,10 @@
         <v>1.08</v>
       </c>
       <c r="AF78">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG78">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK78">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -14499,22 +14499,22 @@
         <v>10</v>
       </c>
       <c r="Q87">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R87">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="S87">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T87">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="U87">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V87">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="W87">
         <v>1.22</v>
@@ -14523,22 +14523,22 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z87">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AA87">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AB87">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AC87">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD87">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE87">
         <v>1.37</v>
@@ -14547,7 +14547,7 @@
         <v>1.67</v>
       </c>
       <c r="AG87">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O96">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P96">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q96">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R96">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S96">
         <v>1.53</v>
       </c>
       <c r="T96">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="U96">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V96">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W96">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X96">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y96">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z96">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AA96">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AB96">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD96">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE96">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG96">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.4</v>
       </c>
       <c r="AK96">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q97">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R97">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S97">
         <v>1.53</v>
       </c>
       <c r="T97">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="U97">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V97">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W97">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X97">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y97">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z97">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA97">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB97">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD97">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE97">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF97">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG97">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.4</v>
       </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="Q101">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="R101">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S101">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T101">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="U101">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="V101">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="AA101">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AB101">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AC101">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="AD101">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE101">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG101">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.25</v>
+        <v>2.23</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="R102">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S102">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T102">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="U102">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="V102">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W102">
+        <v>1.05</v>
+      </c>
+      <c r="X102">
+        <v>1.06</v>
+      </c>
+      <c r="Y102">
+        <v>1.33</v>
+      </c>
+      <c r="Z102">
+        <v>3.2</v>
+      </c>
+      <c r="AA102">
+        <v>2</v>
+      </c>
+      <c r="AB102">
+        <v>1.77</v>
+      </c>
+      <c r="AC102">
+        <v>3.45</v>
+      </c>
+      <c r="AD102">
+        <v>1.25</v>
+      </c>
+      <c r="AE102">
         <v>1.08</v>
       </c>
-      <c r="X102">
-        <v>1.04</v>
-      </c>
-      <c r="Y102">
-        <v>1.2</v>
-      </c>
-      <c r="Z102">
-        <v>3.98</v>
-      </c>
-      <c r="AA102">
-        <v>1.69</v>
-      </c>
-      <c r="AB102">
-        <v>2.01</v>
-      </c>
-      <c r="AC102">
-        <v>2.8</v>
-      </c>
-      <c r="AD102">
-        <v>1.4</v>
-      </c>
-      <c r="AE102">
-        <v>1.14</v>
-      </c>
       <c r="AF102">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG102">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK102">
-        <v>2.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q103">
         <v>2.12</v>
@@ -22480,22 +22480,22 @@
         <v>2.6</v>
       </c>
       <c r="O136">
+        <v>3.25</v>
+      </c>
+      <c r="P136">
+        <v>2.45</v>
+      </c>
+      <c r="Q136">
         <v>3.2</v>
-      </c>
-      <c r="P136">
-        <v>2.4</v>
-      </c>
-      <c r="Q136">
-        <v>3</v>
       </c>
       <c r="R136">
         <v>2.1</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T136">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U136">
         <v>2.5</v>
@@ -22531,10 +22531,10 @@
         <v>1.1</v>
       </c>
       <c r="AF136">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG136">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
         <v>1.44</v>
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q145">
         <v>1.96</v>
       </c>
       <c r="R145">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="S145">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T145">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="U145">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="V145">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="W145">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X145">
         <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z145">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AA145">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB145">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="AC145">
         <v>1.73</v>
       </c>
       <c r="AD145">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AE145">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF145">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG145">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24116,55 +24116,55 @@
         <v>0</v>
       </c>
       <c r="Q146">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="R146">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="S146">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T146">
         <v>4.8</v>
       </c>
       <c r="U146">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V146">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="W146">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X146">
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z146">
         <v>7.7</v>
       </c>
       <c r="AA146">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AB146">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AC146">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AD146">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AE146">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AF146">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG146">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK146">
         <v>2.1</v>
@@ -24279,55 +24279,55 @@
         <v>0</v>
       </c>
       <c r="Q147">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="R147">
         <v>2.63</v>
       </c>
       <c r="S147">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T147">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U147">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="V147">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W147">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X147">
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z147">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA147">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB147">
         <v>3.05</v>
       </c>
       <c r="AC147">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD147">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AE147">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AF147">
         <v>1.32</v>
       </c>
       <c r="AG147">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK147">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24442,10 +24442,10 @@
         <v>0</v>
       </c>
       <c r="Q148">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R148">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="S148">
         <v>1.08</v>
@@ -24454,13 +24454,13 @@
         <v>7</v>
       </c>
       <c r="U148">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V148">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="W148">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X148">
         <v>0</v>
@@ -24472,25 +24472,25 @@
         <v>13</v>
       </c>
       <c r="AA148">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AB148">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AC148">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AD148">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AE148">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF148">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AG148">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK148">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -27696,31 +27696,31 @@
         <v>1.36</v>
       </c>
       <c r="O168">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P168">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="Q168">
         <v>1.73</v>
       </c>
       <c r="R168">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S168">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T168">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="U168">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V168">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W168">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X168">
         <v>1.02</v>
@@ -27729,25 +27729,25 @@
         <v>1.13</v>
       </c>
       <c r="Z168">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA168">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB168">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AC168">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AD168">
+        <v>1.69</v>
+      </c>
+      <c r="AE168">
+        <v>1.25</v>
+      </c>
+      <c r="AF168">
         <v>1.65</v>
-      </c>
-      <c r="AE168">
-        <v>1.29</v>
-      </c>
-      <c r="AF168">
-        <v>1.64</v>
       </c>
       <c r="AG168">
         <v>2.15</v>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK168">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O181">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q181">
         <v>2.9</v>
@@ -29839,7 +29839,7 @@
         <v>1.52</v>
       </c>
       <c r="W181">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X181">
         <v>0</v>
@@ -29978,28 +29978,28 @@
         <v>2.2</v>
       </c>
       <c r="O182">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="P182">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q182">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="R182">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S182">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T182">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="U182">
         <v>2.25</v>
       </c>
       <c r="V182">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W182">
         <v>1.13</v>
@@ -30014,22 +30014,22 @@
         <v>4.5</v>
       </c>
       <c r="AA182">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB182">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AC182">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="AD182">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE182">
         <v>1.22</v>
       </c>
       <c r="AF182">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG182">
         <v>2.5</v>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK182">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30141,61 +30141,61 @@
         <v>3.1</v>
       </c>
       <c r="O183">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P183">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q183">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="R183">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S183">
         <v>1.25</v>
       </c>
       <c r="T183">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="U183">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="V183">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W183">
         <v>1.11</v>
       </c>
       <c r="X183">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y183">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z183">
-        <v>4.8</v>
+        <v>4.99</v>
       </c>
       <c r="AA183">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB183">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AC183">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AD183">
         <v>1.57</v>
       </c>
       <c r="AE183">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF183">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG183">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK183">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30301,16 +30301,16 @@
         </is>
       </c>
       <c r="N184">
-        <v>3.97</v>
+        <v>4.2</v>
       </c>
       <c r="O184">
         <v>4.25</v>
       </c>
       <c r="P184">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="Q184">
-        <v>4</v>
+        <v>4.58</v>
       </c>
       <c r="R184">
         <v>2.5</v>
@@ -30322,13 +30322,13 @@
         <v>3.66</v>
       </c>
       <c r="U184">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="V184">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W184">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X184">
         <v>1.02</v>
@@ -30340,25 +30340,25 @@
         <v>5.2</v>
       </c>
       <c r="AA184">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB184">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AC184">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AD184">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AE184">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF184">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG184">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK184">
         <v>1.22</v>
@@ -30506,7 +30506,7 @@
         <v>2.3</v>
       </c>
       <c r="AB185">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC185">
         <v>4.25</v>
@@ -30515,7 +30515,7 @@
         <v>1.18</v>
       </c>
       <c r="AE185">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF185">
         <v>1.97</v>
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="O209">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P209">
+        <v>3.45</v>
+      </c>
+      <c r="Q209">
+        <v>2.8</v>
+      </c>
+      <c r="R209">
+        <v>1.97</v>
+      </c>
+      <c r="S209">
+        <v>1.54</v>
+      </c>
+      <c r="T209">
+        <v>2.5</v>
+      </c>
+      <c r="U209">
         <v>3.5</v>
       </c>
-      <c r="Q209">
-        <v>2.71</v>
-      </c>
-      <c r="R209">
-        <v>1.92</v>
-      </c>
-      <c r="S209">
-        <v>1.5</v>
-      </c>
-      <c r="T209">
-        <v>2.33</v>
-      </c>
-      <c r="U209">
-        <v>3.32</v>
-      </c>
       <c r="V209">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W209">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X209">
         <v>1.05</v>
       </c>
       <c r="Y209">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z209">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AA209">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="AB209">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC209">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD209">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE209">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF209">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG209">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK209">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34542,61 +34542,61 @@
         <v>2</v>
       </c>
       <c r="O210">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P210">
         <v>3.1</v>
       </c>
       <c r="Q210">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R210">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S210">
         <v>1.32</v>
       </c>
       <c r="T210">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U210">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V210">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W210">
         <v>1.1</v>
       </c>
       <c r="X210">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y210">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z210">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AA210">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB210">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC210">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AD210">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE210">
         <v>1.13</v>
       </c>
       <c r="AF210">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG210">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK210">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35843,16 +35843,16 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O218">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P218">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q218">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="R218">
         <v>2.03</v>
@@ -35861,7 +35861,7 @@
         <v>1.36</v>
       </c>
       <c r="T218">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U218">
         <v>2.75</v>
@@ -35870,7 +35870,7 @@
         <v>1.36</v>
       </c>
       <c r="W218">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X218">
         <v>1.02</v>
@@ -35885,13 +35885,13 @@
         <v>1.91</v>
       </c>
       <c r="AB218">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AC218">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD218">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE218">
         <v>1.05</v>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AK218">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36996,52 +36996,52 @@
         <v>7.93</v>
       </c>
       <c r="R225">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S225">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T225">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="U225">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="V225">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W225">
         <v>1.08</v>
       </c>
       <c r="X225">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y225">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z225">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AA225">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB225">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AC225">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD225">
         <v>1.3</v>
       </c>
       <c r="AE225">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF225">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG225">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK225">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -42701,22 +42701,22 @@
         <v>3.25</v>
       </c>
       <c r="R260">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="S260">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T260">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U260">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V260">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W260">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X260">
         <v>1.05</v>
@@ -42725,7 +42725,7 @@
         <v>1.36</v>
       </c>
       <c r="Z260">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AA260">
         <v>2.17</v>
@@ -42740,7 +42740,7 @@
         <v>1.22</v>
       </c>
       <c r="AE260">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF260">
         <v>1.91</v>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK260">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42858,19 +42858,19 @@
         <v>8.9</v>
       </c>
       <c r="P261">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q261">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="R261">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S261">
         <v>1.22</v>
       </c>
       <c r="T261">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U261">
         <v>2</v>
@@ -42879,7 +42879,7 @@
         <v>1.6</v>
       </c>
       <c r="W261">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X261">
         <v>1.01</v>
@@ -42903,13 +42903,13 @@
         <v>1.65</v>
       </c>
       <c r="AE261">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF261">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AG261">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -43839,22 +43839,22 @@
         <v>0</v>
       </c>
       <c r="Q267">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="R267">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S267">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T267">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="U267">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="V267">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W267">
         <v>1.1</v>
@@ -43869,25 +43869,25 @@
         <v>4.2</v>
       </c>
       <c r="AA267">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AB267">
         <v>2.2</v>
       </c>
       <c r="AC267">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="AD267">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE267">
         <v>1.12</v>
       </c>
       <c r="AF267">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG267">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK267">
         <v>1.53</v>
@@ -44482,19 +44482,19 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S271">
         <v>0</v>
@@ -44503,10 +44503,10 @@
         <v>0</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W271">
         <v>0</v>
@@ -44521,25 +44521,25 @@
         <v>0</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE271">
         <v>0</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -45460,28 +45460,28 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q277">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="R277">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="S277">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T277">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U277">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V277">
         <v>1.33</v>
@@ -45496,29 +45496,29 @@
         <v>1.3</v>
       </c>
       <c r="Z277">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA277">
         <v>2.02</v>
       </c>
       <c r="AB277">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC277">
         <v>3.42</v>
       </c>
       <c r="AD277">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE277">
         <v>1.05</v>
       </c>
       <c r="AF277">
+        <v>1.85</v>
+      </c>
+      <c r="AG277">
         <v>1.84</v>
       </c>
-      <c r="AG277">
-        <v>1.85</v>
-      </c>
       <c r="AH277" t="inlineStr">
         <is>
           <t>[]</t>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK277">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
+        <v>3.35</v>
+      </c>
+      <c r="O280">
         <v>3.6</v>
       </c>
-      <c r="O280">
-        <v>3.5</v>
-      </c>
       <c r="P280">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q280">
         <v>3.8</v>
@@ -45970,10 +45970,10 @@
         <v>3.2</v>
       </c>
       <c r="U280">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V280">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W280">
         <v>1.11</v>
@@ -45985,25 +45985,25 @@
         <v>1.22</v>
       </c>
       <c r="Z280">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA280">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB280">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC280">
         <v>2.7</v>
       </c>
       <c r="AD280">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE280">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF280">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG280">
         <v>2.18</v>
@@ -46019,7 +46019,7 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK280">
         <v>1.22</v>
@@ -46118,7 +46118,7 @@
         <v>2.8</v>
       </c>
       <c r="P281">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O282">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P282">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q282">
         <v>3.1</v>
@@ -46320,7 +46320,7 @@
         <v>1.7</v>
       </c>
       <c r="AC282">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AD282">
         <v>1.22</v>
@@ -46453,16 +46453,16 @@
         <v>2.44</v>
       </c>
       <c r="S283">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T283">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="U283">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V283">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W283">
         <v>1.11</v>
@@ -46471,10 +46471,10 @@
         <v>1</v>
       </c>
       <c r="Y283">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z283">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AA283">
         <v>1.72</v>
@@ -46486,16 +46486,16 @@
         <v>2.76</v>
       </c>
       <c r="AD283">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE283">
         <v>1.1</v>
       </c>
       <c r="AF283">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG283">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O284">
         <v>3.3</v>
       </c>
       <c r="P284">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q284">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="R284">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S284">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T284">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="U284">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V284">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W284">
         <v>1.03</v>
       </c>
       <c r="X284">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y284">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z284">
         <v>2.75</v>
       </c>
       <c r="AA284">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AB284">
         <v>1.6</v>
       </c>
       <c r="AC284">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="AD284">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE284">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF284">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG284">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK284">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -47422,7 +47422,7 @@
         <v>2.62</v>
       </c>
       <c r="P289">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q289">
         <v>3.5</v>
@@ -47431,31 +47431,31 @@
         <v>1.75</v>
       </c>
       <c r="S289">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="T289">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U289">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="V289">
         <v>1.17</v>
       </c>
       <c r="W289">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X289">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Y289">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Z289">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AA289">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="AB289">
         <v>1.26</v>
@@ -47486,7 +47486,7 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AK289">
         <v>1.36</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,80 +47579,80 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="O290">
+        <v>2.75</v>
+      </c>
+      <c r="P290">
         <v>3.35</v>
       </c>
-      <c r="P290">
-        <v>4.85</v>
-      </c>
       <c r="Q290">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="R290">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="S290">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T290">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U290">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="V290">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W290">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X290">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y290">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Z290">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AA290">
-        <v>2.49</v>
+        <v>3.01</v>
       </c>
       <c r="AB290">
+        <v>1.38</v>
+      </c>
+      <c r="AC290">
+        <v>6.23</v>
+      </c>
+      <c r="AD290">
+        <v>1.07</v>
+      </c>
+      <c r="AE290">
+        <v>1.03</v>
+      </c>
+      <c r="AF290">
+        <v>2.2</v>
+      </c>
+      <c r="AG290">
+        <v>1.62</v>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ290">
         <v>1.44</v>
       </c>
-      <c r="AC290">
-        <v>5.1</v>
-      </c>
-      <c r="AD290">
-        <v>1.14</v>
-      </c>
-      <c r="AE290">
-        <v>1.04</v>
-      </c>
-      <c r="AF290">
-        <v>2.18</v>
-      </c>
-      <c r="AG290">
-        <v>1.46</v>
-      </c>
-      <c r="AH290" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI290" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ290">
-        <v>1.11</v>
-      </c>
       <c r="AK290">
-        <v>2.08</v>
+        <v>1.4</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="O291">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="P291">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="Q291">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="R291">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S291">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T291">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="U291">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V291">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W291">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X291">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y291">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Z291">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA291">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AB291">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AC291">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AD291">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AE291">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF291">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AG291">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AK291">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47905,19 +47905,19 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="O292">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="P292">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="Q292">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R292">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S292">
         <v>1.33</v>
@@ -47929,37 +47929,37 @@
         <v>2.45</v>
       </c>
       <c r="V292">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W292">
         <v>1.07</v>
       </c>
       <c r="X292">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z292">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA292">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB292">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC292">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AD292">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE292">
         <v>1.11</v>
       </c>
       <c r="AF292">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG292">
         <v>1.6</v>
@@ -48557,19 +48557,19 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O296">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P296">
-        <v>4.68</v>
+        <v>4.4</v>
       </c>
       <c r="Q296">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="R296">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S296">
         <v>1.38</v>
@@ -48578,43 +48578,43 @@
         <v>2.73</v>
       </c>
       <c r="U296">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="V296">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W296">
         <v>1.06</v>
       </c>
       <c r="X296">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y296">
         <v>1.29</v>
       </c>
       <c r="Z296">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA296">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB296">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC296">
         <v>3.28</v>
       </c>
       <c r="AD296">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE296">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF296">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG296">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O299">
         <v>2.8</v>
       </c>
       <c r="P299">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,80 +49209,80 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="O300">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P300">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="Q300">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="R300">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S300">
+        <v>1.64</v>
+      </c>
+      <c r="T300">
+        <v>2.2</v>
+      </c>
+      <c r="U300">
+        <v>3.9</v>
+      </c>
+      <c r="V300">
+        <v>1.18</v>
+      </c>
+      <c r="W300">
+        <v>1.03</v>
+      </c>
+      <c r="X300">
+        <v>1.1</v>
+      </c>
+      <c r="Y300">
+        <v>1.62</v>
+      </c>
+      <c r="Z300">
+        <v>2.16</v>
+      </c>
+      <c r="AA300">
+        <v>3.1</v>
+      </c>
+      <c r="AB300">
+        <v>1.34</v>
+      </c>
+      <c r="AC300">
+        <v>5.55</v>
+      </c>
+      <c r="AD300">
+        <v>1.08</v>
+      </c>
+      <c r="AE300">
+        <v>1.03</v>
+      </c>
+      <c r="AF300">
+        <v>2.23</v>
+      </c>
+      <c r="AG300">
+        <v>1.53</v>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ300">
         <v>1.44</v>
       </c>
-      <c r="T300">
-        <v>2.44</v>
-      </c>
-      <c r="U300">
-        <v>3.08</v>
-      </c>
-      <c r="V300">
-        <v>1.3</v>
-      </c>
-      <c r="W300">
-        <v>1.02</v>
-      </c>
-      <c r="X300">
-        <v>1.03</v>
-      </c>
-      <c r="Y300">
+      <c r="AK300">
         <v>1.4</v>
-      </c>
-      <c r="Z300">
-        <v>2.72</v>
-      </c>
-      <c r="AA300">
-        <v>2.21</v>
-      </c>
-      <c r="AB300">
-        <v>1.53</v>
-      </c>
-      <c r="AC300">
-        <v>4.2</v>
-      </c>
-      <c r="AD300">
-        <v>1.18</v>
-      </c>
-      <c r="AE300">
-        <v>1.01</v>
-      </c>
-      <c r="AF300">
-        <v>2.05</v>
-      </c>
-      <c r="AG300">
-        <v>1.67</v>
-      </c>
-      <c r="AH300" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI300" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ300">
-        <v>1.33</v>
-      </c>
-      <c r="AK300">
-        <v>1.91</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,61 +49372,61 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="O301">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P301">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Q301">
+        <v>2.44</v>
+      </c>
+      <c r="R301">
+        <v>2</v>
+      </c>
+      <c r="S301">
+        <v>1.4</v>
+      </c>
+      <c r="T301">
         <v>2.45</v>
       </c>
-      <c r="R301">
-        <v>1.95</v>
-      </c>
-      <c r="S301">
-        <v>1.56</v>
-      </c>
-      <c r="T301">
-        <v>2.41</v>
-      </c>
       <c r="U301">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="V301">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W301">
+        <v>1.03</v>
+      </c>
+      <c r="X301">
+        <v>1.06</v>
+      </c>
+      <c r="Y301">
+        <v>1.41</v>
+      </c>
+      <c r="Z301">
+        <v>2.76</v>
+      </c>
+      <c r="AA301">
+        <v>2.17</v>
+      </c>
+      <c r="AB301">
+        <v>1.55</v>
+      </c>
+      <c r="AC301">
+        <v>4.1</v>
+      </c>
+      <c r="AD301">
+        <v>1.2</v>
+      </c>
+      <c r="AE301">
         <v>1.01</v>
       </c>
-      <c r="X301">
-        <v>1.07</v>
-      </c>
-      <c r="Y301">
-        <v>1.53</v>
-      </c>
-      <c r="Z301">
-        <v>2.52</v>
-      </c>
-      <c r="AA301">
-        <v>2.43</v>
-      </c>
-      <c r="AB301">
-        <v>1.48</v>
-      </c>
-      <c r="AC301">
-        <v>5.01</v>
-      </c>
-      <c r="AD301">
-        <v>1.12</v>
-      </c>
-      <c r="AE301">
-        <v>1.04</v>
-      </c>
       <c r="AF301">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG301">
         <v>1.6</v>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK301">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>3.08</v>
+        <v>2.67</v>
       </c>
       <c r="O303">
-        <v>3.55</v>
+        <v>3.88</v>
       </c>
       <c r="P303">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -50519,10 +50519,10 @@
         <v>2.95</v>
       </c>
       <c r="P308">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q308">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="R308">
         <v>1.82</v>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK308">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50634,22 +50634,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P309">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q309">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R309">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T309">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U309">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V309">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W309">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X309">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y309">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z309">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA309">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB309">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC309">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD309">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF309">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG309">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK309">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50797,7 +50797,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O310">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P310">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q310">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R310">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S310">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T310">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="U310">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V310">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W310">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X310">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y310">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z310">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="AA310">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB310">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC310">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD310">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE310">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF310">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG310">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK310">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -50955,27 +50955,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,64 +51002,64 @@
         </is>
       </c>
       <c r="N311">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O311">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P311">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q311">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R311">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S311">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T311">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U311">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V311">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W311">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X311">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y311">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z311">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA311">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB311">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC311">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD311">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE311">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF311">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG311">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK311">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51106,7 +51106,7 @@
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>2026-09-13 17:00:00</t>
+          <t>2026-09-13 16:30:00</t>
         </is>
       </c>
     </row>
@@ -51165,31 +51165,31 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="O312">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P312">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Q312">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="R312">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="S312">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T312">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U312">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V312">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W312">
         <v>1.04</v>
@@ -51198,10 +51198,10 @@
         <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z312">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA312">
         <v>1.89</v>
@@ -51210,19 +51210,19 @@
         <v>1.93</v>
       </c>
       <c r="AC312">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AD312">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE312">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF312">
         <v>2.11</v>
       </c>
       <c r="AG312">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK312">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51337,19 +51337,19 @@
         <v>6</v>
       </c>
       <c r="Q313">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R313">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="S313">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T313">
         <v>3.5</v>
       </c>
       <c r="U313">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V313">
         <v>1.52</v>
@@ -51358,16 +51358,16 @@
         <v>1.12</v>
       </c>
       <c r="X313">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y313">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z313">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA313">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB313">
         <v>2.25</v>
@@ -51379,10 +51379,10 @@
         <v>1.44</v>
       </c>
       <c r="AE313">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF313">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG313">
         <v>1.88</v>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK313">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51497,19 +51497,19 @@
         <v>3.2</v>
       </c>
       <c r="P314">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q314">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="R314">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="S314">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T314">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="U314">
         <v>3.25</v>
@@ -51518,28 +51518,28 @@
         <v>1.27</v>
       </c>
       <c r="W314">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X314">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y314">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z314">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AA314">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AB314">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC314">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="AD314">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE314">
         <v>1.05</v>
@@ -51548,7 +51548,7 @@
         <v>1.94</v>
       </c>
       <c r="AG314">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK314">
         <v>1.75</v>
@@ -51654,64 +51654,64 @@
         </is>
       </c>
       <c r="N315">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O315">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P315">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q315">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R315">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S315">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T315">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U315">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V315">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W315">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X315">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y315">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z315">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA315">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB315">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC315">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD315">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE315">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF315">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG315">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK315">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51817,16 +51817,16 @@
         </is>
       </c>
       <c r="N316">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O316">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P316">
         <v>5</v>
       </c>
       <c r="Q316">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R316">
         <v>2.05</v>
@@ -51841,7 +51841,7 @@
         <v>3.3</v>
       </c>
       <c r="V316">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W316">
         <v>1.04</v>
@@ -51856,7 +51856,7 @@
         <v>2.46</v>
       </c>
       <c r="AA316">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB316">
         <v>1.54</v>
@@ -52306,64 +52306,64 @@
         </is>
       </c>
       <c r="N319">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O319">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P319">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q319">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R319">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S319">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T319">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U319">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V319">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W319">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X319">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y319">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z319">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA319">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB319">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC319">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AD319">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE319">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF319">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG319">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK319">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52475,7 +52475,7 @@
         <v>3.8</v>
       </c>
       <c r="P320">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q320">
         <v>0</v>
@@ -52632,31 +52632,31 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O321">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P321">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="Q321">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R321">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S321">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T321">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U321">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="V321">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W321">
         <v>1.03</v>
@@ -52668,13 +52668,13 @@
         <v>1.36</v>
       </c>
       <c r="Z321">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA321">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AB321">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC321">
         <v>4.15</v>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK321">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52795,19 +52795,19 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O322">
         <v>3.35</v>
       </c>
       <c r="P322">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q322">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="R322">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="S322">
         <v>1.45</v>
@@ -52825,22 +52825,22 @@
         <v>1.05</v>
       </c>
       <c r="X322">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y322">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z322">
         <v>2.63</v>
       </c>
       <c r="AA322">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AB322">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC322">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="AD322">
         <v>1.19</v>
@@ -52849,7 +52849,7 @@
         <v>1.05</v>
       </c>
       <c r="AF322">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AG322">
         <v>1.6</v>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK322">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>5.7</v>
+        <v>5.02</v>
       </c>
       <c r="O323">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P323">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -53124,7 +53124,7 @@
         <v>1.25</v>
       </c>
       <c r="O324">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="P324">
         <v>7.5</v>
@@ -53133,7 +53133,7 @@
         <v>1.62</v>
       </c>
       <c r="R324">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="S324">
         <v>1.22</v>
@@ -53142,7 +53142,7 @@
         <v>4</v>
       </c>
       <c r="U324">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="V324">
         <v>1.73</v>
@@ -53166,19 +53166,19 @@
         <v>3</v>
       </c>
       <c r="AC324">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AD324">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE324">
         <v>1.3</v>
       </c>
       <c r="AF324">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG324">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK324">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53284,64 +53284,64 @@
         </is>
       </c>
       <c r="N325">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O325">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="P325">
         <v>2.7</v>
       </c>
       <c r="Q325">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="R325">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S325">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T325">
         <v>3</v>
       </c>
       <c r="U325">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V325">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W325">
         <v>1.1</v>
       </c>
       <c r="X325">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y325">
         <v>1.24</v>
       </c>
       <c r="Z325">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="AA325">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AB325">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC325">
         <v>3.07</v>
       </c>
       <c r="AD325">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE325">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF325">
         <v>1.65</v>
       </c>
       <c r="AG325">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53453,19 +53453,19 @@
         <v>3.5</v>
       </c>
       <c r="P326">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Q326">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="R326">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S326">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T326">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U326">
         <v>3.34</v>
@@ -53477,34 +53477,34 @@
         <v>1.05</v>
       </c>
       <c r="X326">
+        <v>1.03</v>
+      </c>
+      <c r="Y326">
+        <v>1.34</v>
+      </c>
+      <c r="Z326">
+        <v>2.95</v>
+      </c>
+      <c r="AA326">
+        <v>2.22</v>
+      </c>
+      <c r="AB326">
+        <v>1.65</v>
+      </c>
+      <c r="AC326">
+        <v>3.98</v>
+      </c>
+      <c r="AD326">
+        <v>1.21</v>
+      </c>
+      <c r="AE326">
         <v>1.06</v>
-      </c>
-      <c r="Y326">
-        <v>1.36</v>
-      </c>
-      <c r="Z326">
-        <v>2.77</v>
-      </c>
-      <c r="AA326">
-        <v>2.25</v>
-      </c>
-      <c r="AB326">
-        <v>1.63</v>
-      </c>
-      <c r="AC326">
-        <v>3.92</v>
-      </c>
-      <c r="AD326">
-        <v>1.19</v>
-      </c>
-      <c r="AE326">
-        <v>1.02</v>
       </c>
       <c r="AF326">
         <v>2.12</v>
       </c>
       <c r="AG326">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK326">
         <v>2.1</v>
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O327">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P327">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q327">
-        <v>4.45</v>
+        <v>3.75</v>
       </c>
       <c r="R327">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="S327">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T327">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U327">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="V327">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W327">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X327">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y327">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z327">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="AA327">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB327">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC327">
         <v>3</v>
       </c>
       <c r="AD327">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE327">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF327">
         <v>1.67</v>
       </c>
       <c r="AG327">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK327">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53782,7 +53782,7 @@
         <v>0</v>
       </c>
       <c r="Q328">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="R328">
         <v>3</v>
@@ -53794,13 +53794,13 @@
         <v>4.8</v>
       </c>
       <c r="U328">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="V328">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W328">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X328">
         <v>1.01</v>
@@ -53818,13 +53818,13 @@
         <v>3.04</v>
       </c>
       <c r="AC328">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD328">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AE328">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF328">
         <v>1.67</v>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK328">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -54108,13 +54108,13 @@
         <v>2.37</v>
       </c>
       <c r="Q330">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="R330">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S330">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T330">
         <v>3.8</v>
@@ -54126,25 +54126,25 @@
         <v>1.67</v>
       </c>
       <c r="W330">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X330">
         <v>1.02</v>
       </c>
       <c r="Y330">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z330">
-        <v>5.59</v>
+        <v>5.5</v>
       </c>
       <c r="AA330">
         <v>1.44</v>
       </c>
       <c r="AB330">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AC330">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD330">
         <v>1.68</v>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK330">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL330">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="O19">
         <v>3.55</v>
@@ -3415,7 +3415,7 @@
         <v>3.15</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R19">
         <v>2.26</v>
@@ -3454,7 +3454,7 @@
         <v>2.33</v>
       </c>
       <c r="AD19">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE19">
         <v>1.16</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
         <v>1.67</v>
@@ -14330,13 +14330,13 @@
         <v>2.45</v>
       </c>
       <c r="O86">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="P86">
         <v>2.41</v>
       </c>
       <c r="Q86">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="R86">
         <v>2.5</v>
@@ -14366,13 +14366,13 @@
         <v>5</v>
       </c>
       <c r="AA86">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB86">
         <v>2.53</v>
       </c>
       <c r="AC86">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD86">
         <v>1.59</v>
@@ -14381,10 +14381,10 @@
         <v>1.19</v>
       </c>
       <c r="AF86">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG86">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
         <v>1.42</v>
@@ -29160,25 +29160,25 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="O177">
+        <v>3.45</v>
+      </c>
+      <c r="P177">
         <v>3.6</v>
       </c>
-      <c r="P177">
-        <v>3.8</v>
-      </c>
       <c r="Q177">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="R177">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S177">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T177">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="U177">
         <v>2.34</v>
@@ -29187,7 +29187,7 @@
         <v>1.5</v>
       </c>
       <c r="W177">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X177">
         <v>1.04</v>
@@ -29196,25 +29196,25 @@
         <v>1.22</v>
       </c>
       <c r="Z177">
-        <v>3.84</v>
+        <v>4.01</v>
       </c>
       <c r="AA177">
         <v>1.7</v>
       </c>
       <c r="AB177">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC177">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD177">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE177">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF177">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG177">
         <v>2.1</v>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK177">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -45469,7 +45469,7 @@
         <v>3.9</v>
       </c>
       <c r="Q277">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="R277">
         <v>2.04</v>
@@ -45499,7 +45499,7 @@
         <v>3</v>
       </c>
       <c r="AA277">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB277">
         <v>1.68</v>
@@ -45514,10 +45514,10 @@
         <v>1.05</v>
       </c>
       <c r="AF277">
+        <v>1.84</v>
+      </c>
+      <c r="AG277">
         <v>1.85</v>
-      </c>
-      <c r="AG277">
-        <v>1.84</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>1.24</v>
       </c>
       <c r="AK277">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -49704,7 +49704,7 @@
         <v>3.88</v>
       </c>
       <c r="P303">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -50537,7 +50537,7 @@
         <v>3.6</v>
       </c>
       <c r="V308">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W308">
         <v>1.04</v>
@@ -50558,10 +50558,10 @@
         <v>1.45</v>
       </c>
       <c r="AC308">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="AD308">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE308">
         <v>1.02</v>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK308">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -51841,10 +51841,10 @@
         <v>3.3</v>
       </c>
       <c r="V316">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W316">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X316">
         <v>1.07</v>
@@ -51856,10 +51856,10 @@
         <v>2.46</v>
       </c>
       <c r="AA316">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB316">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AC316">
         <v>4.83</v>
@@ -51871,7 +51871,7 @@
         <v>1.03</v>
       </c>
       <c r="AF316">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AG316">
         <v>1.62</v>
@@ -52478,55 +52478,55 @@
         <v>3.5</v>
       </c>
       <c r="Q320">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R320">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T320">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U320">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V320">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W320">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X320">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y320">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z320">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA320">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB320">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE320">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF320">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK320">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52632,19 +52632,19 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O321">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P321">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="Q321">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R321">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S321">
         <v>1.44</v>
@@ -52677,7 +52677,7 @@
         <v>1.61</v>
       </c>
       <c r="AC321">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD321">
         <v>1.16</v>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK321">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52825,7 +52825,7 @@
         <v>1.05</v>
       </c>
       <c r="X322">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y322">
         <v>1.38</v>
@@ -52846,10 +52846,10 @@
         <v>1.19</v>
       </c>
       <c r="AE322">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF322">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AG322">
         <v>1.6</v>
@@ -52958,7 +52958,7 @@
         </is>
       </c>
       <c r="N323">
-        <v>5.02</v>
+        <v>4.92</v>
       </c>
       <c r="O323">
         <v>4</v>
@@ -53136,16 +53136,16 @@
         <v>3.04</v>
       </c>
       <c r="S324">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T324">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U324">
         <v>2.08</v>
       </c>
       <c r="V324">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W324">
         <v>1.16</v>
@@ -53154,7 +53154,7 @@
         <v>1.01</v>
       </c>
       <c r="Y324">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z324">
         <v>6</v>
@@ -53166,19 +53166,19 @@
         <v>3</v>
       </c>
       <c r="AC324">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AD324">
         <v>1.72</v>
       </c>
       <c r="AE324">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF324">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG324">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -54108,10 +54108,10 @@
         <v>2.37</v>
       </c>
       <c r="Q330">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="R330">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S330">
         <v>1.2</v>
@@ -54126,7 +54126,7 @@
         <v>1.67</v>
       </c>
       <c r="W330">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X330">
         <v>1.02</v>
@@ -54135,19 +54135,19 @@
         <v>1.14</v>
       </c>
       <c r="Z330">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA330">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB330">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AC330">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AD330">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE330">
         <v>1.28</v>
@@ -54169,7 +54169,7 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK330">
         <v>1.47</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="O6">
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U6">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="AA6">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
+        <v>2.35</v>
+      </c>
+      <c r="AC6">
         <v>2.38</v>
       </c>
-      <c r="AC6">
-        <v>2.21</v>
-      </c>
       <c r="AD6">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AE6">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
         <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>2.15</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R7">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S7">
         <v>1.25</v>
@@ -1477,34 +1477,34 @@
         <v>1.58</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
         <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA7">
         <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE7">
         <v>1.2</v>
       </c>
       <c r="AF7">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
         <v>2.5</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AK7">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>2.95</v>
       </c>
       <c r="P9">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="Q9">
         <v>3.42</v>
@@ -1791,25 +1791,25 @@
         <v>1.91</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U9">
         <v>2.92</v>
       </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
         <v>3.25</v>
@@ -1824,13 +1824,13 @@
         <v>3.42</v>
       </c>
       <c r="AD9">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
         <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG9">
         <v>1.91</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK9">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="O12">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -2283,13 +2283,13 @@
         <v>1.44</v>
       </c>
       <c r="T12">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U12">
         <v>3</v>
       </c>
       <c r="V12">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
         <v>1.02</v>
@@ -2298,25 +2298,25 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z12">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="AA12">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AB12">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC12">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AD12">
         <v>1.22</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
         <v>1.85</v>
@@ -2338,7 +2338,7 @@
         <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,10 +2431,10 @@
         <v>2.07</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2609,28 +2609,28 @@
         <v>1.36</v>
       </c>
       <c r="T14">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
       <c r="U14">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="V14">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z14">
         <v>3.5</v>
       </c>
       <c r="AA14">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
         <v>1.9</v>
@@ -2642,13 +2642,13 @@
         <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
         <v>1.74</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK14">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P16">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P17">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P18">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>3.15</v>
       </c>
       <c r="Q19">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
         <v>2.26</v>
@@ -3424,7 +3424,7 @@
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
         <v>2.26</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
         <v>1.67</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="Q21">
-        <v>3.79</v>
+        <v>3.52</v>
       </c>
       <c r="R21">
         <v>1.89</v>
@@ -3750,7 +3750,7 @@
         <v>1.49</v>
       </c>
       <c r="T21">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="U21">
         <v>3.18</v>
@@ -3759,7 +3759,7 @@
         <v>1.28</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
         <v>1.05</v>
@@ -3771,13 +3771,13 @@
         <v>2.62</v>
       </c>
       <c r="AA21">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AD21">
         <v>1.17</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AK21">
         <v>1.36</v>
@@ -3904,43 +3904,43 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
         <v>2</v>
       </c>
       <c r="S22">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T22">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U22">
         <v>3.2</v>
       </c>
       <c r="V22">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z22">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AA22">
         <v>2.23</v>
       </c>
       <c r="AB22">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AD22">
         <v>1.19</v>
@@ -3949,10 +3949,10 @@
         <v>1.03</v>
       </c>
       <c r="AF22">
+        <v>1.86</v>
+      </c>
+      <c r="AG22">
         <v>1.83</v>
-      </c>
-      <c r="AG22">
-        <v>1.86</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O26">
         <v>3</v>
@@ -4556,16 +4556,16 @@
         <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>3.6</v>
+        <v>3.89</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U26">
         <v>3</v>
@@ -4601,10 +4601,10 @@
         <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG26">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
         <v>1.33</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>5.21</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="P28">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
         <v>2.91</v>
@@ -5404,7 +5404,7 @@
         <v>2.14</v>
       </c>
       <c r="AB31">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC31">
         <v>3.85</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="O32">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P32">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>4.59</v>
+        <v>4.33</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="O39">
         <v>3.2</v>
       </c>
       <c r="P39">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6998,25 +6998,25 @@
         <v>3.25</v>
       </c>
       <c r="P41">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="Q41">
+        <v>3.01</v>
+      </c>
+      <c r="R41">
+        <v>2.24</v>
+      </c>
+      <c r="S41">
+        <v>1.33</v>
+      </c>
+      <c r="T41">
         <v>3</v>
       </c>
-      <c r="R41">
-        <v>2.1</v>
-      </c>
-      <c r="S41">
-        <v>1.4</v>
-      </c>
-      <c r="T41">
-        <v>2.67</v>
-      </c>
       <c r="U41">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W41">
         <v>1.06</v>
@@ -7025,10 +7025,10 @@
         <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="AA41">
         <v>1.91</v>
@@ -7037,10 +7037,10 @@
         <v>1.8</v>
       </c>
       <c r="AC41">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="AD41">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE41">
         <v>1.08</v>
@@ -7170,7 +7170,7 @@
         <v>2.38</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T42">
         <v>3.6</v>
@@ -7182,7 +7182,7 @@
         <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7197,22 +7197,22 @@
         <v>1.63</v>
       </c>
       <c r="AB42">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC42">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="AD42">
         <v>1.5</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
         <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P43">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7662,7 +7662,7 @@
         <v>1.3</v>
       </c>
       <c r="T45">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="U45">
         <v>2.75</v>
@@ -7671,34 +7671,34 @@
         <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
         <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA45">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB45">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC45">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD45">
         <v>1.33</v>
       </c>
       <c r="AE45">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG45">
         <v>1.85</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8462,16 +8462,16 @@
         <v>1.93</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q50">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R50">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
         <v>1.33</v>
@@ -8480,7 +8480,7 @@
         <v>2.86</v>
       </c>
       <c r="U50">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V50">
         <v>1.44</v>
@@ -8495,19 +8495,19 @@
         <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="AA50">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB50">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AD50">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P53">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="Q53">
-        <v>3.37</v>
+        <v>3.92</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8972,7 +8972,7 @@
         <v>2.55</v>
       </c>
       <c r="V53">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W53">
         <v>1.08</v>
@@ -8981,22 +8981,22 @@
         <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB53">
         <v>2</v>
       </c>
       <c r="AC53">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="AD53">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
         <v>1.14</v>
@@ -9005,7 +9005,7 @@
         <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9283,16 +9283,16 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="R55">
         <v>2.21</v>
       </c>
       <c r="S55">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T55">
-        <v>3.03</v>
+        <v>2.82</v>
       </c>
       <c r="U55">
         <v>2.75</v>
@@ -9301,7 +9301,7 @@
         <v>1.4</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.04</v>
@@ -9310,13 +9310,13 @@
         <v>1.2</v>
       </c>
       <c r="Z55">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA55">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AB55">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC55">
         <v>2.88</v>
@@ -9331,7 +9331,7 @@
         <v>1.75</v>
       </c>
       <c r="AG55">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O59">
         <v>3.35</v>
       </c>
       <c r="P59">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q59">
         <v>2.81</v>
       </c>
       <c r="R59">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S59">
         <v>1.25</v>
@@ -9950,25 +9950,25 @@
         <v>2.25</v>
       </c>
       <c r="V59">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W59">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X59">
         <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z59">
         <v>4.5</v>
       </c>
       <c r="AA59">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AB59">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC59">
         <v>2.45</v>
@@ -10098,10 +10098,10 @@
         <v>2.11</v>
       </c>
       <c r="Q60">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="R60">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S60">
         <v>1.26</v>
@@ -10113,7 +10113,7 @@
         <v>2.31</v>
       </c>
       <c r="V60">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W60">
         <v>1.12</v>
@@ -10146,7 +10146,7 @@
         <v>1.5</v>
       </c>
       <c r="AG60">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
       <c r="AK60">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O61">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
         <v>2.87</v>
@@ -10264,19 +10264,19 @@
         <v>2.4</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T61">
         <v>3.8</v>
       </c>
       <c r="U61">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W61">
         <v>1.17</v>
@@ -10285,31 +10285,31 @@
         <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
         <v>5</v>
       </c>
       <c r="AA61">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AC61">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AD61">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE61">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG61">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK61">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,22 +10424,22 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R62">
         <v>2.5</v>
       </c>
       <c r="S62">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W62">
         <v>1.18</v>
@@ -10448,7 +10448,7 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
         <v>5.75</v>
@@ -10457,10 +10457,10 @@
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="AC62">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD62">
         <v>1.82</v>
@@ -10488,7 +10488,7 @@
         <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10910,58 +10910,58 @@
         <v>3.24</v>
       </c>
       <c r="P65">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="Q65">
-        <v>2.95</v>
+        <v>2.54</v>
       </c>
       <c r="R65">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="S65">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T65">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="U65">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="V65">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W65">
         <v>1.02</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z65">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="AA65">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="AB65">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC65">
         <v>4.29</v>
       </c>
       <c r="AD65">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE65">
         <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AG65">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.36</v>
       </c>
       <c r="AK65">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O69">
-        <v>5.5</v>
+        <v>6.12</v>
       </c>
       <c r="P69">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11728,10 +11728,10 @@
         <v>4.3</v>
       </c>
       <c r="Q70">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="R70">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
         <v>1.3</v>
@@ -11740,7 +11740,7 @@
         <v>3</v>
       </c>
       <c r="U70">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="V70">
         <v>1.44</v>
@@ -11749,34 +11749,34 @@
         <v>1.1</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA70">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB70">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC70">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD70">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE70">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG70">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,13 +11891,13 @@
         <v>2.6</v>
       </c>
       <c r="Q71">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S71">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
         <v>3.9</v>
@@ -11915,13 +11915,13 @@
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z71">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA71">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB71">
         <v>2.63</v>
@@ -11930,7 +11930,7 @@
         <v>2.09</v>
       </c>
       <c r="AD71">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE71">
         <v>1.29</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK71">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12054,7 +12054,7 @@
         <v>4</v>
       </c>
       <c r="Q72">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="R72">
         <v>1.98</v>
@@ -12066,7 +12066,7 @@
         <v>2.68</v>
       </c>
       <c r="U72">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="V72">
         <v>1.32</v>
@@ -12078,31 +12078,31 @@
         <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z72">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="AA72">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AB72">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC72">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AD72">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE72">
         <v>1.03</v>
       </c>
       <c r="AF72">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG72">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK72">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12211,13 +12211,13 @@
         <v>2.18</v>
       </c>
       <c r="O73">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="P73">
-        <v>2.71</v>
+        <v>3.56</v>
       </c>
       <c r="Q73">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="R73">
         <v>2.09</v>
@@ -12250,7 +12250,7 @@
         <v>2.2</v>
       </c>
       <c r="AB73">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC73">
         <v>3.8</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AK73">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
         <v>4.5</v>
       </c>
       <c r="Q74">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R74">
         <v>2.1</v>
       </c>
       <c r="S74">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T74">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="U74">
         <v>2.9</v>
       </c>
       <c r="V74">
+        <v>1.33</v>
+      </c>
+      <c r="W74">
+        <v>1.03</v>
+      </c>
+      <c r="X74">
+        <v>1.01</v>
+      </c>
+      <c r="Y74">
         <v>1.36</v>
       </c>
-      <c r="W74">
+      <c r="Z74">
+        <v>2.9</v>
+      </c>
+      <c r="AA74">
+        <v>2.16</v>
+      </c>
+      <c r="AB74">
+        <v>1.68</v>
+      </c>
+      <c r="AC74">
+        <v>3.44</v>
+      </c>
+      <c r="AD74">
+        <v>1.22</v>
+      </c>
+      <c r="AE74">
         <v>1.04</v>
       </c>
-      <c r="X74">
-        <v>1.03</v>
-      </c>
-      <c r="Y74">
-        <v>1.3</v>
-      </c>
-      <c r="Z74">
-        <v>3.2</v>
-      </c>
-      <c r="AA74">
-        <v>2.04</v>
-      </c>
-      <c r="AB74">
-        <v>1.78</v>
-      </c>
-      <c r="AC74">
-        <v>3.12</v>
-      </c>
-      <c r="AD74">
-        <v>1.28</v>
-      </c>
-      <c r="AE74">
-        <v>1.1</v>
-      </c>
       <c r="AF74">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AG74">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
         <v>2.09</v>
@@ -12697,61 +12697,61 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="O76">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P76">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q76">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="R76">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U76">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="V76">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
         <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA76">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB76">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC76">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="AD76">
         <v>1.28</v>
       </c>
       <c r="AE76">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF76">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG76">
         <v>1.85</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK76">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13192,19 +13192,19 @@
         <v>3.2</v>
       </c>
       <c r="P79">
-        <v>3.37</v>
+        <v>2.98</v>
       </c>
       <c r="Q79">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="R79">
         <v>2</v>
       </c>
       <c r="S79">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T79">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U79">
         <v>3.1</v>
@@ -13213,7 +13213,7 @@
         <v>1.31</v>
       </c>
       <c r="W79">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X79">
         <v>1.02</v>
@@ -13234,16 +13234,16 @@
         <v>3.72</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE79">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF79">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG79">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.33</v>
       </c>
       <c r="AK79">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O80">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P80">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="Q80">
         <v>4.2</v>
@@ -13379,28 +13379,28 @@
         <v>1.15</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z80">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA80">
         <v>1.5</v>
       </c>
       <c r="AB80">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AC80">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AD80">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE80">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF80">
         <v>1.48</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
         <v>1.25</v>
@@ -13512,46 +13512,46 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="O81">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
         <v>4.33</v>
       </c>
       <c r="Q81">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R81">
         <v>2.38</v>
       </c>
       <c r="S81">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T81">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U81">
         <v>2.2</v>
       </c>
       <c r="V81">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W81">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X81">
         <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="AA81">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB81">
         <v>2.23</v>
@@ -13563,10 +13563,10 @@
         <v>1.5</v>
       </c>
       <c r="AE81">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF81">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG81">
         <v>2.25</v>
@@ -13585,7 +13585,7 @@
         <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,28 +13675,28 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="O82">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
         <v>4.05</v>
       </c>
       <c r="Q82">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="R82">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
         <v>1.34</v>
       </c>
       <c r="T82">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="U82">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V82">
         <v>1.43</v>
@@ -13705,16 +13705,16 @@
         <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y82">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z82">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AA82">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB82">
         <v>1.9</v>
@@ -13723,13 +13723,13 @@
         <v>2.88</v>
       </c>
       <c r="AD82">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE82">
         <v>1.09</v>
       </c>
       <c r="AF82">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG82">
         <v>2</v>
@@ -14004,10 +14004,10 @@
         <v>2.1</v>
       </c>
       <c r="O84">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P84">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q84">
         <v>2.8</v>
@@ -14016,25 +14016,25 @@
         <v>1.96</v>
       </c>
       <c r="S84">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T84">
         <v>2.75</v>
       </c>
       <c r="U84">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V84">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W84">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
         <v>1.04</v>
       </c>
       <c r="Y84">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z84">
         <v>2.88</v>
@@ -14043,22 +14043,22 @@
         <v>2.17</v>
       </c>
       <c r="AB84">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC84">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD84">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE84">
         <v>1.06</v>
       </c>
       <c r="AF84">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG84">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK84">
         <v>1.62</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14330,13 +14330,13 @@
         <v>2.45</v>
       </c>
       <c r="O86">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="P86">
         <v>2.41</v>
       </c>
       <c r="Q86">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="R86">
         <v>2.5</v>
@@ -14345,7 +14345,7 @@
         <v>1.22</v>
       </c>
       <c r="T86">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U86">
         <v>2.17</v>
@@ -14384,7 +14384,7 @@
         <v>1.41</v>
       </c>
       <c r="AG86">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK86">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>3.4</v>
       </c>
       <c r="P88">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
@@ -14668,16 +14668,16 @@
         <v>2.24</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T88">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="U88">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="V88">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W88">
         <v>1.08</v>
@@ -14695,16 +14695,16 @@
         <v>1.7</v>
       </c>
       <c r="AB88">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC88">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AD88">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE88">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF88">
         <v>1.57</v>
@@ -14843,10 +14843,10 @@
         <v>1.48</v>
       </c>
       <c r="W89">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y89">
         <v>1.25</v>
@@ -14858,7 +14858,7 @@
         <v>1.83</v>
       </c>
       <c r="AB89">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC89">
         <v>2.95</v>
@@ -14870,7 +14870,7 @@
         <v>1.1</v>
       </c>
       <c r="AF89">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG89">
         <v>2</v>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK89">
         <v>2</v>
@@ -14979,31 +14979,31 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="O90">
         <v>4.4</v>
       </c>
       <c r="P90">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q90">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R90">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="S90">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T90">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="U90">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="V90">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W90">
         <v>1.17</v>
@@ -15018,25 +15018,25 @@
         <v>6</v>
       </c>
       <c r="AA90">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AB90">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AC90">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AD90">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AE90">
         <v>1.29</v>
       </c>
       <c r="AF90">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG90">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15169,10 +15169,10 @@
         <v>1.55</v>
       </c>
       <c r="W91">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X91">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
         <v>1.2</v>
@@ -15187,13 +15187,13 @@
         <v>2.08</v>
       </c>
       <c r="AC91">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AD91">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE91">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF91">
         <v>1.57</v>
@@ -15477,52 +15477,52 @@
         <v>3.5</v>
       </c>
       <c r="Q93">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R93">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S93">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T93">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="U93">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="V93">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W93">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X93">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y93">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z93">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA93">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB93">
         <v>1.7</v>
       </c>
       <c r="AC93">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AD93">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE93">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF93">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG93">
         <v>1.75</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK93">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15634,49 +15634,49 @@
         <v>1.83</v>
       </c>
       <c r="O94">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P94">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q94">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R94">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S94">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T94">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="U94">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V94">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W94">
         <v>1.06</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z94">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA94">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB94">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC94">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AD94">
         <v>1.19</v>
@@ -15704,7 +15704,7 @@
         <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q96">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R96">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S96">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T96">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="U96">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V96">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W96">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y96">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z96">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA96">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AB96">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC96">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD96">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE96">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF96">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG96">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.4</v>
       </c>
       <c r="AK96">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O97">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>3.32</v>
+      </c>
+      <c r="R97">
+        <v>1.85</v>
+      </c>
+      <c r="S97">
+        <v>1.63</v>
+      </c>
+      <c r="T97">
+        <v>2.13</v>
+      </c>
+      <c r="U97">
+        <v>3.7</v>
+      </c>
+      <c r="V97">
+        <v>1.2</v>
+      </c>
+      <c r="W97">
+        <v>1.03</v>
+      </c>
+      <c r="X97">
+        <v>1.13</v>
+      </c>
+      <c r="Y97">
+        <v>1.41</v>
+      </c>
+      <c r="Z97">
         <v>2.65</v>
       </c>
-      <c r="Q97">
-        <v>3.4</v>
-      </c>
-      <c r="R97">
-        <v>1.95</v>
-      </c>
-      <c r="S97">
-        <v>1.53</v>
-      </c>
-      <c r="T97">
-        <v>2.28</v>
-      </c>
-      <c r="U97">
-        <v>3.5</v>
-      </c>
-      <c r="V97">
-        <v>1.25</v>
-      </c>
-      <c r="W97">
-        <v>1.04</v>
-      </c>
-      <c r="X97">
-        <v>1.11</v>
-      </c>
-      <c r="Y97">
-        <v>1.5</v>
-      </c>
-      <c r="Z97">
-        <v>2.45</v>
-      </c>
       <c r="AA97">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AB97">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC97">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AD97">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE97">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG97">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.4</v>
       </c>
       <c r="AK97">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O99">
         <v>3.15</v>
@@ -16461,49 +16461,49 @@
         <v>2.05</v>
       </c>
       <c r="S99">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T99">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U99">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="V99">
         <v>1.3</v>
       </c>
       <c r="W99">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X99">
         <v>1.05</v>
       </c>
       <c r="Y99">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z99">
         <v>2.88</v>
       </c>
       <c r="AA99">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB99">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC99">
         <v>3.91</v>
       </c>
       <c r="AD99">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE99">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF99">
         <v>1.85</v>
       </c>
       <c r="AG99">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK99">
         <v>1.59</v>
@@ -16618,16 +16618,16 @@
         <v>3.1</v>
       </c>
       <c r="Q100">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R100">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S100">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T100">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U100">
         <v>2.5</v>
@@ -16645,7 +16645,7 @@
         <v>1.25</v>
       </c>
       <c r="Z100">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="AA100">
         <v>1.85</v>
@@ -16657,7 +16657,7 @@
         <v>3.12</v>
       </c>
       <c r="AD100">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE100">
         <v>1.11</v>
@@ -16666,7 +16666,7 @@
         <v>1.55</v>
       </c>
       <c r="AG100">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16781,55 +16781,55 @@
         <v>5.04</v>
       </c>
       <c r="Q101">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R101">
         <v>2.3</v>
       </c>
       <c r="S101">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U101">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V101">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W101">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
         <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z101">
-        <v>3.98</v>
+        <v>3.91</v>
       </c>
       <c r="AA101">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AB101">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AC101">
         <v>2.8</v>
       </c>
       <c r="AD101">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE101">
         <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG101">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK101">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16950,19 +16950,19 @@
         <v>2.02</v>
       </c>
       <c r="S102">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T102">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="U102">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
         <v>1.06</v>
@@ -16989,10 +16989,10 @@
         <v>1.08</v>
       </c>
       <c r="AF102">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG102">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17922,46 +17922,46 @@
         <v>3.8</v>
       </c>
       <c r="Q108">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R108">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S108">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T108">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="U108">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="V108">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W108">
         <v>1.04</v>
       </c>
       <c r="X108">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y108">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="Z108">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AA108">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="AB108">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC108">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD108">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE108">
         <v>1.01</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK108">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18085,10 +18085,10 @@
         <v>2.62</v>
       </c>
       <c r="Q109">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="R109">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="S109">
         <v>1.44</v>
@@ -18106,31 +18106,31 @@
         <v>1.05</v>
       </c>
       <c r="X109">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y109">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z109">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AA109">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AB109">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC109">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AD109">
         <v>1.13</v>
       </c>
       <c r="AE109">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF109">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG109">
         <v>1.73</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,71 +18248,71 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R110">
         <v>2.05</v>
       </c>
       <c r="S110">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U110">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="V110">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W110">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y110">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z110">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AA110">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AB110">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC110">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD110">
+        <v>1.2</v>
+      </c>
+      <c r="AE110">
+        <v>1.06</v>
+      </c>
+      <c r="AF110">
+        <v>1.84</v>
+      </c>
+      <c r="AG110">
+        <v>1.83</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
+        <v>1.25</v>
+      </c>
+      <c r="AK110">
         <v>1.21</v>
-      </c>
-      <c r="AE110">
-        <v>1.03</v>
-      </c>
-      <c r="AF110">
-        <v>1.81</v>
-      </c>
-      <c r="AG110">
-        <v>1.86</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.73</v>
-      </c>
-      <c r="AK110">
-        <v>1.22</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,61 +18402,61 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O111">
         <v>2.87</v>
       </c>
       <c r="P111">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q111">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="R111">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S111">
         <v>1.54</v>
       </c>
       <c r="T111">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="U111">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V111">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="W111">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X111">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y111">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z111">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AA111">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB111">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC111">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AD111">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE111">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AG111">
         <v>1.7</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK111">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O112">
         <v>3.2</v>
       </c>
       <c r="P112">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="Q112">
         <v>2.98</v>
@@ -18580,25 +18580,25 @@
         <v>1.96</v>
       </c>
       <c r="S112">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="T112">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U112">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V112">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W112">
         <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y112">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z112">
         <v>2.64</v>
@@ -18607,19 +18607,19 @@
         <v>2.3</v>
       </c>
       <c r="AB112">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC112">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD112">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE112">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF112">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AG112">
         <v>1.85</v>
@@ -18731,61 +18731,61 @@
         <v>2.74</v>
       </c>
       <c r="O113">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P113">
-        <v>2.81</v>
+        <v>2.4</v>
       </c>
       <c r="Q113">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="R113">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S113">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T113">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U113">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="V113">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W113">
         <v>1.03</v>
       </c>
       <c r="X113">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z113">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA113">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AB113">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC113">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AD113">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE113">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG113">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AK113">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,19 +18891,19 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="O114">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="P114">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="Q114">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R114">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="S114">
         <v>1.21</v>
@@ -18927,28 +18927,28 @@
         <v>1.12</v>
       </c>
       <c r="Z114">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AA114">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB114">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AC114">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AD114">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AE114">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF114">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG114">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK114">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19226,25 +19226,25 @@
         <v>0</v>
       </c>
       <c r="Q116">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="R116">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="S116">
         <v>1.08</v>
       </c>
       <c r="T116">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="U116">
         <v>1.57</v>
       </c>
       <c r="V116">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="W116">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X116">
         <v>1</v>
@@ -19262,19 +19262,19 @@
         <v>4.4</v>
       </c>
       <c r="AC116">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AD116">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AE116">
         <v>1.67</v>
       </c>
       <c r="AF116">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AG116">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19395,10 +19395,10 @@
         <v>1.99</v>
       </c>
       <c r="S117">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T117">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="U117">
         <v>3.04</v>
@@ -19416,16 +19416,16 @@
         <v>1.33</v>
       </c>
       <c r="Z117">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AA117">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB117">
         <v>1.7</v>
       </c>
       <c r="AC117">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AD117">
         <v>1.22</v>
@@ -19453,7 +19453,7 @@
         <v>1.28</v>
       </c>
       <c r="AK117">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19552,10 +19552,10 @@
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="R118">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="S118">
         <v>1.45</v>
@@ -19564,43 +19564,43 @@
         <v>2.55</v>
       </c>
       <c r="U118">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="V118">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W118">
         <v>1.03</v>
       </c>
       <c r="X118">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y118">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z118">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AA118">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="AB118">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AC118">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD118">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE118">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF118">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG118">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>1.33</v>
       </c>
       <c r="AK118">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -22000,31 +22000,31 @@
         <v>2.69</v>
       </c>
       <c r="R133">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S133">
         <v>1.36</v>
       </c>
       <c r="T133">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U133">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V133">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W133">
         <v>1.06</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y133">
         <v>1.26</v>
       </c>
       <c r="Z133">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA133">
         <v>1.85</v>
@@ -22033,19 +22033,19 @@
         <v>1.85</v>
       </c>
       <c r="AC133">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD133">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE133">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF133">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG133">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK133">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22154,22 +22154,22 @@
         <v>2.07</v>
       </c>
       <c r="O134">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P134">
         <v>3.55</v>
       </c>
       <c r="Q134">
-        <v>2.54</v>
+        <v>2.79</v>
       </c>
       <c r="R134">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="S134">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="T134">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="U134">
         <v>3.36</v>
@@ -22187,10 +22187,10 @@
         <v>1.46</v>
       </c>
       <c r="Z134">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="AA134">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AB134">
         <v>1.56</v>
@@ -22208,7 +22208,7 @@
         <v>2.05</v>
       </c>
       <c r="AG134">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AK134">
         <v>1.6</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P135">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q135">
         <v>2.17</v>
@@ -22356,7 +22356,7 @@
         <v>2</v>
       </c>
       <c r="AB135">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC135">
         <v>3.46</v>
@@ -22365,13 +22365,13 @@
         <v>1.28</v>
       </c>
       <c r="AE135">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG135">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>1.21</v>
       </c>
       <c r="AK135">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O149">
         <v>4</v>
       </c>
       <c r="P149">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -24626,34 +24626,34 @@
         <v>1.06</v>
       </c>
       <c r="X149">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y149">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z149">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="AA149">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB149">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AC149">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD149">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE149">
         <v>1.07</v>
       </c>
       <c r="AF149">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG149">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>1.11</v>
       </c>
       <c r="AK149">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24922,7 +24922,7 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O151">
         <v>3.25</v>
@@ -24937,34 +24937,34 @@
         <v>2.1</v>
       </c>
       <c r="S151">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T151">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="U151">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="V151">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W151">
         <v>1.05</v>
       </c>
       <c r="X151">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y151">
         <v>1.33</v>
       </c>
       <c r="Z151">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA151">
         <v>2.1</v>
       </c>
       <c r="AB151">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC151">
         <v>3.5</v>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK151">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25139,7 +25139,7 @@
         <v>1.11</v>
       </c>
       <c r="AF152">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG152">
         <v>2</v>
@@ -25257,7 +25257,7 @@
         <v>0</v>
       </c>
       <c r="Q153">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="R153">
         <v>2.3</v>
@@ -25266,13 +25266,13 @@
         <v>1.28</v>
       </c>
       <c r="T153">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U153">
         <v>2.38</v>
       </c>
       <c r="V153">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W153">
         <v>1.09</v>
@@ -25281,16 +25281,16 @@
         <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z153">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA153">
         <v>1.67</v>
       </c>
       <c r="AB153">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC153">
         <v>2.62</v>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK153">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25411,37 +25411,37 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="O154">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P154">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="Q154">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R154">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S154">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T154">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U154">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="V154">
         <v>1.5</v>
       </c>
       <c r="W154">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X154">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
         <v>1.2</v>
@@ -25459,10 +25459,10 @@
         <v>2.48</v>
       </c>
       <c r="AD154">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE154">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF154">
         <v>1.53</v>
@@ -25481,7 +25481,7 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK154">
         <v>1.58</v>
@@ -26552,7 +26552,7 @@
         </is>
       </c>
       <c r="N161">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O161">
         <v>3.15</v>
@@ -26715,49 +26715,49 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O162">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P162">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q162">
-        <v>3.42</v>
+        <v>2.94</v>
       </c>
       <c r="R162">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="S162">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="T162">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="U162">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V162">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W162">
         <v>1.01</v>
       </c>
       <c r="X162">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y162">
         <v>1.5</v>
       </c>
       <c r="Z162">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AA162">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB162">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC162">
         <v>5</v>
@@ -26769,10 +26769,10 @@
         <v>1.04</v>
       </c>
       <c r="AF162">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AG162">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>1.33</v>
       </c>
       <c r="AK162">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O163">
         <v>8</v>
       </c>
       <c r="P163">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Q163">
         <v>8.5</v>
@@ -26893,19 +26893,19 @@
         <v>3.1</v>
       </c>
       <c r="S163">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T163">
         <v>4.75</v>
       </c>
       <c r="U163">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="V163">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W163">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X163">
         <v>1.01</v>
@@ -26914,28 +26914,28 @@
         <v>1.02</v>
       </c>
       <c r="Z163">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA163">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AB163">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AC163">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AD163">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AE163">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF163">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG163">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>1.09</v>
       </c>
       <c r="AK163">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,34 +27041,34 @@
         </is>
       </c>
       <c r="N164">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O164">
         <v>3.5</v>
       </c>
       <c r="P164">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q164">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="R164">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S164">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T164">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U164">
         <v>2.23</v>
       </c>
       <c r="V164">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W164">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X164">
         <v>1.03</v>
@@ -27080,19 +27080,19 @@
         <v>4.2</v>
       </c>
       <c r="AA164">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB164">
         <v>2.25</v>
       </c>
       <c r="AC164">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AD164">
         <v>1.5</v>
       </c>
       <c r="AE164">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF164">
         <v>1.5</v>
@@ -27111,7 +27111,7 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK164">
         <v>1.3</v>
@@ -27207,25 +27207,25 @@
         <v>2.05</v>
       </c>
       <c r="O165">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P165">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="Q165">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="R165">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S165">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T165">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U165">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="V165">
         <v>1.75</v>
@@ -27240,22 +27240,22 @@
         <v>1.07</v>
       </c>
       <c r="Z165">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA165">
         <v>1.34</v>
       </c>
       <c r="AB165">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="AC165">
         <v>1.89</v>
       </c>
       <c r="AD165">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE165">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF165">
         <v>1.36</v>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK165">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27370,13 +27370,13 @@
         <v>2.75</v>
       </c>
       <c r="O166">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P166">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q166">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R166">
         <v>1.97</v>
@@ -27385,13 +27385,13 @@
         <v>1.4</v>
       </c>
       <c r="T166">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="U166">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V166">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W166">
         <v>1.06</v>
@@ -27412,16 +27412,16 @@
         <v>1.72</v>
       </c>
       <c r="AC166">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD166">
         <v>1.25</v>
       </c>
       <c r="AE166">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF166">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG166">
         <v>1.87</v>
@@ -27440,7 +27440,7 @@
         <v>1.5</v>
       </c>
       <c r="AK166">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27533,31 +27533,31 @@
         <v>2.3</v>
       </c>
       <c r="O167">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P167">
         <v>2.65</v>
       </c>
       <c r="Q167">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="R167">
         <v>2.23</v>
       </c>
       <c r="S167">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T167">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U167">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="V167">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W167">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X167">
         <v>1.01</v>
@@ -27572,7 +27572,7 @@
         <v>1.45</v>
       </c>
       <c r="AB167">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="AC167">
         <v>2.2</v>
@@ -28508,25 +28508,25 @@
         </is>
       </c>
       <c r="N173">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O173">
         <v>4</v>
       </c>
       <c r="P173">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q173">
         <v>6.5</v>
       </c>
       <c r="R173">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S173">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T173">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U173">
         <v>2.7</v>
@@ -28544,16 +28544,16 @@
         <v>1.26</v>
       </c>
       <c r="Z173">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA173">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB173">
         <v>1.85</v>
       </c>
       <c r="AC173">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="AD173">
         <v>1.26</v>
@@ -28562,10 +28562,10 @@
         <v>1.06</v>
       </c>
       <c r="AF173">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG173">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>2.55</v>
       </c>
       <c r="AK173">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,16 +28671,16 @@
         </is>
       </c>
       <c r="N174">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="O174">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P174">
         <v>1.48</v>
       </c>
       <c r="Q174">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="R174">
         <v>2.58</v>
@@ -28692,7 +28692,7 @@
         <v>4.8</v>
       </c>
       <c r="U174">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V174">
         <v>1.83</v>
@@ -28704,10 +28704,10 @@
         <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z174">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA174">
         <v>1.36</v>
@@ -28722,13 +28722,13 @@
         <v>1.85</v>
       </c>
       <c r="AE174">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AF174">
         <v>1.47</v>
       </c>
       <c r="AG174">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28834,25 +28834,25 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O175">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="P175">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q175">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="R175">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S175">
         <v>1.14</v>
       </c>
       <c r="T175">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U175">
         <v>2.04</v>
@@ -28861,7 +28861,7 @@
         <v>1.78</v>
       </c>
       <c r="W175">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X175">
         <v>1.01</v>
@@ -28891,7 +28891,7 @@
         <v>1.37</v>
       </c>
       <c r="AG175">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29169,16 +29169,16 @@
         <v>3.6</v>
       </c>
       <c r="Q177">
+        <v>2.3</v>
+      </c>
+      <c r="R177">
         <v>2.36</v>
       </c>
-      <c r="R177">
-        <v>2.18</v>
-      </c>
       <c r="S177">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T177">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="U177">
         <v>2.34</v>
@@ -29187,7 +29187,7 @@
         <v>1.5</v>
       </c>
       <c r="W177">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X177">
         <v>1.04</v>
@@ -29214,7 +29214,7 @@
         <v>1.11</v>
       </c>
       <c r="AF177">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG177">
         <v>2.1</v>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK177">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29486,61 +29486,61 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="O179">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P179">
         <v>2.75</v>
       </c>
       <c r="Q179">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R179">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S179">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T179">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U179">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V179">
         <v>1.6</v>
       </c>
       <c r="W179">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X179">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y179">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z179">
-        <v>5.58</v>
+        <v>5</v>
       </c>
       <c r="AA179">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB179">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AC179">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD179">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE179">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF179">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AG179">
         <v>2.5</v>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK179">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="O180">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="P180">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -30464,22 +30464,22 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="O185">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="P185">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q185">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R185">
         <v>1.9</v>
       </c>
       <c r="S185">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T185">
         <v>2.45</v>
@@ -30509,19 +30509,19 @@
         <v>1.55</v>
       </c>
       <c r="AC185">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD185">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE185">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF185">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG185">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -31125,55 +31125,55 @@
         <v>0</v>
       </c>
       <c r="Q189">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="R189">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="S189">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="T189">
         <v>2.36</v>
       </c>
       <c r="U189">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="V189">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W189">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X189">
         <v>1.06</v>
       </c>
       <c r="Y189">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="Z189">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AA189">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
       <c r="AB189">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC189">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="AD189">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE189">
         <v>1.01</v>
       </c>
       <c r="AF189">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AG189">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>1.21</v>
       </c>
       <c r="AK189">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31282,16 +31282,16 @@
         <v>1.44</v>
       </c>
       <c r="O190">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P190">
         <v>5.75</v>
       </c>
       <c r="Q190">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R190">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="S190">
         <v>1.3</v>
@@ -31303,7 +31303,7 @@
         <v>2.58</v>
       </c>
       <c r="V190">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W190">
         <v>1.1</v>
@@ -31315,10 +31315,10 @@
         <v>1.23</v>
       </c>
       <c r="Z190">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="AA190">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB190">
         <v>2.17</v>
@@ -31327,16 +31327,16 @@
         <v>2.52</v>
       </c>
       <c r="AD190">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE190">
         <v>1.15</v>
       </c>
       <c r="AF190">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG190">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK190">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31442,16 +31442,16 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="O191">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="P191">
         <v>2.1</v>
       </c>
       <c r="Q191">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="R191">
         <v>2.4</v>
@@ -31460,10 +31460,10 @@
         <v>1.25</v>
       </c>
       <c r="T191">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U191">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V191">
         <v>1.6</v>
@@ -31475,7 +31475,7 @@
         <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z191">
         <v>5.21</v>
@@ -31490,7 +31490,7 @@
         <v>2.4</v>
       </c>
       <c r="AD191">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE191">
         <v>1.2</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O195">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="P195">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -33561,10 +33561,10 @@
         </is>
       </c>
       <c r="N204">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O204">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="P204">
         <v>2.04</v>
@@ -33573,7 +33573,7 @@
         <v>4</v>
       </c>
       <c r="R204">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S204">
         <v>1.44</v>
@@ -33582,7 +33582,7 @@
         <v>2.59</v>
       </c>
       <c r="U204">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V204">
         <v>1.36</v>
@@ -33594,28 +33594,28 @@
         <v>1.03</v>
       </c>
       <c r="Y204">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z204">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AA204">
         <v>1.94</v>
       </c>
       <c r="AB204">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AC204">
-        <v>3.64</v>
+        <v>3.12</v>
       </c>
       <c r="AD204">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE204">
         <v>1.1</v>
       </c>
       <c r="AF204">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG204">
         <v>1.85</v>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK204">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O205">
-        <v>3.31</v>
+        <v>3.22</v>
       </c>
       <c r="P205">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q205">
         <v>2.63</v>
@@ -33739,16 +33739,16 @@
         <v>2.05</v>
       </c>
       <c r="S205">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T205">
         <v>2.65</v>
       </c>
       <c r="U205">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V205">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W205">
         <v>1.04</v>
@@ -33766,7 +33766,7 @@
         <v>2.2</v>
       </c>
       <c r="AB205">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC205">
         <v>3.8</v>
@@ -33775,7 +33775,7 @@
         <v>1.24</v>
       </c>
       <c r="AE205">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF205">
         <v>1.83</v>
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="O209">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P209">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q209">
         <v>2.8</v>
       </c>
       <c r="R209">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="S209">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="T209">
         <v>2.5</v>
       </c>
       <c r="U209">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V209">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W209">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X209">
+        <v>1.1</v>
+      </c>
+      <c r="Y209">
+        <v>1.44</v>
+      </c>
+      <c r="Z209">
+        <v>2.5</v>
+      </c>
+      <c r="AA209">
+        <v>2.5</v>
+      </c>
+      <c r="AB209">
+        <v>1.44</v>
+      </c>
+      <c r="AC209">
+        <v>4.8</v>
+      </c>
+      <c r="AD209">
+        <v>1.17</v>
+      </c>
+      <c r="AE209">
         <v>1.05</v>
       </c>
-      <c r="Y209">
-        <v>1.4</v>
-      </c>
-      <c r="Z209">
-        <v>2.7</v>
-      </c>
-      <c r="AA209">
-        <v>2.28</v>
-      </c>
-      <c r="AB209">
-        <v>1.49</v>
-      </c>
-      <c r="AC209">
-        <v>4.4</v>
-      </c>
-      <c r="AD209">
-        <v>1.16</v>
-      </c>
-      <c r="AE209">
-        <v>1</v>
-      </c>
       <c r="AF209">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG209">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK209">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34702,19 +34702,19 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O211">
         <v>3.5</v>
       </c>
       <c r="P211">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q211">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R211">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="S211">
         <v>1.38</v>
@@ -34723,19 +34723,19 @@
         <v>2.77</v>
       </c>
       <c r="U211">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="V211">
         <v>1.42</v>
       </c>
       <c r="W211">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X211">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z211">
         <v>3.28</v>
@@ -34744,7 +34744,7 @@
         <v>1.91</v>
       </c>
       <c r="AB211">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC211">
         <v>3.04</v>
@@ -34756,10 +34756,10 @@
         <v>1.12</v>
       </c>
       <c r="AF211">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG211">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -35680,10 +35680,10 @@
         </is>
       </c>
       <c r="N217">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O217">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P217">
         <v>1.2</v>
@@ -35698,13 +35698,13 @@
         <v>1.07</v>
       </c>
       <c r="T217">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="U217">
         <v>1.7</v>
       </c>
       <c r="V217">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="W217">
         <v>1.36</v>
@@ -35716,19 +35716,19 @@
         <v>1.03</v>
       </c>
       <c r="Z217">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="AA217">
         <v>1.16</v>
       </c>
       <c r="AB217">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AC217">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AD217">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AE217">
         <v>1.73</v>
@@ -35737,7 +35737,7 @@
         <v>1.5</v>
       </c>
       <c r="AG217">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK217">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>5.91</v>
+        <v>5.87</v>
       </c>
       <c r="O220">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="P220">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q220">
         <v>5</v>
@@ -36184,10 +36184,10 @@
         <v>2.3</v>
       </c>
       <c r="S220">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T220">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="U220">
         <v>2.47</v>
@@ -36196,34 +36196,34 @@
         <v>1.47</v>
       </c>
       <c r="W220">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X220">
         <v>1.04</v>
       </c>
       <c r="Y220">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z220">
         <v>3.7</v>
       </c>
       <c r="AA220">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB220">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC220">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD220">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE220">
         <v>1.13</v>
       </c>
       <c r="AF220">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG220">
         <v>1.9</v>
@@ -36239,7 +36239,7 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>2.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK220">
         <v>1.15</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O221">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P221">
-        <v>5.88</v>
+        <v>5.93</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>7.85</v>
+        <v>6.5</v>
       </c>
       <c r="O225">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P225">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q225">
-        <v>7.93</v>
+        <v>6.5</v>
       </c>
       <c r="R225">
         <v>2.43</v>
       </c>
       <c r="S225">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T225">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="U225">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="V225">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W225">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X225">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y225">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z225">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AA225">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB225">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC225">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD225">
         <v>1.3</v>
       </c>
       <c r="AE225">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF225">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG225">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK225">
         <v>1.09</v>
@@ -37310,31 +37310,31 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O227">
         <v>3.2</v>
       </c>
       <c r="P227">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q227">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="R227">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S227">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T227">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U227">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="V227">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W227">
         <v>1.07</v>
@@ -37343,16 +37343,16 @@
         <v>1.03</v>
       </c>
       <c r="Y227">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z227">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA227">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AB227">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC227">
         <v>3.5</v>
@@ -37364,10 +37364,10 @@
         <v>1.05</v>
       </c>
       <c r="AF227">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG227">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK227">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37479,7 +37479,7 @@
         <v>3.1</v>
       </c>
       <c r="P228">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q228">
         <v>2.73</v>
@@ -37491,7 +37491,7 @@
         <v>1.4</v>
       </c>
       <c r="T228">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U228">
         <v>3.02</v>
@@ -37512,13 +37512,13 @@
         <v>2.92</v>
       </c>
       <c r="AA228">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB228">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC228">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD228">
         <v>1.2</v>
@@ -37530,7 +37530,7 @@
         <v>1.83</v>
       </c>
       <c r="AG228">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK228">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37799,19 +37799,19 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O230">
         <v>3.95</v>
       </c>
       <c r="P230">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q230">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R230">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S230">
         <v>1.2</v>
@@ -37823,7 +37823,7 @@
         <v>2.08</v>
       </c>
       <c r="V230">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W230">
         <v>1.17</v>
@@ -37832,16 +37832,16 @@
         <v>1.02</v>
       </c>
       <c r="Y230">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z230">
-        <v>5.93</v>
+        <v>6.01</v>
       </c>
       <c r="AA230">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB230">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC230">
         <v>2.1</v>
@@ -37850,10 +37850,10 @@
         <v>1.67</v>
       </c>
       <c r="AE230">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF230">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG230">
         <v>2.5</v>
@@ -37971,10 +37971,10 @@
         <v>1.95</v>
       </c>
       <c r="Q231">
-        <v>4</v>
+        <v>4.34</v>
       </c>
       <c r="R231">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S231">
         <v>1.44</v>
@@ -37983,31 +37983,31 @@
         <v>2.63</v>
       </c>
       <c r="U231">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V231">
         <v>1.29</v>
       </c>
       <c r="W231">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X231">
         <v>1.05</v>
       </c>
       <c r="Y231">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z231">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AA231">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB231">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC231">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AD231">
         <v>1.17</v>
@@ -38016,7 +38016,7 @@
         <v>1.03</v>
       </c>
       <c r="AF231">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG231">
         <v>1.74</v>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK231">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38134,16 +38134,16 @@
         <v>2.67</v>
       </c>
       <c r="Q232">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="R232">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S232">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T232">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U232">
         <v>2.77</v>
@@ -38152,10 +38152,10 @@
         <v>1.38</v>
       </c>
       <c r="W232">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X232">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y232">
         <v>1.25</v>
@@ -38167,22 +38167,22 @@
         <v>1.94</v>
       </c>
       <c r="AB232">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC232">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD232">
         <v>1.26</v>
       </c>
       <c r="AE232">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF232">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG232">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK232">
         <v>1.53</v>
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O233">
         <v>2.9</v>
       </c>
       <c r="P233">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q233">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="R233">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S233">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T233">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="U233">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V233">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W233">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X233">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y233">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z233">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="AA233">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AB233">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC233">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD233">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE233">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF233">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG233">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38451,16 +38451,16 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O234">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P234">
         <v>2.6</v>
       </c>
       <c r="Q234">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="R234">
         <v>2</v>
@@ -38478,16 +38478,16 @@
         <v>1.32</v>
       </c>
       <c r="W234">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X234">
         <v>1.04</v>
       </c>
       <c r="Y234">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z234">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA234">
         <v>2.15</v>
@@ -38496,19 +38496,19 @@
         <v>1.61</v>
       </c>
       <c r="AC234">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AD234">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE234">
         <v>1.03</v>
       </c>
       <c r="AF234">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG234">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>1.38</v>
       </c>
       <c r="AK234">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38623,7 +38623,7 @@
         <v>0</v>
       </c>
       <c r="Q235">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R235">
         <v>1.91</v>
@@ -38635,10 +38635,10 @@
         <v>2.26</v>
       </c>
       <c r="U235">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V235">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W235">
         <v>1.01</v>
@@ -38647,10 +38647,10 @@
         <v>1.06</v>
       </c>
       <c r="Y235">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Z235">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AA235">
         <v>2.56</v>
@@ -38659,7 +38659,7 @@
         <v>1.4</v>
       </c>
       <c r="AC235">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AD235">
         <v>1.1</v>
@@ -38668,10 +38668,10 @@
         <v>1.03</v>
       </c>
       <c r="AF235">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AG235">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK235">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38783,37 +38783,37 @@
         <v>3.6</v>
       </c>
       <c r="P236">
-        <v>4.88</v>
+        <v>4.72</v>
       </c>
       <c r="Q236">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R236">
         <v>2.15</v>
       </c>
       <c r="S236">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T236">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U236">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="V236">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W236">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X236">
         <v>1.05</v>
       </c>
       <c r="Y236">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z236">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA236">
         <v>2.16</v>
@@ -38825,13 +38825,13 @@
         <v>3.6</v>
       </c>
       <c r="AD236">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE236">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF236">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG236">
         <v>1.77</v>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK236">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38949,55 +38949,55 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="R237">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S237">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T237">
         <v>2.55</v>
       </c>
       <c r="U237">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V237">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W237">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X237">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y237">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="Z237">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AA237">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AB237">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC237">
-        <v>4.45</v>
+        <v>4.1</v>
       </c>
       <c r="AD237">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE237">
         <v>1.01</v>
       </c>
       <c r="AF237">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AG237">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O238">
         <v>2.95</v>
@@ -39115,19 +39115,19 @@
         <v>3.82</v>
       </c>
       <c r="R238">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S238">
         <v>1.45</v>
       </c>
       <c r="T238">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="U238">
         <v>3.3</v>
       </c>
       <c r="V238">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W238">
         <v>1.02</v>
@@ -39145,7 +39145,7 @@
         <v>2.29</v>
       </c>
       <c r="AB238">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC238">
         <v>4.15</v>
@@ -39157,10 +39157,10 @@
         <v>1.02</v>
       </c>
       <c r="AF238">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AG238">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AK238">
         <v>1.3</v>
@@ -39601,16 +39601,16 @@
         <v>4.25</v>
       </c>
       <c r="Q241">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="R241">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S241">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T241">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U241">
         <v>2.28</v>
@@ -39628,13 +39628,13 @@
         <v>1.17</v>
       </c>
       <c r="Z241">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AA241">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB241">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AC241">
         <v>2.55</v>
@@ -39643,7 +39643,7 @@
         <v>1.48</v>
       </c>
       <c r="AE241">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF241">
         <v>1.57</v>
@@ -39665,7 +39665,7 @@
         <v>1.18</v>
       </c>
       <c r="AK241">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="O244">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P244">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="Q244">
         <v>2.35</v>
@@ -40105,10 +40105,10 @@
         <v>3.2</v>
       </c>
       <c r="V244">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W244">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X244">
         <v>1.03</v>
@@ -40120,13 +40120,13 @@
         <v>2.8</v>
       </c>
       <c r="AA244">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AB244">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AC244">
-        <v>4.22</v>
+        <v>4.29</v>
       </c>
       <c r="AD244">
         <v>1.22</v>
@@ -40135,10 +40135,10 @@
         <v>1.04</v>
       </c>
       <c r="AF244">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG244">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK244">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="O245">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="P245">
-        <v>5.86</v>
+        <v>5.8</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40428,10 +40428,10 @@
         <v>2.2</v>
       </c>
       <c r="U246">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="V246">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W246">
         <v>1</v>
@@ -40449,13 +40449,13 @@
         <v>3</v>
       </c>
       <c r="AB246">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC246">
         <v>7</v>
       </c>
       <c r="AD246">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE246">
         <v>1.03</v>
@@ -40480,7 +40480,7 @@
         <v>1.45</v>
       </c>
       <c r="AK246">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O247">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="P247">
-        <v>9.449999999999999</v>
+        <v>11</v>
       </c>
       <c r="Q247">
         <v>1.65</v>
@@ -40585,49 +40585,49 @@
         <v>2.87</v>
       </c>
       <c r="S247">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T247">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="U247">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="V247">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W247">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X247">
         <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z247">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA247">
         <v>1.53</v>
       </c>
       <c r="AB247">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="AC247">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AD247">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE247">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF247">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG247">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK247">
-        <v>3.51</v>
+        <v>3.92</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O249">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P249">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41059,58 +41059,58 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O250">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P250">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Q250">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R250">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="S250">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T250">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U250">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V250">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W250">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X250">
         <v>1.02</v>
       </c>
       <c r="Y250">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z250">
         <v>5</v>
       </c>
       <c r="AA250">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB250">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC250">
         <v>2.23</v>
       </c>
       <c r="AD250">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE250">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF250">
         <v>1.8</v>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK250">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="O251">
         <v>3.4</v>
       </c>
       <c r="P251">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="Q251">
         <v>3</v>
@@ -41237,22 +41237,22 @@
         <v>2.2</v>
       </c>
       <c r="S251">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T251">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U251">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="V251">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W251">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X251">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y251">
         <v>1.2</v>
@@ -41261,25 +41261,25 @@
         <v>3.9</v>
       </c>
       <c r="AA251">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AB251">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC251">
         <v>3</v>
       </c>
       <c r="AD251">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE251">
         <v>1.09</v>
       </c>
       <c r="AF251">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG251">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41385,49 +41385,49 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q252">
-        <v>6.55</v>
+        <v>5.95</v>
       </c>
       <c r="R252">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="S252">
         <v>1.22</v>
       </c>
       <c r="T252">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="U252">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="V252">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W252">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X252">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y252">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z252">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA252">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB252">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC252">
         <v>2.48</v>
@@ -41439,10 +41439,10 @@
         <v>1.22</v>
       </c>
       <c r="AF252">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AG252">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK252">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O253">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="P253">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="O256">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="P256">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42366,13 +42366,13 @@
         <v>1.7</v>
       </c>
       <c r="O258">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P258">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q258">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="R258">
         <v>2.3</v>
@@ -42381,13 +42381,13 @@
         <v>1.32</v>
       </c>
       <c r="T258">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="U258">
         <v>2.5</v>
       </c>
       <c r="V258">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W258">
         <v>1.11</v>
@@ -42396,10 +42396,10 @@
         <v>1.04</v>
       </c>
       <c r="Y258">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z258">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AA258">
         <v>1.73</v>
@@ -42529,19 +42529,19 @@
         <v>1.85</v>
       </c>
       <c r="O259">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P259">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q259">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R259">
-        <v>2.39</v>
+        <v>2.16</v>
       </c>
       <c r="S259">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T259">
         <v>3.4</v>
@@ -42559,13 +42559,13 @@
         <v>1.02</v>
       </c>
       <c r="Y259">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z259">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA259">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB259">
         <v>1.82</v>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK259">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42689,55 +42689,55 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="O260">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P260">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
       </c>
       <c r="R260">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S260">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T260">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U260">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V260">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W260">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X260">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y260">
         <v>1.36</v>
       </c>
       <c r="Z260">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AA260">
         <v>2.17</v>
       </c>
       <c r="AB260">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC260">
         <v>4.1</v>
       </c>
       <c r="AD260">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE260">
         <v>1.03</v>
@@ -42762,7 +42762,7 @@
         <v>1.35</v>
       </c>
       <c r="AK260">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="O261">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="P261">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q261">
         <v>1.48</v>
@@ -42879,22 +42879,22 @@
         <v>1.6</v>
       </c>
       <c r="W261">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X261">
         <v>1.01</v>
       </c>
       <c r="Y261">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z261">
-        <v>5.08</v>
+        <v>4.8</v>
       </c>
       <c r="AA261">
         <v>1.48</v>
       </c>
       <c r="AB261">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AC261">
         <v>2.2</v>
@@ -42909,7 +42909,7 @@
         <v>2.3</v>
       </c>
       <c r="AG261">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK261">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O262">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P262">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O263">
         <v>3.25</v>
       </c>
       <c r="P263">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="O264">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="P264">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43676,7 +43676,7 @@
         <v>0</v>
       </c>
       <c r="Q266">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R266">
         <v>2</v>
@@ -43700,22 +43700,22 @@
         <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z266">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA266">
         <v>2.09</v>
       </c>
       <c r="AB266">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC266">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD266">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE266">
         <v>1.03</v>
@@ -43740,7 +43740,7 @@
         <v>1.3</v>
       </c>
       <c r="AK266">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44002,10 +44002,10 @@
         <v>0</v>
       </c>
       <c r="Q268">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="R268">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S268">
         <v>1.35</v>
@@ -44014,13 +44014,13 @@
         <v>2.82</v>
       </c>
       <c r="U268">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V268">
         <v>1.44</v>
       </c>
       <c r="W268">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X268">
         <v>1.04</v>
@@ -44035,13 +44035,13 @@
         <v>1.8</v>
       </c>
       <c r="AB268">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC268">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD268">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE268">
         <v>1.13</v>
@@ -44050,7 +44050,7 @@
         <v>1.62</v>
       </c>
       <c r="AG268">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O270">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P270">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q270">
         <v>2.53</v>
@@ -44337,7 +44337,7 @@
         <v>1.25</v>
       </c>
       <c r="T270">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U270">
         <v>2.25</v>
@@ -44370,13 +44370,13 @@
         <v>1.51</v>
       </c>
       <c r="AE270">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF270">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG270">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44654,55 +44654,55 @@
         <v>0</v>
       </c>
       <c r="Q272">
-        <v>7</v>
+        <v>7.65</v>
       </c>
       <c r="R272">
         <v>2.61</v>
       </c>
       <c r="S272">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T272">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U272">
         <v>2.2</v>
       </c>
       <c r="V272">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W272">
         <v>1.15</v>
       </c>
       <c r="X272">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y272">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z272">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA272">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB272">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC272">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AD272">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE272">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF272">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG272">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="AK272">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44980,7 +44980,7 @@
         <v>1.48</v>
       </c>
       <c r="Q274">
-        <v>5.74</v>
+        <v>5.68</v>
       </c>
       <c r="R274">
         <v>2.45</v>
@@ -44995,7 +44995,7 @@
         <v>2.23</v>
       </c>
       <c r="V274">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W274">
         <v>1.13</v>
@@ -45004,7 +45004,7 @@
         <v>1.03</v>
       </c>
       <c r="Y274">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z274">
         <v>4.75</v>
@@ -45022,13 +45022,13 @@
         <v>1.53</v>
       </c>
       <c r="AE274">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF274">
         <v>1.65</v>
       </c>
       <c r="AG274">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AK274">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45134,49 +45134,49 @@
         </is>
       </c>
       <c r="N275">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O275">
         <v>3.3</v>
       </c>
       <c r="P275">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q275">
         <v>4.4</v>
       </c>
       <c r="R275">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S275">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T275">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U275">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V275">
         <v>1.4</v>
       </c>
       <c r="W275">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X275">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y275">
         <v>1.29</v>
       </c>
       <c r="Z275">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA275">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB275">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC275">
         <v>3.2</v>
@@ -45188,7 +45188,7 @@
         <v>1.1</v>
       </c>
       <c r="AF275">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG275">
         <v>1.91</v>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AK275">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45297,7 +45297,7 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O276">
         <v>3.4</v>
@@ -45306,10 +45306,10 @@
         <v>4.2</v>
       </c>
       <c r="Q276">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="R276">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S276">
         <v>1.36</v>
@@ -45318,10 +45318,10 @@
         <v>2.88</v>
       </c>
       <c r="U276">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V276">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W276">
         <v>1.08</v>
@@ -45342,7 +45342,7 @@
         <v>1.75</v>
       </c>
       <c r="AC276">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD276">
         <v>1.26</v>
@@ -45623,7 +45623,7 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="O278">
         <v>4.2</v>
@@ -45635,19 +45635,19 @@
         <v>1.91</v>
       </c>
       <c r="R278">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S278">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T278">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U278">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="V278">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W278">
         <v>1.11</v>
@@ -45665,19 +45665,19 @@
         <v>1.65</v>
       </c>
       <c r="AB278">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AC278">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD278">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE278">
         <v>1.18</v>
       </c>
       <c r="AF278">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG278">
         <v>2</v>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK278">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45786,55 +45786,55 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O279">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P279">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q279">
-        <v>3.57</v>
+        <v>3.68</v>
       </c>
       <c r="R279">
         <v>2.26</v>
       </c>
       <c r="S279">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T279">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U279">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V279">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W279">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X279">
         <v>1.03</v>
       </c>
       <c r="Y279">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z279">
         <v>3.5</v>
       </c>
       <c r="AA279">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB279">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC279">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD279">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE279">
         <v>1.13</v>
@@ -46284,22 +46284,22 @@
         <v>2.9</v>
       </c>
       <c r="Q282">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R282">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S282">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T282">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U282">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V282">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W282">
         <v>1.02</v>
@@ -46320,7 +46320,7 @@
         <v>1.7</v>
       </c>
       <c r="AC282">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AD282">
         <v>1.22</v>
@@ -46348,7 +46348,7 @@
         <v>1.33</v>
       </c>
       <c r="AK282">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46444,25 +46444,25 @@
         <v>4.35</v>
       </c>
       <c r="P283">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q283">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="R283">
         <v>2.44</v>
       </c>
       <c r="S283">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T283">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U283">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V283">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W283">
         <v>1.11</v>
@@ -46471,31 +46471,31 @@
         <v>1</v>
       </c>
       <c r="Y283">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z283">
         <v>3.9</v>
       </c>
       <c r="AA283">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB283">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC283">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AD283">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE283">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF283">
         <v>1.83</v>
       </c>
       <c r="AG283">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK283">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46764,7 +46764,7 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="O285">
         <v>4.8</v>
@@ -46782,13 +46782,13 @@
         <v>1.25</v>
       </c>
       <c r="T285">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="U285">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V285">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W285">
         <v>1.14</v>
@@ -46797,19 +46797,19 @@
         <v>1.03</v>
       </c>
       <c r="Y285">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z285">
-        <v>5.02</v>
+        <v>5.51</v>
       </c>
       <c r="AA285">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AB285">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="AC285">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD285">
         <v>1.6</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O286">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P286">
-        <v>5.5</v>
+        <v>5.64</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -47090,10 +47090,10 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="O287">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="P287">
         <v>11</v>
@@ -47102,7 +47102,7 @@
         <v>1.43</v>
       </c>
       <c r="R287">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="S287">
         <v>1.1</v>
@@ -47111,10 +47111,10 @@
         <v>5.5</v>
       </c>
       <c r="U287">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V287">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="W287">
         <v>1.35</v>
@@ -47129,13 +47129,13 @@
         <v>12</v>
       </c>
       <c r="AA287">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AB287">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AC287">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AD287">
         <v>2.56</v>
@@ -47163,7 +47163,7 @@
         <v>1.08</v>
       </c>
       <c r="AK287">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47259,28 +47259,28 @@
         <v>3.8</v>
       </c>
       <c r="P288">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q288">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R288">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S288">
         <v>1.25</v>
       </c>
       <c r="T288">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="U288">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="V288">
         <v>1.62</v>
       </c>
       <c r="W288">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X288">
         <v>1.03</v>
@@ -47295,7 +47295,7 @@
         <v>1.57</v>
       </c>
       <c r="AB288">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="AC288">
         <v>2.34</v>
@@ -47310,7 +47310,7 @@
         <v>1.57</v>
       </c>
       <c r="AG288">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="O290">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="P290">
-        <v>3.35</v>
+        <v>5.9</v>
       </c>
       <c r="Q290">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="R290">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S290">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T290">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="U290">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="V290">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W290">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X290">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y290">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Z290">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA290">
-        <v>3.01</v>
+        <v>2.49</v>
       </c>
       <c r="AB290">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC290">
-        <v>6.23</v>
+        <v>5.1</v>
       </c>
       <c r="AD290">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AE290">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF290">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AG290">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AK290">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,80 +47742,80 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="O291">
+        <v>2.75</v>
+      </c>
+      <c r="P291">
         <v>3.35</v>
       </c>
-      <c r="P291">
-        <v>5.9</v>
-      </c>
       <c r="Q291">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="R291">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S291">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T291">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="U291">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="V291">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W291">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X291">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y291">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Z291">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AA291">
-        <v>2.49</v>
+        <v>3.01</v>
       </c>
       <c r="AB291">
+        <v>1.38</v>
+      </c>
+      <c r="AC291">
+        <v>6.23</v>
+      </c>
+      <c r="AD291">
+        <v>1.07</v>
+      </c>
+      <c r="AE291">
+        <v>1.03</v>
+      </c>
+      <c r="AF291">
+        <v>2.2</v>
+      </c>
+      <c r="AG291">
+        <v>1.62</v>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ291">
         <v>1.44</v>
       </c>
-      <c r="AC291">
-        <v>5.1</v>
-      </c>
-      <c r="AD291">
-        <v>1.15</v>
-      </c>
-      <c r="AE291">
-        <v>1.01</v>
-      </c>
-      <c r="AF291">
-        <v>2.38</v>
-      </c>
-      <c r="AG291">
-        <v>1.53</v>
-      </c>
-      <c r="AH291" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI291" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ291">
-        <v>1.11</v>
-      </c>
       <c r="AK291">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="O292">
         <v>5</v>
@@ -47914,52 +47914,52 @@
         <v>9.25</v>
       </c>
       <c r="Q292">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R292">
         <v>2.4</v>
       </c>
       <c r="S292">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T292">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U292">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V292">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W292">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X292">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y292">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z292">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AA292">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB292">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC292">
-        <v>2.72</v>
+        <v>2.93</v>
       </c>
       <c r="AD292">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE292">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF292">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG292">
         <v>1.6</v>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AK292">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48077,10 +48077,10 @@
         <v>2.21</v>
       </c>
       <c r="Q293">
-        <v>4.12</v>
+        <v>3.75</v>
       </c>
       <c r="R293">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S293">
         <v>1.44</v>
@@ -48089,13 +48089,13 @@
         <v>2.63</v>
       </c>
       <c r="U293">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V293">
         <v>1.29</v>
       </c>
       <c r="W293">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X293">
         <v>1.05</v>
@@ -48104,28 +48104,28 @@
         <v>1.4</v>
       </c>
       <c r="Z293">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AA293">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AB293">
         <v>1.53</v>
       </c>
       <c r="AC293">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD293">
         <v>1.17</v>
       </c>
       <c r="AE293">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF293">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG293">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48394,52 +48394,52 @@
         </is>
       </c>
       <c r="N295">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="O295">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="P295">
         <v>1.61</v>
       </c>
       <c r="Q295">
-        <v>5.76</v>
+        <v>5.35</v>
       </c>
       <c r="R295">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S295">
         <v>1.29</v>
       </c>
       <c r="T295">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U295">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V295">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W295">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X295">
         <v>1</v>
       </c>
       <c r="Y295">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z295">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="AA295">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AB295">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC295">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="AD295">
         <v>1.36</v>
@@ -48448,10 +48448,10 @@
         <v>1.13</v>
       </c>
       <c r="AF295">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG295">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK295">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -49535,31 +49535,31 @@
         </is>
       </c>
       <c r="N302">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O302">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="P302">
         <v>3.25</v>
       </c>
       <c r="Q302">
-        <v>2.66</v>
+        <v>3.09</v>
       </c>
       <c r="R302">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="S302">
         <v>1.44</v>
       </c>
       <c r="T302">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="U302">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="V302">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W302">
         <v>1.05</v>
@@ -49574,7 +49574,7 @@
         <v>2.57</v>
       </c>
       <c r="AA302">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB302">
         <v>1.6</v>
@@ -49861,10 +49861,10 @@
         </is>
       </c>
       <c r="N304">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O304">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P304">
         <v>2.31</v>
@@ -49879,37 +49879,37 @@
         <v>1.3</v>
       </c>
       <c r="T304">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U304">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V304">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W304">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X304">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y304">
         <v>1.2</v>
       </c>
       <c r="Z304">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA304">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB304">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC304">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AD304">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE304">
         <v>1.18</v>
@@ -49931,7 +49931,7 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK304">
         <v>1.4</v>
@@ -50033,19 +50033,19 @@
         <v>3.7</v>
       </c>
       <c r="Q305">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R305">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S305">
         <v>1.4</v>
       </c>
       <c r="T305">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U305">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="V305">
         <v>1.33</v>
@@ -50060,19 +50060,19 @@
         <v>1.36</v>
       </c>
       <c r="Z305">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AA305">
         <v>2.15</v>
       </c>
       <c r="AB305">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC305">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD305">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE305">
         <v>1.03</v>
@@ -50081,7 +50081,7 @@
         <v>1.93</v>
       </c>
       <c r="AG305">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>1.27</v>
       </c>
       <c r="AK305">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O306">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="P306">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q306">
-        <v>4.79</v>
+        <v>4.2</v>
       </c>
       <c r="R306">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="S306">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T306">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U306">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V306">
         <v>1.3</v>
       </c>
       <c r="W306">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X306">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y306">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z306">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AA306">
         <v>2.35</v>
       </c>
       <c r="AB306">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC306">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD306">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE306">
         <v>1.01</v>
       </c>
       <c r="AF306">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG306">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AK306">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50350,34 +50350,34 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O307">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P307">
         <v>3.1</v>
       </c>
       <c r="Q307">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="R307">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S307">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T307">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="U307">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="V307">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W307">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X307">
         <v>1.04</v>
@@ -50395,10 +50395,10 @@
         <v>1.5</v>
       </c>
       <c r="AC307">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AD307">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE307">
         <v>1.01</v>
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O310">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P310">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X310">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,10 +51002,10 @@
         </is>
       </c>
       <c r="N311">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O311">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P311">
         <v>1.48</v>
@@ -51014,16 +51014,16 @@
         <v>5</v>
       </c>
       <c r="R311">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S311">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T311">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U311">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V311">
         <v>1.48</v>
@@ -51035,28 +51035,28 @@
         <v>1.05</v>
       </c>
       <c r="Y311">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z311">
         <v>4.1</v>
       </c>
       <c r="AA311">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB311">
         <v>2</v>
       </c>
       <c r="AC311">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AD311">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE311">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF311">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG311">
         <v>1.87</v>
@@ -51072,7 +51072,7 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK311">
         <v>1.09</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -1815,10 +1815,10 @@
         <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB9">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC9">
         <v>3.42</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="R10">
         <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
         <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA10">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB10">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC10">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="AD10">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
         <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="U11">
         <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA11">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="R12">
         <v>2</v>
@@ -2295,7 +2295,7 @@
         <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
         <v>1.35</v>
@@ -2304,13 +2304,13 @@
         <v>2.76</v>
       </c>
       <c r="AA12">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AB12">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC12">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="AD12">
         <v>1.22</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AK14">
         <v>1.53</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>2.14</v>
+      </c>
+      <c r="R61">
+        <v>2.5</v>
+      </c>
+      <c r="S61">
+        <v>1.2</v>
+      </c>
+      <c r="T61">
+        <v>4</v>
+      </c>
+      <c r="U61">
+        <v>1.95</v>
+      </c>
+      <c r="V61">
+        <v>1.77</v>
+      </c>
+      <c r="W61">
+        <v>1.18</v>
+      </c>
+      <c r="X61">
+        <v>1.01</v>
+      </c>
+      <c r="Y61">
+        <v>1.07</v>
+      </c>
+      <c r="Z61">
+        <v>5.75</v>
+      </c>
+      <c r="AA61">
+        <v>1.4</v>
+      </c>
+      <c r="AB61">
         <v>2.87</v>
       </c>
-      <c r="Q61">
-        <v>2.4</v>
-      </c>
-      <c r="R61">
-        <v>2.45</v>
-      </c>
-      <c r="S61">
-        <v>1.22</v>
-      </c>
-      <c r="T61">
-        <v>3.8</v>
-      </c>
-      <c r="U61">
-        <v>2.2</v>
-      </c>
-      <c r="V61">
-        <v>1.63</v>
-      </c>
-      <c r="W61">
-        <v>1.17</v>
-      </c>
-      <c r="X61">
-        <v>1.02</v>
-      </c>
-      <c r="Y61">
-        <v>1.1</v>
-      </c>
-      <c r="Z61">
-        <v>5</v>
-      </c>
-      <c r="AA61">
-        <v>1.44</v>
-      </c>
-      <c r="AB61">
-        <v>2.5</v>
-      </c>
       <c r="AC61">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AD61">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AE61">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF61">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG61">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q62">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="R62">
+        <v>2.45</v>
+      </c>
+      <c r="S62">
+        <v>1.22</v>
+      </c>
+      <c r="T62">
+        <v>3.8</v>
+      </c>
+      <c r="U62">
+        <v>2.2</v>
+      </c>
+      <c r="V62">
+        <v>1.63</v>
+      </c>
+      <c r="W62">
+        <v>1.17</v>
+      </c>
+      <c r="X62">
+        <v>1.02</v>
+      </c>
+      <c r="Y62">
+        <v>1.1</v>
+      </c>
+      <c r="Z62">
+        <v>5</v>
+      </c>
+      <c r="AA62">
+        <v>1.44</v>
+      </c>
+      <c r="AB62">
         <v>2.5</v>
       </c>
-      <c r="S62">
-        <v>1.2</v>
-      </c>
-      <c r="T62">
-        <v>4</v>
-      </c>
-      <c r="U62">
-        <v>1.95</v>
-      </c>
-      <c r="V62">
-        <v>1.77</v>
-      </c>
-      <c r="W62">
-        <v>1.18</v>
-      </c>
-      <c r="X62">
-        <v>1.01</v>
-      </c>
-      <c r="Y62">
-        <v>1.07</v>
-      </c>
-      <c r="Z62">
-        <v>5.75</v>
-      </c>
-      <c r="AA62">
-        <v>1.4</v>
-      </c>
-      <c r="AB62">
-        <v>2.87</v>
-      </c>
       <c r="AC62">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AD62">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AE62">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF62">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG62">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK62">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="O72">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P72">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="Q72">
-        <v>2.53</v>
+        <v>3.19</v>
       </c>
       <c r="R72">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="S72">
         <v>1.44</v>
       </c>
       <c r="T72">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="U72">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V72">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W72">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X72">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z72">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA72">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB72">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC72">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD72">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE72">
         <v>1.03</v>
       </c>
       <c r="AF72">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AG72">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK72">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="O73">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="Q73">
-        <v>3.19</v>
+        <v>2.53</v>
       </c>
       <c r="R73">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="S73">
         <v>1.44</v>
       </c>
       <c r="T73">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="U73">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V73">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W73">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z73">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA73">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB73">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC73">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD73">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE73">
         <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AG73">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK73">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -13684,10 +13684,10 @@
         <v>4.05</v>
       </c>
       <c r="Q82">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S82">
         <v>1.34</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -1616,10 +1616,10 @@
         <v>2.75</v>
       </c>
       <c r="O8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O9">
         <v>2.95</v>
       </c>
       <c r="P9">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="Q9">
         <v>3.42</v>
@@ -1815,16 +1815,16 @@
         <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
         <v>3.42</v>
       </c>
       <c r="AD9">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE9">
         <v>1.04</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
         <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="U10">
         <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="AD10">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="R11">
         <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
         <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA11">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG11">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O13">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>2.95</v>
       </c>
       <c r="P16">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O17">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="P17">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>3.15</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R19">
         <v>2.26</v>
@@ -3439,10 +3439,10 @@
         <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="AA19">
         <v>1.56</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P31">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q31">
         <v>2.64</v>
@@ -5395,13 +5395,13 @@
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AA31">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB31">
         <v>1.65</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O32">
         <v>2.83</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB32">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5854,10 +5854,10 @@
         <v>1.75</v>
       </c>
       <c r="O34">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P34">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -7324,7 +7324,7 @@
         <v>3.25</v>
       </c>
       <c r="P43">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7662,7 +7662,7 @@
         <v>1.3</v>
       </c>
       <c r="T45">
-        <v>2.33</v>
+        <v>3.2</v>
       </c>
       <c r="U45">
         <v>2.75</v>
@@ -7671,7 +7671,7 @@
         <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
         <v>1.04</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="O54">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P54">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Q54">
-        <v>6.93</v>
+        <v>6.44</v>
       </c>
       <c r="R54">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
         <v>1.22</v>
@@ -9132,13 +9132,13 @@
         <v>3.75</v>
       </c>
       <c r="U54">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V54">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W54">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
         <v>1.01</v>
@@ -9147,7 +9147,7 @@
         <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="AA54">
         <v>1.5</v>
@@ -9156,19 +9156,19 @@
         <v>2.35</v>
       </c>
       <c r="AC54">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AD54">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE54">
         <v>1.24</v>
       </c>
       <c r="AF54">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG54">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AK54">
         <v>1.05</v>
@@ -11734,19 +11734,19 @@
         <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
         <v>3</v>
       </c>
       <c r="U70">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V70">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W70">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X70">
         <v>1.04</v>
@@ -13675,22 +13675,22 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="O82">
         <v>3.6</v>
       </c>
       <c r="P82">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="Q82">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R82">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S82">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T82">
         <v>2.79</v>
@@ -13702,7 +13702,7 @@
         <v>1.43</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X82">
         <v>1.05</v>
@@ -13729,7 +13729,7 @@
         <v>1.09</v>
       </c>
       <c r="AF82">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG82">
         <v>2</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA86">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB86">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14493,10 +14493,10 @@
         <v>2.45</v>
       </c>
       <c r="O87">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="P87">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q87">
         <v>2.7</v>
@@ -14508,7 +14508,7 @@
         <v>1.22</v>
       </c>
       <c r="T87">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U87">
         <v>2.17</v>
@@ -14523,7 +14523,7 @@
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z87">
         <v>5</v>
@@ -14535,7 +14535,7 @@
         <v>2.53</v>
       </c>
       <c r="AC87">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD87">
         <v>1.59</v>
@@ -14544,7 +14544,7 @@
         <v>1.19</v>
       </c>
       <c r="AF87">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AG87">
         <v>2.62</v>
@@ -28834,34 +28834,34 @@
         </is>
       </c>
       <c r="N175">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O175">
         <v>3.6</v>
       </c>
       <c r="P175">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q175">
-        <v>4.86</v>
+        <v>4.6</v>
       </c>
       <c r="R175">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S175">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T175">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="U175">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="V175">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W175">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X175">
         <v>1</v>
@@ -28873,25 +28873,25 @@
         <v>3.34</v>
       </c>
       <c r="AA175">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB175">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC175">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD175">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE175">
         <v>1.08</v>
       </c>
       <c r="AF175">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG175">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AK175">
         <v>1.16</v>
@@ -28997,25 +28997,25 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="O176">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P176">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q176">
         <v>2.3</v>
       </c>
       <c r="R176">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="S176">
         <v>1.28</v>
       </c>
       <c r="T176">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U176">
         <v>2.34</v>
@@ -29042,13 +29042,13 @@
         <v>2.07</v>
       </c>
       <c r="AC176">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="AD176">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE176">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF176">
         <v>1.65</v>
@@ -30962,13 +30962,13 @@
         <v>0</v>
       </c>
       <c r="Q188">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R188">
         <v>1.85</v>
       </c>
       <c r="S188">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T188">
         <v>2.36</v>
@@ -30980,7 +30980,7 @@
         <v>1.25</v>
       </c>
       <c r="W188">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X188">
         <v>1.06</v>
@@ -30992,7 +30992,7 @@
         <v>2.38</v>
       </c>
       <c r="AA188">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="AB188">
         <v>1.48</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O194">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P194">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -37319,22 +37319,22 @@
         <v>3.55</v>
       </c>
       <c r="Q227">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="R227">
         <v>2</v>
       </c>
       <c r="S227">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T227">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="U227">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V227">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W227">
         <v>1.07</v>
@@ -37364,10 +37364,10 @@
         <v>1.05</v>
       </c>
       <c r="AF227">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG227">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK227">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37482,22 +37482,22 @@
         <v>3.35</v>
       </c>
       <c r="Q228">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="R228">
         <v>1.97</v>
       </c>
       <c r="S228">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T228">
         <v>2.56</v>
       </c>
       <c r="U228">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="V228">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W228">
         <v>1.07</v>
@@ -37530,7 +37530,7 @@
         <v>1.83</v>
       </c>
       <c r="AG228">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK228">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -42040,10 +42040,10 @@
         <v>2.1</v>
       </c>
       <c r="O256">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P256">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42076,10 +42076,10 @@
         <v>0</v>
       </c>
       <c r="AA256">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB256">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AC256">
         <v>0</v>
@@ -43018,10 +43018,10 @@
         <v>1.92</v>
       </c>
       <c r="O262">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P262">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43344,10 +43344,10 @@
         <v>2.15</v>
       </c>
       <c r="O264">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="P264">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43380,10 +43380,10 @@
         <v>0</v>
       </c>
       <c r="AA264">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB264">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC264">
         <v>0</v>
@@ -46930,10 +46930,10 @@
         <v>1.6</v>
       </c>
       <c r="O286">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="P286">
-        <v>5.64</v>
+        <v>5</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -50519,7 +50519,7 @@
         <v>2.95</v>
       </c>
       <c r="P308">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q308">
         <v>2.8</v>
@@ -50546,10 +50546,10 @@
         <v>1.08</v>
       </c>
       <c r="Y308">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z308">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AA308">
         <v>2.72</v>
@@ -50561,7 +50561,7 @@
         <v>5.1</v>
       </c>
       <c r="AD308">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE308">
         <v>1.02</v>
@@ -51820,10 +51820,10 @@
         <v>1.67</v>
       </c>
       <c r="O316">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P316">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q316">
         <v>2.3</v>
@@ -51835,16 +51835,16 @@
         <v>1.5</v>
       </c>
       <c r="T316">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U316">
         <v>3.3</v>
       </c>
       <c r="V316">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W316">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X316">
         <v>1.07</v>
@@ -51856,7 +51856,7 @@
         <v>2.6</v>
       </c>
       <c r="AA316">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB316">
         <v>1.54</v>
@@ -51865,7 +51865,7 @@
         <v>4.8</v>
       </c>
       <c r="AD316">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE316">
         <v>1.03</v>
@@ -51874,7 +51874,7 @@
         <v>2.1</v>
       </c>
       <c r="AG316">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -52469,13 +52469,13 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O320">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P320">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="Q320">
         <v>2.27</v>
@@ -52484,7 +52484,7 @@
         <v>2.44</v>
       </c>
       <c r="S320">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T320">
         <v>3.75</v>
@@ -52505,19 +52505,19 @@
         <v>1.14</v>
       </c>
       <c r="Z320">
-        <v>5.75</v>
+        <v>5.58</v>
       </c>
       <c r="AA320">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB320">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AC320">
         <v>2.2</v>
       </c>
       <c r="AD320">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE320">
         <v>1.25</v>
@@ -52632,13 +52632,13 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O321">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P321">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="Q321">
         <v>2.3</v>
@@ -52647,7 +52647,7 @@
         <v>2.1</v>
       </c>
       <c r="S321">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T321">
         <v>2.56</v>
@@ -52665,10 +52665,10 @@
         <v>1.04</v>
       </c>
       <c r="Y321">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z321">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA321">
         <v>2.25</v>
@@ -52677,7 +52677,7 @@
         <v>1.61</v>
       </c>
       <c r="AC321">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="AD321">
         <v>1.24</v>
@@ -52795,7 +52795,7 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O322">
         <v>3.4</v>
@@ -52846,7 +52846,7 @@
         <v>1.19</v>
       </c>
       <c r="AE322">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF322">
         <v>2.16</v>
@@ -53121,7 +53121,7 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O324">
         <v>5.6</v>
@@ -54099,10 +54099,10 @@
         </is>
       </c>
       <c r="N330">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O330">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P330">
         <v>2.37</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P6">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="Q6">
         <v>2.45</v>
@@ -1302,13 +1302,13 @@
         <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
         <v>1.53</v>
@@ -1323,22 +1323,22 @@
         <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA6">
         <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD6">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
         <v>1.5</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q7">
         <v>3.02</v>
@@ -1471,13 +1471,13 @@
         <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="V7">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
         <v>1.03</v>
@@ -1498,13 +1498,13 @@
         <v>2.38</v>
       </c>
       <c r="AD7">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE7">
         <v>1.2</v>
       </c>
       <c r="AF7">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG7">
         <v>2.5</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1788,10 +1788,10 @@
         <v>3.42</v>
       </c>
       <c r="R9">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
         <v>2.88</v>
@@ -1815,10 +1815,10 @@
         <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB9">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC9">
         <v>3.42</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="R10">
         <v>2.2</v>
@@ -1975,7 +1975,7 @@
         <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA10">
         <v>1.95</v>
@@ -2012,7 +2012,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         <v>2.8</v>
       </c>
       <c r="Q11">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="R11">
         <v>2.2</v>
@@ -2156,7 +2156,7 @@
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
         <v>2</v>
@@ -2274,7 +2274,7 @@
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="R12">
         <v>2</v>
@@ -2283,7 +2283,7 @@
         <v>1.44</v>
       </c>
       <c r="T12">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -2609,7 +2609,7 @@
         <v>1.36</v>
       </c>
       <c r="T14">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="U14">
         <v>2.75</v>
@@ -2636,7 +2636,7 @@
         <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="AD14">
         <v>1.33</v>
@@ -2648,7 +2648,7 @@
         <v>1.74</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AK14">
         <v>1.53</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="O19">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
         <v>2.26</v>
@@ -3427,7 +3427,7 @@
         <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V19">
         <v>1.57</v>
@@ -3735,13 +3735,13 @@
         <v>2.6</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P21">
         <v>2.51</v>
       </c>
       <c r="Q21">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
         <v>1.89</v>
@@ -3750,7 +3750,7 @@
         <v>1.49</v>
       </c>
       <c r="T21">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U21">
         <v>3.18</v>
@@ -3759,7 +3759,7 @@
         <v>1.28</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
         <v>1.05</v>
@@ -3774,16 +3774,16 @@
         <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC21">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AD21">
         <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
         <v>1.85</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3910,7 +3910,7 @@
         <v>2</v>
       </c>
       <c r="S22">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
         <v>2.6</v>
@@ -3919,28 +3919,28 @@
         <v>3.2</v>
       </c>
       <c r="V22">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AA22">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
         <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AD22">
         <v>1.19</v>
@@ -3949,7 +3949,7 @@
         <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
         <v>1.83</v>
@@ -3968,7 +3968,7 @@
         <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,25 +4547,25 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q26">
         <v>3.89</v>
       </c>
       <c r="R26">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T26">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U26">
         <v>3</v>
@@ -4595,7 +4595,7 @@
         <v>4</v>
       </c>
       <c r="AD26">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE26">
         <v>1.02</v>
@@ -4876,10 +4876,10 @@
         <v>5</v>
       </c>
       <c r="O28">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5039,10 +5039,10 @@
         <v>2.25</v>
       </c>
       <c r="O29">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="P29">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="O41">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P41">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="Q41">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="R41">
         <v>2.24</v>
@@ -7155,22 +7155,22 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="O42">
         <v>3.74</v>
       </c>
       <c r="P42">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="Q42">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R42">
         <v>2.38</v>
       </c>
       <c r="S42">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
         <v>3.6</v>
@@ -7182,13 +7182,13 @@
         <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
         <v>4.6</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7686,7 +7686,7 @@
         <v>1.75</v>
       </c>
       <c r="AB45">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC45">
         <v>2.9</v>
@@ -8465,10 +8465,10 @@
         <v>3.4</v>
       </c>
       <c r="P50">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R50">
         <v>2.25</v>
@@ -8477,13 +8477,13 @@
         <v>1.33</v>
       </c>
       <c r="T50">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
         <v>1.11</v>
@@ -8498,7 +8498,7 @@
         <v>3.8</v>
       </c>
       <c r="AA50">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
         <v>2</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O53">
         <v>3.45</v>
       </c>
       <c r="P53">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q53">
-        <v>3.92</v>
+        <v>3.37</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8978,34 +8978,34 @@
         <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
         <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB53">
         <v>2</v>
       </c>
       <c r="AC53">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE53">
         <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="O54">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P54">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Q54">
-        <v>6.44</v>
+        <v>8</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S54">
         <v>1.22</v>
@@ -9132,13 +9132,13 @@
         <v>3.75</v>
       </c>
       <c r="U54">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="V54">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X54">
         <v>1.01</v>
@@ -9147,28 +9147,28 @@
         <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="AA54">
         <v>1.5</v>
       </c>
       <c r="AB54">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC54">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD54">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE54">
         <v>1.24</v>
       </c>
       <c r="AF54">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG54">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="AK54">
         <v>1.05</v>
@@ -9283,16 +9283,16 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>5.07</v>
+        <v>5.32</v>
       </c>
       <c r="R55">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T55">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="U55">
         <v>2.75</v>
@@ -9301,37 +9301,37 @@
         <v>1.4</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AA55">
         <v>1.68</v>
       </c>
       <c r="AB55">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC55">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD55">
         <v>1.35</v>
       </c>
       <c r="AE55">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF55">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG55">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="AK55">
         <v>1.11</v>
@@ -9612,7 +9612,7 @@
         <v>2.88</v>
       </c>
       <c r="R57">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S57">
         <v>1.3</v>
@@ -9645,19 +9645,19 @@
         <v>2</v>
       </c>
       <c r="AC57">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD57">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE57">
         <v>1.13</v>
       </c>
       <c r="AF57">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG57">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O59">
         <v>3.35</v>
       </c>
       <c r="P59">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q59">
         <v>2.81</v>
@@ -9944,7 +9944,7 @@
         <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U59">
         <v>2.25</v>
@@ -9959,7 +9959,7 @@
         <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z59">
         <v>4.5</v>
@@ -10089,31 +10089,31 @@
         </is>
       </c>
       <c r="N60">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O60">
         <v>3.68</v>
       </c>
       <c r="P60">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="Q60">
-        <v>3.64</v>
+        <v>3.73</v>
       </c>
       <c r="R60">
         <v>2.45</v>
       </c>
       <c r="S60">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T60">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U60">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V60">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W60">
         <v>1.12</v>
@@ -10122,31 +10122,31 @@
         <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>5.08</v>
+        <v>4.6</v>
       </c>
       <c r="AA60">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AB60">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AC60">
         <v>2.5</v>
       </c>
       <c r="AD60">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE60">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF60">
         <v>1.5</v>
       </c>
       <c r="AG60">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R61">
         <v>2.5</v>
@@ -10279,13 +10279,13 @@
         <v>1.77</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z61">
         <v>5.75</v>
@@ -10294,10 +10294,10 @@
         <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.87</v>
+        <v>3.11</v>
       </c>
       <c r="AC61">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AD61">
         <v>1.82</v>
@@ -10306,7 +10306,7 @@
         <v>1.25</v>
       </c>
       <c r="AF61">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG61">
         <v>2.7</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK61">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10421,7 +10421,7 @@
         <v>3.75</v>
       </c>
       <c r="P62">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -10430,16 +10430,16 @@
         <v>2.45</v>
       </c>
       <c r="S62">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V62">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
         <v>1.17</v>
@@ -10451,28 +10451,28 @@
         <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AA62">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB62">
         <v>2.5</v>
       </c>
       <c r="AC62">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AD62">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE62">
         <v>1.24</v>
       </c>
       <c r="AF62">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG62">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10904,25 +10904,25 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="O65">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="Q65">
         <v>2.54</v>
       </c>
       <c r="R65">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S65">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T65">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="U65">
         <v>3.38</v>
@@ -10943,13 +10943,13 @@
         <v>2.73</v>
       </c>
       <c r="AA65">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AB65">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC65">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="AD65">
         <v>1.17</v>
@@ -10958,7 +10958,7 @@
         <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AG65">
         <v>1.75</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK65">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11559,10 +11559,10 @@
         <v>1.27</v>
       </c>
       <c r="O69">
-        <v>6.12</v>
+        <v>6.05</v>
       </c>
       <c r="P69">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11773,10 +11773,10 @@
         <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG70">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>2.6</v>
       </c>
       <c r="Q71">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="R71">
         <v>2.38</v>
@@ -11903,13 +11903,13 @@
         <v>3.9</v>
       </c>
       <c r="U71">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V71">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X71">
         <v>1.02</v>
@@ -11927,16 +11927,16 @@
         <v>2.63</v>
       </c>
       <c r="AC71">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AD71">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE71">
         <v>1.29</v>
       </c>
       <c r="AF71">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG71">
         <v>2.9</v>
@@ -12051,7 +12051,7 @@
         <v>3.15</v>
       </c>
       <c r="P72">
-        <v>3.56</v>
+        <v>2.71</v>
       </c>
       <c r="Q72">
         <v>3.19</v>
@@ -12102,7 +12102,7 @@
         <v>1.84</v>
       </c>
       <c r="AG72">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.34</v>
       </c>
       <c r="AK72">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12244,7 +12244,7 @@
         <v>1.35</v>
       </c>
       <c r="Z73">
-        <v>2.74</v>
+        <v>2.93</v>
       </c>
       <c r="AA73">
         <v>2.17</v>
@@ -12256,7 +12256,7 @@
         <v>3.75</v>
       </c>
       <c r="AD73">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE73">
         <v>1.03</v>
@@ -12371,28 +12371,28 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P74">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q74">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="R74">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S74">
         <v>1.43</v>
       </c>
       <c r="T74">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="U74">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V74">
         <v>1.33</v>
@@ -12401,7 +12401,7 @@
         <v>1.03</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
         <v>1.36</v>
@@ -12697,16 +12697,16 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O76">
         <v>3.7</v>
       </c>
       <c r="P76">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="Q76">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="R76">
         <v>2.1</v>
@@ -12718,16 +12718,16 @@
         <v>2.85</v>
       </c>
       <c r="U76">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V76">
         <v>1.36</v>
       </c>
       <c r="W76">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y76">
         <v>1.3</v>
@@ -12736,19 +12736,19 @@
         <v>3.28</v>
       </c>
       <c r="AA76">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AB76">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC76">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD76">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF76">
         <v>1.91</v>
@@ -13192,25 +13192,25 @@
         <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="Q79">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="R79">
         <v>2</v>
       </c>
       <c r="S79">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T79">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U79">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V79">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W79">
         <v>1.05</v>
@@ -13243,7 +13243,7 @@
         <v>1.75</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O80">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P80">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="Q80">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R80">
         <v>2.4</v>
@@ -13382,10 +13382,10 @@
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z80">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="AA80">
         <v>1.5</v>
@@ -13394,7 +13394,7 @@
         <v>2.55</v>
       </c>
       <c r="AC80">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD80">
         <v>1.62</v>
@@ -13403,7 +13403,7 @@
         <v>1.24</v>
       </c>
       <c r="AF80">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG80">
         <v>2.45</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,34 +13512,34 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O81">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P81">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q81">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R81">
         <v>2.38</v>
       </c>
       <c r="S81">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T81">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U81">
         <v>2.2</v>
       </c>
       <c r="V81">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W81">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
         <v>1.04</v>
@@ -13551,7 +13551,7 @@
         <v>4.8</v>
       </c>
       <c r="AA81">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB81">
         <v>2.23</v>
@@ -13566,7 +13566,7 @@
         <v>1.18</v>
       </c>
       <c r="AF81">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG81">
         <v>2.25</v>
@@ -13585,7 +13585,7 @@
         <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,10 +13684,10 @@
         <v>4.1</v>
       </c>
       <c r="Q82">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R82">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S82">
         <v>1.35</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -14167,10 +14167,10 @@
         <v>2.1</v>
       </c>
       <c r="O85">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P85">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="Q85">
         <v>2.8</v>
@@ -14179,25 +14179,25 @@
         <v>1.96</v>
       </c>
       <c r="S85">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T85">
         <v>2.75</v>
       </c>
       <c r="U85">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="V85">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W85">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
         <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z85">
         <v>2.88</v>
@@ -14209,7 +14209,7 @@
         <v>1.64</v>
       </c>
       <c r="AC85">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AD85">
         <v>1.19</v>
@@ -14218,7 +14218,7 @@
         <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG85">
         <v>1.83</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
         <v>1.62</v>
@@ -14336,7 +14336,7 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>6.29</v>
+        <v>5.9</v>
       </c>
       <c r="R86">
         <v>2.05</v>
@@ -14348,13 +14348,13 @@
         <v>2.9</v>
       </c>
       <c r="U86">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V86">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W86">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X86">
         <v>1.02</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AK86">
         <v>1.08</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O87">
         <v>3.85</v>
       </c>
       <c r="P87">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q87">
         <v>2.7</v>
@@ -14532,22 +14532,22 @@
         <v>1.53</v>
       </c>
       <c r="AB87">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AC87">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD87">
         <v>1.59</v>
       </c>
       <c r="AE87">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF87">
         <v>1.42</v>
       </c>
       <c r="AG87">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O89">
         <v>3.4</v>
@@ -14837,7 +14837,7 @@
         <v>2.95</v>
       </c>
       <c r="U89">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="V89">
         <v>1.49</v>
@@ -14867,13 +14867,13 @@
         <v>1.42</v>
       </c>
       <c r="AE89">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF89">
         <v>1.57</v>
       </c>
       <c r="AG89">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>3.4</v>
       </c>
       <c r="P90">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q90">
         <v>2.4</v>
@@ -15006,7 +15006,7 @@
         <v>1.48</v>
       </c>
       <c r="W90">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X90">
         <v>1.05</v>
@@ -15142,22 +15142,22 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="O91">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P91">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="Q91">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R91">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="S91">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="T91">
         <v>3.65</v>
@@ -15166,10 +15166,10 @@
         <v>2.09</v>
       </c>
       <c r="V91">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W91">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X91">
         <v>1.01</v>
@@ -15181,19 +15181,19 @@
         <v>6</v>
       </c>
       <c r="AA91">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB91">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="AC91">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AD91">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AE91">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF91">
         <v>1.44</v>
@@ -15326,7 +15326,7 @@
         <v>3.3</v>
       </c>
       <c r="U92">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V92">
         <v>1.55</v>
@@ -15646,19 +15646,19 @@
         <v>2</v>
       </c>
       <c r="S94">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T94">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="U94">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="V94">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W94">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X94">
         <v>1.06</v>
@@ -15667,16 +15667,16 @@
         <v>1.36</v>
       </c>
       <c r="Z94">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA94">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB94">
         <v>1.7</v>
       </c>
       <c r="AC94">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AD94">
         <v>1.2</v>
@@ -15685,7 +15685,7 @@
         <v>1.06</v>
       </c>
       <c r="AF94">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG94">
         <v>1.75</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O95">
         <v>3.2</v>
       </c>
       <c r="P95">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -15812,7 +15812,7 @@
         <v>1.4</v>
       </c>
       <c r="T95">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="U95">
         <v>3</v>
@@ -15824,7 +15824,7 @@
         <v>1.06</v>
       </c>
       <c r="X95">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y95">
         <v>1.33</v>
@@ -15839,13 +15839,13 @@
         <v>1.67</v>
       </c>
       <c r="AC95">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="AD95">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE95">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF95">
         <v>1.91</v>
@@ -16159,7 +16159,7 @@
         <v>2.45</v>
       </c>
       <c r="AA97">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AB97">
         <v>1.44</v>
@@ -16298,16 +16298,16 @@
         <v>1.85</v>
       </c>
       <c r="S98">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="T98">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="U98">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="V98">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W98">
         <v>1.03</v>
@@ -16446,10 +16446,10 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O99">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="P99">
         <v>6.9</v>
@@ -16458,7 +16458,7 @@
         <v>1.83</v>
       </c>
       <c r="R99">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S99">
         <v>1.29</v>
@@ -16479,25 +16479,25 @@
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z99">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA99">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB99">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC99">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="AD99">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE99">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF99">
         <v>1.87</v>
@@ -16609,7 +16609,7 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O100">
         <v>3.15</v>
@@ -16624,10 +16624,10 @@
         <v>2.05</v>
       </c>
       <c r="S100">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T100">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U100">
         <v>3.2</v>
@@ -16636,7 +16636,7 @@
         <v>1.3</v>
       </c>
       <c r="W100">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
         <v>1.05</v>
@@ -16651,7 +16651,7 @@
         <v>2.2</v>
       </c>
       <c r="AB100">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC100">
         <v>3.91</v>
@@ -16666,7 +16666,7 @@
         <v>1.85</v>
       </c>
       <c r="AG100">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>2.2</v>
       </c>
       <c r="S101">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T101">
         <v>2.82</v>
@@ -16796,10 +16796,10 @@
         <v>2.5</v>
       </c>
       <c r="V101">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W101">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X101">
         <v>1.05</v>
@@ -16950,19 +16950,19 @@
         <v>2.02</v>
       </c>
       <c r="S102">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T102">
         <v>2.66</v>
       </c>
       <c r="U102">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W102">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
         <v>1.06</v>
@@ -16989,10 +16989,10 @@
         <v>1.08</v>
       </c>
       <c r="AF102">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG102">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK102">
         <v>1.25</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O103">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="P103">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="Q103">
         <v>2.05</v>
@@ -17131,31 +17131,31 @@
         <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z103">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="AA103">
         <v>1.64</v>
       </c>
       <c r="AB103">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC103">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD103">
         <v>1.36</v>
       </c>
       <c r="AE103">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF103">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O104">
         <v>4</v>
@@ -17270,10 +17270,10 @@
         <v>5</v>
       </c>
       <c r="Q104">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R104">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="S104">
         <v>1.25</v>
@@ -17297,7 +17297,7 @@
         <v>1.18</v>
       </c>
       <c r="Z104">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="AA104">
         <v>1.6</v>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK104">
         <v>2.52</v>
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17925,16 +17925,16 @@
         <v>2.5</v>
       </c>
       <c r="R108">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S108">
         <v>1.5</v>
       </c>
       <c r="T108">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U108">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V108">
         <v>1.25</v>
@@ -17961,10 +17961,10 @@
         <v>5</v>
       </c>
       <c r="AD108">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE108">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF108">
         <v>2.1</v>
@@ -17986,7 +17986,7 @@
         <v>1.33</v>
       </c>
       <c r="AK108">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18085,25 +18085,25 @@
         <v>2.62</v>
       </c>
       <c r="Q109">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R109">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="S109">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T109">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="U109">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V109">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W109">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X109">
         <v>1.1</v>
@@ -18112,10 +18112,10 @@
         <v>1.44</v>
       </c>
       <c r="Z109">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AA109">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB109">
         <v>1.5</v>
@@ -18124,13 +18124,13 @@
         <v>4.75</v>
       </c>
       <c r="AD109">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE109">
         <v>1.04</v>
       </c>
       <c r="AF109">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG109">
         <v>1.73</v>
@@ -18149,7 +18149,7 @@
         <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18257,13 +18257,13 @@
         <v>1.4</v>
       </c>
       <c r="T110">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U110">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W110">
         <v>1.06</v>
@@ -18278,22 +18278,22 @@
         <v>2.9</v>
       </c>
       <c r="AA110">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB110">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC110">
         <v>3.8</v>
       </c>
       <c r="AD110">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE110">
         <v>1.06</v>
       </c>
       <c r="AF110">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG110">
         <v>1.83</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18408,7 +18408,7 @@
         <v>2.87</v>
       </c>
       <c r="P111">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -18426,10 +18426,10 @@
         <v>3.25</v>
       </c>
       <c r="V111">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W111">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X111">
         <v>1.11</v>
@@ -18456,7 +18456,7 @@
         <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG111">
         <v>1.7</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O112">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P112">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="Q112">
         <v>2.98</v>
@@ -18598,16 +18598,16 @@
         <v>1.06</v>
       </c>
       <c r="Y112">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z112">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AA112">
         <v>2.3</v>
       </c>
       <c r="AB112">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC112">
         <v>4.25</v>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AK112">
         <v>1.5</v>
@@ -18731,13 +18731,13 @@
         <v>2.74</v>
       </c>
       <c r="O113">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P113">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="Q113">
-        <v>3.44</v>
+        <v>2.93</v>
       </c>
       <c r="R113">
         <v>2.02</v>
@@ -18746,7 +18746,7 @@
         <v>1.42</v>
       </c>
       <c r="T113">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U113">
         <v>2.99</v>
@@ -18770,22 +18770,22 @@
         <v>2.09</v>
       </c>
       <c r="AB113">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC113">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AD113">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE113">
         <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG113">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AK113">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,25 +18891,25 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O114">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P114">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q114">
         <v>1.75</v>
       </c>
       <c r="R114">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="S114">
         <v>1.21</v>
       </c>
       <c r="T114">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U114">
         <v>2.13</v>
@@ -18918,7 +18918,7 @@
         <v>1.74</v>
       </c>
       <c r="W114">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X114">
         <v>1.01</v>
@@ -18930,16 +18930,16 @@
         <v>6.25</v>
       </c>
       <c r="AA114">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB114">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AC114">
         <v>2.07</v>
       </c>
       <c r="AD114">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE114">
         <v>1.33</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK114">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19226,16 +19226,16 @@
         <v>0</v>
       </c>
       <c r="Q116">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="R116">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="S116">
         <v>1.08</v>
       </c>
       <c r="T116">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="U116">
         <v>1.57</v>
@@ -19256,25 +19256,25 @@
         <v>10</v>
       </c>
       <c r="AA116">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AB116">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AC116">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AD116">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AE116">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF116">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AG116">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK116">
         <v>13</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O117">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P117">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q117">
         <v>2.9</v>
@@ -19395,19 +19395,19 @@
         <v>1.99</v>
       </c>
       <c r="S117">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T117">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U117">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V117">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X117">
         <v>1.06</v>
@@ -19555,7 +19555,7 @@
         <v>3.9</v>
       </c>
       <c r="R118">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="S118">
         <v>1.45</v>
@@ -19576,7 +19576,7 @@
         <v>1.05</v>
       </c>
       <c r="Y118">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z118">
         <v>2.6</v>
@@ -19588,19 +19588,19 @@
         <v>1.51</v>
       </c>
       <c r="AC118">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD118">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE118">
         <v>1</v>
       </c>
       <c r="AF118">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG118">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>1.33</v>
       </c>
       <c r="AK118">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q132">
         <v>2.63</v>
@@ -21840,10 +21840,10 @@
         <v>2.2</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U132">
         <v>2.4</v>
@@ -21852,10 +21852,10 @@
         <v>1.43</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
         <v>1.18</v>
@@ -21876,7 +21876,7 @@
         <v>1.32</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF132">
         <v>1.53</v>
@@ -22024,13 +22024,13 @@
         <v>1.26</v>
       </c>
       <c r="Z133">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA133">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB133">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC133">
         <v>3.3</v>
@@ -22154,16 +22154,16 @@
         <v>2.07</v>
       </c>
       <c r="O134">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P134">
         <v>3.55</v>
       </c>
       <c r="Q134">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="R134">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S134">
         <v>1.51</v>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AK134">
         <v>1.6</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O135">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P135">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q135">
         <v>2.17</v>
@@ -22329,10 +22329,10 @@
         <v>2.08</v>
       </c>
       <c r="S135">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T135">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U135">
         <v>2.9</v>
@@ -22371,7 +22371,7 @@
         <v>1.89</v>
       </c>
       <c r="AG135">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O149">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P149">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -24611,7 +24611,7 @@
         <v>2.14</v>
       </c>
       <c r="S149">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T149">
         <v>3.04</v>
@@ -24632,7 +24632,7 @@
         <v>1.27</v>
       </c>
       <c r="Z149">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA149">
         <v>1.84</v>
@@ -24669,7 +24669,7 @@
         <v>1.11</v>
       </c>
       <c r="AK149">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="O151">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P151">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -24937,10 +24937,10 @@
         <v>2.1</v>
       </c>
       <c r="S151">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T151">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U151">
         <v>3</v>
@@ -24949,31 +24949,31 @@
         <v>1.33</v>
       </c>
       <c r="W151">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X151">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y151">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z151">
         <v>3</v>
       </c>
       <c r="AA151">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AB151">
         <v>1.73</v>
       </c>
       <c r="AC151">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD151">
         <v>1.25</v>
       </c>
       <c r="AE151">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF151">
         <v>1.83</v>
@@ -25100,13 +25100,13 @@
         <v>2.1</v>
       </c>
       <c r="S152">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T152">
         <v>3</v>
       </c>
       <c r="U152">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V152">
         <v>1.4</v>
@@ -25139,7 +25139,7 @@
         <v>1.11</v>
       </c>
       <c r="AF152">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG152">
         <v>2</v>
@@ -25257,7 +25257,7 @@
         <v>0</v>
       </c>
       <c r="Q153">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="R153">
         <v>2.3</v>
@@ -25266,7 +25266,7 @@
         <v>1.28</v>
       </c>
       <c r="T153">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U153">
         <v>2.38</v>
@@ -25290,7 +25290,7 @@
         <v>1.67</v>
       </c>
       <c r="AB153">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC153">
         <v>2.62</v>
@@ -25302,10 +25302,10 @@
         <v>1.12</v>
       </c>
       <c r="AF153">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG153">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK153">
         <v>1.62</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="O154">
         <v>3.4</v>
       </c>
       <c r="P154">
-        <v>3.04</v>
+        <v>2.87</v>
       </c>
       <c r="Q154">
         <v>2.63</v>
@@ -25432,7 +25432,7 @@
         <v>3.6</v>
       </c>
       <c r="U154">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V154">
         <v>1.5</v>
@@ -25450,22 +25450,22 @@
         <v>4.5</v>
       </c>
       <c r="AA154">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB154">
         <v>2.1</v>
       </c>
       <c r="AC154">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AD154">
         <v>1.44</v>
       </c>
       <c r="AE154">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF154">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG154">
         <v>2.35</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O159">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P159">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="Q159">
         <v>2.3</v>
@@ -26247,16 +26247,16 @@
         <v>3.2</v>
       </c>
       <c r="U159">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V159">
         <v>1.44</v>
       </c>
       <c r="W159">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X159">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y159">
         <v>1.22</v>
@@ -26274,16 +26274,16 @@
         <v>2.75</v>
       </c>
       <c r="AD159">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE159">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF159">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG159">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>1.22</v>
       </c>
       <c r="AK159">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26389,7 +26389,7 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O160">
         <v>3.15</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O161">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P161">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q161">
         <v>2.94</v>
@@ -26570,13 +26570,13 @@
         <v>1.48</v>
       </c>
       <c r="T161">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="U161">
         <v>3.75</v>
       </c>
       <c r="V161">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W161">
         <v>1.01</v>
@@ -26588,10 +26588,10 @@
         <v>1.5</v>
       </c>
       <c r="Z161">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="AA161">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB161">
         <v>1.44</v>
@@ -26606,7 +26606,7 @@
         <v>1.04</v>
       </c>
       <c r="AF161">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG161">
         <v>1.7</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="O162">
         <v>8</v>
       </c>
       <c r="P162">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Q162">
         <v>8.5</v>
@@ -26736,19 +26736,19 @@
         <v>4.75</v>
       </c>
       <c r="U162">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V162">
         <v>1.98</v>
       </c>
       <c r="W162">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X162">
         <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z162">
         <v>8.300000000000001</v>
@@ -26878,16 +26878,16 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O163">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P163">
         <v>2.07</v>
       </c>
       <c r="Q163">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="R163">
         <v>2.4</v>
@@ -26917,13 +26917,13 @@
         <v>4.2</v>
       </c>
       <c r="AA163">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB163">
         <v>2.25</v>
       </c>
       <c r="AC163">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AD163">
         <v>1.5</v>
@@ -27041,16 +27041,16 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O164">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P164">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q164">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="R164">
         <v>2.63</v>
@@ -27059,16 +27059,16 @@
         <v>1.2</v>
       </c>
       <c r="T164">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="U164">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V164">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W164">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X164">
         <v>1.01</v>
@@ -27213,7 +27213,7 @@
         <v>2.34</v>
       </c>
       <c r="Q165">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="R165">
         <v>1.97</v>
@@ -27222,34 +27222,34 @@
         <v>1.4</v>
       </c>
       <c r="T165">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U165">
         <v>3</v>
       </c>
       <c r="V165">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W165">
         <v>1.06</v>
       </c>
       <c r="X165">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y165">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z165">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AA165">
         <v>2.1</v>
       </c>
       <c r="AB165">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC165">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD165">
         <v>1.25</v>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AK165">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27388,10 +27388,10 @@
         <v>3.4</v>
       </c>
       <c r="U166">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="V166">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="W166">
         <v>1.13</v>
@@ -28345,31 +28345,31 @@
         </is>
       </c>
       <c r="N172">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="O172">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P172">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q172">
         <v>6.5</v>
       </c>
       <c r="R172">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S172">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T172">
+        <v>2.93</v>
+      </c>
+      <c r="U172">
         <v>2.77</v>
       </c>
-      <c r="U172">
-        <v>2.7</v>
-      </c>
       <c r="V172">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W172">
         <v>1.08</v>
@@ -28381,7 +28381,7 @@
         <v>1.26</v>
       </c>
       <c r="Z172">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AA172">
         <v>1.9</v>
@@ -28393,7 +28393,7 @@
         <v>3.2</v>
       </c>
       <c r="AD172">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE172">
         <v>1.06</v>
@@ -28418,7 +28418,7 @@
         <v>2.55</v>
       </c>
       <c r="AK172">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>5.3</v>
+        <v>6.15</v>
       </c>
       <c r="O173">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P173">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q173">
         <v>5.3</v>
@@ -28674,16 +28674,16 @@
         <v>1.6</v>
       </c>
       <c r="O174">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="P174">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="Q174">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="R174">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S174">
         <v>1.14</v>
@@ -28710,10 +28710,10 @@
         <v>6.25</v>
       </c>
       <c r="AA174">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB174">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AC174">
         <v>1.87</v>
@@ -28722,7 +28722,7 @@
         <v>1.9</v>
       </c>
       <c r="AE174">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF174">
         <v>1.37</v>
@@ -28843,10 +28843,10 @@
         <v>1.75</v>
       </c>
       <c r="Q175">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="R175">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S175">
         <v>1.33</v>
@@ -28861,37 +28861,37 @@
         <v>1.41</v>
       </c>
       <c r="W175">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X175">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y175">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z175">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA175">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AB175">
         <v>1.92</v>
       </c>
       <c r="AC175">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD175">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE175">
         <v>1.08</v>
       </c>
       <c r="AF175">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG175">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>1.91</v>
       </c>
       <c r="AK175">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29033,19 +29033,19 @@
         <v>1.22</v>
       </c>
       <c r="Z176">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="AA176">
         <v>1.7</v>
       </c>
       <c r="AB176">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC176">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AD176">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE176">
         <v>1.14</v>
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="O178">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P178">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="Q178">
         <v>2.63</v>
@@ -29371,7 +29371,7 @@
         <v>2.25</v>
       </c>
       <c r="AD178">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE178">
         <v>1.24</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O179">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P179">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29661,10 +29661,10 @@
         <v>2.91</v>
       </c>
       <c r="R180">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S180">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T180">
         <v>3.6</v>
@@ -29676,7 +29676,7 @@
         <v>1.5</v>
       </c>
       <c r="W180">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X180">
         <v>1</v>
@@ -29688,7 +29688,7 @@
         <v>4.23</v>
       </c>
       <c r="AA180">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB180">
         <v>2.13</v>
@@ -29719,7 +29719,7 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK180">
         <v>1.5</v>
@@ -30301,16 +30301,16 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="O184">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P184">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q184">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R184">
         <v>1.9</v>
@@ -31119,13 +31119,13 @@
         <v>1.44</v>
       </c>
       <c r="O189">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="P189">
         <v>5.75</v>
       </c>
       <c r="Q189">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R189">
         <v>2.24</v>
@@ -31137,34 +31137,34 @@
         <v>3.2</v>
       </c>
       <c r="U189">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="V189">
         <v>1.5</v>
       </c>
       <c r="W189">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X189">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y189">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z189">
-        <v>3.93</v>
+        <v>4.56</v>
       </c>
       <c r="AA189">
         <v>1.73</v>
       </c>
       <c r="AB189">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC189">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AD189">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AE189">
         <v>1.15</v>
@@ -31279,10 +31279,10 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O190">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P190">
         <v>2.1</v>
@@ -31297,25 +31297,25 @@
         <v>1.25</v>
       </c>
       <c r="T190">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U190">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V190">
         <v>1.6</v>
       </c>
       <c r="W190">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X190">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y190">
         <v>1.16</v>
       </c>
       <c r="Z190">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="AA190">
         <v>1.57</v>
@@ -33564,10 +33564,10 @@
         <v>3.45</v>
       </c>
       <c r="O204">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="P204">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q204">
         <v>4</v>
@@ -33576,46 +33576,46 @@
         <v>2.05</v>
       </c>
       <c r="S204">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T204">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U204">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V204">
         <v>1.36</v>
       </c>
       <c r="W204">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X204">
         <v>1.03</v>
       </c>
       <c r="Y204">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z204">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="AA204">
         <v>1.94</v>
       </c>
       <c r="AB204">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AC204">
-        <v>3.12</v>
+        <v>3.63</v>
       </c>
       <c r="AD204">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE204">
         <v>1.1</v>
       </c>
       <c r="AF204">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG204">
         <v>1.85</v>
@@ -33724,19 +33724,19 @@
         </is>
       </c>
       <c r="N205">
+        <v>1.93</v>
+      </c>
+      <c r="O205">
+        <v>3.31</v>
+      </c>
+      <c r="P205">
+        <v>3.25</v>
+      </c>
+      <c r="Q205">
+        <v>2.8</v>
+      </c>
+      <c r="R205">
         <v>2</v>
-      </c>
-      <c r="O205">
-        <v>3.22</v>
-      </c>
-      <c r="P205">
-        <v>3.4</v>
-      </c>
-      <c r="Q205">
-        <v>2.63</v>
-      </c>
-      <c r="R205">
-        <v>2.05</v>
       </c>
       <c r="S205">
         <v>1.44</v>
@@ -33745,19 +33745,19 @@
         <v>2.65</v>
       </c>
       <c r="U205">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V205">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W205">
         <v>1.04</v>
       </c>
       <c r="X205">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y205">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z205">
         <v>2.9</v>
@@ -33766,16 +33766,16 @@
         <v>2.2</v>
       </c>
       <c r="AB205">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC205">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="AD205">
         <v>1.24</v>
       </c>
       <c r="AE205">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF205">
         <v>1.83</v>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK205">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33887,61 +33887,61 @@
         </is>
       </c>
       <c r="N206">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O206">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P206">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q206">
         <v>4.95</v>
       </c>
       <c r="R206">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="S206">
         <v>1.29</v>
       </c>
       <c r="T206">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U206">
         <v>2.4</v>
       </c>
       <c r="V206">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W206">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X206">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y206">
         <v>1.22</v>
       </c>
       <c r="Z206">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA206">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB206">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC206">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="AD206">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE206">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF206">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG206">
         <v>2.2</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O208">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P208">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q208">
         <v>3</v>
@@ -34267,10 +34267,10 @@
         <v>1.22</v>
       </c>
       <c r="AF208">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG208">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O209">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P209">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q209">
         <v>2.8</v>
@@ -34397,13 +34397,13 @@
         <v>2.5</v>
       </c>
       <c r="U209">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V209">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W209">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X209">
         <v>1.1</v>
@@ -34702,37 +34702,37 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O211">
         <v>3.5</v>
       </c>
       <c r="P211">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
       </c>
       <c r="R211">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S211">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T211">
         <v>2.77</v>
       </c>
       <c r="U211">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V211">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W211">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X211">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y211">
         <v>1.28</v>
@@ -34744,7 +34744,7 @@
         <v>1.91</v>
       </c>
       <c r="AB211">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC211">
         <v>3.04</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O217">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="P217">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Q217">
         <v>6.95</v>
@@ -35734,7 +35734,7 @@
         <v>1.73</v>
       </c>
       <c r="AF217">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG217">
         <v>2.34</v>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="AK217">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q219">
         <v>2.17</v>
@@ -36021,10 +36021,10 @@
         <v>2.18</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U219">
         <v>2.55</v>
@@ -36033,16 +36033,16 @@
         <v>1.38</v>
       </c>
       <c r="W219">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X219">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y219">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z219">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA219">
         <v>1.8</v>
@@ -36057,13 +36057,13 @@
         <v>1.26</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF219">
         <v>1.74</v>
       </c>
       <c r="AG219">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36169,10 +36169,10 @@
         </is>
       </c>
       <c r="N220">
-        <v>5.87</v>
+        <v>5.82</v>
       </c>
       <c r="O220">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="P220">
         <v>1.55</v>
@@ -36181,19 +36181,19 @@
         <v>5</v>
       </c>
       <c r="R220">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S220">
         <v>1.3</v>
       </c>
       <c r="T220">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U220">
         <v>2.47</v>
       </c>
       <c r="V220">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W220">
         <v>1.07</v>
@@ -36214,16 +36214,16 @@
         <v>2.05</v>
       </c>
       <c r="AC220">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD220">
         <v>1.38</v>
       </c>
       <c r="AE220">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF220">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG220">
         <v>1.9</v>
@@ -36239,7 +36239,7 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="AK220">
         <v>1.15</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="O221">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="P221">
-        <v>5.93</v>
+        <v>5.8</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G223">
@@ -36667,55 +36667,55 @@
         <v>0</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T223">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U223">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V223">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W223">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X223">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z223">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA223">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB223">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC223">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD223">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG223">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK223">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G224">
@@ -36830,55 +36830,55 @@
         <v>0</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,19 +36984,19 @@
         </is>
       </c>
       <c r="N225">
-        <v>6.5</v>
+        <v>7.85</v>
       </c>
       <c r="O225">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P225">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Q225">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R225">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S225">
         <v>1.35</v>
@@ -37008,7 +37008,7 @@
         <v>2.75</v>
       </c>
       <c r="V225">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W225">
         <v>1.04</v>
@@ -37041,7 +37041,7 @@
         <v>2</v>
       </c>
       <c r="AG225">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK225">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37799,19 +37799,19 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O230">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P230">
         <v>3.5</v>
       </c>
       <c r="Q230">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="R230">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S230">
         <v>1.2</v>
@@ -37838,7 +37838,7 @@
         <v>6.01</v>
       </c>
       <c r="AA230">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB230">
         <v>2.7</v>
@@ -37850,7 +37850,7 @@
         <v>1.67</v>
       </c>
       <c r="AE230">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF230">
         <v>1.42</v>
@@ -37971,16 +37971,16 @@
         <v>1.95</v>
       </c>
       <c r="Q231">
-        <v>4.34</v>
+        <v>4</v>
       </c>
       <c r="R231">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S231">
         <v>1.44</v>
       </c>
       <c r="T231">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U231">
         <v>3.3</v>
@@ -38016,7 +38016,7 @@
         <v>1.03</v>
       </c>
       <c r="AF231">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG231">
         <v>1.74</v>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK231">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38152,19 +38152,19 @@
         <v>1.38</v>
       </c>
       <c r="W232">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X232">
         <v>1.05</v>
       </c>
       <c r="Y232">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z232">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA232">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AB232">
         <v>1.75</v>
@@ -38195,7 +38195,7 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK232">
         <v>1.53</v>
@@ -38297,10 +38297,10 @@
         <v>3.1</v>
       </c>
       <c r="Q233">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="R233">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S233">
         <v>1.48</v>
@@ -38309,28 +38309,28 @@
         <v>2.62</v>
       </c>
       <c r="U233">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="V233">
         <v>1.32</v>
       </c>
       <c r="W233">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X233">
         <v>1.08</v>
       </c>
       <c r="Y233">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z233">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="AA233">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AB233">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC233">
         <v>4.2</v>
@@ -38339,13 +38339,13 @@
         <v>1.18</v>
       </c>
       <c r="AE233">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF233">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG233">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK233">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38460,7 +38460,7 @@
         <v>2.6</v>
       </c>
       <c r="Q234">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R234">
         <v>2</v>
@@ -38472,22 +38472,22 @@
         <v>2.75</v>
       </c>
       <c r="U234">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="V234">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W234">
         <v>1.05</v>
       </c>
       <c r="X234">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y234">
         <v>1.36</v>
       </c>
       <c r="Z234">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AA234">
         <v>2.15</v>
@@ -38496,16 +38496,16 @@
         <v>1.61</v>
       </c>
       <c r="AC234">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD234">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE234">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF234">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG234">
         <v>1.85</v>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AK234">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38623,7 +38623,7 @@
         <v>0</v>
       </c>
       <c r="Q235">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R235">
         <v>1.91</v>
@@ -38635,25 +38635,25 @@
         <v>2.26</v>
       </c>
       <c r="U235">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V235">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W235">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X235">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y235">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z235">
         <v>2.3</v>
       </c>
       <c r="AA235">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AB235">
         <v>1.4</v>
@@ -38662,7 +38662,7 @@
         <v>5</v>
       </c>
       <c r="AD235">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE235">
         <v>1.03</v>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK235">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38780,10 +38780,10 @@
         <v>1.75</v>
       </c>
       <c r="O236">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P236">
-        <v>4.72</v>
+        <v>4.62</v>
       </c>
       <c r="Q236">
         <v>2.3</v>
@@ -38798,7 +38798,7 @@
         <v>2.88</v>
       </c>
       <c r="U236">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="V236">
         <v>1.34</v>
@@ -38949,13 +38949,13 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="R237">
         <v>1.95</v>
       </c>
       <c r="S237">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T237">
         <v>2.55</v>
@@ -38964,19 +38964,19 @@
         <v>2.9</v>
       </c>
       <c r="V237">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W237">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X237">
         <v>1.02</v>
       </c>
       <c r="Y237">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z237">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA237">
         <v>2.21</v>
@@ -39112,7 +39112,7 @@
         <v>2.3</v>
       </c>
       <c r="Q238">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="R238">
         <v>1.91</v>
@@ -39127,7 +39127,7 @@
         <v>3.3</v>
       </c>
       <c r="V238">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W238">
         <v>1.02</v>
@@ -39136,19 +39136,19 @@
         <v>1.05</v>
       </c>
       <c r="Y238">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z238">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AA238">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB238">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC238">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD238">
         <v>1.16</v>
@@ -39157,10 +39157,10 @@
         <v>1.02</v>
       </c>
       <c r="AF238">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AG238">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AK238">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q239">
         <v>2.43</v>
@@ -39281,10 +39281,10 @@
         <v>2.4</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U239">
         <v>2.12</v>
@@ -39293,37 +39293,37 @@
         <v>1.56</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA239">
         <v>1.5</v>
       </c>
       <c r="AB239">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AC239">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD239">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE239">
         <v>1.2</v>
       </c>
       <c r="AF239">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG239">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39607,16 +39607,16 @@
         <v>2.4</v>
       </c>
       <c r="S241">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T241">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="U241">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="V241">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W241">
         <v>1.12</v>
@@ -40087,7 +40087,7 @@
         <v>3.48</v>
       </c>
       <c r="P244">
-        <v>4.92</v>
+        <v>4.55</v>
       </c>
       <c r="Q244">
         <v>2.35</v>
@@ -40105,28 +40105,28 @@
         <v>3.2</v>
       </c>
       <c r="V244">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W244">
         <v>1.06</v>
       </c>
       <c r="X244">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y244">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z244">
         <v>2.8</v>
       </c>
       <c r="AA244">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB244">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC244">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="AD244">
         <v>1.22</v>
@@ -40135,10 +40135,10 @@
         <v>1.04</v>
       </c>
       <c r="AF244">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG244">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>0</v>
       </c>
       <c r="Q246">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="R246">
         <v>1.85</v>
@@ -40431,7 +40431,7 @@
         <v>4.5</v>
       </c>
       <c r="V246">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W246">
         <v>1</v>
@@ -40443,7 +40443,7 @@
         <v>1.67</v>
       </c>
       <c r="Z246">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AA246">
         <v>3</v>
@@ -40455,7 +40455,7 @@
         <v>7</v>
       </c>
       <c r="AD246">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE246">
         <v>1.03</v>
@@ -40480,7 +40480,7 @@
         <v>1.45</v>
       </c>
       <c r="AK246">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40570,64 +40570,64 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="O247">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="P247">
-        <v>11</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q247">
+        <v>1.63</v>
+      </c>
+      <c r="R247">
+        <v>2.93</v>
+      </c>
+      <c r="S247">
+        <v>1.23</v>
+      </c>
+      <c r="T247">
+        <v>3.78</v>
+      </c>
+      <c r="U247">
+        <v>2.23</v>
+      </c>
+      <c r="V247">
         <v>1.65</v>
       </c>
-      <c r="R247">
-        <v>2.87</v>
-      </c>
-      <c r="S247">
-        <v>1.24</v>
-      </c>
-      <c r="T247">
-        <v>3.7</v>
-      </c>
-      <c r="U247">
-        <v>2.27</v>
-      </c>
-      <c r="V247">
-        <v>1.63</v>
-      </c>
       <c r="W247">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X247">
         <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z247">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA247">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB247">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AC247">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AD247">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE247">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF247">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AG247">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>1.14</v>
       </c>
       <c r="AK247">
-        <v>3.92</v>
+        <v>3.51</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O249">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P249">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -40935,10 +40935,10 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB249">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC249">
         <v>0</v>
@@ -41059,19 +41059,19 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O250">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P250">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q250">
         <v>1.74</v>
       </c>
       <c r="R250">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="S250">
         <v>1.24</v>
@@ -41110,7 +41110,7 @@
         <v>1.54</v>
       </c>
       <c r="AE250">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF250">
         <v>1.8</v>
@@ -41132,7 +41132,7 @@
         <v>1.06</v>
       </c>
       <c r="AK250">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41222,7 +41222,7 @@
         </is>
       </c>
       <c r="N251">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O251">
         <v>3.4</v>
@@ -41249,7 +41249,7 @@
         <v>1.48</v>
       </c>
       <c r="W251">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X251">
         <v>1.04</v>
@@ -41270,7 +41270,7 @@
         <v>3</v>
       </c>
       <c r="AD251">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE251">
         <v>1.09</v>
@@ -41385,19 +41385,19 @@
         </is>
       </c>
       <c r="N252">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="O252">
-        <v>4.25</v>
+        <v>4.7</v>
       </c>
       <c r="P252">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Q252">
         <v>5.95</v>
       </c>
       <c r="R252">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="S252">
         <v>1.22</v>
@@ -41406,22 +41406,22 @@
         <v>3.64</v>
       </c>
       <c r="U252">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="V252">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W252">
         <v>1.08</v>
       </c>
       <c r="X252">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y252">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z252">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA252">
         <v>1.66</v>
@@ -41439,10 +41439,10 @@
         <v>1.22</v>
       </c>
       <c r="AF252">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG252">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK252">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41548,10 +41548,10 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O253">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="P253">
         <v>3.8</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB253">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -42363,7 +42363,7 @@
         </is>
       </c>
       <c r="N258">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O258">
         <v>3.6</v>
@@ -42372,10 +42372,10 @@
         <v>4</v>
       </c>
       <c r="Q258">
+        <v>2.2</v>
+      </c>
+      <c r="R258">
         <v>2.29</v>
-      </c>
-      <c r="R258">
-        <v>2.3</v>
       </c>
       <c r="S258">
         <v>1.32</v>
@@ -42387,7 +42387,7 @@
         <v>2.5</v>
       </c>
       <c r="V258">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W258">
         <v>1.11</v>
@@ -42396,10 +42396,10 @@
         <v>1.04</v>
       </c>
       <c r="Y258">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z258">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AA258">
         <v>1.73</v>
@@ -42420,7 +42420,7 @@
         <v>1.69</v>
       </c>
       <c r="AG258">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK258">
         <v>2</v>
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O259">
         <v>3.5</v>
       </c>
       <c r="P259">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q259">
         <v>2.43</v>
@@ -42541,10 +42541,10 @@
         <v>2.16</v>
       </c>
       <c r="S259">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T259">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="U259">
         <v>2.44</v>
@@ -42553,28 +42553,28 @@
         <v>1.46</v>
       </c>
       <c r="W259">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X259">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y259">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z259">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA259">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB259">
         <v>1.82</v>
       </c>
       <c r="AC259">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="AD259">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE259">
         <v>1.17</v>
@@ -42689,19 +42689,19 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="O260">
         <v>3.25</v>
       </c>
       <c r="P260">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q260">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R260">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S260">
         <v>1.46</v>
@@ -42722,7 +42722,7 @@
         <v>1.03</v>
       </c>
       <c r="Y260">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z260">
         <v>2.8</v>
@@ -42855,13 +42855,13 @@
         <v>1.06</v>
       </c>
       <c r="O261">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="P261">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q261">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R261">
         <v>3</v>
@@ -42870,7 +42870,7 @@
         <v>1.22</v>
       </c>
       <c r="T261">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U261">
         <v>2</v>
@@ -42885,13 +42885,13 @@
         <v>1.01</v>
       </c>
       <c r="Y261">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z261">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA261">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AB261">
         <v>2.63</v>
@@ -42909,7 +42909,7 @@
         <v>2.3</v>
       </c>
       <c r="AG261">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -43682,10 +43682,10 @@
         <v>2</v>
       </c>
       <c r="S266">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T266">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U266">
         <v>2.99</v>
@@ -43697,7 +43697,7 @@
         <v>1.06</v>
       </c>
       <c r="X266">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y266">
         <v>1.33</v>
@@ -43737,7 +43737,7 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK266">
         <v>1.67</v>
@@ -44011,16 +44011,16 @@
         <v>1.35</v>
       </c>
       <c r="T268">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="U268">
         <v>2.5</v>
       </c>
       <c r="V268">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W268">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X268">
         <v>1.04</v>
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O270">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P270">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q270">
         <v>2.53</v>
@@ -44337,19 +44337,19 @@
         <v>1.25</v>
       </c>
       <c r="T270">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U270">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V270">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W270">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X270">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y270">
         <v>1.13</v>
@@ -44367,13 +44367,13 @@
         <v>2.5</v>
       </c>
       <c r="AD270">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE270">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF270">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG270">
         <v>2.4</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="O271">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P271">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Q271">
         <v>4.1</v>
@@ -44497,10 +44497,10 @@
         <v>2.38</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U271">
         <v>2.17</v>
@@ -44509,16 +44509,16 @@
         <v>1.53</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA271">
         <v>1.56</v>
@@ -44533,7 +44533,7 @@
         <v>1.47</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF271">
         <v>1.56</v>
@@ -44654,46 +44654,46 @@
         <v>0</v>
       </c>
       <c r="Q272">
-        <v>7.65</v>
+        <v>7</v>
       </c>
       <c r="R272">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="S272">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T272">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U272">
         <v>2.2</v>
       </c>
       <c r="V272">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W272">
         <v>1.15</v>
       </c>
       <c r="X272">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y272">
         <v>1.15</v>
       </c>
       <c r="Z272">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA272">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB272">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AC272">
         <v>2.3</v>
       </c>
       <c r="AD272">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE272">
         <v>1.2</v>
@@ -44715,7 +44715,7 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>3.3</v>
+        <v>1.07</v>
       </c>
       <c r="AK272">
         <v>1.01</v>
@@ -44980,10 +44980,10 @@
         <v>1.48</v>
       </c>
       <c r="Q274">
-        <v>5.68</v>
+        <v>5.5</v>
       </c>
       <c r="R274">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S274">
         <v>1.22</v>
@@ -44995,7 +44995,7 @@
         <v>2.23</v>
       </c>
       <c r="V274">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W274">
         <v>1.13</v>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AK274">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45134,7 +45134,7 @@
         </is>
       </c>
       <c r="N275">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O275">
         <v>3.3</v>
@@ -45146,13 +45146,13 @@
         <v>4.4</v>
       </c>
       <c r="R275">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="S275">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T275">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U275">
         <v>2.88</v>
@@ -45161,7 +45161,7 @@
         <v>1.4</v>
       </c>
       <c r="W275">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X275">
         <v>1.05</v>
@@ -45179,7 +45179,7 @@
         <v>1.78</v>
       </c>
       <c r="AC275">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD275">
         <v>1.3</v>
@@ -45191,7 +45191,7 @@
         <v>1.81</v>
       </c>
       <c r="AG275">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="AK275">
         <v>1.22</v>
@@ -45297,16 +45297,16 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O276">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P276">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q276">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="R276">
         <v>2.2</v>
@@ -45351,7 +45351,7 @@
         <v>1.1</v>
       </c>
       <c r="AF276">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG276">
         <v>1.85</v>
@@ -45641,19 +45641,19 @@
         <v>1.29</v>
       </c>
       <c r="T278">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U278">
         <v>2.35</v>
       </c>
       <c r="V278">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W278">
         <v>1.11</v>
       </c>
       <c r="X278">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y278">
         <v>1.18</v>
@@ -45795,19 +45795,19 @@
         <v>2.13</v>
       </c>
       <c r="Q279">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="R279">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S279">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T279">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U279">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V279">
         <v>1.41</v>
@@ -46275,10 +46275,10 @@
         </is>
       </c>
       <c r="N282">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O282">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P282">
         <v>2.9</v>
@@ -46290,16 +46290,16 @@
         <v>2.1</v>
       </c>
       <c r="S282">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T282">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="U282">
         <v>2.88</v>
       </c>
       <c r="V282">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W282">
         <v>1.02</v>
@@ -46314,13 +46314,13 @@
         <v>2.95</v>
       </c>
       <c r="AA282">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB282">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC282">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AD282">
         <v>1.22</v>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK282">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46438,10 +46438,10 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="O283">
-        <v>4.35</v>
+        <v>3.95</v>
       </c>
       <c r="P283">
         <v>6</v>
@@ -46456,16 +46456,16 @@
         <v>1.32</v>
       </c>
       <c r="T283">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="U283">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="V283">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W283">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X283">
         <v>1</v>
@@ -46489,7 +46489,7 @@
         <v>1.35</v>
       </c>
       <c r="AE283">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF283">
         <v>1.83</v>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK283">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46764,7 +46764,7 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O285">
         <v>4.8</v>
@@ -46797,19 +46797,19 @@
         <v>1.03</v>
       </c>
       <c r="Y285">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z285">
-        <v>5.51</v>
+        <v>5.1</v>
       </c>
       <c r="AA285">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB285">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AC285">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD285">
         <v>1.6</v>
@@ -47090,31 +47090,31 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="O287">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P287">
         <v>11</v>
       </c>
       <c r="Q287">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R287">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="S287">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="T287">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="U287">
         <v>1.63</v>
       </c>
       <c r="V287">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W287">
         <v>1.35</v>
@@ -47123,10 +47123,10 @@
         <v>1</v>
       </c>
       <c r="Y287">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Z287">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA287">
         <v>1.18</v>
@@ -47138,7 +47138,7 @@
         <v>1.52</v>
       </c>
       <c r="AD287">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AE287">
         <v>1.67</v>
@@ -47147,7 +47147,7 @@
         <v>1.5</v>
       </c>
       <c r="AG287">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>1.08</v>
       </c>
       <c r="AK287">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47253,28 +47253,28 @@
         </is>
       </c>
       <c r="N288">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O288">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P288">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Q288">
         <v>4.75</v>
       </c>
       <c r="R288">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S288">
         <v>1.25</v>
       </c>
       <c r="T288">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U288">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V288">
         <v>1.62</v>
@@ -47292,13 +47292,13 @@
         <v>4.8</v>
       </c>
       <c r="AA288">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB288">
         <v>2.45</v>
       </c>
       <c r="AC288">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD288">
         <v>1.53</v>
@@ -47307,7 +47307,7 @@
         <v>1.2</v>
       </c>
       <c r="AF288">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG288">
         <v>2.2</v>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AK288">
         <v>1.09</v>
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O292">
         <v>5</v>
       </c>
       <c r="P292">
-        <v>9.25</v>
+        <v>8.75</v>
       </c>
       <c r="Q292">
         <v>1.73</v>
@@ -47920,28 +47920,28 @@
         <v>2.4</v>
       </c>
       <c r="S292">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T292">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U292">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V292">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W292">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X292">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z292">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="AA292">
         <v>1.72</v>
@@ -47978,7 +47978,7 @@
         <v>1.04</v>
       </c>
       <c r="AK292">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48089,13 +48089,13 @@
         <v>2.63</v>
       </c>
       <c r="U293">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V293">
         <v>1.29</v>
       </c>
       <c r="W293">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X293">
         <v>1.05</v>
@@ -48113,13 +48113,13 @@
         <v>1.53</v>
       </c>
       <c r="AC293">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AD293">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE293">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF293">
         <v>1.95</v>
@@ -48138,7 +48138,7 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK293">
         <v>1.25</v>
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="O294">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="P294">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q294">
         <v>7.5</v>
@@ -48273,22 +48273,22 @@
         <v>1.36</v>
       </c>
       <c r="AB294">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AC294">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AD294">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE294">
         <v>1.3</v>
       </c>
       <c r="AF294">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG294">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48394,52 +48394,52 @@
         </is>
       </c>
       <c r="N295">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="O295">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="P295">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="Q295">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="R295">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S295">
         <v>1.29</v>
       </c>
       <c r="T295">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="U295">
         <v>2.55</v>
       </c>
       <c r="V295">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W295">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X295">
         <v>1</v>
       </c>
       <c r="Y295">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z295">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="AA295">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB295">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AC295">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="AD295">
         <v>1.36</v>
@@ -48451,7 +48451,7 @@
         <v>1.78</v>
       </c>
       <c r="AG295">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK295">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="O302">
+        <v>2.9</v>
+      </c>
+      <c r="P302">
         <v>2.95</v>
       </c>
-      <c r="P302">
+      <c r="Q302">
         <v>3.25</v>
       </c>
-      <c r="Q302">
-        <v>3.09</v>
-      </c>
       <c r="R302">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S302">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T302">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U302">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V302">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W302">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X302">
         <v>1.11</v>
       </c>
       <c r="Y302">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z302">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AA302">
         <v>2.5</v>
       </c>
       <c r="AB302">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC302">
         <v>4.33</v>
       </c>
       <c r="AD302">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE302">
         <v>1.02</v>
       </c>
       <c r="AF302">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG302">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49861,10 +49861,10 @@
         </is>
       </c>
       <c r="N304">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O304">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P304">
         <v>2.31</v>
@@ -49876,22 +49876,22 @@
         <v>2.3</v>
       </c>
       <c r="S304">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T304">
         <v>3.3</v>
       </c>
       <c r="U304">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V304">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W304">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X304">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y304">
         <v>1.2</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O305">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P305">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q305">
         <v>2.4</v>
@@ -50042,7 +50042,7 @@
         <v>1.4</v>
       </c>
       <c r="T305">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U305">
         <v>3.2</v>
@@ -50051,7 +50051,7 @@
         <v>1.33</v>
       </c>
       <c r="W305">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X305">
         <v>1.04</v>
@@ -50094,7 +50094,7 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK305">
         <v>1.8</v>
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O306">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P306">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q306">
         <v>4.2</v>
@@ -50205,37 +50205,37 @@
         <v>1.54</v>
       </c>
       <c r="T306">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="U306">
         <v>3.25</v>
       </c>
       <c r="V306">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W306">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X306">
         <v>1.08</v>
       </c>
       <c r="Y306">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z306">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AA306">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB306">
         <v>1.52</v>
       </c>
       <c r="AC306">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD306">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE306">
         <v>1.01</v>
@@ -50244,7 +50244,7 @@
         <v>1.95</v>
       </c>
       <c r="AG306">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>2.2</v>
       </c>
       <c r="O307">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P307">
         <v>3.1</v>
@@ -50365,19 +50365,19 @@
         <v>1.86</v>
       </c>
       <c r="S307">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T307">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="U307">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="V307">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="W307">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X307">
         <v>1.04</v>
@@ -50401,7 +50401,7 @@
         <v>1.13</v>
       </c>
       <c r="AE307">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF307">
         <v>2</v>
@@ -50420,7 +50420,7 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK307">
         <v>1.53</v>
@@ -50546,16 +50546,16 @@
         <v>1.08</v>
       </c>
       <c r="Y308">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z308">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AA308">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AB308">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AC308">
         <v>5.1</v>
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="O310">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P310">
+        <v>3.75</v>
+      </c>
+      <c r="Q310">
+        <v>2.52</v>
+      </c>
+      <c r="R310">
+        <v>1.95</v>
+      </c>
+      <c r="S310">
+        <v>1.35</v>
+      </c>
+      <c r="T310">
         <v>2.9</v>
       </c>
-      <c r="Q310">
-        <v>2.93</v>
-      </c>
-      <c r="R310">
-        <v>1.98</v>
-      </c>
-      <c r="S310">
-        <v>1.42</v>
-      </c>
-      <c r="T310">
-        <v>2.53</v>
-      </c>
       <c r="U310">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="V310">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W310">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X310">
         <v>1.05</v>
       </c>
       <c r="Y310">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z310">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="AA310">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB310">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AC310">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AD310">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE310">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF310">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AG310">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK310">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,16 +51002,16 @@
         </is>
       </c>
       <c r="N311">
+        <v>5.1</v>
+      </c>
+      <c r="O311">
+        <v>4.2</v>
+      </c>
+      <c r="P311">
+        <v>1.43</v>
+      </c>
+      <c r="Q311">
         <v>5.5</v>
-      </c>
-      <c r="O311">
-        <v>4.1</v>
-      </c>
-      <c r="P311">
-        <v>1.48</v>
-      </c>
-      <c r="Q311">
-        <v>5</v>
       </c>
       <c r="R311">
         <v>2.3</v>
@@ -51020,10 +51020,10 @@
         <v>1.33</v>
       </c>
       <c r="T311">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U311">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V311">
         <v>1.48</v>
@@ -51053,10 +51053,10 @@
         <v>1.4</v>
       </c>
       <c r="AE311">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF311">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG311">
         <v>1.87</v>
@@ -51072,7 +51072,7 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK311">
         <v>1.09</v>
@@ -51820,7 +51820,7 @@
         <v>1.67</v>
       </c>
       <c r="O316">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P316">
         <v>4.8</v>
@@ -52632,13 +52632,13 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O321">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="P321">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q321">
         <v>2.3</v>
@@ -52665,10 +52665,10 @@
         <v>1.04</v>
       </c>
       <c r="Y321">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z321">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA321">
         <v>2.25</v>
@@ -52795,7 +52795,7 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O322">
         <v>3.4</v>
@@ -52825,7 +52825,7 @@
         <v>1.05</v>
       </c>
       <c r="X322">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y322">
         <v>1.38</v>
@@ -52849,7 +52849,7 @@
         <v>1.05</v>
       </c>
       <c r="AF322">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG322">
         <v>1.6</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="R2">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U2">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
         <v>1.1</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AA2">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB2">
         <v>2.05</v>
       </c>
       <c r="AC2">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AD2">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK2">
         <v>1.57</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O3">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
         <v>2.6</v>
@@ -822,7 +822,7 @@
         <v>3.23</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
         <v>1.01</v>
@@ -846,10 +846,10 @@
         <v>3.75</v>
       </c>
       <c r="AD3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
         <v>1.84</v>
@@ -871,7 +871,7 @@
         <v>1.4</v>
       </c>
       <c r="AK3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>2.71</v>
       </c>
       <c r="O4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
         <v>2.18</v>
@@ -976,10 +976,10 @@
         <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U4">
         <v>3</v>
@@ -988,13 +988,13 @@
         <v>1.35</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
         <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
         <v>2.88</v>
@@ -1006,19 +1006,19 @@
         <v>1.64</v>
       </c>
       <c r="AC4">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AD4">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
         <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
         <v>3.25</v>
       </c>
       <c r="P5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q5">
         <v>3.95</v>
@@ -1163,7 +1163,7 @@
         <v>3.4</v>
       </c>
       <c r="AA5">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
         <v>1.79</v>
@@ -1175,13 +1175,13 @@
         <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG5">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>1.6</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
         <v>1.03</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q10">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="R10">
         <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
         <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
+        <v>3.3</v>
+      </c>
+      <c r="AA10">
+        <v>1.9</v>
+      </c>
+      <c r="AB10">
+        <v>1.8</v>
+      </c>
+      <c r="AC10">
         <v>3.4</v>
       </c>
-      <c r="AA10">
-        <v>1.95</v>
-      </c>
-      <c r="AB10">
-        <v>1.85</v>
-      </c>
-      <c r="AC10">
-        <v>3.11</v>
-      </c>
       <c r="AD10">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.85</v>
+        <v>2.37</v>
       </c>
       <c r="R11">
         <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="U11">
         <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA11">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3418,7 +3418,7 @@
         <v>2.5</v>
       </c>
       <c r="R19">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="S19">
         <v>1.25</v>
@@ -3442,28 +3442,28 @@
         <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="AA19">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC19">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD19">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
         <v>1.48</v>
       </c>
       <c r="AG19">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
         <v>1</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P24">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q24">
         <v>2.1</v>
@@ -4248,7 +4248,7 @@
         <v>1.56</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,25 +4257,25 @@
         <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>4.48</v>
+        <v>4.52</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AC24">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AD24">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE24">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
         <v>2.15</v>
@@ -4294,7 +4294,7 @@
         <v>1.13</v>
       </c>
       <c r="AK24">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4423,13 +4423,13 @@
         <v>3.73</v>
       </c>
       <c r="AA25">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB25">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC25">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD25">
         <v>1.32</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="O41">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q41">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="S41">
         <v>1.33</v>
@@ -7164,7 +7164,7 @@
         <v>3.01</v>
       </c>
       <c r="Q42">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R42">
         <v>2.38</v>
@@ -7228,7 +7228,7 @@
         <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G51">
@@ -8631,55 +8631,55 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.95</v>
+        <v>1.65</v>
       </c>
       <c r="R51">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U51">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="V51">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA51">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB51">
         <v>2.38</v>
       </c>
       <c r="AC51">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AD51">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE51">
         <v>1.22</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK51">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G52">
@@ -8794,55 +8794,55 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>1.65</v>
+        <v>2.95</v>
       </c>
       <c r="R52">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U52">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="V52">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA52">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AB52">
         <v>2.38</v>
       </c>
       <c r="AC52">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD52">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE52">
         <v>1.22</v>
       </c>
       <c r="AF52">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="AG52">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>2.05</v>
       </c>
       <c r="Q53">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="R53">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S53">
         <v>1.29</v>
@@ -9021,7 +9021,7 @@
         <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9446,16 +9446,16 @@
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>4.24</v>
+        <v>4.29</v>
       </c>
       <c r="R56">
         <v>1.93</v>
       </c>
       <c r="S56">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T56">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="U56">
         <v>2.97</v>
@@ -9476,10 +9476,10 @@
         <v>2.88</v>
       </c>
       <c r="AA56">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB56">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC56">
         <v>3.58</v>
@@ -9494,7 +9494,7 @@
         <v>1.81</v>
       </c>
       <c r="AG56">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="O58">
         <v>3.8</v>
@@ -9784,13 +9784,13 @@
         <v>3.12</v>
       </c>
       <c r="U58">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="V58">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X58">
         <v>1.01</v>
@@ -9814,7 +9814,7 @@
         <v>1.38</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF58">
         <v>1.77</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AK58">
         <v>1.13</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q61">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S61">
         <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="V61">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W61">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5.75</v>
+        <v>5.15</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB61">
-        <v>3.11</v>
+        <v>2.5</v>
       </c>
       <c r="AC61">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AD61">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AE61">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AG61">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="R62">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W62">
+        <v>1.19</v>
+      </c>
+      <c r="X62">
+        <v>1.01</v>
+      </c>
+      <c r="Y62">
+        <v>1.11</v>
+      </c>
+      <c r="Z62">
+        <v>5.75</v>
+      </c>
+      <c r="AA62">
+        <v>1.4</v>
+      </c>
+      <c r="AB62">
+        <v>3.11</v>
+      </c>
+      <c r="AC62">
+        <v>1.91</v>
+      </c>
+      <c r="AD62">
+        <v>1.82</v>
+      </c>
+      <c r="AE62">
+        <v>1.25</v>
+      </c>
+      <c r="AF62">
+        <v>1.38</v>
+      </c>
+      <c r="AG62">
+        <v>2.7</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.17</v>
       </c>
-      <c r="X62">
-        <v>1.02</v>
-      </c>
-      <c r="Y62">
-        <v>1.1</v>
-      </c>
-      <c r="Z62">
-        <v>5.15</v>
-      </c>
-      <c r="AA62">
-        <v>1.5</v>
-      </c>
-      <c r="AB62">
-        <v>2.5</v>
-      </c>
-      <c r="AC62">
-        <v>2.18</v>
-      </c>
-      <c r="AD62">
-        <v>1.66</v>
-      </c>
-      <c r="AE62">
-        <v>1.24</v>
-      </c>
-      <c r="AF62">
-        <v>1.41</v>
-      </c>
-      <c r="AG62">
-        <v>2.69</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.28</v>
-      </c>
       <c r="AK62">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O63">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P63">
         <v>4.8</v>
@@ -10590,7 +10590,7 @@
         <v>1.97</v>
       </c>
       <c r="R63">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="S63">
         <v>1.22</v>
@@ -10602,7 +10602,7 @@
         <v>2.18</v>
       </c>
       <c r="V63">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W63">
         <v>1.11</v>
@@ -10611,10 +10611,10 @@
         <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z63">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AA63">
         <v>1.5</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="Q66">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="R66">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="S66">
+        <v>1.43</v>
+      </c>
+      <c r="T66">
+        <v>2.5</v>
+      </c>
+      <c r="U66">
+        <v>2.88</v>
+      </c>
+      <c r="V66">
         <v>1.35</v>
       </c>
-      <c r="T66">
-        <v>2.98</v>
-      </c>
-      <c r="U66">
-        <v>2.6</v>
-      </c>
-      <c r="V66">
-        <v>1.4</v>
-      </c>
       <c r="W66">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z66">
-        <v>3.48</v>
+        <v>2.97</v>
       </c>
       <c r="AA66">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AB66">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC66">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD66">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE66">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AK66">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
+        <v>2.6</v>
+      </c>
+      <c r="O67">
+        <v>3.4</v>
+      </c>
+      <c r="P67">
+        <v>2.55</v>
+      </c>
+      <c r="Q67">
+        <v>3.1</v>
+      </c>
+      <c r="R67">
+        <v>2.15</v>
+      </c>
+      <c r="S67">
+        <v>1.3</v>
+      </c>
+      <c r="T67">
         <v>3</v>
       </c>
-      <c r="O67">
-        <v>3.02</v>
-      </c>
-      <c r="P67">
-        <v>2.27</v>
-      </c>
-      <c r="Q67">
-        <v>3.74</v>
-      </c>
-      <c r="R67">
-        <v>2.13</v>
-      </c>
-      <c r="S67">
-        <v>1.42</v>
-      </c>
-      <c r="T67">
-        <v>2.53</v>
-      </c>
       <c r="U67">
+        <v>2.62</v>
+      </c>
+      <c r="V67">
+        <v>1.4</v>
+      </c>
+      <c r="W67">
+        <v>1.06</v>
+      </c>
+      <c r="X67">
+        <v>1</v>
+      </c>
+      <c r="Y67">
+        <v>1.23</v>
+      </c>
+      <c r="Z67">
+        <v>3.5</v>
+      </c>
+      <c r="AA67">
+        <v>1.8</v>
+      </c>
+      <c r="AB67">
+        <v>1.89</v>
+      </c>
+      <c r="AC67">
         <v>2.88</v>
       </c>
-      <c r="V67">
-        <v>1.33</v>
-      </c>
-      <c r="W67">
-        <v>1.04</v>
-      </c>
-      <c r="X67">
-        <v>1.03</v>
-      </c>
-      <c r="Y67">
-        <v>1.3</v>
-      </c>
-      <c r="Z67">
-        <v>2.97</v>
-      </c>
-      <c r="AA67">
-        <v>2</v>
-      </c>
-      <c r="AB67">
-        <v>1.71</v>
-      </c>
-      <c r="AC67">
-        <v>3.34</v>
-      </c>
       <c r="AD67">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE67">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O69">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="P69">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -12386,10 +12386,10 @@
         <v>2.14</v>
       </c>
       <c r="S74">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T74">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U74">
         <v>3</v>
@@ -12398,10 +12398,10 @@
         <v>1.33</v>
       </c>
       <c r="W74">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
         <v>1.36</v>
@@ -12416,19 +12416,19 @@
         <v>1.68</v>
       </c>
       <c r="AC74">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="AD74">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE74">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF74">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AG74">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>1.25</v>
       </c>
       <c r="AK74">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12549,10 +12549,10 @@
         <v>2.28</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U75">
         <v>2.28</v>
@@ -12561,31 +12561,31 @@
         <v>1.48</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
         <v>1.18</v>
       </c>
       <c r="Z75">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA75">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB75">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC75">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD75">
         <v>1.41</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF75">
         <v>1.5</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O77">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="P77">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q77">
         <v>1.55</v>
@@ -12881,34 +12881,34 @@
         <v>4.8</v>
       </c>
       <c r="U77">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V77">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W77">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X77">
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z77">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA77">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AB77">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AC77">
+        <v>1.9</v>
+      </c>
+      <c r="AD77">
         <v>1.85</v>
-      </c>
-      <c r="AD77">
-        <v>1.86</v>
       </c>
       <c r="AE77">
         <v>1.36</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O78">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
         <v>3.55</v>
@@ -13038,7 +13038,7 @@
         <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T78">
         <v>3.1</v>
@@ -13210,7 +13210,7 @@
         <v>3</v>
       </c>
       <c r="V79">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W79">
         <v>1.05</v>
@@ -14179,7 +14179,7 @@
         <v>1.96</v>
       </c>
       <c r="S85">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T85">
         <v>2.75</v>
@@ -14218,7 +14218,7 @@
         <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG85">
         <v>1.83</v>
@@ -14547,7 +14547,7 @@
         <v>1.42</v>
       </c>
       <c r="AG87">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14656,31 +14656,31 @@
         <v>1.25</v>
       </c>
       <c r="O88">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P88">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="Q88">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R88">
         <v>2.83</v>
       </c>
       <c r="S88">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T88">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U88">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V88">
         <v>1.85</v>
       </c>
       <c r="W88">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14689,10 +14689,10 @@
         <v>1.11</v>
       </c>
       <c r="Z88">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="AA88">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB88">
         <v>3.1</v>
@@ -14707,7 +14707,7 @@
         <v>1.38</v>
       </c>
       <c r="AF88">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG88">
         <v>2.05</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AK88">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>2.5</v>
       </c>
       <c r="R92">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S92">
         <v>1.28</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
         <v>1.7</v>
@@ -16491,7 +16491,7 @@
         <v>2.2</v>
       </c>
       <c r="AC99">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AD99">
         <v>1.4</v>
@@ -16519,7 +16519,7 @@
         <v>1.09</v>
       </c>
       <c r="AK99">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O101">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P101">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q101">
         <v>2.64</v>
@@ -16790,16 +16790,16 @@
         <v>1.35</v>
       </c>
       <c r="T101">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="U101">
         <v>2.5</v>
       </c>
       <c r="V101">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W101">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X101">
         <v>1.05</v>
@@ -16829,7 +16829,7 @@
         <v>1.55</v>
       </c>
       <c r="AG101">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>2.71</v>
       </c>
       <c r="Q112">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="R112">
         <v>1.96</v>
@@ -18592,7 +18592,7 @@
         <v>1.3</v>
       </c>
       <c r="W112">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X112">
         <v>1.06</v>
@@ -18912,10 +18912,10 @@
         <v>4.5</v>
       </c>
       <c r="U114">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="V114">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W114">
         <v>1.2</v>
@@ -18930,7 +18930,7 @@
         <v>6.25</v>
       </c>
       <c r="AA114">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB114">
         <v>2.8</v>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK114">
         <v>3.1</v>
@@ -22516,25 +22516,25 @@
         <v>3.58</v>
       </c>
       <c r="AA136">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB136">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC136">
         <v>2.7</v>
       </c>
       <c r="AD136">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE136">
         <v>1.1</v>
       </c>
       <c r="AF136">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG136">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -23633,10 +23633,10 @@
         <v>3.25</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U143">
         <v>1.73</v>
@@ -23645,16 +23645,16 @@
         <v>1.86</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X143">
         <v>0</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA143">
         <v>1.26</v>
@@ -23790,7 +23790,7 @@
         <v>2.15</v>
       </c>
       <c r="Q144">
-        <v>3.53</v>
+        <v>3.44</v>
       </c>
       <c r="R144">
         <v>2.23</v>
@@ -23805,7 +23805,7 @@
         <v>2.38</v>
       </c>
       <c r="V144">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W144">
         <v>1.08</v>
@@ -23823,7 +23823,7 @@
         <v>1.65</v>
       </c>
       <c r="AB144">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC144">
         <v>2.52</v>
@@ -23835,10 +23835,10 @@
         <v>1.13</v>
       </c>
       <c r="AF144">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG144">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK144">
         <v>1.32</v>
@@ -23944,16 +23944,16 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O145">
         <v>4.15</v>
       </c>
       <c r="P145">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="Q145">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R145">
         <v>2.8</v>
@@ -23971,7 +23971,7 @@
         <v>1.94</v>
       </c>
       <c r="W145">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X145">
         <v>1.01</v>
@@ -23980,7 +23980,7 @@
         <v>1.06</v>
       </c>
       <c r="Z145">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA145">
         <v>1.27</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,19 +24107,19 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q146">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R146">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="S146">
         <v>1.14</v>
@@ -24128,44 +24128,44 @@
         <v>5</v>
       </c>
       <c r="U146">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="V146">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="W146">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X146">
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z146">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="AA146">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AB146">
+        <v>3</v>
+      </c>
+      <c r="AC146">
+        <v>1.93</v>
+      </c>
+      <c r="AD146">
+        <v>1.88</v>
+      </c>
+      <c r="AE146">
+        <v>1.44</v>
+      </c>
+      <c r="AF146">
+        <v>1.32</v>
+      </c>
+      <c r="AG146">
         <v>3.2</v>
       </c>
-      <c r="AC146">
-        <v>1.73</v>
-      </c>
-      <c r="AD146">
-        <v>1.94</v>
-      </c>
-      <c r="AE146">
-        <v>1.4</v>
-      </c>
-      <c r="AF146">
-        <v>1.31</v>
-      </c>
-      <c r="AG146">
-        <v>3.14</v>
-      </c>
       <c r="AH146" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK146">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q147">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="R147">
-        <v>2.46</v>
+        <v>2.95</v>
       </c>
       <c r="S147">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="T147">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="U147">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="V147">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="W147">
+        <v>1.41</v>
+      </c>
+      <c r="X147">
+        <v>0</v>
+      </c>
+      <c r="Y147">
+        <v>1.03</v>
+      </c>
+      <c r="Z147">
+        <v>13</v>
+      </c>
+      <c r="AA147">
+        <v>1.16</v>
+      </c>
+      <c r="AB147">
+        <v>4.5</v>
+      </c>
+      <c r="AC147">
+        <v>1.45</v>
+      </c>
+      <c r="AD147">
+        <v>2.62</v>
+      </c>
+      <c r="AE147">
+        <v>1.82</v>
+      </c>
+      <c r="AF147">
         <v>1.22</v>
       </c>
-      <c r="X147">
-        <v>1.01</v>
-      </c>
-      <c r="Y147">
-        <v>1.05</v>
-      </c>
-      <c r="Z147">
-        <v>6.4</v>
-      </c>
-      <c r="AA147">
-        <v>1.36</v>
-      </c>
-      <c r="AB147">
-        <v>3</v>
-      </c>
-      <c r="AC147">
-        <v>1.93</v>
-      </c>
-      <c r="AD147">
-        <v>1.88</v>
-      </c>
-      <c r="AE147">
-        <v>1.44</v>
-      </c>
-      <c r="AF147">
-        <v>1.32</v>
-      </c>
       <c r="AG147">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK147">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q148">
+        <v>2.05</v>
+      </c>
+      <c r="R148">
+        <v>2.8</v>
+      </c>
+      <c r="S148">
+        <v>1.14</v>
+      </c>
+      <c r="T148">
+        <v>5</v>
+      </c>
+      <c r="U148">
+        <v>1.8</v>
+      </c>
+      <c r="V148">
         <v>1.98</v>
       </c>
-      <c r="R148">
-        <v>2.95</v>
-      </c>
-      <c r="S148">
-        <v>1.11</v>
-      </c>
-      <c r="T148">
-        <v>6.6</v>
-      </c>
-      <c r="U148">
-        <v>1.53</v>
-      </c>
-      <c r="V148">
-        <v>2.38</v>
-      </c>
       <c r="W148">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="X148">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y148">
         <v>1.03</v>
       </c>
       <c r="Z148">
-        <v>13</v>
+        <v>7.7</v>
       </c>
       <c r="AA148">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AB148">
-        <v>5.18</v>
+        <v>3.2</v>
       </c>
       <c r="AC148">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AD148">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="AE148">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AF148">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AG148">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK148">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -26395,7 +26395,7 @@
         <v>3.15</v>
       </c>
       <c r="P160">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26579,7 +26579,7 @@
         <v>1.26</v>
       </c>
       <c r="W161">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X161">
         <v>1.1</v>
@@ -26606,7 +26606,7 @@
         <v>1.04</v>
       </c>
       <c r="AF161">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG161">
         <v>1.7</v>
@@ -26625,7 +26625,7 @@
         <v>1.33</v>
       </c>
       <c r="AK161">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27533,10 +27533,10 @@
         <v>1.36</v>
       </c>
       <c r="O167">
-        <v>5.15</v>
+        <v>4.5</v>
       </c>
       <c r="P167">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q167">
         <v>1.73</v>
@@ -27551,7 +27551,7 @@
         <v>3.85</v>
       </c>
       <c r="U167">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="V167">
         <v>1.75</v>
@@ -27584,7 +27584,7 @@
         <v>1.25</v>
       </c>
       <c r="AF167">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG167">
         <v>2.15</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="O176">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P176">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q176">
         <v>2.3</v>
@@ -29012,7 +29012,7 @@
         <v>2.43</v>
       </c>
       <c r="S176">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T176">
         <v>3.2</v>
@@ -29039,7 +29039,7 @@
         <v>1.7</v>
       </c>
       <c r="AB176">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC176">
         <v>2.88</v>
@@ -29812,19 +29812,19 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O181">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="P181">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Q181">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="R181">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S181">
         <v>1.22</v>
@@ -29851,13 +29851,13 @@
         <v>4.5</v>
       </c>
       <c r="AA181">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB181">
         <v>2.41</v>
       </c>
       <c r="AC181">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AD181">
         <v>1.47</v>
@@ -29866,7 +29866,7 @@
         <v>1.22</v>
       </c>
       <c r="AF181">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG181">
         <v>2.5</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AK181">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29981,7 +29981,7 @@
         <v>3.9</v>
       </c>
       <c r="P182">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q182">
         <v>3.6</v>
@@ -29993,7 +29993,7 @@
         <v>1.25</v>
       </c>
       <c r="T182">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="U182">
         <v>2.2</v>
@@ -30029,10 +30029,10 @@
         <v>1.18</v>
       </c>
       <c r="AF182">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG182">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK182">
         <v>1.3</v>
@@ -30138,16 +30138,16 @@
         </is>
       </c>
       <c r="N183">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="O183">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P183">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="Q183">
-        <v>4.6</v>
+        <v>4.54</v>
       </c>
       <c r="R183">
         <v>2.45</v>
@@ -30156,16 +30156,16 @@
         <v>1.2</v>
       </c>
       <c r="T183">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="U183">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V183">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W183">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X183">
         <v>1.02</v>
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="AK183">
         <v>1.22</v>
@@ -32420,25 +32420,25 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="O197">
         <v>3.75</v>
       </c>
       <c r="P197">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q197">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R197">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S197">
         <v>1.17</v>
       </c>
       <c r="T197">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="U197">
         <v>1.85</v>
@@ -32459,13 +32459,13 @@
         <v>7.4</v>
       </c>
       <c r="AA197">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB197">
         <v>3.5</v>
       </c>
       <c r="AC197">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AD197">
         <v>2.02</v>
@@ -32586,10 +32586,10 @@
         <v>4.8</v>
       </c>
       <c r="O198">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="P198">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q198">
         <v>4.65</v>
@@ -32607,10 +32607,10 @@
         <v>1.91</v>
       </c>
       <c r="V198">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="W198">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X198">
         <v>1.01</v>
@@ -32625,22 +32625,22 @@
         <v>1.3</v>
       </c>
       <c r="AB198">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AC198">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD198">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AE198">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF198">
         <v>1.4</v>
       </c>
       <c r="AG198">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK198">
         <v>1.13</v>
@@ -32764,7 +32764,7 @@
         <v>1.13</v>
       </c>
       <c r="T199">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="U199">
         <v>1.8</v>
@@ -32918,10 +32918,10 @@
         <v>4.15</v>
       </c>
       <c r="Q200">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R200">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="S200">
         <v>1.13</v>
@@ -32954,7 +32954,7 @@
         <v>3.58</v>
       </c>
       <c r="AC200">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AD200">
         <v>2.08</v>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O201">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P201">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Q201">
         <v>4.33</v>
@@ -33087,16 +33087,16 @@
         <v>2.8</v>
       </c>
       <c r="S201">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T201">
         <v>5</v>
       </c>
       <c r="U201">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V201">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="W201">
         <v>1.25</v>
@@ -33108,7 +33108,7 @@
         <v>1.05</v>
       </c>
       <c r="Z201">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AA201">
         <v>1.23</v>
@@ -33126,7 +33126,7 @@
         <v>1.45</v>
       </c>
       <c r="AF201">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG201">
         <v>3</v>
@@ -33142,7 +33142,7 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AK201">
         <v>1.14</v>
@@ -33235,19 +33235,19 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="O202">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P202">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q202">
         <v>2.32</v>
       </c>
       <c r="R202">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="S202">
         <v>1.17</v>
@@ -33268,7 +33268,7 @@
         <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z202">
         <v>6</v>
@@ -33305,7 +33305,7 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK202">
         <v>1.68</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="O203">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P203">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q203">
         <v>2.9</v>
@@ -33416,46 +33416,46 @@
         <v>1.2</v>
       </c>
       <c r="T203">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U203">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="V203">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="W203">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X203">
         <v>1.01</v>
       </c>
       <c r="Y203">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z203">
-        <v>6.02</v>
+        <v>6.42</v>
       </c>
       <c r="AA203">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AB203">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AC203">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AD203">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AE203">
         <v>1.25</v>
       </c>
       <c r="AF203">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG203">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>1.4</v>
       </c>
       <c r="T204">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="U204">
         <v>2.81</v>
@@ -33588,7 +33588,7 @@
         <v>1.36</v>
       </c>
       <c r="W204">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X204">
         <v>1.03</v>
@@ -33609,7 +33609,7 @@
         <v>3.63</v>
       </c>
       <c r="AD204">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE204">
         <v>1.1</v>
@@ -33733,19 +33733,19 @@
         <v>3.25</v>
       </c>
       <c r="Q205">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R205">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S205">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T205">
         <v>2.65</v>
       </c>
       <c r="U205">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="V205">
         <v>1.32</v>
@@ -33754,7 +33754,7 @@
         <v>1.04</v>
       </c>
       <c r="X205">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y205">
         <v>1.4</v>
@@ -33769,7 +33769,7 @@
         <v>1.68</v>
       </c>
       <c r="AC205">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AD205">
         <v>1.24</v>
@@ -33893,19 +33893,19 @@
         <v>4.1</v>
       </c>
       <c r="P206">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Q206">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="R206">
         <v>2.55</v>
       </c>
       <c r="S206">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T206">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="U206">
         <v>2.4</v>
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q207">
         <v>2.43</v>
@@ -34068,22 +34068,22 @@
         <v>1.36</v>
       </c>
       <c r="T207">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U207">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V207">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W207">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X207">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y207">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z207">
         <v>3.05</v>
@@ -34101,7 +34101,7 @@
         <v>1.25</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF207">
         <v>1.82</v>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK207">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34726,7 +34726,7 @@
         <v>2.7</v>
       </c>
       <c r="V211">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W211">
         <v>1.08</v>
@@ -34741,7 +34741,7 @@
         <v>3.28</v>
       </c>
       <c r="AA211">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB211">
         <v>1.85</v>
@@ -34775,7 +34775,7 @@
         <v>1.19</v>
       </c>
       <c r="AK211">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -35680,16 +35680,16 @@
         </is>
       </c>
       <c r="N217">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O217">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="P217">
         <v>1.18</v>
       </c>
       <c r="Q217">
-        <v>6.95</v>
+        <v>6.66</v>
       </c>
       <c r="R217">
         <v>3.5</v>
@@ -35701,10 +35701,10 @@
         <v>5.5</v>
       </c>
       <c r="U217">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="V217">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="W217">
         <v>1.36</v>
@@ -35750,7 +35750,7 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AK217">
         <v>1.02</v>
@@ -35858,10 +35858,10 @@
         <v>2.1</v>
       </c>
       <c r="S218">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T218">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U218">
         <v>2.7</v>
@@ -35900,7 +35900,7 @@
         <v>1.63</v>
       </c>
       <c r="AG218">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AK218">
         <v>1.4</v>
@@ -38798,7 +38798,7 @@
         <v>2.88</v>
       </c>
       <c r="U236">
-        <v>2.81</v>
+        <v>3.19</v>
       </c>
       <c r="V236">
         <v>1.34</v>
@@ -38819,10 +38819,10 @@
         <v>2.16</v>
       </c>
       <c r="AB236">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC236">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="AD236">
         <v>1.25</v>
@@ -40081,10 +40081,10 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O244">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P244">
         <v>4.55</v>
@@ -40105,7 +40105,7 @@
         <v>3.2</v>
       </c>
       <c r="V244">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W244">
         <v>1.06</v>
@@ -40117,7 +40117,7 @@
         <v>1.39</v>
       </c>
       <c r="Z244">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA244">
         <v>2.2</v>
@@ -40126,10 +40126,10 @@
         <v>1.65</v>
       </c>
       <c r="AC244">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD244">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE244">
         <v>1.04</v>
@@ -40138,7 +40138,7 @@
         <v>2</v>
       </c>
       <c r="AG244">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>1.21</v>
       </c>
       <c r="AK244">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O249">
-        <v>3.58</v>
+        <v>3.17</v>
       </c>
       <c r="P249">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -43842,7 +43842,7 @@
         <v>2.8</v>
       </c>
       <c r="R267">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S267">
         <v>1.3</v>
@@ -43851,10 +43851,10 @@
         <v>3.6</v>
       </c>
       <c r="U267">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="V267">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W267">
         <v>1.1</v>
@@ -43875,13 +43875,13 @@
         <v>2.2</v>
       </c>
       <c r="AC267">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="AD267">
         <v>1.46</v>
       </c>
       <c r="AE267">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF267">
         <v>1.5</v>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK267">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -45481,7 +45481,7 @@
         <v>2.63</v>
       </c>
       <c r="U277">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V277">
         <v>1.33</v>
@@ -45533,7 +45533,7 @@
         <v>1.25</v>
       </c>
       <c r="AK277">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O280">
         <v>3.6</v>
       </c>
       <c r="P280">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q280">
         <v>3.8</v>
@@ -45988,7 +45988,7 @@
         <v>3.95</v>
       </c>
       <c r="AA280">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB280">
         <v>2</v>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
+        <v>1.89</v>
+      </c>
+      <c r="AK280">
         <v>1.2</v>
-      </c>
-      <c r="AK280">
-        <v>1.18</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46616,16 +46616,16 @@
         <v>2</v>
       </c>
       <c r="S284">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="T284">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="U284">
         <v>3.2</v>
       </c>
       <c r="V284">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W284">
         <v>1.05</v>
@@ -46640,10 +46640,10 @@
         <v>2.75</v>
       </c>
       <c r="AA284">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AB284">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC284">
         <v>4.1</v>
@@ -48255,7 +48255,7 @@
         <v>1.95</v>
       </c>
       <c r="V294">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W294">
         <v>1.16</v>
@@ -48285,10 +48285,10 @@
         <v>1.3</v>
       </c>
       <c r="AF294">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG294">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48394,25 +48394,25 @@
         </is>
       </c>
       <c r="N295">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="O295">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="P295">
         <v>1.67</v>
       </c>
       <c r="Q295">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="R295">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S295">
         <v>1.29</v>
       </c>
       <c r="T295">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U295">
         <v>2.55</v>
@@ -48424,19 +48424,19 @@
         <v>1.08</v>
       </c>
       <c r="X295">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y295">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z295">
-        <v>3.35</v>
+        <v>3.89</v>
       </c>
       <c r="AA295">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB295">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC295">
         <v>3.1</v>
@@ -48448,7 +48448,7 @@
         <v>1.13</v>
       </c>
       <c r="AF295">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG295">
         <v>1.91</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O296">
         <v>3.75</v>
       </c>
       <c r="P296">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q296">
         <v>2.33</v>
@@ -48602,7 +48602,7 @@
         <v>1.83</v>
       </c>
       <c r="AC296">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="AD296">
         <v>1.29</v>
@@ -48611,7 +48611,7 @@
         <v>1.11</v>
       </c>
       <c r="AF296">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG296">
         <v>1.9</v>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK296">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48726,7 +48726,7 @@
         <v>3.3</v>
       </c>
       <c r="P297">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q297">
         <v>2.3</v>
@@ -48741,7 +48741,7 @@
         <v>2.88</v>
       </c>
       <c r="U297">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V297">
         <v>1.36</v>
@@ -48750,7 +48750,7 @@
         <v>1.07</v>
       </c>
       <c r="X297">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y297">
         <v>1.27</v>
@@ -48762,16 +48762,16 @@
         <v>1.9</v>
       </c>
       <c r="AB297">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC297">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD297">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE297">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF297">
         <v>1.79</v>
@@ -48886,10 +48886,10 @@
         <v>1.17</v>
       </c>
       <c r="O298">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="P298">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q298">
         <v>1.44</v>
@@ -48925,10 +48925,10 @@
         <v>1.27</v>
       </c>
       <c r="AB298">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AC298">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AD298">
         <v>1.94</v>
@@ -48940,7 +48940,7 @@
         <v>1.67</v>
       </c>
       <c r="AG298">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,7 +48953,7 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK298">
         <v>4.5</v>
@@ -49544,7 +49544,7 @@
         <v>2.95</v>
       </c>
       <c r="Q302">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="R302">
         <v>1.95</v>
@@ -49562,16 +49562,16 @@
         <v>1.28</v>
       </c>
       <c r="W302">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X302">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y302">
         <v>1.41</v>
       </c>
       <c r="Z302">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AA302">
         <v>2.5</v>
@@ -49586,13 +49586,13 @@
         <v>1.14</v>
       </c>
       <c r="AE302">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF302">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG302">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK302">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="O303">
-        <v>4.16</v>
+        <v>3.55</v>
       </c>
       <c r="P303">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49737,10 +49737,10 @@
         <v>0</v>
       </c>
       <c r="AA303">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB303">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC303">
         <v>0</v>
@@ -51165,10 +51165,10 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O312">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P312">
         <v>7.5</v>
@@ -51177,28 +51177,28 @@
         <v>1.85</v>
       </c>
       <c r="R312">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S312">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T312">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="U312">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="V312">
         <v>1.42</v>
       </c>
       <c r="W312">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X312">
         <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z312">
         <v>3.4</v>
@@ -51219,10 +51219,10 @@
         <v>1.09</v>
       </c>
       <c r="AF312">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG312">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51349,10 +51349,10 @@
         <v>3.5</v>
       </c>
       <c r="U313">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V313">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W313">
         <v>1.13</v>
@@ -51379,7 +51379,7 @@
         <v>1.44</v>
       </c>
       <c r="AE313">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF313">
         <v>1.77</v>
@@ -51398,7 +51398,7 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK313">
         <v>2.8</v>
@@ -51491,13 +51491,13 @@
         </is>
       </c>
       <c r="N314">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O314">
         <v>3.2</v>
       </c>
       <c r="P314">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q314">
         <v>2.46</v>
@@ -51518,34 +51518,34 @@
         <v>1.27</v>
       </c>
       <c r="W314">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X314">
         <v>1.09</v>
       </c>
       <c r="Y314">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z314">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AA314">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB314">
         <v>1.61</v>
       </c>
       <c r="AC314">
-        <v>4.14</v>
+        <v>4.5</v>
       </c>
       <c r="AD314">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE314">
         <v>1.05</v>
       </c>
       <c r="AF314">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG314">
         <v>1.74</v>
@@ -51980,19 +51980,19 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O317">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P317">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q317">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R317">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S317">
         <v>1.22</v>
@@ -52001,10 +52001,10 @@
         <v>3.8</v>
       </c>
       <c r="U317">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="V317">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W317">
         <v>1.15</v>
@@ -52013,10 +52013,10 @@
         <v>1.02</v>
       </c>
       <c r="Y317">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z317">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA317">
         <v>1.54</v>
@@ -52031,13 +52031,13 @@
         <v>1.48</v>
       </c>
       <c r="AE317">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF317">
         <v>1.44</v>
       </c>
       <c r="AG317">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52143,16 +52143,16 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="O318">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P318">
         <v>3.25</v>
       </c>
       <c r="Q318">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="R318">
         <v>1.83</v>
@@ -52176,22 +52176,22 @@
         <v>1.06</v>
       </c>
       <c r="Y318">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z318">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AA318">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AB318">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AC318">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AD318">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE318">
         <v>1.01</v>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK318">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52469,19 +52469,19 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O320">
-        <v>3.72</v>
+        <v>3.57</v>
       </c>
       <c r="P320">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="Q320">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="R320">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S320">
         <v>1.23</v>
@@ -52490,10 +52490,10 @@
         <v>3.75</v>
       </c>
       <c r="U320">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V320">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W320">
         <v>1.14</v>
@@ -52505,16 +52505,16 @@
         <v>1.14</v>
       </c>
       <c r="Z320">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="AA320">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB320">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AC320">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD320">
         <v>1.65</v>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK320">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,64 +52632,64 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O321">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="P321">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q321">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="R321">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S321">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T321">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="U321">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="V321">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W321">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X321">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y321">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z321">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA321">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB321">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC321">
-        <v>4.05</v>
+        <v>4.52</v>
       </c>
       <c r="AD321">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE321">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF321">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AG321">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK321">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="O322">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="P322">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="Q322">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="R322">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S322">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T322">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="U322">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="V322">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W322">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X322">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y322">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z322">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AA322">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB322">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC322">
-        <v>4.52</v>
+        <v>4.05</v>
       </c>
       <c r="AD322">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE322">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF322">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AG322">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK322">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>4.92</v>
+        <v>4.97</v>
       </c>
       <c r="O323">
         <v>4.1</v>
       </c>
       <c r="P323">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -52997,10 +52997,10 @@
         <v>0</v>
       </c>
       <c r="AA323">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AB323">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AC323">
         <v>0</v>
@@ -53133,7 +53133,7 @@
         <v>1.62</v>
       </c>
       <c r="R324">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="S324">
         <v>1.18</v>
@@ -53148,13 +53148,13 @@
         <v>1.8</v>
       </c>
       <c r="W324">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X324">
         <v>1.01</v>
       </c>
       <c r="Y324">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z324">
         <v>6</v>
@@ -53166,10 +53166,10 @@
         <v>3</v>
       </c>
       <c r="AC324">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AD324">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AE324">
         <v>1.3</v>
@@ -53194,7 +53194,7 @@
         <v>1.04</v>
       </c>
       <c r="AK324">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="O325">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P325">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q325">
         <v>2.85</v>
@@ -53314,25 +53314,25 @@
         <v>1.1</v>
       </c>
       <c r="X325">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y325">
         <v>1.24</v>
       </c>
       <c r="Z325">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AA325">
         <v>1.82</v>
       </c>
       <c r="AB325">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC325">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD325">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE325">
         <v>1.11</v>
@@ -53447,37 +53447,37 @@
         </is>
       </c>
       <c r="N326">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O326">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P326">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="Q326">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="R326">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="S326">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="T326">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="U326">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V326">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W326">
         <v>1.05</v>
       </c>
       <c r="X326">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y326">
         <v>1.34</v>
@@ -53486,22 +53486,22 @@
         <v>2.95</v>
       </c>
       <c r="AA326">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AB326">
         <v>1.65</v>
       </c>
       <c r="AC326">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="AD326">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE326">
         <v>1.06</v>
       </c>
       <c r="AF326">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AG326">
         <v>1.65</v>
@@ -53610,13 +53610,13 @@
         </is>
       </c>
       <c r="N327">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="O327">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P327">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="Q327">
         <v>3.75</v>
@@ -53661,7 +53661,7 @@
         <v>1.31</v>
       </c>
       <c r="AE327">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF327">
         <v>1.67</v>
@@ -53794,10 +53794,10 @@
         <v>4.8</v>
       </c>
       <c r="U328">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="V328">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W328">
         <v>1.2</v>
@@ -53815,7 +53815,7 @@
         <v>1.3</v>
       </c>
       <c r="AB328">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AC328">
         <v>1.9</v>
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="O329">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P329">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Q329">
         <v>5.5</v>
@@ -53981,7 +53981,7 @@
         <v>2.88</v>
       </c>
       <c r="AC329">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AD329">
         <v>1.73</v>
@@ -53990,7 +53990,7 @@
         <v>1.3</v>
       </c>
       <c r="AF329">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG329">
         <v>2.38</v>
@@ -54006,7 +54006,7 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.13</v>
+        <v>2.68</v>
       </c>
       <c r="AK329">
         <v>1.1</v>
@@ -54135,7 +54135,7 @@
         <v>1.14</v>
       </c>
       <c r="Z330">
-        <v>5.75</v>
+        <v>5.61</v>
       </c>
       <c r="AA330">
         <v>1.47</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -4556,10 +4556,10 @@
         <v>2.29</v>
       </c>
       <c r="Q26">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S26">
         <v>1.43</v>
@@ -4598,7 +4598,7 @@
         <v>1.2</v>
       </c>
       <c r="AE26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF26">
         <v>1.85</v>
@@ -12703,7 +12703,7 @@
         <v>3.7</v>
       </c>
       <c r="P76">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="Q76">
         <v>2.38</v>
@@ -16651,7 +16651,7 @@
         <v>2.2</v>
       </c>
       <c r="AB100">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC100">
         <v>3.91</v>
@@ -16666,7 +16666,7 @@
         <v>1.85</v>
       </c>
       <c r="AG100">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,61 +23944,61 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.55</v>
+        <v>2.08</v>
       </c>
       <c r="O145">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="P145">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q145">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="R145">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="S145">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T145">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="U145">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="V145">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="W145">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="X145">
         <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z145">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA145">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AB145">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AC145">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AD145">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AE145">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AF145">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AG145">
         <v>3.2</v>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK145">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
       <c r="O146">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="P146">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="Q146">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="R146">
-        <v>2.46</v>
+        <v>2.95</v>
       </c>
       <c r="S146">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="T146">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="U146">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="V146">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="W146">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="X146">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y146">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z146">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AA146">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AB146">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AC146">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AD146">
-        <v>1.88</v>
+        <v>2.62</v>
       </c>
       <c r="AE146">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AF146">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AG146">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK146">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,80 +24270,80 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O147">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="P147">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="Q147">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R147">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="S147">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="T147">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="U147">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="V147">
+        <v>1.94</v>
+      </c>
+      <c r="W147">
+        <v>1.26</v>
+      </c>
+      <c r="X147">
+        <v>1.01</v>
+      </c>
+      <c r="Y147">
+        <v>1.06</v>
+      </c>
+      <c r="Z147">
+        <v>7.5</v>
+      </c>
+      <c r="AA147">
+        <v>1.27</v>
+      </c>
+      <c r="AB147">
+        <v>3.4</v>
+      </c>
+      <c r="AC147">
+        <v>1.73</v>
+      </c>
+      <c r="AD147">
+        <v>2.05</v>
+      </c>
+      <c r="AE147">
+        <v>1.41</v>
+      </c>
+      <c r="AF147">
+        <v>1.34</v>
+      </c>
+      <c r="AG147">
+        <v>3.2</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ147">
+        <v>1.18</v>
+      </c>
+      <c r="AK147">
         <v>2.38</v>
-      </c>
-      <c r="W147">
-        <v>1.41</v>
-      </c>
-      <c r="X147">
-        <v>0</v>
-      </c>
-      <c r="Y147">
-        <v>1.03</v>
-      </c>
-      <c r="Z147">
-        <v>13</v>
-      </c>
-      <c r="AA147">
-        <v>1.16</v>
-      </c>
-      <c r="AB147">
-        <v>4.5</v>
-      </c>
-      <c r="AC147">
-        <v>1.45</v>
-      </c>
-      <c r="AD147">
-        <v>2.62</v>
-      </c>
-      <c r="AE147">
-        <v>1.82</v>
-      </c>
-      <c r="AF147">
-        <v>1.22</v>
-      </c>
-      <c r="AG147">
-        <v>3.9</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>1.17</v>
-      </c>
-      <c r="AK147">
-        <v>2.28</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -26715,7 +26715,7 @@
         </is>
       </c>
       <c r="N162">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="O162">
         <v>8</v>
@@ -26730,19 +26730,19 @@
         <v>3.1</v>
       </c>
       <c r="S162">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T162">
         <v>4.75</v>
       </c>
       <c r="U162">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V162">
         <v>1.98</v>
       </c>
       <c r="W162">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X162">
         <v>1.01</v>
@@ -26751,13 +26751,13 @@
         <v>1.06</v>
       </c>
       <c r="Z162">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AA162">
         <v>1.26</v>
       </c>
       <c r="AB162">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AC162">
         <v>1.77</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O165">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P165">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q165">
         <v>3.24</v>
@@ -34053,10 +34053,10 @@
         <v>1.85</v>
       </c>
       <c r="O207">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P207">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q207">
         <v>2.43</v>
@@ -34068,22 +34068,22 @@
         <v>1.36</v>
       </c>
       <c r="T207">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U207">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V207">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W207">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X207">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y207">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z207">
         <v>3.05</v>
@@ -34101,7 +34101,7 @@
         <v>1.25</v>
       </c>
       <c r="AE207">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF207">
         <v>1.82</v>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK207">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G223">
@@ -36667,55 +36667,55 @@
         <v>0</v>
       </c>
       <c r="Q223">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="R223">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S223">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T223">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U223">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V223">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W223">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X223">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y223">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z223">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="AA223">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AB223">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC223">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AD223">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE223">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF223">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG223">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK223">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G224">
@@ -36830,55 +36830,55 @@
         <v>0</v>
       </c>
       <c r="Q224">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R224">
+        <v>2.05</v>
+      </c>
+      <c r="S224">
+        <v>1.44</v>
+      </c>
+      <c r="T224">
+        <v>2.5</v>
+      </c>
+      <c r="U224">
+        <v>3.2</v>
+      </c>
+      <c r="V224">
+        <v>1.3</v>
+      </c>
+      <c r="W224">
+        <v>1.06</v>
+      </c>
+      <c r="X224">
+        <v>1.09</v>
+      </c>
+      <c r="Y224">
+        <v>1.39</v>
+      </c>
+      <c r="Z224">
+        <v>2.59</v>
+      </c>
+      <c r="AA224">
         <v>2.2</v>
       </c>
-      <c r="S224">
-        <v>1.36</v>
-      </c>
-      <c r="T224">
-        <v>2.47</v>
-      </c>
-      <c r="U224">
-        <v>2.8</v>
-      </c>
-      <c r="V224">
-        <v>1.36</v>
-      </c>
-      <c r="W224">
-        <v>1.07</v>
-      </c>
-      <c r="X224">
-        <v>1.05</v>
-      </c>
-      <c r="Y224">
-        <v>1.32</v>
-      </c>
-      <c r="Z224">
-        <v>3.04</v>
-      </c>
-      <c r="AA224">
-        <v>1.99</v>
-      </c>
       <c r="AB224">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC224">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AD224">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE224">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF224">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG224">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK224">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -40431,7 +40431,7 @@
         <v>4.5</v>
       </c>
       <c r="V246">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W246">
         <v>1</v>
@@ -40464,7 +40464,7 @@
         <v>2.39</v>
       </c>
       <c r="AG246">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O277">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P277">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q277">
         <v>2.44</v>
@@ -45533,7 +45533,7 @@
         <v>1.25</v>
       </c>
       <c r="AK277">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O293">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P293">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="Q293">
         <v>3.75</v>
@@ -48119,7 +48119,7 @@
         <v>1.16</v>
       </c>
       <c r="AE293">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF293">
         <v>1.95</v>
@@ -48904,10 +48904,10 @@
         <v>5</v>
       </c>
       <c r="U298">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="V298">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="W298">
         <v>1.29</v>
@@ -49870,10 +49870,10 @@
         <v>2.31</v>
       </c>
       <c r="Q304">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="R304">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S304">
         <v>1.29</v>
@@ -50519,7 +50519,7 @@
         <v>2.95</v>
       </c>
       <c r="P308">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q308">
         <v>2.8</v>
@@ -50558,7 +50558,7 @@
         <v>1.46</v>
       </c>
       <c r="AC308">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="AD308">
         <v>1.13</v>
@@ -52795,7 +52795,7 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="O322">
         <v>2.97</v>
@@ -52840,7 +52840,7 @@
         <v>1.61</v>
       </c>
       <c r="AC322">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD322">
         <v>1.24</v>
@@ -52865,7 +52865,7 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK322">
         <v>1.87</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -1290,10 +1290,10 @@
         <v>2.05</v>
       </c>
       <c r="O6">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>2.99</v>
+        <v>3.34</v>
       </c>
       <c r="Q6">
         <v>2.45</v>
@@ -1305,16 +1305,16 @@
         <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
         <v>1.02</v>
@@ -1323,28 +1323,28 @@
         <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AA6">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB6">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC6">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD6">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE6">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
         <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1616,10 +1616,10 @@
         <v>2.75</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,52 +1776,52 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P9">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q9">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S9">
         <v>1.43</v>
       </c>
       <c r="T9">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AA9">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="AD9">
         <v>1.23</v>
@@ -1833,7 +1833,7 @@
         <v>1.74</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK9">
         <v>1.4</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.85</v>
+        <v>2.37</v>
       </c>
       <c r="R10">
         <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="U10">
         <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA10">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="AD10">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q11">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="R11">
         <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
         <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
+        <v>3.3</v>
+      </c>
+      <c r="AA11">
+        <v>1.9</v>
+      </c>
+      <c r="AB11">
+        <v>1.8</v>
+      </c>
+      <c r="AC11">
         <v>3.4</v>
       </c>
-      <c r="AA11">
-        <v>1.95</v>
-      </c>
-      <c r="AB11">
-        <v>1.85</v>
-      </c>
-      <c r="AC11">
-        <v>3.11</v>
-      </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O13">
         <v>3.6</v>
       </c>
       <c r="P13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB13">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O16">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P16">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O17">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="P17">
         <v>2.5</v>
@@ -3246,10 +3246,10 @@
         <v>3.4</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="O19">
         <v>3.5</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -3427,22 +3427,22 @@
         <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W19">
         <v>1.14</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
         <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="AA19">
         <v>1.57</v>
@@ -3451,19 +3451,19 @@
         <v>2.25</v>
       </c>
       <c r="AC19">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AD19">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3738,19 +3738,19 @@
         <v>2.85</v>
       </c>
       <c r="P21">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S21">
         <v>1.49</v>
       </c>
       <c r="T21">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="U21">
         <v>3.18</v>
@@ -3765,7 +3765,7 @@
         <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z21">
         <v>2.62</v>
@@ -3786,10 +3786,10 @@
         <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG21">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.38</v>
       </c>
       <c r="AK21">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,19 +3904,19 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
         <v>2</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T22">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="V22">
         <v>1.33</v>
@@ -3934,10 +3934,10 @@
         <v>2.74</v>
       </c>
       <c r="AA22">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB22">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC22">
         <v>3.74</v>
@@ -3952,7 +3952,7 @@
         <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="P28">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O29">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P29">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB30">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q31">
         <v>2.64</v>
@@ -5395,10 +5395,10 @@
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z31">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AA31">
         <v>2.2</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
         <v>1.67</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="O32">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="P32">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O39">
         <v>3.3</v>
@@ -7170,28 +7170,28 @@
         <v>2.38</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
         <v>3.6</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="V42">
         <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA42">
         <v>1.63</v>
@@ -7203,7 +7203,7 @@
         <v>2.65</v>
       </c>
       <c r="AD42">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE42">
         <v>1.16</v>
@@ -7212,7 +7212,7 @@
         <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O43">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="P43">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O45">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P45">
-        <v>5.5</v>
+        <v>5.39</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="R45">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T45">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="U45">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="V45">
         <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
         <v>1.04</v>
@@ -7683,25 +7683,25 @@
         <v>3.7</v>
       </c>
       <c r="AA45">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB45">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC45">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AD45">
         <v>1.33</v>
       </c>
       <c r="AE45">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AG45">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK45">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -9283,22 +9283,22 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>5.32</v>
+        <v>5.5</v>
       </c>
       <c r="R55">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S55">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T55">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="U55">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V55">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W55">
         <v>1.07</v>
@@ -9310,10 +9310,10 @@
         <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AA55">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB55">
         <v>2</v>
@@ -9331,7 +9331,7 @@
         <v>1.68</v>
       </c>
       <c r="AG55">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK55">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9944,16 +9944,16 @@
         <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U59">
         <v>2.25</v>
       </c>
       <c r="V59">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W59">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
         <v>1.03</v>
@@ -9962,16 +9962,16 @@
         <v>1.1</v>
       </c>
       <c r="Z59">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="AA59">
         <v>1.57</v>
       </c>
       <c r="AB59">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC59">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AD59">
         <v>1.5</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK59">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10910,25 +10910,25 @@
         <v>3.2</v>
       </c>
       <c r="P65">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="Q65">
-        <v>2.54</v>
+        <v>2.83</v>
       </c>
       <c r="R65">
         <v>1.95</v>
       </c>
       <c r="S65">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T65">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="U65">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="V65">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
         <v>1.02</v>
@@ -10937,19 +10937,19 @@
         <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z65">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AA65">
         <v>2.39</v>
       </c>
       <c r="AB65">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC65">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="AD65">
         <v>1.17</v>
@@ -10977,7 +10977,7 @@
         <v>1.37</v>
       </c>
       <c r="AK65">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="Q66">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="R66">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S66">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U66">
+        <v>2.62</v>
+      </c>
+      <c r="V66">
+        <v>1.4</v>
+      </c>
+      <c r="W66">
+        <v>1.06</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="Y66">
+        <v>1.23</v>
+      </c>
+      <c r="Z66">
+        <v>3.5</v>
+      </c>
+      <c r="AA66">
+        <v>1.8</v>
+      </c>
+      <c r="AB66">
+        <v>1.89</v>
+      </c>
+      <c r="AC66">
         <v>2.88</v>
       </c>
-      <c r="V66">
-        <v>1.35</v>
-      </c>
-      <c r="W66">
-        <v>1.04</v>
-      </c>
-      <c r="X66">
-        <v>1.03</v>
-      </c>
-      <c r="Y66">
-        <v>1.3</v>
-      </c>
-      <c r="Z66">
-        <v>2.97</v>
-      </c>
-      <c r="AA66">
-        <v>2.05</v>
-      </c>
-      <c r="AB66">
-        <v>1.75</v>
-      </c>
-      <c r="AC66">
-        <v>3.34</v>
-      </c>
       <c r="AD66">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE66">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG66">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="Q67">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="R67">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S67">
+        <v>1.43</v>
+      </c>
+      <c r="T67">
+        <v>2.5</v>
+      </c>
+      <c r="U67">
+        <v>2.88</v>
+      </c>
+      <c r="V67">
+        <v>1.35</v>
+      </c>
+      <c r="W67">
+        <v>1.04</v>
+      </c>
+      <c r="X67">
+        <v>1.03</v>
+      </c>
+      <c r="Y67">
         <v>1.3</v>
       </c>
-      <c r="T67">
-        <v>3</v>
-      </c>
-      <c r="U67">
-        <v>2.62</v>
-      </c>
-      <c r="V67">
-        <v>1.4</v>
-      </c>
-      <c r="W67">
-        <v>1.06</v>
-      </c>
-      <c r="X67">
-        <v>1</v>
-      </c>
-      <c r="Y67">
-        <v>1.23</v>
-      </c>
       <c r="Z67">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA67">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB67">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AC67">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD67">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE67">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AK67">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="O70">
         <v>3.6</v>
@@ -11734,25 +11734,25 @@
         <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T70">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="U70">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V70">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W70">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X70">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z70">
         <v>3.6</v>
@@ -11761,22 +11761,22 @@
         <v>1.85</v>
       </c>
       <c r="AB70">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC70">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD70">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE70">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF70">
         <v>1.73</v>
       </c>
       <c r="AG70">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
         <v>1.95</v>
@@ -12371,34 +12371,34 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P74">
         <v>4.6</v>
       </c>
       <c r="Q74">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R74">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="S74">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T74">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U74">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V74">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W74">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X74">
         <v>1.01</v>
@@ -12407,16 +12407,16 @@
         <v>1.36</v>
       </c>
       <c r="Z74">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA74">
         <v>2.16</v>
       </c>
       <c r="AB74">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC74">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD74">
         <v>1.25</v>
@@ -12425,10 +12425,10 @@
         <v>1.07</v>
       </c>
       <c r="AF74">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AG74">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>1.25</v>
       </c>
       <c r="AK74">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13192,19 +13192,19 @@
         <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="Q79">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R79">
         <v>2</v>
       </c>
       <c r="S79">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T79">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -13216,34 +13216,34 @@
         <v>1.05</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y79">
         <v>1.33</v>
       </c>
       <c r="Z79">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="AA79">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB79">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC79">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD79">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE79">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF79">
         <v>1.75</v>
       </c>
       <c r="AG79">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK79">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O80">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="P80">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -13364,16 +13364,16 @@
         <v>2.4</v>
       </c>
       <c r="S80">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="U80">
         <v>2.16</v>
       </c>
       <c r="V80">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W80">
         <v>1.15</v>
@@ -13382,10 +13382,10 @@
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z80">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA80">
         <v>1.5</v>
@@ -13394,7 +13394,7 @@
         <v>2.55</v>
       </c>
       <c r="AC80">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AD80">
         <v>1.62</v>
@@ -13406,7 +13406,7 @@
         <v>1.47</v>
       </c>
       <c r="AG80">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="AK80">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="O81">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P81">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -13536,7 +13536,7 @@
         <v>2.2</v>
       </c>
       <c r="V81">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W81">
         <v>1.11</v>
@@ -13548,13 +13548,13 @@
         <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="AA81">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB81">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC81">
         <v>2.45</v>
@@ -13563,10 +13563,10 @@
         <v>1.5</v>
       </c>
       <c r="AE81">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF81">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG81">
         <v>2.25</v>
@@ -13585,7 +13585,7 @@
         <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,22 +13675,22 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O82">
         <v>3.6</v>
       </c>
       <c r="P82">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="Q82">
         <v>2.27</v>
       </c>
       <c r="R82">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S82">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T82">
         <v>2.79</v>
@@ -13699,13 +13699,13 @@
         <v>2.6</v>
       </c>
       <c r="V82">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W82">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
         <v>1.25</v>
@@ -13717,10 +13717,10 @@
         <v>1.8</v>
       </c>
       <c r="AB82">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC82">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD82">
         <v>1.33</v>
@@ -13729,7 +13729,7 @@
         <v>1.09</v>
       </c>
       <c r="AF82">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG82">
         <v>2</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O85">
         <v>3.1</v>
@@ -14173,34 +14173,34 @@
         <v>3.65</v>
       </c>
       <c r="Q85">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R85">
         <v>1.96</v>
       </c>
       <c r="S85">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T85">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U85">
-        <v>3.24</v>
+        <v>2.86</v>
       </c>
       <c r="V85">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X85">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y85">
         <v>1.36</v>
       </c>
       <c r="Z85">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA85">
         <v>2.17</v>
@@ -14209,16 +14209,16 @@
         <v>1.64</v>
       </c>
       <c r="AC85">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AD85">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE85">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF85">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG85">
         <v>1.83</v>
@@ -14237,7 +14237,7 @@
         <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,10 +14336,10 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="R86">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S86">
         <v>1.35</v>
@@ -14357,13 +14357,13 @@
         <v>1.05</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y86">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z86">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA86">
         <v>2</v>
@@ -14372,19 +14372,19 @@
         <v>1.8</v>
       </c>
       <c r="AC86">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD86">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE86">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF86">
         <v>1.85</v>
       </c>
       <c r="AG86">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>2.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK86">
         <v>1.08</v>
@@ -14490,16 +14490,16 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="O87">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P87">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q87">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="R87">
         <v>2.5</v>
@@ -14520,7 +14520,7 @@
         <v>1.14</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
         <v>1.15</v>
@@ -14532,22 +14532,22 @@
         <v>1.53</v>
       </c>
       <c r="AB87">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="AC87">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AD87">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE87">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF87">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG87">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="O89">
         <v>3.4</v>
       </c>
       <c r="P89">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
       </c>
       <c r="R89">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S89">
         <v>1.29</v>
@@ -14846,10 +14846,10 @@
         <v>1.08</v>
       </c>
       <c r="X89">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z89">
         <v>4.1</v>
@@ -14858,16 +14858,16 @@
         <v>1.7</v>
       </c>
       <c r="AB89">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC89">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AD89">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE89">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF89">
         <v>1.57</v>
@@ -15009,7 +15009,7 @@
         <v>1.07</v>
       </c>
       <c r="X90">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y90">
         <v>1.25</v>
@@ -15021,16 +15021,16 @@
         <v>1.83</v>
       </c>
       <c r="AB90">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC90">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD90">
         <v>1.34</v>
       </c>
       <c r="AE90">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
         <v>1.7</v>
@@ -15052,7 +15052,7 @@
         <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15160,16 +15160,16 @@
         <v>1.24</v>
       </c>
       <c r="T91">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="U91">
         <v>2.09</v>
       </c>
       <c r="V91">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="W91">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X91">
         <v>1.01</v>
@@ -15181,25 +15181,25 @@
         <v>6</v>
       </c>
       <c r="AA91">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB91">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AC91">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AD91">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AE91">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF91">
         <v>1.44</v>
       </c>
       <c r="AG91">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK91">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15631,10 +15631,10 @@
         </is>
       </c>
       <c r="N94">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O94">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P94">
         <v>3.5</v>
@@ -15646,16 +15646,16 @@
         <v>2</v>
       </c>
       <c r="S94">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T94">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U94">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="V94">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W94">
         <v>1.04</v>
@@ -15667,13 +15667,13 @@
         <v>1.36</v>
       </c>
       <c r="Z94">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA94">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB94">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC94">
         <v>4</v>
@@ -15682,13 +15682,13 @@
         <v>1.2</v>
       </c>
       <c r="AE94">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF94">
         <v>1.91</v>
       </c>
       <c r="AG94">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15797,49 +15797,49 @@
         <v>1.8</v>
       </c>
       <c r="O95">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P95">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
       </c>
       <c r="R95">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S95">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T95">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U95">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V95">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W95">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X95">
         <v>1.06</v>
       </c>
       <c r="Y95">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z95">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA95">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB95">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC95">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="AD95">
         <v>1.22</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK95">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16120,25 +16120,25 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O97">
         <v>2.9</v>
       </c>
       <c r="P97">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q97">
         <v>3.4</v>
       </c>
       <c r="R97">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S97">
         <v>1.5</v>
       </c>
       <c r="T97">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U97">
         <v>3.5</v>
@@ -16159,10 +16159,10 @@
         <v>2.45</v>
       </c>
       <c r="AA97">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AB97">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC97">
         <v>5</v>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
         <v>1.39</v>
@@ -16298,10 +16298,10 @@
         <v>1.85</v>
       </c>
       <c r="S98">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="T98">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="U98">
         <v>3.75</v>
@@ -16313,13 +16313,13 @@
         <v>1.03</v>
       </c>
       <c r="X98">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y98">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="Z98">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="AA98">
         <v>2.62</v>
@@ -16328,10 +16328,10 @@
         <v>1.4</v>
       </c>
       <c r="AC98">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AD98">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE98">
         <v>1.03</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK98">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>5.15</v>
+        <v>4.5</v>
       </c>
       <c r="R105">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S105">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T105">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U105">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V105">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W105">
         <v>1.1</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z105">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA105">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB105">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC105">
         <v>2.52</v>
       </c>
       <c r="AD105">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE105">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF105">
         <v>1.67</v>
       </c>
       <c r="AG105">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK105">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G106">
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>1.95</v>
+        <v>2.96</v>
       </c>
       <c r="R106">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S106">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T106">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="U106">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="V106">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X106">
         <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z106">
-        <v>3.96</v>
+        <v>3.34</v>
       </c>
       <c r="AA106">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AB106">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC106">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD106">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE106">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF106">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AK106">
-        <v>2.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="R107">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U107">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="V107">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z107">
-        <v>3.34</v>
+        <v>3.96</v>
       </c>
       <c r="AA107">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AB107">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AC107">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AD107">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG107">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK107">
-        <v>1.47</v>
+        <v>2.55</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O108">
         <v>3.1</v>
@@ -17931,28 +17931,28 @@
         <v>1.5</v>
       </c>
       <c r="T108">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U108">
         <v>3.2</v>
       </c>
       <c r="V108">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W108">
         <v>1.04</v>
       </c>
       <c r="X108">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y108">
         <v>1.44</v>
       </c>
       <c r="Z108">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AA108">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AB108">
         <v>1.44</v>
@@ -17964,7 +17964,7 @@
         <v>1.14</v>
       </c>
       <c r="AE108">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF108">
         <v>2.1</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK108">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18079,52 +18079,52 @@
         <v>2.5</v>
       </c>
       <c r="O109">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P109">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q109">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R109">
         <v>1.95</v>
       </c>
       <c r="S109">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T109">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="U109">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V109">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W109">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X109">
         <v>1.1</v>
       </c>
       <c r="Y109">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z109">
         <v>2.5</v>
       </c>
       <c r="AA109">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AB109">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC109">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD109">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE109">
         <v>1.04</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK109">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18254,46 +18254,46 @@
         <v>2.05</v>
       </c>
       <c r="S110">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T110">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="U110">
         <v>3.03</v>
       </c>
       <c r="V110">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W110">
         <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y110">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z110">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="AA110">
         <v>2.05</v>
       </c>
       <c r="AB110">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC110">
         <v>3.8</v>
       </c>
       <c r="AD110">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE110">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF110">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG110">
         <v>1.83</v>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AK110">
         <v>1.29</v>
@@ -18402,16 +18402,16 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O111">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P111">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="Q111">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="R111">
         <v>1.91</v>
@@ -18420,22 +18420,22 @@
         <v>1.54</v>
       </c>
       <c r="T111">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="U111">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V111">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="W111">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X111">
         <v>1.11</v>
       </c>
       <c r="Y111">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z111">
         <v>2.4</v>
@@ -18444,7 +18444,7 @@
         <v>2.5</v>
       </c>
       <c r="AB111">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC111">
         <v>5</v>
@@ -18456,10 +18456,10 @@
         <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG111">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK111">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,7 +18565,7 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="O112">
         <v>3.1</v>
@@ -18595,7 +18595,7 @@
         <v>1.03</v>
       </c>
       <c r="X112">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y112">
         <v>1.4</v>
@@ -18607,7 +18607,7 @@
         <v>2.3</v>
       </c>
       <c r="AB112">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC112">
         <v>4.25</v>
@@ -18619,7 +18619,7 @@
         <v>1.06</v>
       </c>
       <c r="AF112">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG112">
         <v>1.85</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O114">
         <v>5.5</v>
@@ -18903,13 +18903,13 @@
         <v>1.75</v>
       </c>
       <c r="R114">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S114">
         <v>1.21</v>
       </c>
       <c r="T114">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U114">
         <v>2.11</v>
@@ -18918,7 +18918,7 @@
         <v>1.76</v>
       </c>
       <c r="W114">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X114">
         <v>1.01</v>
@@ -18933,7 +18933,7 @@
         <v>1.4</v>
       </c>
       <c r="AB114">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="AC114">
         <v>2.07</v>
@@ -18942,7 +18942,7 @@
         <v>1.73</v>
       </c>
       <c r="AE114">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF114">
         <v>1.57</v>
@@ -19226,25 +19226,25 @@
         <v>0</v>
       </c>
       <c r="Q116">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R116">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="S116">
         <v>1.08</v>
       </c>
       <c r="T116">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="U116">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V116">
         <v>2.1</v>
       </c>
       <c r="W116">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X116">
         <v>1</v>
@@ -19253,7 +19253,7 @@
         <v>1.01</v>
       </c>
       <c r="Z116">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA116">
         <v>1.2</v>
@@ -19262,19 +19262,19 @@
         <v>5</v>
       </c>
       <c r="AC116">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AD116">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AE116">
         <v>1.68</v>
       </c>
       <c r="AF116">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AG116">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19380,34 +19380,34 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O117">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P117">
+        <v>3.21</v>
+      </c>
+      <c r="Q117">
         <v>3</v>
       </c>
-      <c r="Q117">
-        <v>2.9</v>
-      </c>
       <c r="R117">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S117">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T117">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U117">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="V117">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W117">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X117">
         <v>1.06</v>
@@ -19419,22 +19419,22 @@
         <v>3.1</v>
       </c>
       <c r="AA117">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB117">
         <v>1.7</v>
       </c>
       <c r="AC117">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD117">
         <v>1.22</v>
       </c>
       <c r="AE117">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF117">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG117">
         <v>1.87</v>
@@ -19453,7 +19453,7 @@
         <v>1.28</v>
       </c>
       <c r="AK117">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19579,7 +19579,7 @@
         <v>1.45</v>
       </c>
       <c r="Z118">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AA118">
         <v>2.39</v>
@@ -19588,10 +19588,10 @@
         <v>1.51</v>
       </c>
       <c r="AC118">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD118">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE118">
         <v>1</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK118">
         <v>1.36</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="O134">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="P134">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="Q134">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="R134">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="S134">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="T134">
-        <v>2.48</v>
+        <v>2.89</v>
       </c>
       <c r="U134">
-        <v>3.36</v>
+        <v>2.9</v>
       </c>
       <c r="V134">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="W134">
+        <v>1.03</v>
+      </c>
+      <c r="X134">
         <v>1.01</v>
       </c>
-      <c r="X134">
-        <v>1.06</v>
-      </c>
       <c r="Y134">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="Z134">
-        <v>2.46</v>
+        <v>3.32</v>
       </c>
       <c r="AA134">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="AB134">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AC134">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="AD134">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AE134">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF134">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AG134">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK134">
-        <v>1.6</v>
+        <v>2.06</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="O135">
+        <v>3</v>
+      </c>
+      <c r="P135">
         <v>3.55</v>
       </c>
-      <c r="P135">
-        <v>5.3</v>
-      </c>
       <c r="Q135">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="R135">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="S135">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="T135">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="U135">
-        <v>2.9</v>
+        <v>3.36</v>
       </c>
       <c r="V135">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W135">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X135">
+        <v>1.06</v>
+      </c>
+      <c r="Y135">
+        <v>1.46</v>
+      </c>
+      <c r="Z135">
+        <v>2.46</v>
+      </c>
+      <c r="AA135">
+        <v>2.46</v>
+      </c>
+      <c r="AB135">
+        <v>1.56</v>
+      </c>
+      <c r="AC135">
+        <v>4.33</v>
+      </c>
+      <c r="AD135">
+        <v>1.14</v>
+      </c>
+      <c r="AE135">
         <v>1.01</v>
       </c>
-      <c r="Y135">
-        <v>1.28</v>
-      </c>
-      <c r="Z135">
-        <v>3.32</v>
-      </c>
-      <c r="AA135">
-        <v>2</v>
-      </c>
-      <c r="AB135">
-        <v>1.76</v>
-      </c>
-      <c r="AC135">
-        <v>3.46</v>
-      </c>
-      <c r="AD135">
-        <v>1.28</v>
-      </c>
-      <c r="AE135">
-        <v>1.11</v>
-      </c>
       <c r="AF135">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AG135">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK135">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O149">
         <v>3.8</v>
@@ -24605,16 +24605,16 @@
         <v>4.45</v>
       </c>
       <c r="Q149">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R149">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S149">
         <v>1.36</v>
       </c>
       <c r="T149">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="U149">
         <v>2.73</v>
@@ -24632,28 +24632,28 @@
         <v>1.27</v>
       </c>
       <c r="Z149">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AA149">
         <v>1.84</v>
       </c>
       <c r="AB149">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AC149">
         <v>3</v>
       </c>
       <c r="AD149">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE149">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF149">
         <v>1.8</v>
       </c>
       <c r="AG149">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>1.11</v>
       </c>
       <c r="AK149">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O151">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P151">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -24937,16 +24937,16 @@
         <v>2.1</v>
       </c>
       <c r="S151">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T151">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U151">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V151">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W151">
         <v>1.04</v>
@@ -24955,16 +24955,16 @@
         <v>1.06</v>
       </c>
       <c r="Y151">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z151">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AA151">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB151">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC151">
         <v>3.35</v>
@@ -24973,13 +24973,13 @@
         <v>1.25</v>
       </c>
       <c r="AE151">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF151">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG151">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -25094,25 +25094,25 @@
         <v>0</v>
       </c>
       <c r="Q152">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="R152">
         <v>2.1</v>
       </c>
       <c r="S152">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T152">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U152">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V152">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W152">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X152">
         <v>1.01</v>
@@ -25130,10 +25130,10 @@
         <v>1.8</v>
       </c>
       <c r="AC152">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="AD152">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE152">
         <v>1.11</v>
@@ -25158,7 +25158,7 @@
         <v>1.25</v>
       </c>
       <c r="AK152">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25260,7 +25260,7 @@
         <v>2.55</v>
       </c>
       <c r="R153">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S153">
         <v>1.28</v>
@@ -25269,43 +25269,43 @@
         <v>3.25</v>
       </c>
       <c r="U153">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V153">
         <v>1.5</v>
       </c>
       <c r="W153">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X153">
         <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z153">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA153">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB153">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC153">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD153">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE153">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF153">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG153">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>1.33</v>
       </c>
       <c r="AK153">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25414,49 +25414,49 @@
         <v>2.1</v>
       </c>
       <c r="O154">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P154">
         <v>2.87</v>
       </c>
       <c r="Q154">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="R154">
         <v>2.3</v>
       </c>
       <c r="S154">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T154">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U154">
         <v>2.4</v>
       </c>
       <c r="V154">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W154">
         <v>1.11</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z154">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA154">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB154">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC154">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AD154">
         <v>1.44</v>
@@ -25468,7 +25468,7 @@
         <v>1.55</v>
       </c>
       <c r="AG154">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK154">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -26392,7 +26392,7 @@
         <v>2</v>
       </c>
       <c r="O160">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P160">
         <v>3.75</v>
@@ -26561,16 +26561,16 @@
         <v>2.9</v>
       </c>
       <c r="Q161">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="R161">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S161">
         <v>1.48</v>
       </c>
       <c r="T161">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U161">
         <v>3.75</v>
@@ -26579,10 +26579,10 @@
         <v>1.26</v>
       </c>
       <c r="W161">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X161">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y161">
         <v>1.5</v>
@@ -26591,22 +26591,22 @@
         <v>2.54</v>
       </c>
       <c r="AA161">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AB161">
         <v>1.44</v>
       </c>
       <c r="AC161">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD161">
         <v>1.15</v>
       </c>
       <c r="AE161">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF161">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG161">
         <v>1.7</v>
@@ -26625,7 +26625,7 @@
         <v>1.33</v>
       </c>
       <c r="AK161">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="O163">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P163">
-        <v>2.07</v>
+        <v>2.8</v>
       </c>
       <c r="Q163">
-        <v>3.92</v>
+        <v>2.52</v>
       </c>
       <c r="R163">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S163">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T163">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="U163">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="V163">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="W163">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X163">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y163">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z163">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA163">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AB163">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AC163">
-        <v>2.48</v>
+        <v>1.89</v>
       </c>
       <c r="AD163">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AE163">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AF163">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG163">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK163">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="O164">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P164">
-        <v>2.8</v>
+        <v>2.07</v>
       </c>
       <c r="Q164">
-        <v>2.52</v>
+        <v>3.92</v>
       </c>
       <c r="R164">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S164">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T164">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="U164">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="V164">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="W164">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X164">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y164">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z164">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA164">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AB164">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC164">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="AD164">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AE164">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AF164">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG164">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK164">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27376,7 +27376,7 @@
         <v>2.65</v>
       </c>
       <c r="Q166">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="R166">
         <v>2.23</v>
@@ -27385,43 +27385,43 @@
         <v>1.28</v>
       </c>
       <c r="T166">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U166">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V166">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W166">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X166">
         <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z166">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA166">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB166">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AC166">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD166">
         <v>1.55</v>
       </c>
       <c r="AE166">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF166">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG166">
         <v>2.45</v>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AK166">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -28363,28 +28363,28 @@
         <v>1.33</v>
       </c>
       <c r="T172">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="U172">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="V172">
         <v>1.38</v>
       </c>
       <c r="W172">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X172">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y172">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z172">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AA172">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB172">
         <v>1.85</v>
@@ -28393,7 +28393,7 @@
         <v>3.2</v>
       </c>
       <c r="AD172">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE172">
         <v>1.06</v>
@@ -28402,7 +28402,7 @@
         <v>2</v>
       </c>
       <c r="AG172">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>2.55</v>
       </c>
       <c r="AK172">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="O173">
         <v>5</v>
       </c>
       <c r="P173">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q173">
         <v>5.3</v>
@@ -28541,31 +28541,31 @@
         <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z173">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA173">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AB173">
         <v>2.94</v>
       </c>
       <c r="AC173">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD173">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE173">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF173">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG173">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>2.62</v>
+        <v>1.09</v>
       </c>
       <c r="AK173">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28677,25 +28677,25 @@
         <v>4</v>
       </c>
       <c r="P174">
-        <v>4.1</v>
+        <v>4.31</v>
       </c>
       <c r="Q174">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="R174">
         <v>2.55</v>
       </c>
       <c r="S174">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T174">
         <v>4.8</v>
       </c>
       <c r="U174">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="V174">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="W174">
         <v>1.2</v>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK174">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28834,49 +28834,49 @@
         </is>
       </c>
       <c r="N175">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="O175">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P175">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="Q175">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="R175">
         <v>2.2</v>
       </c>
       <c r="S175">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T175">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U175">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="V175">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W175">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X175">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
         <v>1.25</v>
       </c>
       <c r="Z175">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AA175">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB175">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC175">
         <v>3.2</v>
@@ -28885,13 +28885,13 @@
         <v>1.3</v>
       </c>
       <c r="AE175">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF175">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG175">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AK175">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29009,7 +29009,7 @@
         <v>2.3</v>
       </c>
       <c r="R176">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S176">
         <v>1.3</v>
@@ -29018,7 +29018,7 @@
         <v>3.2</v>
       </c>
       <c r="U176">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="V176">
         <v>1.5</v>
@@ -29027,7 +29027,7 @@
         <v>1.11</v>
       </c>
       <c r="X176">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
         <v>1.22</v>
@@ -29039,7 +29039,7 @@
         <v>1.7</v>
       </c>
       <c r="AB176">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC176">
         <v>2.88</v>
@@ -29048,7 +29048,7 @@
         <v>1.36</v>
       </c>
       <c r="AE176">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF176">
         <v>1.65</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK176">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29489,10 +29489,10 @@
         <v>3</v>
       </c>
       <c r="O179">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P179">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -30301,46 +30301,46 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O184">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P184">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q184">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="R184">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S184">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T184">
         <v>2.45</v>
       </c>
       <c r="U184">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V184">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W184">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X184">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y184">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z184">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AA184">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AB184">
         <v>1.55</v>
@@ -30349,16 +30349,16 @@
         <v>4.5</v>
       </c>
       <c r="AD184">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE184">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF184">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG184">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK184">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30965,13 +30965,13 @@
         <v>2.84</v>
       </c>
       <c r="R188">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S188">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T188">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U188">
         <v>3.42</v>
@@ -30980,7 +30980,7 @@
         <v>1.25</v>
       </c>
       <c r="W188">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X188">
         <v>1.06</v>
@@ -30998,7 +30998,7 @@
         <v>1.48</v>
       </c>
       <c r="AC188">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AD188">
         <v>1.13</v>
@@ -31023,7 +31023,7 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK188">
         <v>1.62</v>
@@ -31119,31 +31119,31 @@
         <v>1.44</v>
       </c>
       <c r="O189">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="P189">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q189">
         <v>1.91</v>
       </c>
       <c r="R189">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S189">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="T189">
         <v>3.2</v>
       </c>
       <c r="U189">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V189">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W189">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X189">
         <v>1.03</v>
@@ -31155,19 +31155,19 @@
         <v>4.56</v>
       </c>
       <c r="AA189">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AB189">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC189">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD189">
         <v>1.52</v>
       </c>
       <c r="AE189">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF189">
         <v>1.83</v>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK189">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31288,7 +31288,7 @@
         <v>2.1</v>
       </c>
       <c r="Q190">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R190">
         <v>2.4</v>
@@ -31300,28 +31300,28 @@
         <v>3.8</v>
       </c>
       <c r="U190">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="V190">
         <v>1.6</v>
       </c>
       <c r="W190">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X190">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y190">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z190">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="AA190">
         <v>1.57</v>
       </c>
       <c r="AB190">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AC190">
         <v>2.4</v>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="AK190">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31931,10 +31931,10 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O194">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P194">
         <v>3.3</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB194">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -33564,28 +33564,28 @@
         <v>3.45</v>
       </c>
       <c r="O204">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P204">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q204">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="R204">
         <v>2.05</v>
       </c>
       <c r="S204">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T204">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="U204">
         <v>2.81</v>
       </c>
       <c r="V204">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W204">
         <v>1.05</v>
@@ -33594,22 +33594,22 @@
         <v>1.03</v>
       </c>
       <c r="Y204">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z204">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AA204">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AB204">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AC204">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="AD204">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE204">
         <v>1.1</v>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK204">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="O205">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
       <c r="P205">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="Q205">
         <v>2.63</v>
@@ -33745,7 +33745,7 @@
         <v>2.65</v>
       </c>
       <c r="U205">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="V205">
         <v>1.32</v>
@@ -33757,7 +33757,7 @@
         <v>1.04</v>
       </c>
       <c r="Y205">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z205">
         <v>2.9</v>
@@ -33769,7 +33769,7 @@
         <v>1.68</v>
       </c>
       <c r="AC205">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="AD205">
         <v>1.24</v>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK205">
         <v>1.67</v>
@@ -34391,10 +34391,10 @@
         <v>1.91</v>
       </c>
       <c r="S209">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T209">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="U209">
         <v>3.5</v>
@@ -34403,22 +34403,22 @@
         <v>1.25</v>
       </c>
       <c r="W209">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X209">
         <v>1.1</v>
       </c>
       <c r="Y209">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z209">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AA209">
         <v>2.5</v>
       </c>
       <c r="AB209">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC209">
         <v>4.8</v>
@@ -34449,7 +34449,7 @@
         <v>1.36</v>
       </c>
       <c r="AK209">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -35680,22 +35680,22 @@
         </is>
       </c>
       <c r="N217">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O217">
-        <v>8.5</v>
+        <v>8.35</v>
       </c>
       <c r="P217">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Q217">
-        <v>6.66</v>
+        <v>6.86</v>
       </c>
       <c r="R217">
         <v>3.5</v>
       </c>
       <c r="S217">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="T217">
         <v>5.5</v>
@@ -35704,7 +35704,7 @@
         <v>1.65</v>
       </c>
       <c r="V217">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="W217">
         <v>1.36</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="O221">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="P221">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36371,10 +36371,10 @@
         <v>0</v>
       </c>
       <c r="AA221">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB221">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC221">
         <v>0</v>
@@ -36667,52 +36667,52 @@
         <v>0</v>
       </c>
       <c r="Q223">
+        <v>2.45</v>
+      </c>
+      <c r="R223">
         <v>2.1</v>
       </c>
-      <c r="R223">
-        <v>2.2</v>
-      </c>
       <c r="S223">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T223">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U223">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V223">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W223">
         <v>1.07</v>
       </c>
       <c r="X223">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y223">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z223">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA223">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="AB223">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC223">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD223">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE223">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF223">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG223">
         <v>1.75</v>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK223">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36836,10 +36836,10 @@
         <v>2.05</v>
       </c>
       <c r="S224">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T224">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U224">
         <v>3.2</v>
@@ -36848,37 +36848,37 @@
         <v>1.3</v>
       </c>
       <c r="W224">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X224">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y224">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z224">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AA224">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AB224">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC224">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="AD224">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE224">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF224">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AG224">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK224">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,7 +36984,7 @@
         </is>
       </c>
       <c r="N225">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="O225">
         <v>4.15</v>
@@ -36993,46 +36993,46 @@
         <v>1.38</v>
       </c>
       <c r="Q225">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="R225">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S225">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T225">
         <v>3.2</v>
       </c>
       <c r="U225">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="V225">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W225">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X225">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y225">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z225">
         <v>3.75</v>
       </c>
       <c r="AA225">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB225">
         <v>1.9</v>
       </c>
       <c r="AC225">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD225">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE225">
         <v>1.1</v>
@@ -37054,7 +37054,7 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK225">
         <v>1.02</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O227">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P227">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="Q227">
         <v>2.57</v>
@@ -37325,10 +37325,10 @@
         <v>2</v>
       </c>
       <c r="S227">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T227">
-        <v>2.53</v>
+        <v>2.68</v>
       </c>
       <c r="U227">
         <v>2.9</v>
@@ -37364,7 +37364,7 @@
         <v>1.05</v>
       </c>
       <c r="AF227">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG227">
         <v>1.85</v>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK227">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37488,19 +37488,19 @@
         <v>1.97</v>
       </c>
       <c r="S228">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T228">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="U228">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="V228">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W228">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X228">
         <v>1.03</v>
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK228">
         <v>1.63</v>
@@ -37802,13 +37802,13 @@
         <v>1.7</v>
       </c>
       <c r="O230">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P230">
         <v>3.5</v>
       </c>
       <c r="Q230">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="R230">
         <v>2.38</v>
@@ -37820,10 +37820,10 @@
         <v>4</v>
       </c>
       <c r="U230">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="V230">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="W230">
         <v>1.17</v>
@@ -37832,7 +37832,7 @@
         <v>1.02</v>
       </c>
       <c r="Y230">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z230">
         <v>6.01</v>
@@ -37850,10 +37850,10 @@
         <v>1.67</v>
       </c>
       <c r="AE230">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF230">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG230">
         <v>2.5</v>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK230">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O231">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P231">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q231">
         <v>4</v>
@@ -37980,7 +37980,7 @@
         <v>1.44</v>
       </c>
       <c r="T231">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U231">
         <v>3.3</v>
@@ -38125,49 +38125,49 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="O232">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="P232">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="Q232">
         <v>2.9</v>
       </c>
       <c r="R232">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S232">
         <v>1.38</v>
       </c>
       <c r="T232">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U232">
         <v>2.77</v>
       </c>
       <c r="V232">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W232">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X232">
         <v>1.05</v>
       </c>
       <c r="Y232">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z232">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA232">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB232">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC232">
         <v>3.4</v>
@@ -38179,10 +38179,10 @@
         <v>1.1</v>
       </c>
       <c r="AF232">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG232">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK232">
         <v>1.53</v>
@@ -38288,16 +38288,16 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O233">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P233">
         <v>3.1</v>
       </c>
       <c r="Q233">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R233">
         <v>2</v>
@@ -38309,7 +38309,7 @@
         <v>2.62</v>
       </c>
       <c r="U233">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="V233">
         <v>1.32</v>
@@ -38318,34 +38318,34 @@
         <v>1.02</v>
       </c>
       <c r="X233">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y233">
         <v>1.4</v>
       </c>
       <c r="Z233">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AA233">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB233">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC233">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="AD233">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE233">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF233">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG233">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK233">
         <v>1.5</v>
@@ -38451,10 +38451,10 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O234">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P234">
         <v>2.6</v>
@@ -38472,7 +38472,7 @@
         <v>2.75</v>
       </c>
       <c r="U234">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V234">
         <v>1.3</v>
@@ -38490,10 +38490,10 @@
         <v>2.8</v>
       </c>
       <c r="AA234">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB234">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC234">
         <v>3.9</v>
@@ -38521,7 +38521,7 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK234">
         <v>1.4</v>
@@ -38623,13 +38623,13 @@
         <v>0</v>
       </c>
       <c r="Q235">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R235">
         <v>1.91</v>
       </c>
       <c r="S235">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T235">
         <v>2.26</v>
@@ -38647,28 +38647,28 @@
         <v>1.11</v>
       </c>
       <c r="Y235">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z235">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AA235">
         <v>2.5</v>
       </c>
       <c r="AB235">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC235">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AD235">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE235">
         <v>1.03</v>
       </c>
       <c r="AF235">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG235">
         <v>1.65</v>
@@ -38687,7 +38687,7 @@
         <v>1.36</v>
       </c>
       <c r="AK235">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38795,10 +38795,10 @@
         <v>1.38</v>
       </c>
       <c r="T236">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U236">
-        <v>3.19</v>
+        <v>2.82</v>
       </c>
       <c r="V236">
         <v>1.34</v>
@@ -38819,13 +38819,13 @@
         <v>2.16</v>
       </c>
       <c r="AB236">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC236">
         <v>3.68</v>
       </c>
       <c r="AD236">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE236">
         <v>1.08</v>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK236">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38949,25 +38949,25 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="R237">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S237">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T237">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="U237">
         <v>2.9</v>
       </c>
       <c r="V237">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W237">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X237">
         <v>1.02</v>
@@ -38994,7 +38994,7 @@
         <v>1.01</v>
       </c>
       <c r="AF237">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG237">
         <v>1.7</v>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK237">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39103,7 +39103,7 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="O238">
         <v>2.95</v>
@@ -39118,10 +39118,10 @@
         <v>1.91</v>
       </c>
       <c r="S238">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T238">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U238">
         <v>3.3</v>
@@ -39157,7 +39157,7 @@
         <v>1.02</v>
       </c>
       <c r="AF238">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AG238">
         <v>1.76</v>
@@ -39176,7 +39176,7 @@
         <v>1.48</v>
       </c>
       <c r="AK238">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39601,7 +39601,7 @@
         <v>4.25</v>
       </c>
       <c r="Q241">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R241">
         <v>2.4</v>
@@ -39616,10 +39616,10 @@
         <v>2.27</v>
       </c>
       <c r="V241">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W241">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X241">
         <v>1.01</v>
@@ -39631,25 +39631,25 @@
         <v>4.7</v>
       </c>
       <c r="AA241">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB241">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC241">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AD241">
         <v>1.48</v>
       </c>
       <c r="AE241">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF241">
         <v>1.57</v>
       </c>
       <c r="AG241">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK241">
         <v>2.05</v>
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O244">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P244">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="Q244">
         <v>2.35</v>
       </c>
       <c r="R244">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S244">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T244">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U244">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V244">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W244">
+        <v>1.05</v>
+      </c>
+      <c r="X244">
+        <v>1.01</v>
+      </c>
+      <c r="Y244">
+        <v>1.34</v>
+      </c>
+      <c r="Z244">
+        <v>3.26</v>
+      </c>
+      <c r="AA244">
+        <v>2.1</v>
+      </c>
+      <c r="AB244">
+        <v>1.81</v>
+      </c>
+      <c r="AC244">
+        <v>3.24</v>
+      </c>
+      <c r="AD244">
+        <v>1.26</v>
+      </c>
+      <c r="AE244">
         <v>1.06</v>
       </c>
-      <c r="X244">
-        <v>1.02</v>
-      </c>
-      <c r="Y244">
-        <v>1.39</v>
-      </c>
-      <c r="Z244">
-        <v>2.88</v>
-      </c>
-      <c r="AA244">
-        <v>2.2</v>
-      </c>
-      <c r="AB244">
-        <v>1.65</v>
-      </c>
-      <c r="AC244">
-        <v>4.33</v>
-      </c>
-      <c r="AD244">
-        <v>1.2</v>
-      </c>
-      <c r="AE244">
-        <v>1.04</v>
-      </c>
       <c r="AF244">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG244">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK244">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="O245">
         <v>4.2</v>
       </c>
       <c r="P245">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB245">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40573,16 +40573,16 @@
         <v>1.16</v>
       </c>
       <c r="O247">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="P247">
-        <v>9.550000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Q247">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R247">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="S247">
         <v>1.23</v>
@@ -40591,10 +40591,10 @@
         <v>3.78</v>
       </c>
       <c r="U247">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V247">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W247">
         <v>1.14</v>
@@ -40603,31 +40603,31 @@
         <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z247">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AA247">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB247">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AC247">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD247">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE247">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF247">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG247">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK247">
         <v>3.51</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O249">
-        <v>3.17</v>
+        <v>3.58</v>
       </c>
       <c r="P249">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41065,13 +41065,13 @@
         <v>5.25</v>
       </c>
       <c r="P250">
-        <v>9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q250">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R250">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="S250">
         <v>1.24</v>
@@ -41086,7 +41086,7 @@
         <v>1.6</v>
       </c>
       <c r="W250">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X250">
         <v>1.02</v>
@@ -41095,22 +41095,22 @@
         <v>1.14</v>
       </c>
       <c r="Z250">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA250">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB250">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AC250">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AD250">
         <v>1.54</v>
       </c>
       <c r="AE250">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF250">
         <v>1.8</v>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK250">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41222,10 +41222,10 @@
         </is>
       </c>
       <c r="N251">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="O251">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P251">
         <v>2.65</v>
@@ -41237,10 +41237,10 @@
         <v>2.2</v>
       </c>
       <c r="S251">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T251">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U251">
         <v>2.45</v>
@@ -41249,10 +41249,10 @@
         <v>1.48</v>
       </c>
       <c r="W251">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X251">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y251">
         <v>1.2</v>
@@ -41295,7 +41295,7 @@
         <v>1.44</v>
       </c>
       <c r="AK251">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41551,10 +41551,10 @@
         <v>1.95</v>
       </c>
       <c r="O253">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="P253">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O256">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="P256">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42363,22 +42363,22 @@
         </is>
       </c>
       <c r="N258">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O258">
         <v>3.6</v>
       </c>
       <c r="P258">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="Q258">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R258">
         <v>2.29</v>
       </c>
       <c r="S258">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T258">
         <v>2.89</v>
@@ -42387,7 +42387,7 @@
         <v>2.5</v>
       </c>
       <c r="V258">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W258">
         <v>1.11</v>
@@ -42420,7 +42420,7 @@
         <v>1.69</v>
       </c>
       <c r="AG258">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK258">
         <v>2</v>
@@ -42526,28 +42526,28 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O259">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P259">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q259">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="R259">
         <v>2.16</v>
       </c>
       <c r="S259">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T259">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U259">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V259">
         <v>1.46</v>
@@ -42556,25 +42556,25 @@
         <v>1.07</v>
       </c>
       <c r="X259">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y259">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z259">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA259">
         <v>1.67</v>
       </c>
       <c r="AB259">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AC259">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD259">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE259">
         <v>1.17</v>
@@ -42583,7 +42583,7 @@
         <v>1.58</v>
       </c>
       <c r="AG259">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>1.19</v>
       </c>
       <c r="AK259">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42689,19 +42689,19 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="O260">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P260">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="Q260">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R260">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S260">
         <v>1.46</v>
@@ -42716,37 +42716,37 @@
         <v>1.36</v>
       </c>
       <c r="W260">
+        <v>1.03</v>
+      </c>
+      <c r="X260">
         <v>1.07</v>
       </c>
-      <c r="X260">
-        <v>1.03</v>
-      </c>
       <c r="Y260">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z260">
         <v>2.8</v>
       </c>
       <c r="AA260">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AB260">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC260">
         <v>4.1</v>
       </c>
       <c r="AD260">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE260">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF260">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG260">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AK260">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42852,16 +42852,16 @@
         </is>
       </c>
       <c r="N261">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="O261">
         <v>7.5</v>
       </c>
       <c r="P261">
-        <v>15</v>
+        <v>15.92</v>
       </c>
       <c r="Q261">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R261">
         <v>3</v>
@@ -42870,46 +42870,46 @@
         <v>1.22</v>
       </c>
       <c r="T261">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U261">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V261">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W261">
         <v>1.18</v>
       </c>
       <c r="X261">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y261">
         <v>1.13</v>
       </c>
       <c r="Z261">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AA261">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AB261">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AC261">
         <v>2.2</v>
       </c>
       <c r="AD261">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AE261">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF261">
         <v>2.3</v>
       </c>
       <c r="AG261">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK261">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O262">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="P262">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="O263">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P263">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O264">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="P264">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q266">
         <v>2.5</v>
@@ -43682,37 +43682,37 @@
         <v>2</v>
       </c>
       <c r="S266">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T266">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U266">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="V266">
         <v>1.33</v>
       </c>
       <c r="W266">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X266">
         <v>1.02</v>
       </c>
       <c r="Y266">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z266">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA266">
         <v>2.09</v>
       </c>
       <c r="AB266">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC266">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD266">
         <v>1.22</v>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK266">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44002,7 +44002,7 @@
         <v>0</v>
       </c>
       <c r="Q268">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R268">
         <v>2.05</v>
@@ -44011,19 +44011,19 @@
         <v>1.35</v>
       </c>
       <c r="T268">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U268">
         <v>2.5</v>
       </c>
       <c r="V268">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W268">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X268">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y268">
         <v>1.25</v>
@@ -44032,13 +44032,13 @@
         <v>3.6</v>
       </c>
       <c r="AA268">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB268">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC268">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AD268">
         <v>1.3</v>
@@ -44063,7 +44063,7 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK268">
         <v>1.55</v>
@@ -44319,37 +44319,37 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O270">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P270">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q270">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="R270">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S270">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T270">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U270">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="V270">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W270">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X270">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y270">
         <v>1.13</v>
@@ -44367,16 +44367,16 @@
         <v>2.5</v>
       </c>
       <c r="AD270">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE270">
         <v>1.15</v>
       </c>
       <c r="AF270">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG270">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AK270">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44654,28 +44654,28 @@
         <v>0</v>
       </c>
       <c r="Q272">
-        <v>7</v>
+        <v>7.48</v>
       </c>
       <c r="R272">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="S272">
         <v>1.22</v>
       </c>
       <c r="T272">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U272">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V272">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W272">
         <v>1.15</v>
       </c>
       <c r="X272">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y272">
         <v>1.15</v>
@@ -44718,7 +44718,7 @@
         <v>1.07</v>
       </c>
       <c r="AK272">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44971,28 +44971,28 @@
         </is>
       </c>
       <c r="N274">
-        <v>5</v>
+        <v>5.46</v>
       </c>
       <c r="O274">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P274">
         <v>1.48</v>
       </c>
       <c r="Q274">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R274">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S274">
         <v>1.22</v>
       </c>
       <c r="T274">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="U274">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V274">
         <v>1.62</v>
@@ -45001,7 +45001,7 @@
         <v>1.13</v>
       </c>
       <c r="X274">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y274">
         <v>1.12</v>
@@ -45022,7 +45022,7 @@
         <v>1.53</v>
       </c>
       <c r="AE274">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF274">
         <v>1.65</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>2.63</v>
+        <v>1.2</v>
       </c>
       <c r="AK274">
         <v>1.11</v>
@@ -45134,31 +45134,31 @@
         </is>
       </c>
       <c r="N275">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O275">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P275">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q275">
         <v>4.4</v>
       </c>
       <c r="R275">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S275">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T275">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U275">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V275">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W275">
         <v>1.04</v>
@@ -45167,7 +45167,7 @@
         <v>1.05</v>
       </c>
       <c r="Y275">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z275">
         <v>3.5</v>
@@ -45191,7 +45191,7 @@
         <v>1.81</v>
       </c>
       <c r="AG275">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK275">
         <v>1.22</v>
@@ -45297,37 +45297,37 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O276">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P276">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q276">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R276">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S276">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T276">
         <v>2.88</v>
       </c>
       <c r="U276">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="V276">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W276">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X276">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y276">
         <v>1.3</v>
@@ -45345,13 +45345,13 @@
         <v>3.4</v>
       </c>
       <c r="AD276">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE276">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF276">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG276">
         <v>1.85</v>
@@ -45367,7 +45367,7 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK276">
         <v>2</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O278">
         <v>4.2</v>
       </c>
       <c r="P278">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q278">
         <v>1.91</v>
@@ -45638,7 +45638,7 @@
         <v>2.4</v>
       </c>
       <c r="S278">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T278">
         <v>3.3</v>
@@ -45647,25 +45647,25 @@
         <v>2.35</v>
       </c>
       <c r="V278">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W278">
         <v>1.11</v>
       </c>
       <c r="X278">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y278">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z278">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
       <c r="AA278">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB278">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AC278">
         <v>2.52</v>
@@ -45674,10 +45674,10 @@
         <v>1.41</v>
       </c>
       <c r="AE278">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF278">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG278">
         <v>2</v>
@@ -45696,7 +45696,7 @@
         <v>1.22</v>
       </c>
       <c r="AK278">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45786,16 +45786,16 @@
         </is>
       </c>
       <c r="N279">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O279">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P279">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="Q279">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="R279">
         <v>2.2</v>
@@ -45810,13 +45810,13 @@
         <v>2.62</v>
       </c>
       <c r="V279">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W279">
         <v>1.06</v>
       </c>
       <c r="X279">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y279">
         <v>1.26</v>
@@ -45843,7 +45843,7 @@
         <v>1.65</v>
       </c>
       <c r="AG279">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>1.3</v>
       </c>
       <c r="AK279">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46115,10 +46115,10 @@
         <v>2</v>
       </c>
       <c r="O281">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P281">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46151,10 +46151,10 @@
         <v>0</v>
       </c>
       <c r="AA281">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB281">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC281">
         <v>0</v>
@@ -46278,28 +46278,28 @@
         <v>2.45</v>
       </c>
       <c r="O282">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P282">
         <v>2.9</v>
       </c>
       <c r="Q282">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R282">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S282">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T282">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U282">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="V282">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W282">
         <v>1.02</v>
@@ -46314,16 +46314,16 @@
         <v>2.95</v>
       </c>
       <c r="AA282">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB282">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC282">
         <v>3.9</v>
       </c>
       <c r="AD282">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE282">
         <v>1.03</v>
@@ -46345,7 +46345,7 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK282">
         <v>1.53</v>
@@ -46438,58 +46438,58 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O283">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="P283">
         <v>6</v>
       </c>
       <c r="Q283">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R283">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="S283">
         <v>1.32</v>
       </c>
       <c r="T283">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="U283">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V283">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W283">
         <v>1.07</v>
       </c>
       <c r="X283">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y283">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z283">
         <v>3.9</v>
       </c>
       <c r="AA283">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB283">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC283">
         <v>2.9</v>
       </c>
       <c r="AD283">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE283">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF283">
         <v>1.83</v>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK283">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46764,7 +46764,7 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="O285">
         <v>4.8</v>
@@ -46785,13 +46785,13 @@
         <v>3.55</v>
       </c>
       <c r="U285">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V285">
         <v>1.62</v>
       </c>
       <c r="W285">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X285">
         <v>1.03</v>
@@ -46803,19 +46803,19 @@
         <v>5.1</v>
       </c>
       <c r="AA285">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB285">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC285">
         <v>2.08</v>
       </c>
       <c r="AD285">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE285">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF285">
         <v>1.73</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O286">
         <v>3.35</v>
       </c>
       <c r="P286">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -46966,10 +46966,10 @@
         <v>0</v>
       </c>
       <c r="AA286">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB286">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC286">
         <v>0</v>
@@ -47093,37 +47093,37 @@
         <v>1.15</v>
       </c>
       <c r="O287">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="P287">
         <v>11</v>
       </c>
       <c r="Q287">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R287">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="S287">
         <v>1.12</v>
       </c>
       <c r="T287">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="U287">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V287">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="W287">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X287">
         <v>1</v>
       </c>
       <c r="Y287">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z287">
         <v>11</v>
@@ -47138,13 +47138,13 @@
         <v>1.52</v>
       </c>
       <c r="AD287">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AE287">
         <v>1.67</v>
       </c>
       <c r="AF287">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG287">
         <v>2.25</v>
@@ -47163,7 +47163,7 @@
         <v>1.08</v>
       </c>
       <c r="AK287">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47419,13 +47419,13 @@
         <v>2.7</v>
       </c>
       <c r="O289">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P289">
         <v>2.8</v>
       </c>
       <c r="Q289">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="R289">
         <v>1.75</v>
@@ -47434,40 +47434,40 @@
         <v>1.67</v>
       </c>
       <c r="T289">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="U289">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="V289">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W289">
         <v>1.03</v>
       </c>
       <c r="X289">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Y289">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Z289">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AA289">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="AB289">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC289">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AD289">
         <v>1.04</v>
       </c>
       <c r="AE289">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF289">
         <v>2.4</v>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK289">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,65 +47579,65 @@
         </is>
       </c>
       <c r="N290">
+        <v>1.63</v>
+      </c>
+      <c r="O290">
+        <v>3.35</v>
+      </c>
+      <c r="P290">
+        <v>5.9</v>
+      </c>
+      <c r="Q290">
         <v>2.3</v>
       </c>
-      <c r="O290">
-        <v>2.75</v>
-      </c>
-      <c r="P290">
-        <v>3.35</v>
-      </c>
-      <c r="Q290">
-        <v>2.9</v>
-      </c>
       <c r="R290">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S290">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T290">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U290">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="V290">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W290">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X290">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y290">
+        <v>1.5</v>
+      </c>
+      <c r="Z290">
+        <v>2.45</v>
+      </c>
+      <c r="AA290">
+        <v>2.6</v>
+      </c>
+      <c r="AB290">
+        <v>1.42</v>
+      </c>
+      <c r="AC290">
+        <v>5.05</v>
+      </c>
+      <c r="AD290">
+        <v>1.15</v>
+      </c>
+      <c r="AE290">
+        <v>1.01</v>
+      </c>
+      <c r="AF290">
+        <v>2.18</v>
+      </c>
+      <c r="AG290">
         <v>1.56</v>
       </c>
-      <c r="Z290">
-        <v>2.25</v>
-      </c>
-      <c r="AA290">
-        <v>3.01</v>
-      </c>
-      <c r="AB290">
-        <v>1.38</v>
-      </c>
-      <c r="AC290">
-        <v>6.23</v>
-      </c>
-      <c r="AD290">
-        <v>1.07</v>
-      </c>
-      <c r="AE290">
-        <v>1.03</v>
-      </c>
-      <c r="AF290">
-        <v>2.2</v>
-      </c>
-      <c r="AG290">
-        <v>1.62</v>
-      </c>
       <c r="AH290" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AK290">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="O291">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="P291">
-        <v>5.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q291">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="R291">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S291">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="T291">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="U291">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V291">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W291">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X291">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y291">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Z291">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AA291">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AB291">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC291">
-        <v>5.1</v>
+        <v>6.05</v>
       </c>
       <c r="AD291">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE291">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF291">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG291">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AK291">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="O292">
         <v>5</v>
@@ -47914,16 +47914,16 @@
         <v>8.75</v>
       </c>
       <c r="Q292">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="R292">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S292">
         <v>1.33</v>
       </c>
       <c r="T292">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U292">
         <v>2.64</v>
@@ -47932,16 +47932,16 @@
         <v>1.44</v>
       </c>
       <c r="W292">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X292">
         <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z292">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AA292">
         <v>1.72</v>
@@ -47959,10 +47959,10 @@
         <v>1.1</v>
       </c>
       <c r="AF292">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG292">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AK292">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48080,13 +48080,13 @@
         <v>3.75</v>
       </c>
       <c r="R293">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S293">
         <v>1.44</v>
       </c>
       <c r="T293">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U293">
         <v>3.25</v>
@@ -48098,16 +48098,16 @@
         <v>1.04</v>
       </c>
       <c r="X293">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y293">
         <v>1.4</v>
       </c>
       <c r="Z293">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA293">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AB293">
         <v>1.53</v>
@@ -48119,7 +48119,7 @@
         <v>1.16</v>
       </c>
       <c r="AE293">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF293">
         <v>1.95</v>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AK293">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48403,7 +48403,7 @@
         <v>1.67</v>
       </c>
       <c r="Q295">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="R295">
         <v>2.25</v>
@@ -48412,7 +48412,7 @@
         <v>1.29</v>
       </c>
       <c r="T295">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="U295">
         <v>2.55</v>
@@ -48436,7 +48436,7 @@
         <v>1.84</v>
       </c>
       <c r="AB295">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC295">
         <v>3.1</v>
@@ -48445,13 +48445,13 @@
         <v>1.36</v>
       </c>
       <c r="AE295">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF295">
         <v>1.75</v>
       </c>
       <c r="AG295">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK295">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="O296">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="P296">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q296">
         <v>2.33</v>
@@ -48593,7 +48593,7 @@
         <v>1.29</v>
       </c>
       <c r="Z296">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA296">
         <v>1.93</v>
@@ -48886,16 +48886,16 @@
         <v>1.17</v>
       </c>
       <c r="O298">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P298">
         <v>11</v>
       </c>
       <c r="Q298">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R298">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="S298">
         <v>1.14</v>
@@ -48904,31 +48904,31 @@
         <v>5</v>
       </c>
       <c r="U298">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V298">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="W298">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X298">
         <v>1.01</v>
       </c>
       <c r="Y298">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z298">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="AA298">
         <v>1.27</v>
       </c>
       <c r="AB298">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AC298">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AD298">
         <v>1.94</v>
@@ -48940,7 +48940,7 @@
         <v>1.67</v>
       </c>
       <c r="AG298">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK298">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49046,64 +49046,64 @@
         </is>
       </c>
       <c r="N299">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O299">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P299">
         <v>3.6</v>
       </c>
       <c r="Q299">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R299">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S299">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T299">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U299">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V299">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W299">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X299">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y299">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z299">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA299">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AB299">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC299">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD299">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE299">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF299">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG299">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK299">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49212,7 +49212,7 @@
         <v>2.4</v>
       </c>
       <c r="O300">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="P300">
         <v>3</v>
@@ -49224,40 +49224,40 @@
         <v>1.85</v>
       </c>
       <c r="S300">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="T300">
+        <v>2.25</v>
+      </c>
+      <c r="U300">
+        <v>3.88</v>
+      </c>
+      <c r="V300">
+        <v>1.22</v>
+      </c>
+      <c r="W300">
+        <v>1.04</v>
+      </c>
+      <c r="X300">
+        <v>1.14</v>
+      </c>
+      <c r="Y300">
+        <v>1.58</v>
+      </c>
+      <c r="Z300">
         <v>2.2</v>
       </c>
-      <c r="U300">
-        <v>3.9</v>
-      </c>
-      <c r="V300">
-        <v>1.18</v>
-      </c>
-      <c r="W300">
-        <v>1.03</v>
-      </c>
-      <c r="X300">
-        <v>1.1</v>
-      </c>
-      <c r="Y300">
-        <v>1.62</v>
-      </c>
-      <c r="Z300">
-        <v>2.16</v>
-      </c>
       <c r="AA300">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AB300">
         <v>1.34</v>
       </c>
       <c r="AC300">
-        <v>5.55</v>
+        <v>6.21</v>
       </c>
       <c r="AD300">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE300">
         <v>1.03</v>
@@ -49266,7 +49266,7 @@
         <v>2.23</v>
       </c>
       <c r="AG300">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
+        <v>1.36</v>
+      </c>
+      <c r="AK300">
         <v>1.44</v>
-      </c>
-      <c r="AK300">
-        <v>1.4</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49372,19 +49372,19 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O301">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P301">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q301">
         <v>2.44</v>
       </c>
       <c r="R301">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S301">
         <v>1.4</v>
@@ -49396,7 +49396,7 @@
         <v>3.34</v>
       </c>
       <c r="V301">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W301">
         <v>1.03</v>
@@ -49405,10 +49405,10 @@
         <v>1.06</v>
       </c>
       <c r="Y301">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Z301">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="AA301">
         <v>2.17</v>
@@ -49417,7 +49417,7 @@
         <v>1.55</v>
       </c>
       <c r="AC301">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AD301">
         <v>1.2</v>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK301">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49544,7 +49544,7 @@
         <v>2.95</v>
       </c>
       <c r="Q302">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="R302">
         <v>1.95</v>
@@ -49559,7 +49559,7 @@
         <v>3.3</v>
       </c>
       <c r="V302">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W302">
         <v>1.05</v>
@@ -49571,10 +49571,10 @@
         <v>1.41</v>
       </c>
       <c r="Z302">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AA302">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB302">
         <v>1.59</v>
@@ -49583,10 +49583,10 @@
         <v>4.33</v>
       </c>
       <c r="AD302">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE302">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF302">
         <v>2.05</v>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AK302">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50024,19 +50024,19 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O305">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P305">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q305">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="R305">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S305">
         <v>1.4</v>
@@ -50045,16 +50045,16 @@
         <v>2.75</v>
       </c>
       <c r="U305">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="V305">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W305">
         <v>1.05</v>
       </c>
       <c r="X305">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y305">
         <v>1.36</v>
@@ -50063,13 +50063,13 @@
         <v>2.75</v>
       </c>
       <c r="AA305">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB305">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC305">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD305">
         <v>1.2</v>
@@ -50081,7 +50081,7 @@
         <v>1.93</v>
       </c>
       <c r="AG305">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK305">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50196,55 +50196,55 @@
         <v>2.05</v>
       </c>
       <c r="Q306">
-        <v>4.2</v>
+        <v>4.78</v>
       </c>
       <c r="R306">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S306">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="T306">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="U306">
         <v>3.25</v>
       </c>
       <c r="V306">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W306">
         <v>1.04</v>
       </c>
       <c r="X306">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y306">
         <v>1.44</v>
       </c>
       <c r="Z306">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="AA306">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AB306">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AC306">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD306">
         <v>1.17</v>
       </c>
       <c r="AE306">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF306">
         <v>1.95</v>
       </c>
       <c r="AG306">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AK306">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50353,61 +50353,61 @@
         <v>2.2</v>
       </c>
       <c r="O307">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P307">
         <v>3.1</v>
       </c>
       <c r="Q307">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="R307">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="S307">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T307">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="U307">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="V307">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W307">
+        <v>1.05</v>
+      </c>
+      <c r="X307">
+        <v>1.06</v>
+      </c>
+      <c r="Y307">
+        <v>1.48</v>
+      </c>
+      <c r="Z307">
+        <v>2.43</v>
+      </c>
+      <c r="AA307">
+        <v>2.34</v>
+      </c>
+      <c r="AB307">
+        <v>1.51</v>
+      </c>
+      <c r="AC307">
+        <v>5</v>
+      </c>
+      <c r="AD307">
+        <v>1.14</v>
+      </c>
+      <c r="AE307">
         <v>1.02</v>
-      </c>
-      <c r="X307">
-        <v>1.04</v>
-      </c>
-      <c r="Y307">
-        <v>1.41</v>
-      </c>
-      <c r="Z307">
-        <v>2.52</v>
-      </c>
-      <c r="AA307">
-        <v>2.38</v>
-      </c>
-      <c r="AB307">
-        <v>1.5</v>
-      </c>
-      <c r="AC307">
-        <v>4.6</v>
-      </c>
-      <c r="AD307">
-        <v>1.13</v>
-      </c>
-      <c r="AE307">
-        <v>1</v>
       </c>
       <c r="AF307">
         <v>2</v>
       </c>
       <c r="AG307">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK307">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50516,19 +50516,19 @@
         <v>2.1</v>
       </c>
       <c r="O308">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P308">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q308">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R308">
         <v>1.95</v>
       </c>
       <c r="S308">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="T308">
         <v>2.4</v>
@@ -50546,22 +50546,22 @@
         <v>1.08</v>
       </c>
       <c r="Y308">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z308">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AA308">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AB308">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AC308">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="AD308">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE308">
         <v>1.02</v>
@@ -50570,7 +50570,7 @@
         <v>2.15</v>
       </c>
       <c r="AG308">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK308">
         <v>1.59</v>
@@ -50676,10 +50676,10 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O309">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P309">
         <v>4.55</v>
@@ -50694,28 +50694,28 @@
         <v>1.5</v>
       </c>
       <c r="T309">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="U309">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V309">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W309">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X309">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y309">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Z309">
         <v>2.5</v>
       </c>
       <c r="AA309">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="AB309">
         <v>1.47</v>
@@ -50724,16 +50724,16 @@
         <v>5</v>
       </c>
       <c r="AD309">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE309">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF309">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AG309">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK309">
         <v>1.77</v>
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
+        <v>2.06</v>
+      </c>
+      <c r="O310">
+        <v>2.92</v>
+      </c>
+      <c r="P310">
+        <v>3.7</v>
+      </c>
+      <c r="Q310">
+        <v>2.4</v>
+      </c>
+      <c r="R310">
+        <v>2.2</v>
+      </c>
+      <c r="S310">
+        <v>1.4</v>
+      </c>
+      <c r="T310">
+        <v>2.67</v>
+      </c>
+      <c r="U310">
+        <v>3</v>
+      </c>
+      <c r="V310">
+        <v>1.34</v>
+      </c>
+      <c r="W310">
+        <v>1.06</v>
+      </c>
+      <c r="X310">
+        <v>1.07</v>
+      </c>
+      <c r="Y310">
+        <v>1.33</v>
+      </c>
+      <c r="Z310">
+        <v>3.16</v>
+      </c>
+      <c r="AA310">
+        <v>2.14</v>
+      </c>
+      <c r="AB310">
+        <v>1.53</v>
+      </c>
+      <c r="AC310">
+        <v>3.5</v>
+      </c>
+      <c r="AD310">
+        <v>1.22</v>
+      </c>
+      <c r="AE310">
+        <v>1.07</v>
+      </c>
+      <c r="AF310">
         <v>1.85</v>
       </c>
-      <c r="O310">
-        <v>3.3</v>
-      </c>
-      <c r="P310">
-        <v>3.75</v>
-      </c>
-      <c r="Q310">
-        <v>2.52</v>
-      </c>
-      <c r="R310">
-        <v>1.95</v>
-      </c>
-      <c r="S310">
-        <v>1.35</v>
-      </c>
-      <c r="T310">
-        <v>2.9</v>
-      </c>
-      <c r="U310">
-        <v>2.79</v>
-      </c>
-      <c r="V310">
-        <v>1.4</v>
-      </c>
-      <c r="W310">
-        <v>1.08</v>
-      </c>
-      <c r="X310">
-        <v>1.05</v>
-      </c>
-      <c r="Y310">
-        <v>1.35</v>
-      </c>
-      <c r="Z310">
-        <v>3.08</v>
-      </c>
-      <c r="AA310">
-        <v>2</v>
-      </c>
-      <c r="AB310">
-        <v>1.8</v>
-      </c>
-      <c r="AC310">
-        <v>3.14</v>
-      </c>
-      <c r="AD310">
-        <v>1.27</v>
-      </c>
-      <c r="AE310">
-        <v>1.1</v>
-      </c>
-      <c r="AF310">
-        <v>1.74</v>
-      </c>
       <c r="AG310">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK310">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,7 +51002,7 @@
         </is>
       </c>
       <c r="N311">
-        <v>5.1</v>
+        <v>5.29</v>
       </c>
       <c r="O311">
         <v>4.2</v>
@@ -51017,13 +51017,13 @@
         <v>2.3</v>
       </c>
       <c r="S311">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T311">
-        <v>2.91</v>
+        <v>3.32</v>
       </c>
       <c r="U311">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="V311">
         <v>1.48</v>
@@ -51032,7 +51032,7 @@
         <v>1.08</v>
       </c>
       <c r="X311">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y311">
         <v>1.25</v>
@@ -51041,22 +51041,22 @@
         <v>4.1</v>
       </c>
       <c r="AA311">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB311">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC311">
         <v>3</v>
       </c>
       <c r="AD311">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE311">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF311">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG311">
         <v>1.87</v>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.19</v>
+        <v>2.44</v>
       </c>
       <c r="AK311">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51165,37 +51165,37 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O312">
         <v>4.6</v>
       </c>
       <c r="P312">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q312">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="R312">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S312">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T312">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U312">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V312">
         <v>1.42</v>
       </c>
       <c r="W312">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X312">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y312">
         <v>1.3</v>
@@ -51219,10 +51219,10 @@
         <v>1.09</v>
       </c>
       <c r="AF312">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG312">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>1.22</v>
       </c>
       <c r="AK312">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51657,10 +51657,10 @@
         <v>2.2</v>
       </c>
       <c r="O315">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="P315">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q315">
         <v>2.9</v>
@@ -51681,10 +51681,10 @@
         <v>1.21</v>
       </c>
       <c r="W315">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X315">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y315">
         <v>1.46</v>
@@ -51702,7 +51702,7 @@
         <v>6</v>
       </c>
       <c r="AD315">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE315">
         <v>1.03</v>
@@ -51724,7 +51724,7 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK315">
         <v>1.58</v>
@@ -51841,7 +51841,7 @@
         <v>3.3</v>
       </c>
       <c r="V316">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W316">
         <v>1.04</v>
@@ -51871,10 +51871,10 @@
         <v>1.03</v>
       </c>
       <c r="AF316">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG316">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51980,37 +51980,37 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O317">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P317">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q317">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R317">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S317">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T317">
         <v>3.8</v>
       </c>
       <c r="U317">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V317">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W317">
         <v>1.15</v>
       </c>
       <c r="X317">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y317">
         <v>1.13</v>
@@ -52031,10 +52031,10 @@
         <v>1.48</v>
       </c>
       <c r="AE317">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF317">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG317">
         <v>2.47</v>
@@ -52053,7 +52053,7 @@
         <v>1.17</v>
       </c>
       <c r="AK317">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52315,16 +52315,16 @@
         <v>4.2</v>
       </c>
       <c r="Q319">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="R319">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="S319">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T319">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U319">
         <v>3.75</v>
@@ -52336,22 +52336,22 @@
         <v>1.04</v>
       </c>
       <c r="X319">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y319">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z319">
         <v>2.5</v>
       </c>
       <c r="AA319">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AB319">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC319">
-        <v>5.68</v>
+        <v>6</v>
       </c>
       <c r="AD319">
         <v>1.1</v>
@@ -52360,10 +52360,10 @@
         <v>1.03</v>
       </c>
       <c r="AF319">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AG319">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>1.36</v>
       </c>
       <c r="AK319">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52641,10 +52641,10 @@
         <v>5.25</v>
       </c>
       <c r="Q321">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="R321">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S321">
         <v>1.45</v>
@@ -52668,7 +52668,7 @@
         <v>1.38</v>
       </c>
       <c r="Z321">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AA321">
         <v>2.38</v>
@@ -52683,10 +52683,10 @@
         <v>1.19</v>
       </c>
       <c r="AE321">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF321">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG321">
         <v>1.6</v>
@@ -52702,7 +52702,7 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK321">
         <v>1.99</v>
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="O322">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="P322">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q322">
         <v>2.3</v>
@@ -52825,7 +52825,7 @@
         <v>1.03</v>
       </c>
       <c r="X322">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y322">
         <v>1.36</v>
@@ -52843,16 +52843,16 @@
         <v>4.1</v>
       </c>
       <c r="AD322">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE322">
         <v>1.01</v>
       </c>
       <c r="AF322">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AG322">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -53794,10 +53794,10 @@
         <v>4.8</v>
       </c>
       <c r="U328">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="V328">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W328">
         <v>1.2</v>
@@ -53815,7 +53815,7 @@
         <v>1.3</v>
       </c>
       <c r="AB328">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AC328">
         <v>1.9</v>
@@ -53830,7 +53830,7 @@
         <v>1.67</v>
       </c>
       <c r="AG328">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>1.13</v>
       </c>
       <c r="AK328">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53936,16 +53936,16 @@
         </is>
       </c>
       <c r="N329">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="O329">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P329">
         <v>1.4</v>
       </c>
       <c r="Q329">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="R329">
         <v>2.8</v>
@@ -53957,10 +53957,10 @@
         <v>4.5</v>
       </c>
       <c r="U329">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V329">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="W329">
         <v>1.22</v>
@@ -53969,31 +53969,31 @@
         <v>1.01</v>
       </c>
       <c r="Y329">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z329">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="AA329">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AB329">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC329">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AD329">
         <v>1.73</v>
       </c>
       <c r="AE329">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AF329">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG329">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>2.68</v>
+        <v>1.09</v>
       </c>
       <c r="AK329">
         <v>1.1</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S3">
         <v>1.45</v>
@@ -822,7 +822,7 @@
         <v>3.15</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
         <v>1.01</v>
@@ -831,19 +831,19 @@
         <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA3">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB3">
         <v>1.67</v>
       </c>
       <c r="AC3">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AD3">
         <v>1.22</v>
@@ -871,7 +871,7 @@
         <v>1.4</v>
       </c>
       <c r="AK3">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -976,10 +976,10 @@
         <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
         <v>3</v>
@@ -988,7 +988,7 @@
         <v>1.35</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>1.06</v>
@@ -997,7 +997,7 @@
         <v>1.34</v>
       </c>
       <c r="Z4">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
         <v>2.15</v>
@@ -1009,10 +1009,10 @@
         <v>3.82</v>
       </c>
       <c r="AD4">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
         <v>1.84</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>2.9</v>
       </c>
       <c r="U5">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
         <v>1.36</v>
@@ -1166,7 +1166,7 @@
         <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
         <v>3.14</v>
@@ -1181,7 +1181,7 @@
         <v>1.74</v>
       </c>
       <c r="AG5">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O9">
         <v>3.05</v>
@@ -1791,10 +1791,10 @@
         <v>2.05</v>
       </c>
       <c r="S9">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
         <v>2.8</v>
@@ -1803,7 +1803,7 @@
         <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.04</v>
@@ -1827,7 +1827,7 @@
         <v>1.23</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
         <v>1.73</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P10">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q10">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S10">
         <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="U10">
         <v>2.78</v>
@@ -1972,13 +1972,13 @@
         <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA10">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB10">
         <v>1.8</v>
@@ -1996,7 +1996,7 @@
         <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
         <v>1.57</v>
@@ -2111,10 +2111,10 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S11">
         <v>1.36</v>
@@ -2150,10 +2150,10 @@
         <v>3.25</v>
       </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
         <v>1.67</v>
@@ -2277,7 +2277,7 @@
         <v>2.86</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
         <v>1.44</v>
@@ -2286,10 +2286,10 @@
         <v>2.66</v>
       </c>
       <c r="U12">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="V12">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W12">
         <v>1.02</v>
@@ -2612,10 +2612,10 @@
         <v>2.89</v>
       </c>
       <c r="U14">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V14">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W14">
         <v>1.05</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK14">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4073,16 +4073,16 @@
         <v>2.15</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
         <v>2.6</v>
       </c>
       <c r="U23">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
         <v>1.06</v>
@@ -4106,16 +4106,16 @@
         <v>3.24</v>
       </c>
       <c r="AD23">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
         <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG23">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
         <v>1.3</v>
@@ -4275,7 +4275,7 @@
         <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
         <v>2.15</v>
@@ -4457,7 +4457,7 @@
         <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O26">
         <v>3.1</v>
       </c>
       <c r="P26">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="Q26">
         <v>3.32</v>
@@ -4562,7 +4562,7 @@
         <v>1.96</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T26">
         <v>2.75</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,80 +10252,80 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="R61">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="V61">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AA61">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AB61">
-        <v>2.48</v>
+        <v>3.13</v>
       </c>
       <c r="AC61">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD61">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AE61">
+        <v>1.25</v>
+      </c>
+      <c r="AF61">
+        <v>1.38</v>
+      </c>
+      <c r="AG61">
+        <v>2.9</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
         <v>1.22</v>
       </c>
-      <c r="AF61">
-        <v>1.41</v>
-      </c>
-      <c r="AG61">
-        <v>2.7</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.33</v>
-      </c>
       <c r="AK61">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q62">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="V62">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA62">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AB62">
-        <v>3.13</v>
+        <v>2.48</v>
       </c>
       <c r="AC62">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD62">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AE62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AG62">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK62">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11728,7 +11728,7 @@
         <v>4.3</v>
       </c>
       <c r="Q70">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R70">
         <v>2.25</v>
@@ -11776,7 +11776,7 @@
         <v>1.73</v>
       </c>
       <c r="AG70">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -13711,7 +13711,7 @@
         <v>1.25</v>
       </c>
       <c r="Z82">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA82">
         <v>1.8</v>
@@ -13729,7 +13729,7 @@
         <v>1.1</v>
       </c>
       <c r="AF82">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG82">
         <v>2</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q97">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R97">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S97">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="T97">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="U97">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V97">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W97">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X97">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y97">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Z97">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AA97">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AB97">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC97">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AD97">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE97">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF97">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG97">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R98">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S98">
+        <v>1.64</v>
+      </c>
+      <c r="T98">
+        <v>2.11</v>
+      </c>
+      <c r="U98">
+        <v>3.75</v>
+      </c>
+      <c r="V98">
+        <v>1.22</v>
+      </c>
+      <c r="W98">
+        <v>1.03</v>
+      </c>
+      <c r="X98">
+        <v>1.09</v>
+      </c>
+      <c r="Y98">
+        <v>1.56</v>
+      </c>
+      <c r="Z98">
+        <v>2.23</v>
+      </c>
+      <c r="AA98">
+        <v>2.62</v>
+      </c>
+      <c r="AB98">
+        <v>1.4</v>
+      </c>
+      <c r="AC98">
+        <v>5.15</v>
+      </c>
+      <c r="AD98">
+        <v>1.1</v>
+      </c>
+      <c r="AE98">
+        <v>1.03</v>
+      </c>
+      <c r="AF98">
+        <v>2.2</v>
+      </c>
+      <c r="AG98">
+        <v>1.62</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
+        <v>1.36</v>
+      </c>
+      <c r="AK98">
         <v>1.5</v>
-      </c>
-      <c r="T98">
-        <v>2.33</v>
-      </c>
-      <c r="U98">
-        <v>3.5</v>
-      </c>
-      <c r="V98">
-        <v>1.25</v>
-      </c>
-      <c r="W98">
-        <v>1.04</v>
-      </c>
-      <c r="X98">
-        <v>1.11</v>
-      </c>
-      <c r="Y98">
-        <v>1.5</v>
-      </c>
-      <c r="Z98">
-        <v>2.45</v>
-      </c>
-      <c r="AA98">
-        <v>2.49</v>
-      </c>
-      <c r="AB98">
-        <v>1.42</v>
-      </c>
-      <c r="AC98">
-        <v>5</v>
-      </c>
-      <c r="AD98">
-        <v>1.15</v>
-      </c>
-      <c r="AE98">
-        <v>1.04</v>
-      </c>
-      <c r="AF98">
-        <v>2.05</v>
-      </c>
-      <c r="AG98">
-        <v>1.7</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.33</v>
-      </c>
-      <c r="AK98">
-        <v>1.39</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>2.05</v>
       </c>
       <c r="O100">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P100">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q100">
         <v>2.7</v>
@@ -16624,13 +16624,13 @@
         <v>2.05</v>
       </c>
       <c r="S100">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T100">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U100">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V100">
         <v>1.32</v>
@@ -16654,7 +16654,7 @@
         <v>1.65</v>
       </c>
       <c r="AC100">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="AD100">
         <v>1.26</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G105">
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="R105">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S105">
         <v>1.3</v>
       </c>
       <c r="T105">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U105">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V105">
         <v>1.5</v>
       </c>
       <c r="W105">
+        <v>1.08</v>
+      </c>
+      <c r="X105">
+        <v>1.03</v>
+      </c>
+      <c r="Y105">
+        <v>1.17</v>
+      </c>
+      <c r="Z105">
+        <v>3.96</v>
+      </c>
+      <c r="AA105">
+        <v>1.68</v>
+      </c>
+      <c r="AB105">
+        <v>2.02</v>
+      </c>
+      <c r="AC105">
+        <v>2.6</v>
+      </c>
+      <c r="AD105">
+        <v>1.36</v>
+      </c>
+      <c r="AE105">
         <v>1.1</v>
       </c>
-      <c r="X105">
-        <v>1.02</v>
-      </c>
-      <c r="Y105">
-        <v>1.2</v>
-      </c>
-      <c r="Z105">
-        <v>4.5</v>
-      </c>
-      <c r="AA105">
-        <v>1.64</v>
-      </c>
-      <c r="AB105">
-        <v>2.08</v>
-      </c>
-      <c r="AC105">
-        <v>2.52</v>
-      </c>
-      <c r="AD105">
-        <v>1.44</v>
-      </c>
-      <c r="AE105">
-        <v>1.17</v>
-      </c>
       <c r="AF105">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG105">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK105">
-        <v>1.11</v>
+        <v>2.55</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="R107">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S107">
         <v>1.3</v>
       </c>
       <c r="T107">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U107">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V107">
         <v>1.5</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
+        <v>1.2</v>
+      </c>
+      <c r="Z107">
+        <v>4.5</v>
+      </c>
+      <c r="AA107">
+        <v>1.64</v>
+      </c>
+      <c r="AB107">
+        <v>2.08</v>
+      </c>
+      <c r="AC107">
+        <v>2.52</v>
+      </c>
+      <c r="AD107">
+        <v>1.44</v>
+      </c>
+      <c r="AE107">
         <v>1.17</v>
       </c>
-      <c r="Z107">
-        <v>3.96</v>
-      </c>
-      <c r="AA107">
-        <v>1.68</v>
-      </c>
-      <c r="AB107">
-        <v>2.02</v>
-      </c>
-      <c r="AC107">
-        <v>2.6</v>
-      </c>
-      <c r="AD107">
-        <v>1.36</v>
-      </c>
-      <c r="AE107">
-        <v>1.1</v>
-      </c>
       <c r="AF107">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>2.55</v>
+        <v>1.11</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -27207,16 +27207,16 @@
         <v>2.7</v>
       </c>
       <c r="O165">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P165">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q165">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="R165">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S165">
         <v>1.4</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,34 +29812,34 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="O181">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P181">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="Q181">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="R181">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="S181">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T181">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="U181">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V181">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W181">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X181">
         <v>1.03</v>
@@ -29848,28 +29848,28 @@
         <v>1.14</v>
       </c>
       <c r="Z181">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA181">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB181">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AC181">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AD181">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE181">
         <v>1.22</v>
       </c>
       <c r="AF181">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG181">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>1.22</v>
       </c>
       <c r="AK181">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,80 +29975,80 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="O182">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P182">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="Q182">
-        <v>3.35</v>
+        <v>4.25</v>
       </c>
       <c r="R182">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S182">
+        <v>1.2</v>
+      </c>
+      <c r="T182">
+        <v>3.75</v>
+      </c>
+      <c r="U182">
+        <v>2.05</v>
+      </c>
+      <c r="V182">
+        <v>1.65</v>
+      </c>
+      <c r="W182">
+        <v>1.16</v>
+      </c>
+      <c r="X182">
+        <v>1.02</v>
+      </c>
+      <c r="Y182">
+        <v>1.15</v>
+      </c>
+      <c r="Z182">
+        <v>5.25</v>
+      </c>
+      <c r="AA182">
+        <v>1.48</v>
+      </c>
+      <c r="AB182">
+        <v>2.54</v>
+      </c>
+      <c r="AC182">
+        <v>2.1</v>
+      </c>
+      <c r="AD182">
+        <v>1.67</v>
+      </c>
+      <c r="AE182">
         <v>1.25</v>
       </c>
-      <c r="T182">
-        <v>3.45</v>
-      </c>
-      <c r="U182">
-        <v>2.2</v>
-      </c>
-      <c r="V182">
-        <v>1.57</v>
-      </c>
-      <c r="W182">
-        <v>1.13</v>
-      </c>
-      <c r="X182">
-        <v>1.03</v>
-      </c>
-      <c r="Y182">
-        <v>1.14</v>
-      </c>
-      <c r="Z182">
-        <v>5.5</v>
-      </c>
-      <c r="AA182">
-        <v>1.57</v>
-      </c>
-      <c r="AB182">
-        <v>2.27</v>
-      </c>
-      <c r="AC182">
-        <v>2.38</v>
-      </c>
-      <c r="AD182">
-        <v>1.54</v>
-      </c>
-      <c r="AE182">
+      <c r="AF182">
+        <v>1.46</v>
+      </c>
+      <c r="AG182">
+        <v>2.53</v>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ182">
+        <v>1.18</v>
+      </c>
+      <c r="AK182">
         <v>1.22</v>
-      </c>
-      <c r="AF182">
-        <v>1.48</v>
-      </c>
-      <c r="AG182">
-        <v>2.55</v>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ182">
-        <v>1.22</v>
-      </c>
-      <c r="AK182">
-        <v>1.28</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="O183">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P183">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q183">
-        <v>4.25</v>
+        <v>2.74</v>
       </c>
       <c r="R183">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S183">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T183">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U183">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V183">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="W183">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X183">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y183">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z183">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA183">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB183">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="AC183">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AD183">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE183">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF183">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG183">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK183">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -36667,7 +36667,7 @@
         <v>0</v>
       </c>
       <c r="Q223">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="R223">
         <v>2.1</v>
@@ -36691,16 +36691,16 @@
         <v>1.04</v>
       </c>
       <c r="Y223">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z223">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA223">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AB223">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC223">
         <v>3.5</v>
@@ -36709,13 +36709,13 @@
         <v>1.22</v>
       </c>
       <c r="AE223">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF223">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG223">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK223">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36854,7 +36854,7 @@
         <v>1.07</v>
       </c>
       <c r="Y224">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="Z224">
         <v>2.58</v>
@@ -36878,7 +36878,7 @@
         <v>2.01</v>
       </c>
       <c r="AG224">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK224">
         <v>1.73</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="O300">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="P300">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q300">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="R300">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="S300">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="T300">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U300">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="V300">
+        <v>1.25</v>
+      </c>
+      <c r="W300">
+        <v>1.04</v>
+      </c>
+      <c r="X300">
+        <v>1.1</v>
+      </c>
+      <c r="Y300">
+        <v>1.57</v>
+      </c>
+      <c r="Z300">
+        <v>2.38</v>
+      </c>
+      <c r="AA300">
+        <v>2.88</v>
+      </c>
+      <c r="AB300">
         <v>1.35</v>
       </c>
-      <c r="W300">
-        <v>1.03</v>
-      </c>
-      <c r="X300">
-        <v>1.06</v>
-      </c>
-      <c r="Y300">
-        <v>1.39</v>
-      </c>
-      <c r="Z300">
-        <v>2.63</v>
-      </c>
-      <c r="AA300">
-        <v>2.17</v>
-      </c>
-      <c r="AB300">
-        <v>1.55</v>
-      </c>
       <c r="AC300">
-        <v>4.27</v>
+        <v>6</v>
       </c>
       <c r="AD300">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE300">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF300">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG300">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK300">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
+        <v>1.7</v>
+      </c>
+      <c r="O302">
+        <v>3.3</v>
+      </c>
+      <c r="P302">
+        <v>3.85</v>
+      </c>
+      <c r="Q302">
+        <v>2.44</v>
+      </c>
+      <c r="R302">
         <v>2.1</v>
       </c>
-      <c r="O302">
-        <v>2.87</v>
-      </c>
-      <c r="P302">
-        <v>3.6</v>
-      </c>
-      <c r="Q302">
-        <v>2.8</v>
-      </c>
-      <c r="R302">
-        <v>1.79</v>
-      </c>
       <c r="S302">
+        <v>1.4</v>
+      </c>
+      <c r="T302">
+        <v>2.45</v>
+      </c>
+      <c r="U302">
+        <v>3.34</v>
+      </c>
+      <c r="V302">
+        <v>1.35</v>
+      </c>
+      <c r="W302">
+        <v>1.03</v>
+      </c>
+      <c r="X302">
+        <v>1.06</v>
+      </c>
+      <c r="Y302">
+        <v>1.39</v>
+      </c>
+      <c r="Z302">
+        <v>2.63</v>
+      </c>
+      <c r="AA302">
+        <v>2.17</v>
+      </c>
+      <c r="AB302">
         <v>1.55</v>
       </c>
-      <c r="T302">
-        <v>2.25</v>
-      </c>
-      <c r="U302">
-        <v>3.7</v>
-      </c>
-      <c r="V302">
-        <v>1.25</v>
-      </c>
-      <c r="W302">
-        <v>1.04</v>
-      </c>
-      <c r="X302">
-        <v>1.1</v>
-      </c>
-      <c r="Y302">
-        <v>1.57</v>
-      </c>
-      <c r="Z302">
-        <v>2.38</v>
-      </c>
-      <c r="AA302">
-        <v>2.88</v>
-      </c>
-      <c r="AB302">
-        <v>1.35</v>
-      </c>
       <c r="AC302">
-        <v>6</v>
+        <v>4.27</v>
       </c>
       <c r="AD302">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE302">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF302">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG302">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK302">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -51011,10 +51011,10 @@
         <v>3.7</v>
       </c>
       <c r="Q311">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R311">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S311">
         <v>1.4</v>
@@ -51044,13 +51044,13 @@
         <v>2.14</v>
       </c>
       <c r="AB311">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC311">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD311">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE311">
         <v>1.07</v>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK311">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL311">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -994,7 +994,7 @@
         <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
         <v>2.88</v>
@@ -1006,19 +1006,19 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AD4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE4">
         <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1139,13 +1139,13 @@
         <v>2.15</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T5">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V5">
         <v>1.36</v>
@@ -1163,13 +1163,13 @@
         <v>3.4</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC5">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="AD5">
         <v>1.3</v>
@@ -1181,7 +1181,7 @@
         <v>1.74</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>3.1</v>
       </c>
       <c r="P6">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="Q6">
         <v>2.45</v>
@@ -1308,10 +1308,10 @@
         <v>3.6</v>
       </c>
       <c r="U6">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W6">
         <v>1.13</v>
@@ -1320,19 +1320,19 @@
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA6">
         <v>1.53</v>
       </c>
       <c r="AB6">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AC6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD6">
         <v>1.53</v>
@@ -1344,7 +1344,7 @@
         <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="U10">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
+        <v>1.24</v>
+      </c>
+      <c r="Z10">
+        <v>3.5</v>
+      </c>
+      <c r="AA10">
+        <v>1.95</v>
+      </c>
+      <c r="AB10">
+        <v>1.85</v>
+      </c>
+      <c r="AC10">
+        <v>3.25</v>
+      </c>
+      <c r="AD10">
+        <v>1.35</v>
+      </c>
+      <c r="AE10">
+        <v>1.1</v>
+      </c>
+      <c r="AF10">
+        <v>1.67</v>
+      </c>
+      <c r="AG10">
+        <v>1.94</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.25</v>
       </c>
-      <c r="Z10">
-        <v>3.28</v>
-      </c>
-      <c r="AA10">
-        <v>1.91</v>
-      </c>
-      <c r="AB10">
-        <v>1.8</v>
-      </c>
-      <c r="AC10">
-        <v>3.4</v>
-      </c>
-      <c r="AD10">
-        <v>1.29</v>
-      </c>
-      <c r="AE10">
-        <v>1.11</v>
-      </c>
-      <c r="AF10">
-        <v>1.7</v>
-      </c>
-      <c r="AG10">
-        <v>2.05</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.27</v>
-      </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="R11">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
+        <v>2.7</v>
+      </c>
+      <c r="U11">
         <v>2.78</v>
       </c>
-      <c r="U11">
-        <v>2.75</v>
-      </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA11">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD11">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2277,19 +2277,19 @@
         <v>2.86</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S12">
         <v>1.44</v>
       </c>
       <c r="T12">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="U12">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="V12">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W12">
         <v>1.02</v>
@@ -2304,7 +2304,7 @@
         <v>2.66</v>
       </c>
       <c r="AA12">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB12">
         <v>1.63</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
         <v>1.62</v>
@@ -2606,34 +2606,34 @@
         <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T14">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U14">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V14">
         <v>1.42</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z14">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="AA14">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AB14">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC14">
         <v>3.55</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4260,7 +4260,7 @@
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB24">
         <v>2.32</v>
@@ -4426,7 +4426,7 @@
         <v>1.75</v>
       </c>
       <c r="AB25">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC25">
         <v>3</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="O41">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -7007,19 +7007,19 @@
         <v>2.07</v>
       </c>
       <c r="S41">
+        <v>1.33</v>
+      </c>
+      <c r="T41">
+        <v>3</v>
+      </c>
+      <c r="U41">
+        <v>2.75</v>
+      </c>
+      <c r="V41">
         <v>1.37</v>
       </c>
-      <c r="T41">
-        <v>2.77</v>
-      </c>
-      <c r="U41">
-        <v>2.59</v>
-      </c>
-      <c r="V41">
-        <v>1.42</v>
-      </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.04</v>
@@ -7043,7 +7043,7 @@
         <v>1.29</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
         <v>1.68</v>
@@ -7653,22 +7653,22 @@
         <v>5.39</v>
       </c>
       <c r="Q45">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="R45">
         <v>2.1</v>
       </c>
       <c r="S45">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U45">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W45">
         <v>1.07</v>
@@ -7677,31 +7677,31 @@
         <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z45">
         <v>3.7</v>
       </c>
       <c r="AA45">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB45">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AC45">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AD45">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE45">
         <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG45">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK45">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>1.4</v>
       </c>
       <c r="R51">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S51">
         <v>1.15</v>
@@ -8676,7 +8676,7 @@
         <v>1.39</v>
       </c>
       <c r="AF51">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG51">
         <v>1.8</v>
@@ -8797,34 +8797,34 @@
         <v>2.95</v>
       </c>
       <c r="R52">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
         <v>1.25</v>
       </c>
       <c r="T52">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U52">
         <v>2.07</v>
       </c>
       <c r="V52">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
         <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AA52">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB52">
         <v>2.38</v>
@@ -8839,10 +8839,10 @@
         <v>1.22</v>
       </c>
       <c r="AF52">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG52">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O53">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P53">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q53">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="R53">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
         <v>1.3</v>
@@ -8972,10 +8972,10 @@
         <v>2.45</v>
       </c>
       <c r="V53">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X53">
         <v>1.04</v>
@@ -8984,13 +8984,13 @@
         <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>4.43</v>
+        <v>3.8</v>
       </c>
       <c r="AA53">
         <v>1.71</v>
       </c>
       <c r="AB53">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC53">
         <v>2.88</v>
@@ -8999,7 +8999,7 @@
         <v>1.36</v>
       </c>
       <c r="AE53">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF53">
         <v>1.57</v>
@@ -9120,10 +9120,10 @@
         <v>1.25</v>
       </c>
       <c r="Q54">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="R54">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="S54">
         <v>1.22</v>
@@ -9132,43 +9132,43 @@
         <v>3.75</v>
       </c>
       <c r="U54">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V54">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.14</v>
       </c>
       <c r="Z54">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AA54">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB54">
         <v>2.55</v>
       </c>
       <c r="AC54">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AD54">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE54">
         <v>1.24</v>
       </c>
       <c r="AF54">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AG54">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9283,55 +9283,55 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="R55">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
         <v>1.33</v>
       </c>
       <c r="T55">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U55">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V55">
         <v>1.46</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z55">
         <v>4</v>
       </c>
       <c r="AA55">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB55">
         <v>2</v>
       </c>
       <c r="AC55">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD55">
         <v>1.35</v>
       </c>
       <c r="AE55">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
         <v>1.68</v>
       </c>
       <c r="AG55">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.18</v>
       </c>
       <c r="AK55">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9476,7 +9476,7 @@
         <v>3.25</v>
       </c>
       <c r="AA56">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB56">
         <v>1.66</v>
@@ -9491,10 +9491,10 @@
         <v>1.07</v>
       </c>
       <c r="AF56">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG56">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>4.1</v>
       </c>
       <c r="AA57">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB57">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC57">
         <v>3.1</v>
@@ -9941,7 +9941,7 @@
         <v>2.45</v>
       </c>
       <c r="S59">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T59">
         <v>2.75</v>
@@ -9950,7 +9950,7 @@
         <v>2.25</v>
       </c>
       <c r="V59">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W59">
         <v>1.08</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK59">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10110,7 +10110,7 @@
         <v>3.3</v>
       </c>
       <c r="U60">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="V60">
         <v>1.59</v>
@@ -10261,7 +10261,7 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="R61">
         <v>2.5</v>
@@ -10421,7 +10421,7 @@
         <v>3.75</v>
       </c>
       <c r="P62">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -10442,7 +10442,7 @@
         <v>1.65</v>
       </c>
       <c r="W62">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
@@ -10617,7 +10617,7 @@
         <v>5.1</v>
       </c>
       <c r="AA63">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB63">
         <v>2.85</v>
@@ -10907,61 +10907,61 @@
         <v>2.09</v>
       </c>
       <c r="O65">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P65">
         <v>3.26</v>
       </c>
       <c r="Q65">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="R65">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S65">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T65">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U65">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="V65">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W65">
         <v>1.02</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z65">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AA65">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AB65">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC65">
-        <v>4.29</v>
+        <v>4.19</v>
       </c>
       <c r="AD65">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE65">
         <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AG65">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK65">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O66">
+        <v>3</v>
+      </c>
+      <c r="P66">
+        <v>2.25</v>
+      </c>
+      <c r="Q66">
+        <v>3.3</v>
+      </c>
+      <c r="R66">
+        <v>2.05</v>
+      </c>
+      <c r="S66">
+        <v>1.36</v>
+      </c>
+      <c r="T66">
+        <v>2.53</v>
+      </c>
+      <c r="U66">
+        <v>2.88</v>
+      </c>
+      <c r="V66">
+        <v>1.35</v>
+      </c>
+      <c r="W66">
+        <v>1.04</v>
+      </c>
+      <c r="X66">
+        <v>1.03</v>
+      </c>
+      <c r="Y66">
+        <v>1.3</v>
+      </c>
+      <c r="Z66">
         <v>3.4</v>
       </c>
-      <c r="P66">
-        <v>2.55</v>
-      </c>
-      <c r="Q66">
-        <v>3.1</v>
-      </c>
-      <c r="R66">
-        <v>2.15</v>
-      </c>
-      <c r="S66">
-        <v>1.33</v>
-      </c>
-      <c r="T66">
-        <v>3</v>
-      </c>
-      <c r="U66">
-        <v>2.63</v>
-      </c>
-      <c r="V66">
-        <v>1.44</v>
-      </c>
-      <c r="W66">
+      <c r="AA66">
+        <v>2</v>
+      </c>
+      <c r="AB66">
+        <v>1.8</v>
+      </c>
+      <c r="AC66">
+        <v>3.5</v>
+      </c>
+      <c r="AD66">
+        <v>1.24</v>
+      </c>
+      <c r="AE66">
         <v>1.1</v>
       </c>
-      <c r="X66">
-        <v>1</v>
-      </c>
-      <c r="Y66">
-        <v>1.23</v>
-      </c>
-      <c r="Z66">
-        <v>3.42</v>
-      </c>
-      <c r="AA66">
-        <v>1.79</v>
-      </c>
-      <c r="AB66">
-        <v>1.9</v>
-      </c>
-      <c r="AC66">
-        <v>2.88</v>
-      </c>
-      <c r="AD66">
-        <v>1.32</v>
-      </c>
-      <c r="AE66">
-        <v>1.09</v>
-      </c>
       <c r="AF66">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG66">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="O67">
+        <v>3.4</v>
+      </c>
+      <c r="P67">
+        <v>2.55</v>
+      </c>
+      <c r="Q67">
+        <v>3.1</v>
+      </c>
+      <c r="R67">
+        <v>2.15</v>
+      </c>
+      <c r="S67">
+        <v>1.33</v>
+      </c>
+      <c r="T67">
         <v>3</v>
       </c>
-      <c r="P67">
-        <v>2.25</v>
-      </c>
-      <c r="Q67">
-        <v>3.3</v>
-      </c>
-      <c r="R67">
-        <v>2.05</v>
-      </c>
-      <c r="S67">
-        <v>1.36</v>
-      </c>
-      <c r="T67">
-        <v>2.53</v>
-      </c>
       <c r="U67">
+        <v>2.63</v>
+      </c>
+      <c r="V67">
+        <v>1.44</v>
+      </c>
+      <c r="W67">
+        <v>1.1</v>
+      </c>
+      <c r="X67">
+        <v>1</v>
+      </c>
+      <c r="Y67">
+        <v>1.23</v>
+      </c>
+      <c r="Z67">
+        <v>3.42</v>
+      </c>
+      <c r="AA67">
+        <v>1.79</v>
+      </c>
+      <c r="AB67">
+        <v>1.9</v>
+      </c>
+      <c r="AC67">
         <v>2.88</v>
       </c>
-      <c r="V67">
-        <v>1.35</v>
-      </c>
-      <c r="W67">
-        <v>1.04</v>
-      </c>
-      <c r="X67">
-        <v>1.03</v>
-      </c>
-      <c r="Y67">
-        <v>1.3</v>
-      </c>
-      <c r="Z67">
-        <v>3.4</v>
-      </c>
-      <c r="AA67">
-        <v>2</v>
-      </c>
-      <c r="AB67">
-        <v>1.8</v>
-      </c>
-      <c r="AC67">
-        <v>3.5</v>
-      </c>
       <c r="AD67">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF67">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O69">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="P69">
         <v>10.5</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB69">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11758,13 +11758,13 @@
         <v>3.6</v>
       </c>
       <c r="AA70">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB70">
         <v>1.9</v>
       </c>
       <c r="AC70">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD70">
         <v>1.36</v>
@@ -11773,10 +11773,10 @@
         <v>1.08</v>
       </c>
       <c r="AF70">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG70">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>3.45</v>
       </c>
       <c r="P74">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -12389,7 +12389,7 @@
         <v>1.42</v>
       </c>
       <c r="T74">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U74">
         <v>2.9</v>
@@ -12398,10 +12398,10 @@
         <v>1.36</v>
       </c>
       <c r="W74">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y74">
         <v>1.36</v>
@@ -12422,7 +12422,7 @@
         <v>1.25</v>
       </c>
       <c r="AE74">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF74">
         <v>1.81</v>
@@ -12706,7 +12706,7 @@
         <v>5</v>
       </c>
       <c r="Q76">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="R76">
         <v>2.1</v>
@@ -12715,10 +12715,10 @@
         <v>1.46</v>
       </c>
       <c r="T76">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="U76">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V76">
         <v>1.33</v>
@@ -12727,7 +12727,7 @@
         <v>1.05</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y76">
         <v>1.3</v>
@@ -12739,7 +12739,7 @@
         <v>2.1</v>
       </c>
       <c r="AB76">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC76">
         <v>3.48</v>
@@ -12751,7 +12751,7 @@
         <v>1.05</v>
       </c>
       <c r="AF76">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG76">
         <v>1.85</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13029,13 +13029,13 @@
         <v>3.6</v>
       </c>
       <c r="P78">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q78">
         <v>2.4</v>
       </c>
       <c r="R78">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S78">
         <v>1.33</v>
@@ -13044,7 +13044,7 @@
         <v>2.78</v>
       </c>
       <c r="U78">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="V78">
         <v>1.42</v>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P79">
         <v>2.85</v>
@@ -13201,7 +13201,7 @@
         <v>2</v>
       </c>
       <c r="S79">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T79">
         <v>2.75</v>
@@ -13210,7 +13210,7 @@
         <v>3</v>
       </c>
       <c r="V79">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W79">
         <v>1.05</v>
@@ -13222,19 +13222,19 @@
         <v>1.33</v>
       </c>
       <c r="Z79">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AA79">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
         <v>1.7</v>
       </c>
       <c r="AC79">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AD79">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE79">
         <v>1.1</v>
@@ -13243,7 +13243,7 @@
         <v>1.75</v>
       </c>
       <c r="AG79">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -14342,28 +14342,28 @@
         <v>2.06</v>
       </c>
       <c r="S86">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T86">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U86">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V86">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W86">
+        <v>1.04</v>
+      </c>
+      <c r="X86">
         <v>1.05</v>
       </c>
-      <c r="X86">
-        <v>1.04</v>
-      </c>
       <c r="Y86">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z86">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA86">
         <v>2</v>
@@ -14381,7 +14381,7 @@
         <v>1.1</v>
       </c>
       <c r="AF86">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG86">
         <v>1.73</v>
@@ -15326,16 +15326,16 @@
         <v>3.3</v>
       </c>
       <c r="U92">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="V92">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W92">
         <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
         <v>1.2</v>
@@ -15347,7 +15347,7 @@
         <v>1.65</v>
       </c>
       <c r="AB92">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC92">
         <v>2.43</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
         <v>1.7</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -16295,13 +16295,13 @@
         <v>3.32</v>
       </c>
       <c r="R98">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S98">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="T98">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="U98">
         <v>3.75</v>
@@ -16313,13 +16313,13 @@
         <v>1.03</v>
       </c>
       <c r="X98">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y98">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="Z98">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="AA98">
         <v>2.62</v>
@@ -16331,7 +16331,7 @@
         <v>5.15</v>
       </c>
       <c r="AD98">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE98">
         <v>1.03</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G105">
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="R105">
+        <v>2.31</v>
+      </c>
+      <c r="S105">
+        <v>1.28</v>
+      </c>
+      <c r="T105">
+        <v>3.18</v>
+      </c>
+      <c r="U105">
         <v>2.4</v>
-      </c>
-      <c r="S105">
-        <v>1.3</v>
-      </c>
-      <c r="T105">
-        <v>3.2</v>
-      </c>
-      <c r="U105">
-        <v>2.55</v>
       </c>
       <c r="V105">
         <v>1.5</v>
       </c>
       <c r="W105">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
+        <v>1.2</v>
+      </c>
+      <c r="Z105">
+        <v>4.5</v>
+      </c>
+      <c r="AA105">
+        <v>1.64</v>
+      </c>
+      <c r="AB105">
+        <v>2.2</v>
+      </c>
+      <c r="AC105">
+        <v>2.63</v>
+      </c>
+      <c r="AD105">
+        <v>1.47</v>
+      </c>
+      <c r="AE105">
         <v>1.17</v>
       </c>
-      <c r="Z105">
-        <v>3.96</v>
-      </c>
-      <c r="AA105">
-        <v>1.68</v>
-      </c>
-      <c r="AB105">
-        <v>2.02</v>
-      </c>
-      <c r="AC105">
-        <v>2.6</v>
-      </c>
-      <c r="AD105">
-        <v>1.36</v>
-      </c>
-      <c r="AE105">
-        <v>1.1</v>
-      </c>
       <c r="AF105">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG105">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK105">
-        <v>2.55</v>
+        <v>1.11</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17599,22 +17599,22 @@
         <v>2.96</v>
       </c>
       <c r="R106">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S106">
         <v>1.35</v>
       </c>
       <c r="T106">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="U106">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V106">
         <v>1.4</v>
       </c>
       <c r="W106">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X106">
         <v>1.03</v>
@@ -17629,10 +17629,10 @@
         <v>1.86</v>
       </c>
       <c r="AB106">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AC106">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD106">
         <v>1.28</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK106">
         <v>1.47</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="R107">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S107">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T107">
         <v>3.3</v>
       </c>
       <c r="U107">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V107">
         <v>1.5</v>
       </c>
       <c r="W107">
+        <v>1.08</v>
+      </c>
+      <c r="X107">
+        <v>1.03</v>
+      </c>
+      <c r="Y107">
+        <v>1.17</v>
+      </c>
+      <c r="Z107">
+        <v>3.96</v>
+      </c>
+      <c r="AA107">
+        <v>1.69</v>
+      </c>
+      <c r="AB107">
+        <v>2.04</v>
+      </c>
+      <c r="AC107">
+        <v>2.7</v>
+      </c>
+      <c r="AD107">
+        <v>1.36</v>
+      </c>
+      <c r="AE107">
         <v>1.1</v>
       </c>
-      <c r="X107">
-        <v>1.02</v>
-      </c>
-      <c r="Y107">
-        <v>1.2</v>
-      </c>
-      <c r="Z107">
-        <v>4.5</v>
-      </c>
-      <c r="AA107">
-        <v>1.64</v>
-      </c>
-      <c r="AB107">
-        <v>2.08</v>
-      </c>
-      <c r="AC107">
-        <v>2.52</v>
-      </c>
-      <c r="AD107">
-        <v>1.44</v>
-      </c>
-      <c r="AE107">
-        <v>1.17</v>
-      </c>
       <c r="AF107">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG107">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK107">
-        <v>1.11</v>
+        <v>2.55</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="O112">
         <v>3.1</v>
       </c>
       <c r="P112">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="Q112">
         <v>3.04</v>
@@ -18607,7 +18607,7 @@
         <v>2.3</v>
       </c>
       <c r="AB112">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC112">
         <v>4.25</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18918,7 +18918,7 @@
         <v>1.76</v>
       </c>
       <c r="W114">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X114">
         <v>1.01</v>
@@ -18933,7 +18933,7 @@
         <v>1.4</v>
       </c>
       <c r="AB114">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="AC114">
         <v>2.07</v>
@@ -18942,13 +18942,13 @@
         <v>1.73</v>
       </c>
       <c r="AE114">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF114">
         <v>1.57</v>
       </c>
       <c r="AG114">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19226,10 +19226,10 @@
         <v>0</v>
       </c>
       <c r="Q116">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R116">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="S116">
         <v>1.08</v>
@@ -19244,13 +19244,13 @@
         <v>2.1</v>
       </c>
       <c r="W116">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X116">
         <v>1</v>
       </c>
       <c r="Y116">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Z116">
         <v>11</v>
@@ -19262,13 +19262,13 @@
         <v>5</v>
       </c>
       <c r="AC116">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AD116">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AE116">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AF116">
         <v>2.7</v>
@@ -23790,7 +23790,7 @@
         <v>2.1</v>
       </c>
       <c r="Q144">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R144">
         <v>2.23</v>
@@ -23851,7 +23851,7 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK144">
         <v>1.32</v>
@@ -24635,10 +24635,10 @@
         <v>3.76</v>
       </c>
       <c r="AA149">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AB149">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AC149">
         <v>3</v>
@@ -26238,19 +26238,19 @@
         <v>1.91</v>
       </c>
       <c r="R159">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S159">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T159">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U159">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V159">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W159">
         <v>1.11</v>
@@ -26259,16 +26259,16 @@
         <v>1.03</v>
       </c>
       <c r="Y159">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z159">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="AA159">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB159">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC159">
         <v>2.75</v>
@@ -26277,13 +26277,13 @@
         <v>1.4</v>
       </c>
       <c r="AE159">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF159">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG159">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK159">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26570,10 +26570,10 @@
         <v>1.48</v>
       </c>
       <c r="T161">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U161">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V161">
         <v>1.26</v>
@@ -26588,7 +26588,7 @@
         <v>1.5</v>
       </c>
       <c r="Z161">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AA161">
         <v>2.46</v>
@@ -26600,7 +26600,7 @@
         <v>5.5</v>
       </c>
       <c r="AD161">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE161">
         <v>1.01</v>
@@ -26730,13 +26730,13 @@
         <v>3.1</v>
       </c>
       <c r="S162">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T162">
         <v>4.75</v>
       </c>
       <c r="U162">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V162">
         <v>1.95</v>
@@ -26766,10 +26766,10 @@
         <v>2.1</v>
       </c>
       <c r="AE162">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF162">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG162">
         <v>2.1</v>
@@ -27373,10 +27373,10 @@
         <v>3.35</v>
       </c>
       <c r="P166">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="Q166">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="R166">
         <v>2.23</v>
@@ -27394,19 +27394,19 @@
         <v>1.57</v>
       </c>
       <c r="W166">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X166">
         <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z166">
         <v>4.3</v>
       </c>
       <c r="AA166">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB166">
         <v>2.3</v>
@@ -27440,7 +27440,7 @@
         <v>1.08</v>
       </c>
       <c r="AK166">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27578,13 +27578,13 @@
         <v>2.1</v>
       </c>
       <c r="AD167">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE167">
         <v>1.25</v>
       </c>
       <c r="AF167">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG167">
         <v>2.15</v>
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O175">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P175">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q175">
         <v>3.8</v>
@@ -28855,7 +28855,7 @@
         <v>2.9</v>
       </c>
       <c r="U175">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="V175">
         <v>1.4</v>
@@ -28864,19 +28864,19 @@
         <v>1.08</v>
       </c>
       <c r="X175">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y175">
         <v>1.25</v>
       </c>
       <c r="Z175">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA175">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB175">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC175">
         <v>3.2</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O204">
         <v>3.15</v>
       </c>
       <c r="P204">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q204">
         <v>3.95</v>
@@ -33579,7 +33579,7 @@
         <v>1.42</v>
       </c>
       <c r="T204">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="U204">
         <v>2.81</v>
@@ -33634,7 +33634,7 @@
         <v>1.32</v>
       </c>
       <c r="AK204">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33745,7 +33745,7 @@
         <v>2.65</v>
       </c>
       <c r="U205">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V205">
         <v>1.32</v>
@@ -33754,10 +33754,10 @@
         <v>1.04</v>
       </c>
       <c r="X205">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y205">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z205">
         <v>2.9</v>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK205">
         <v>1.67</v>
@@ -34382,7 +34382,7 @@
         <v>2.85</v>
       </c>
       <c r="P209">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q209">
         <v>2.8</v>
@@ -34391,10 +34391,10 @@
         <v>1.91</v>
       </c>
       <c r="S209">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="T209">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="U209">
         <v>3.5</v>
@@ -34403,7 +34403,7 @@
         <v>1.25</v>
       </c>
       <c r="W209">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X209">
         <v>1.1</v>
@@ -34449,7 +34449,7 @@
         <v>1.36</v>
       </c>
       <c r="AK209">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35680,7 +35680,7 @@
         </is>
       </c>
       <c r="N217">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O217">
         <v>8.35</v>
@@ -35692,7 +35692,7 @@
         <v>6.86</v>
       </c>
       <c r="R217">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S217">
         <v>1.09</v>
@@ -35728,16 +35728,16 @@
         <v>1.47</v>
       </c>
       <c r="AD217">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AE217">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF217">
         <v>1.53</v>
       </c>
       <c r="AG217">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O236">
         <v>3.5</v>
       </c>
       <c r="P236">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="Q236">
         <v>2.3</v>
@@ -38795,7 +38795,7 @@
         <v>1.38</v>
       </c>
       <c r="T236">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U236">
         <v>2.82</v>
@@ -38816,10 +38816,10 @@
         <v>3.25</v>
       </c>
       <c r="AA236">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AB236">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC236">
         <v>3.68</v>
@@ -38850,7 +38850,7 @@
         <v>1.33</v>
       </c>
       <c r="AK236">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -40081,10 +40081,10 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O244">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P244">
         <v>4.9</v>
@@ -40096,10 +40096,10 @@
         <v>2.1</v>
       </c>
       <c r="S244">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T244">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U244">
         <v>3</v>
@@ -40108,37 +40108,37 @@
         <v>1.36</v>
       </c>
       <c r="W244">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X244">
         <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z244">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="AA244">
         <v>2.1</v>
       </c>
       <c r="AB244">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC244">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="AD244">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE244">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF244">
         <v>1.95</v>
       </c>
       <c r="AG244">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK244">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40416,10 +40416,10 @@
         <v>0</v>
       </c>
       <c r="Q246">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R246">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S246">
         <v>1.72</v>
@@ -40431,13 +40431,13 @@
         <v>4.6</v>
       </c>
       <c r="V246">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W246">
         <v>1</v>
       </c>
       <c r="X246">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y246">
         <v>1.67</v>
@@ -40452,7 +40452,7 @@
         <v>1.36</v>
       </c>
       <c r="AC246">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="AD246">
         <v>1.07</v>
@@ -40461,26 +40461,26 @@
         <v>1.01</v>
       </c>
       <c r="AF246">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AG246">
+        <v>1.53</v>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ246">
+        <v>1.4</v>
+      </c>
+      <c r="AK246">
         <v>1.55</v>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ246">
-        <v>1.44</v>
-      </c>
-      <c r="AK246">
-        <v>1.58</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40573,16 +40573,16 @@
         <v>1.16</v>
       </c>
       <c r="O247">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="P247">
-        <v>9.5</v>
+        <v>9.85</v>
       </c>
       <c r="Q247">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R247">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="S247">
         <v>1.23</v>
@@ -40591,10 +40591,10 @@
         <v>3.78</v>
       </c>
       <c r="U247">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V247">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W247">
         <v>1.14</v>
@@ -40612,22 +40612,22 @@
         <v>1.5</v>
       </c>
       <c r="AB247">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="AC247">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AD247">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE247">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF247">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG247">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK247">
-        <v>3.51</v>
+        <v>4.02</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -44334,10 +44334,10 @@
         <v>2.1</v>
       </c>
       <c r="S270">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T270">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U270">
         <v>1.98</v>
@@ -44349,7 +44349,7 @@
         <v>1.08</v>
       </c>
       <c r="X270">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y270">
         <v>1.13</v>
@@ -44367,7 +44367,7 @@
         <v>2.5</v>
       </c>
       <c r="AD270">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE270">
         <v>1.15</v>
@@ -44817,10 +44817,10 @@
         <v>0</v>
       </c>
       <c r="Q273">
-        <v>7.48</v>
+        <v>7</v>
       </c>
       <c r="R273">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="S273">
         <v>1.22</v>
@@ -44832,10 +44832,10 @@
         <v>2.18</v>
       </c>
       <c r="V273">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W273">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X273">
         <v>1.01</v>
@@ -44881,7 +44881,7 @@
         <v>1.07</v>
       </c>
       <c r="AK273">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45312,16 +45312,16 @@
         <v>2.2</v>
       </c>
       <c r="S276">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T276">
+        <v>2.69</v>
+      </c>
+      <c r="U276">
         <v>2.88</v>
       </c>
-      <c r="U276">
-        <v>2.7</v>
-      </c>
       <c r="V276">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W276">
         <v>1.04</v>
@@ -45339,7 +45339,7 @@
         <v>2.02</v>
       </c>
       <c r="AB276">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC276">
         <v>3.28</v>
@@ -45351,10 +45351,10 @@
         <v>1.1</v>
       </c>
       <c r="AF276">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG276">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,65 +47742,65 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="O291">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="P291">
-        <v>3.25</v>
+        <v>5.9</v>
       </c>
       <c r="Q291">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="R291">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S291">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="T291">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="U291">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="V291">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W291">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X291">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y291">
+        <v>1.5</v>
+      </c>
+      <c r="Z291">
+        <v>2.45</v>
+      </c>
+      <c r="AA291">
+        <v>2.6</v>
+      </c>
+      <c r="AB291">
+        <v>1.42</v>
+      </c>
+      <c r="AC291">
+        <v>5.05</v>
+      </c>
+      <c r="AD291">
+        <v>1.15</v>
+      </c>
+      <c r="AE291">
+        <v>1.01</v>
+      </c>
+      <c r="AF291">
+        <v>2.18</v>
+      </c>
+      <c r="AG291">
         <v>1.56</v>
       </c>
-      <c r="Z291">
-        <v>2.25</v>
-      </c>
-      <c r="AA291">
-        <v>2.88</v>
-      </c>
-      <c r="AB291">
-        <v>1.38</v>
-      </c>
-      <c r="AC291">
-        <v>6.05</v>
-      </c>
-      <c r="AD291">
-        <v>1.06</v>
-      </c>
-      <c r="AE291">
-        <v>1.02</v>
-      </c>
-      <c r="AF291">
-        <v>2.3</v>
-      </c>
-      <c r="AG291">
-        <v>1.52</v>
-      </c>
       <c r="AH291" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK291">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="O292">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="P292">
-        <v>5.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q292">
+        <v>2.9</v>
+      </c>
+      <c r="R292">
+        <v>1.85</v>
+      </c>
+      <c r="S292">
+        <v>1.62</v>
+      </c>
+      <c r="T292">
+        <v>2.15</v>
+      </c>
+      <c r="U292">
+        <v>3.8</v>
+      </c>
+      <c r="V292">
+        <v>1.2</v>
+      </c>
+      <c r="W292">
+        <v>1.03</v>
+      </c>
+      <c r="X292">
+        <v>1.09</v>
+      </c>
+      <c r="Y292">
+        <v>1.56</v>
+      </c>
+      <c r="Z292">
+        <v>2.25</v>
+      </c>
+      <c r="AA292">
+        <v>2.88</v>
+      </c>
+      <c r="AB292">
+        <v>1.38</v>
+      </c>
+      <c r="AC292">
+        <v>6.05</v>
+      </c>
+      <c r="AD292">
+        <v>1.06</v>
+      </c>
+      <c r="AE292">
+        <v>1.02</v>
+      </c>
+      <c r="AF292">
         <v>2.3</v>
       </c>
-      <c r="R292">
-        <v>1.91</v>
-      </c>
-      <c r="S292">
-        <v>1.5</v>
-      </c>
-      <c r="T292">
-        <v>2.5</v>
-      </c>
-      <c r="U292">
-        <v>3.75</v>
-      </c>
-      <c r="V292">
-        <v>1.22</v>
-      </c>
-      <c r="W292">
-        <v>1.04</v>
-      </c>
-      <c r="X292">
-        <v>1.11</v>
-      </c>
-      <c r="Y292">
-        <v>1.5</v>
-      </c>
-      <c r="Z292">
-        <v>2.45</v>
-      </c>
-      <c r="AA292">
-        <v>2.6</v>
-      </c>
-      <c r="AB292">
-        <v>1.42</v>
-      </c>
-      <c r="AC292">
-        <v>5.05</v>
-      </c>
-      <c r="AD292">
-        <v>1.15</v>
-      </c>
-      <c r="AE292">
-        <v>1.01</v>
-      </c>
-      <c r="AF292">
-        <v>2.18</v>
-      </c>
       <c r="AG292">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AK292">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48566,10 +48566,10 @@
         <v>1.67</v>
       </c>
       <c r="Q296">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="R296">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S296">
         <v>1.29</v>
@@ -48587,7 +48587,7 @@
         <v>1.08</v>
       </c>
       <c r="X296">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y296">
         <v>1.28</v>
@@ -48614,7 +48614,7 @@
         <v>1.75</v>
       </c>
       <c r="AG296">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O300">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="P300">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q300">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R300">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="S300">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T300">
         <v>2.25</v>
       </c>
       <c r="U300">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="V300">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W300">
         <v>1.04</v>
       </c>
       <c r="X300">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y300">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z300">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AA300">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AB300">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AC300">
-        <v>6</v>
+        <v>6.21</v>
       </c>
       <c r="AD300">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE300">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF300">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG300">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK300">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,61 +49372,61 @@
         </is>
       </c>
       <c r="N301">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="O301">
-        <v>2.71</v>
+        <v>3.3</v>
       </c>
       <c r="P301">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="Q301">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="R301">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S301">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="T301">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U301">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="V301">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="W301">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X301">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Y301">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="Z301">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AA301">
-        <v>2.78</v>
+        <v>2.17</v>
       </c>
       <c r="AB301">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AC301">
-        <v>6.21</v>
+        <v>4.27</v>
       </c>
       <c r="AD301">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE301">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF301">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AG301">
         <v>1.6</v>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK301">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="O302">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="P302">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q302">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="R302">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="S302">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="T302">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U302">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="V302">
+        <v>1.25</v>
+      </c>
+      <c r="W302">
+        <v>1.04</v>
+      </c>
+      <c r="X302">
+        <v>1.1</v>
+      </c>
+      <c r="Y302">
+        <v>1.57</v>
+      </c>
+      <c r="Z302">
+        <v>2.38</v>
+      </c>
+      <c r="AA302">
+        <v>2.88</v>
+      </c>
+      <c r="AB302">
         <v>1.35</v>
       </c>
-      <c r="W302">
-        <v>1.03</v>
-      </c>
-      <c r="X302">
-        <v>1.06</v>
-      </c>
-      <c r="Y302">
-        <v>1.39</v>
-      </c>
-      <c r="Z302">
-        <v>2.63</v>
-      </c>
-      <c r="AA302">
-        <v>2.17</v>
-      </c>
-      <c r="AB302">
-        <v>1.55</v>
-      </c>
       <c r="AC302">
-        <v>4.27</v>
+        <v>6</v>
       </c>
       <c r="AD302">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE302">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF302">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG302">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK302">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49698,7 +49698,7 @@
         </is>
       </c>
       <c r="N303">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O303">
         <v>2.9</v>
@@ -49707,7 +49707,7 @@
         <v>2.95</v>
       </c>
       <c r="Q303">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="R303">
         <v>1.95</v>
@@ -49719,13 +49719,13 @@
         <v>2.45</v>
       </c>
       <c r="U303">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="V303">
         <v>1.3</v>
       </c>
       <c r="W303">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X303">
         <v>1.07</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O305">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="P305">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="Q305">
         <v>3.25</v>
@@ -50063,19 +50063,19 @@
         <v>4.4</v>
       </c>
       <c r="AA305">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB305">
         <v>2.2</v>
       </c>
       <c r="AC305">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AD305">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE305">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF305">
         <v>1.5</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="O322">
         <v>3.3</v>
       </c>
       <c r="P322">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q322">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="R322">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S322">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T322">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U322">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="V322">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W322">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X322">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y322">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z322">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA322">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AB322">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC322">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD322">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE322">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF322">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG322">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AK322">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,65 +52958,65 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O323">
         <v>3.3</v>
       </c>
       <c r="P323">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q323">
+        <v>2.19</v>
+      </c>
+      <c r="R323">
+        <v>2</v>
+      </c>
+      <c r="S323">
+        <v>1.45</v>
+      </c>
+      <c r="T323">
+        <v>2.5</v>
+      </c>
+      <c r="U323">
+        <v>3.3</v>
+      </c>
+      <c r="V323">
+        <v>1.29</v>
+      </c>
+      <c r="W323">
+        <v>1.05</v>
+      </c>
+      <c r="X323">
+        <v>1.08</v>
+      </c>
+      <c r="Y323">
+        <v>1.38</v>
+      </c>
+      <c r="Z323">
+        <v>2.62</v>
+      </c>
+      <c r="AA323">
+        <v>2.37</v>
+      </c>
+      <c r="AB323">
+        <v>1.59</v>
+      </c>
+      <c r="AC323">
+        <v>4.5</v>
+      </c>
+      <c r="AD323">
+        <v>1.19</v>
+      </c>
+      <c r="AE323">
+        <v>1</v>
+      </c>
+      <c r="AF323">
         <v>2.3</v>
       </c>
-      <c r="R323">
-        <v>2.1</v>
-      </c>
-      <c r="S323">
-        <v>1.4</v>
-      </c>
-      <c r="T323">
-        <v>2.56</v>
-      </c>
-      <c r="U323">
-        <v>3.06</v>
-      </c>
-      <c r="V323">
-        <v>1.32</v>
-      </c>
-      <c r="W323">
-        <v>1.03</v>
-      </c>
-      <c r="X323">
-        <v>1.06</v>
-      </c>
-      <c r="Y323">
-        <v>1.36</v>
-      </c>
-      <c r="Z323">
-        <v>2.7</v>
-      </c>
-      <c r="AA323">
-        <v>2.25</v>
-      </c>
-      <c r="AB323">
+      <c r="AG323">
         <v>1.6</v>
       </c>
-      <c r="AC323">
-        <v>4.1</v>
-      </c>
-      <c r="AD323">
-        <v>1.2</v>
-      </c>
-      <c r="AE323">
-        <v>1.01</v>
-      </c>
-      <c r="AF323">
-        <v>2.05</v>
-      </c>
-      <c r="AG323">
-        <v>1.75</v>
-      </c>
       <c r="AH323" t="inlineStr">
         <is>
           <t>[]</t>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AK323">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AL323">
         <v>0</v>
